--- a/datasets/sgt_files/InVitroBioFilm_SGT_scaling.xlsx
+++ b/datasets/sgt_files/InVitroBioFilm_SGT_scaling.xlsx
@@ -440,25 +440,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>12.1</v>
+        <v>11.3</v>
       </c>
       <c r="C2">
-        <v>1.12989675044522</v>
+        <v>1.3</v>
       </c>
       <c r="D2">
-        <v>0.113967</v>
+        <v>0.223665</v>
       </c>
       <c r="E2">
-        <v>0.0111726845525644</v>
+        <v>0.08689313063566455</v>
       </c>
       <c r="F2">
-        <v>1.08278537031645</v>
+        <v>1.05307844348342</v>
       </c>
       <c r="G2">
-        <v>-0.9432208836866045</v>
+        <v>-0.6504019707362143</v>
       </c>
       <c r="H2">
-        <v>-0.928579184308906</v>
+        <v>-0.7360841467267152</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -466,25 +466,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>39.5</v>
+        <v>39</v>
       </c>
       <c r="C3">
-        <v>1.796601730428249</v>
+        <v>3.0840089349921</v>
       </c>
       <c r="D3">
-        <v>0.039636</v>
+        <v>0.047857</v>
       </c>
       <c r="E3">
-        <v>0.002826119915675514</v>
+        <v>0.005268825939218126</v>
       </c>
       <c r="F3">
-        <v>1.59659709562646</v>
+        <v>1.591064607026499</v>
       </c>
       <c r="G3">
-        <v>-1.401910180260961</v>
+        <v>-1.320054529380785</v>
       </c>
       <c r="H3">
-        <v>-1.410745692789158</v>
+        <v>-1.299983122420791</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -492,25 +492,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>80.09999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="C4">
-        <v>3.572891763761611</v>
+        <v>2.478574859336174</v>
       </c>
       <c r="D4">
-        <v>0.019578</v>
+        <v>0.01952</v>
       </c>
       <c r="E4">
-        <v>0.001783419810987369</v>
+        <v>0.001232376205187</v>
       </c>
       <c r="F4">
-        <v>1.903632516084238</v>
+        <v>1.898176483497676</v>
       </c>
       <c r="G4">
-        <v>-1.708231675828481</v>
+        <v>-1.709520186669327</v>
       </c>
       <c r="H4">
-        <v>-1.698871069010518</v>
+        <v>-1.621887446920606</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -518,25 +518,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>137.2</v>
+        <v>130.9</v>
       </c>
       <c r="C5">
-        <v>4.304519588628781</v>
+        <v>4.787599723359411</v>
       </c>
       <c r="D5">
-        <v>0.012534</v>
+        <v>0.012653</v>
       </c>
       <c r="E5">
-        <v>0.0009046155721262668</v>
+        <v>0.001167132335636747</v>
       </c>
       <c r="F5">
-        <v>2.137354111370733</v>
+        <v>2.116939646550756</v>
       </c>
       <c r="G5">
-        <v>-1.901910309636048</v>
+        <v>-1.897806491960256</v>
       </c>
       <c r="H5">
-        <v>-1.918197954724794</v>
+        <v>-1.851187625856062</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -544,25 +544,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>203.4</v>
+        <v>214.1</v>
       </c>
       <c r="C6">
-        <v>4.77772609791171</v>
+        <v>4.670117771534247</v>
       </c>
       <c r="D6">
-        <v>0.008934000000000001</v>
+        <v>0.007606</v>
       </c>
       <c r="E6">
-        <v>0.000431483745026649</v>
+        <v>0.000416579190817571</v>
       </c>
       <c r="F6">
-        <v>2.308350948586726</v>
+        <v>2.330616667294438</v>
       </c>
       <c r="G6">
-        <v>-2.04895405186418</v>
+        <v>-2.118843678924436</v>
       </c>
       <c r="H6">
-        <v>-2.07866324560903</v>
+        <v>-2.075156681738808</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -570,25 +570,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>290.4</v>
+        <v>288.1</v>
       </c>
       <c r="C7">
-        <v>4.742713709821976</v>
+        <v>5.685165882462103</v>
       </c>
       <c r="D7">
-        <v>0.005514</v>
+        <v>0.00615</v>
       </c>
       <c r="E7">
-        <v>0.0003042593922589372</v>
+        <v>0.0003635351121663185</v>
       </c>
       <c r="F7">
-        <v>2.462996612028056</v>
+        <v>2.459543258280413</v>
       </c>
       <c r="G7">
-        <v>-2.258533238230245</v>
+        <v>-2.211124884224583</v>
       </c>
       <c r="H7">
-        <v>-2.22378441727581</v>
+        <v>-2.210293191789403</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -596,25 +596,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>397.9</v>
+        <v>394</v>
       </c>
       <c r="C8">
-        <v>4.958606435055898</v>
+        <v>3.346640106136302</v>
       </c>
       <c r="D8">
-        <v>0.004329999999999999</v>
+        <v>0.004235000000000001</v>
       </c>
       <c r="E8">
-        <v>0.0001732114956410868</v>
+        <v>0.0001603347193287288</v>
       </c>
       <c r="F8">
-        <v>2.599773939146388</v>
+        <v>2.595496221825574</v>
       </c>
       <c r="G8">
-        <v>-2.363512103646635</v>
+        <v>-2.373146585333274</v>
       </c>
       <c r="H8">
-        <v>-2.352137747897287</v>
+        <v>-2.352794508887963</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -622,25 +622,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>515.9</v>
+        <v>515.2</v>
       </c>
       <c r="C9">
-        <v>5.700779673771728</v>
+        <v>3.805843460317889</v>
       </c>
       <c r="D9">
-        <v>0.003257</v>
+        <v>0.003294</v>
       </c>
       <c r="E9">
-        <v>0.0001395711686241507</v>
+        <v>0.0001124000790826136</v>
       </c>
       <c r="F9">
-        <v>2.712565527873308</v>
+        <v>2.711975854351756</v>
       </c>
       <c r="G9">
-        <v>-2.487182241435127</v>
+        <v>-2.482276405166265</v>
       </c>
       <c r="H9">
-        <v>-2.457982600872541</v>
+        <v>-2.474884536330605</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -648,25 +648,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>667</v>
+        <v>662.5</v>
       </c>
       <c r="C10">
-        <v>4.695151163109069</v>
+        <v>6.057593948462082</v>
       </c>
       <c r="D10">
-        <v>0.002504999999999999</v>
+        <v>0.002638000000000001</v>
       </c>
       <c r="E10">
-        <v>7.528095524249295E-05</v>
+        <v>7.209253313161726E-05</v>
       </c>
       <c r="F10">
-        <v>2.824125833916549</v>
+        <v>2.821185882608845</v>
       </c>
       <c r="G10">
-        <v>-2.601192269796736</v>
+        <v>-2.578725208789654</v>
       </c>
       <c r="H10">
-        <v>-2.56267200479263</v>
+        <v>-2.589354809439706</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -674,25 +674,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>811.5</v>
+        <v>812.9</v>
       </c>
       <c r="C11">
-        <v>8.364275886836296</v>
+        <v>9.599131905195039</v>
       </c>
       <c r="D11">
-        <v>0.002171</v>
+        <v>0.00213</v>
       </c>
       <c r="E11">
-        <v>6.04510821518799E-05</v>
+        <v>6.881537295950343E-05</v>
       </c>
       <c r="F11">
-        <v>2.909288524162251</v>
+        <v>2.910037123553051</v>
       </c>
       <c r="G11">
-        <v>-2.66334017654558</v>
+        <v>-2.671620396561262</v>
       </c>
       <c r="H11">
-        <v>-2.642589599089996</v>
+        <v>-2.68248568743035</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -718,7 +718,7 @@
         <v>-2.338187314462739</v>
       </c>
       <c r="H12">
-        <v>-2.441950929022662</v>
+        <v>-2.457595894667791</v>
       </c>
     </row>
   </sheetData>
@@ -741,290 +741,290 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>12.1</v>
+        <v>11.3</v>
       </c>
       <c r="B2">
-        <v>0.114118894657337</v>
+        <v>0.2234229411226657</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>20.17474747474747</v>
+        <v>19.3969696969697</v>
       </c>
       <c r="B3">
-        <v>0.07153840198621657</v>
+        <v>0.1156212373834673</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>28.24949494949495</v>
+        <v>27.4939393939394</v>
       </c>
       <c r="B4">
-        <v>0.05259964516128546</v>
+        <v>0.07556595810281702</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>36.32424242424242</v>
+        <v>35.59090909090909</v>
       </c>
       <c r="B5">
-        <v>0.04180625295572488</v>
+        <v>0.05516354196624016</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>44.3989898989899</v>
+        <v>43.68787878787879</v>
       </c>
       <c r="B6">
-        <v>0.03480208572938091</v>
+        <v>0.04296524975839557</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>52.47373737373737</v>
+        <v>51.78484848484848</v>
       </c>
       <c r="B7">
-        <v>0.02987537705570119</v>
+        <v>0.03492127028347099</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>60.54848484848484</v>
+        <v>59.88181818181819</v>
       </c>
       <c r="B8">
-        <v>0.02621373526820083</v>
+        <v>0.02925286548600948</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>68.62323232323232</v>
+        <v>67.97878787878788</v>
       </c>
       <c r="B9">
-        <v>0.02338103360402072</v>
+        <v>0.02506208489084306</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>76.69797979797978</v>
+        <v>76.07575757575758</v>
       </c>
       <c r="B10">
-        <v>0.02112174936903392</v>
+        <v>0.02184900993129131</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>84.77272727272725</v>
+        <v>84.17272727272727</v>
       </c>
       <c r="B11">
-        <v>0.01927604335909764</v>
+        <v>0.01931428318245793</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>92.84747474747473</v>
+        <v>92.26969696969697</v>
       </c>
       <c r="B12">
-        <v>0.01773870091217781</v>
+        <v>0.01726822968450587</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>100.9222222222222</v>
+        <v>100.3666666666667</v>
       </c>
       <c r="B13">
-        <v>0.01643757540808223</v>
+        <v>0.01558512248656729</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>108.9969696969697</v>
+        <v>108.4636363636364</v>
       </c>
       <c r="B14">
-        <v>0.01532150915408134</v>
+        <v>0.01417848879016148</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>117.0717171717172</v>
+        <v>116.5606060606061</v>
       </c>
       <c r="B15">
-        <v>0.01435319723341663</v>
+        <v>0.01298699511530168</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>125.1464646464646</v>
+        <v>124.6575757575758</v>
       </c>
       <c r="B16">
-        <v>0.0135047825124472</v>
+        <v>0.01196599002919759</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>133.2212121212121</v>
+        <v>132.7545454545455</v>
       </c>
       <c r="B17">
-        <v>0.01275503402534345</v>
+        <v>0.0110822316650582</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>141.2959595959596</v>
+        <v>140.8515151515152</v>
       </c>
       <c r="B18">
-        <v>0.01208748145851442</v>
+        <v>0.01031048744007662</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>149.3707070707071</v>
+        <v>148.9484848484849</v>
       </c>
       <c r="B19">
-        <v>0.01148914749613198</v>
+        <v>0.009631275999786809</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>157.4454545454545</v>
+        <v>157.0454545454546</v>
       </c>
       <c r="B20">
-        <v>0.01094966553484734</v>
+        <v>0.009029328839544866</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>165.520202020202</v>
+        <v>165.1424242424243</v>
       </c>
       <c r="B21">
-        <v>0.01046065249826879</v>
+        <v>0.008492518339989152</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>173.5949494949495</v>
+        <v>173.2393939393939</v>
       </c>
       <c r="B22">
-        <v>0.01001525453838841</v>
+        <v>0.008011095705198019</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>181.6696969696969</v>
+        <v>181.3363636363637</v>
       </c>
       <c r="B23">
-        <v>0.009607812388484292</v>
+        <v>0.007577139428687919</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>189.7444444444444</v>
+        <v>189.4333333333334</v>
       </c>
       <c r="B24">
-        <v>0.009233611095551531</v>
+        <v>0.007184149648374311</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>197.8191919191919</v>
+        <v>197.5303030303031</v>
       </c>
       <c r="B25">
-        <v>0.008888690275485224</v>
+        <v>0.006826745424516108</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>205.8939393939393</v>
+        <v>205.6272727272728</v>
       </c>
       <c r="B26">
-        <v>0.00856969845168928</v>
+        <v>0.006500435816382649</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>213.9686868686868</v>
+        <v>213.7242424242424</v>
       </c>
       <c r="B27">
-        <v>0.008273779955781664</v>
+        <v>0.006201444662158525</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>222.0434343434343</v>
+        <v>221.8212121212121</v>
       </c>
       <c r="B28">
-        <v>0.007998486190224757</v>
+        <v>0.005926574970018011</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>230.1181818181818</v>
+        <v>229.9181818181818</v>
       </c>
       <c r="B29">
-        <v>0.007741705333417221</v>
+        <v>0.00567310289062023</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>238.1929292929293</v>
+        <v>238.0151515151516</v>
       </c>
       <c r="B30">
-        <v>0.007501606158254927</v>
+        <v>0.005438694034608454</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>246.2676767676767</v>
+        <v>246.1121212121213</v>
       </c>
       <c r="B31">
-        <v>0.007276592760105602</v>
+        <v>0.00522133684803717</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>254.3424242424242</v>
+        <v>254.2090909090909</v>
       </c>
       <c r="B32">
-        <v>0.007065267796277352</v>
+        <v>0.005019289137692525</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>262.4171717171717</v>
+        <v>262.3060606060606</v>
       </c>
       <c r="B33">
-        <v>0.006866402423782412</v>
+        <v>0.004831034826267896</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>270.4919191919192</v>
+        <v>270.4030303030303</v>
       </c>
       <c r="B34">
-        <v>0.006678911551119365</v>
+        <v>0.0046552487335509</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>278.5666666666667</v>
+        <v>278.5000000000001</v>
       </c>
       <c r="B35">
-        <v>0.006501833337750171</v>
+        <v>0.004490767704652825</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>286.6414141414141</v>
+        <v>286.5969696969697</v>
       </c>
       <c r="B36">
-        <v>0.006334312112962199</v>
+        <v>0.004336566794921568</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>294.7161616161616</v>
+        <v>294.6939393939394</v>
       </c>
       <c r="B37">
-        <v>0.006175584065620148</v>
+        <v>0.004191739511663775</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1032,511 +1032,511 @@
         <v>302.7909090909091</v>
       </c>
       <c r="B38">
-        <v>0.006024965193333106</v>
+        <v>0.004055481331892936</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>310.8656565656565</v>
+        <v>310.8878787878788</v>
       </c>
       <c r="B39">
-        <v>0.005881841104820782</v>
+        <v>0.003927075881962371</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>318.940404040404</v>
+        <v>318.9848484848485</v>
       </c>
       <c r="B40">
-        <v>0.005745658350741072</v>
+        <v>0.003805883292700867</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>327.0151515151515</v>
+        <v>327.0818181818182</v>
       </c>
       <c r="B41">
-        <v>0.005615917021766245</v>
+        <v>0.003691330342352621</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>335.089898989899</v>
+        <v>335.1787878787879</v>
       </c>
       <c r="B42">
-        <v>0.005492164402560705</v>
+        <v>0.00358290207638999</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>343.1646464646465</v>
+        <v>343.2757575757576</v>
       </c>
       <c r="B43">
-        <v>0.005373989509709177</v>
+        <v>0.003480134653385886</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>351.2393939393939</v>
+        <v>351.3727272727273</v>
       </c>
       <c r="B44">
-        <v>0.005261018372958773</v>
+        <v>0.003382609213512734</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>359.3141414141414</v>
+        <v>359.469696969697</v>
       </c>
       <c r="B45">
-        <v>0.005152909944174143</v>
+        <v>0.003289946603801274</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>367.3888888888889</v>
+        <v>367.5666666666667</v>
       </c>
       <c r="B46">
-        <v>0.005049352538531013</v>
+        <v>0.003201802824248834</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>375.4636363636363</v>
+        <v>375.6636363636364</v>
       </c>
       <c r="B47">
-        <v>0.004950060728737752</v>
+        <v>0.003117865082885064</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>383.5383838383838</v>
+        <v>383.7606060606061</v>
       </c>
       <c r="B48">
-        <v>0.004854772626283929</v>
+        <v>0.003037848367260696</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>391.6131313131313</v>
+        <v>391.8575757575758</v>
       </c>
       <c r="B49">
-        <v>0.004763247494494139</v>
+        <v>0.002961492455503649</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>399.6878787878787</v>
+        <v>399.9545454545455</v>
       </c>
       <c r="B50">
-        <v>0.004675263647001852</v>
+        <v>0.002888559302845906</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>407.7626262626262</v>
+        <v>408.0515151515152</v>
       </c>
       <c r="B51">
-        <v>0.004590616592533375</v>
+        <v>0.002818830749954937</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>415.8373737373737</v>
+        <v>416.1484848484849</v>
       </c>
       <c r="B52">
-        <v>0.004509117392907075</v>
+        <v>0.002752106507966855</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>423.9121212121212</v>
+        <v>424.2454545454546</v>
       </c>
       <c r="B53">
-        <v>0.004430591206145848</v>
+        <v>0.002688202382178486</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>431.9868686868687</v>
+        <v>432.3424242424243</v>
       </c>
       <c r="B54">
-        <v>0.004354875990761184</v>
+        <v>0.002626948702199065</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>440.0616161616161</v>
+        <v>440.439393939394</v>
       </c>
       <c r="B55">
-        <v>0.004281821350746441</v>
+        <v>0.002568188931217557</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>448.1363636363636</v>
+        <v>448.5363636363637</v>
       </c>
       <c r="B56">
-        <v>0.004211287503737038</v>
+        <v>0.00251177843109041</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>456.2111111111111</v>
+        <v>456.6333333333334</v>
       </c>
       <c r="B57">
-        <v>0.00414314435725427</v>
+        <v>0.002457583363342884</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>464.2858585858585</v>
+        <v>464.7303030303031</v>
       </c>
       <c r="B58">
-        <v>0.00407727068002698</v>
+        <v>0.002405479709022215</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>472.360606060606</v>
+        <v>472.8272727272728</v>
       </c>
       <c r="B59">
-        <v>0.004013553357146009</v>
+        <v>0.002355352392737675</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>480.4353535353535</v>
+        <v>480.9242424242425</v>
       </c>
       <c r="B60">
-        <v>0.003951886719303136</v>
+        <v>0.002307094498248114</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>488.510101010101</v>
+        <v>489.0212121212122</v>
       </c>
       <c r="B61">
-        <v>0.003892171937642248</v>
+        <v>0.00226060656467445</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>496.5848484848485</v>
+        <v>497.1181818181819</v>
       </c>
       <c r="B62">
-        <v>0.003834316476841483</v>
+        <v>0.00221579595387411</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>504.6595959595959</v>
+        <v>505.2151515151515</v>
       </c>
       <c r="B63">
-        <v>0.003778233599980349</v>
+        <v>0.002172576280758743</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>512.7343434343434</v>
+        <v>513.3121212121213</v>
       </c>
       <c r="B64">
-        <v>0.003723841919549707</v>
+        <v>0.002130866899400167</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>520.8090909090909</v>
+        <v>521.4090909090909</v>
       </c>
       <c r="B65">
-        <v>0.003671064989655256</v>
+        <v>0.00209059243868117</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>528.8838383838383</v>
+        <v>529.5060606060606</v>
       </c>
       <c r="B66">
-        <v>0.003619830935063521</v>
+        <v>0.002051682382031121</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>536.9585858585858</v>
+        <v>537.6030303030303</v>
       </c>
       <c r="B67">
-        <v>0.003570072113257467</v>
+        <v>0.002014070686461129</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>545.0333333333333</v>
+        <v>545.7</v>
       </c>
       <c r="B68">
-        <v>0.003521724806118537</v>
+        <v>0.001977695436696093</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>553.1080808080808</v>
+        <v>553.7969696969697</v>
       </c>
       <c r="B69">
-        <v>0.003474728938243024</v>
+        <v>0.001942498530705191</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>561.1828282828283</v>
+        <v>561.8939393939394</v>
       </c>
       <c r="B70">
-        <v>0.003429027819241569</v>
+        <v>0.001908425393369704</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>569.2575757575758</v>
+        <v>569.9909090909091</v>
       </c>
       <c r="B71">
-        <v>0.003384567907668399</v>
+        <v>0.001875424715407219</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>577.3323232323232</v>
+        <v>578.0878787878788</v>
       </c>
       <c r="B72">
-        <v>0.003341298594487549</v>
+        <v>0.001843448215002397</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>585.4070707070706</v>
+        <v>586.1848484848484</v>
       </c>
       <c r="B73">
-        <v>0.00329917200421184</v>
+        <v>0.001812450419883519</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>593.4818181818181</v>
+        <v>594.2818181818182</v>
       </c>
       <c r="B74">
-        <v>0.003258142812051314</v>
+        <v>0.001782388467836827</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>601.5565656565656</v>
+        <v>602.3787878787879</v>
       </c>
       <c r="B75">
-        <v>0.003218168075584502</v>
+        <v>0.001753221923872184</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>609.631313131313</v>
+        <v>610.4757575757576</v>
       </c>
       <c r="B76">
-        <v>0.003179207079621927</v>
+        <v>0.001724912612448014</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>617.7060606060605</v>
+        <v>618.5727272727273</v>
       </c>
       <c r="B77">
-        <v>0.003141221193068869</v>
+        <v>0.001697424463334556</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>625.780808080808</v>
+        <v>626.6696969696969</v>
       </c>
       <c r="B78">
-        <v>0.003104173736716384</v>
+        <v>0.00167072336984511</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>633.8555555555555</v>
+        <v>634.7666666666667</v>
       </c>
       <c r="B79">
-        <v>0.003068029860997553</v>
+        <v>0.00164477705829798</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>641.930303030303</v>
+        <v>642.8636363636364</v>
       </c>
       <c r="B80">
-        <v>0.003032756432841862</v>
+        <v>0.001619554967689372</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>650.0050505050505</v>
+        <v>650.9606060606061</v>
       </c>
       <c r="B81">
-        <v>0.002998321930845916</v>
+        <v>0.001595028138661609</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82">
-        <v>658.0797979797979</v>
+        <v>659.0575757575757</v>
       </c>
       <c r="B82">
-        <v>0.002964696348054624</v>
+        <v>0.001571169110943376</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83">
-        <v>666.1545454545454</v>
+        <v>667.1545454545454</v>
       </c>
       <c r="B83">
-        <v>0.002931851101714743</v>
+        <v>0.001547951828520692</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84">
-        <v>674.2292929292929</v>
+        <v>675.2515151515152</v>
       </c>
       <c r="B84">
-        <v>0.002899758949423204</v>
+        <v>0.001525351551870314</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85">
-        <v>682.3040404040404</v>
+        <v>683.3484848484849</v>
       </c>
       <c r="B85">
-        <v>0.002868393911146696</v>
+        <v>0.001503344776652226</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86">
-        <v>690.3787878787878</v>
+        <v>691.4454545454546</v>
       </c>
       <c r="B86">
-        <v>0.002837731196637552</v>
+        <v>0.001481909158315892</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87">
-        <v>698.4535353535352</v>
+        <v>699.5424242424242</v>
       </c>
       <c r="B87">
-        <v>0.002807747137814382</v>
+        <v>0.001461023442126762</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88">
-        <v>706.5282828282827</v>
+        <v>707.6393939393939</v>
       </c>
       <c r="B88">
-        <v>0.002778419125714995</v>
+        <v>0.001440667398165869</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89">
-        <v>714.6030303030302</v>
+        <v>715.7363636363636</v>
       </c>
       <c r="B89">
-        <v>0.002749725551664224</v>
+        <v>0.001420821760896863</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90">
-        <v>722.6777777777777</v>
+        <v>723.8333333333334</v>
       </c>
       <c r="B90">
-        <v>0.002721645752330935</v>
+        <v>0.001401468172932123</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91">
-        <v>730.7525252525252</v>
+        <v>731.9303030303031</v>
       </c>
       <c r="B91">
-        <v>0.00269415995837694</v>
+        <v>0.001382589132662983</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92">
-        <v>738.8272727272727</v>
+        <v>740.0272727272727</v>
       </c>
       <c r="B92">
-        <v>0.002667249246426297</v>
+        <v>0.001364167945449245</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93">
-        <v>746.9020202020201</v>
+        <v>748.1242424242424</v>
       </c>
       <c r="B93">
-        <v>0.00264089549410671</v>
+        <v>0.001346188678090202</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94">
-        <v>754.9767676767676</v>
+        <v>756.2212121212121</v>
       </c>
       <c r="B94">
-        <v>0.002615081337935753</v>
+        <v>0.001328636116323822</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95">
-        <v>763.0515151515151</v>
+        <v>764.3181818181819</v>
       </c>
       <c r="B95">
-        <v>0.002589790133843706</v>
+        <v>0.001311495725122791</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96">
-        <v>771.1262626262626</v>
+        <v>772.4151515151515</v>
       </c>
       <c r="B96">
-        <v>0.002565005920142038</v>
+        <v>0.00129475361157598</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97">
-        <v>779.2010101010101</v>
+        <v>780.5121212121212</v>
       </c>
       <c r="B97">
-        <v>0.002540713382762229</v>
+        <v>0.001278396490161965</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98">
-        <v>787.2757575757574</v>
+        <v>788.6090909090909</v>
       </c>
       <c r="B98">
-        <v>0.002516897822603894</v>
+        <v>0.001262411650237472</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99">
-        <v>795.3505050505049</v>
+        <v>796.7060606060606</v>
       </c>
       <c r="B99">
-        <v>0.002493545124844073</v>
+        <v>0.001246786925578432</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100">
-        <v>803.4252525252524</v>
+        <v>804.8030303030304</v>
       </c>
       <c r="B100">
-        <v>0.002470641730071381</v>
+        <v>0.001231510665824734</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101">
-        <v>811.5</v>
+        <v>812.9</v>
       </c>
       <c r="B101">
-        <v>0.002448174607119392</v>
+        <v>0.001216571709691934</v>
       </c>
     </row>
   </sheetData>
@@ -1580,25 +1580,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>12.1</v>
+        <v>11.3</v>
       </c>
       <c r="C2">
-        <v>1.12989675044522</v>
+        <v>1.3</v>
       </c>
       <c r="D2">
-        <v>0.113967</v>
+        <v>0.223665</v>
       </c>
       <c r="E2">
-        <v>0.0111726845525644</v>
+        <v>0.08689313063566455</v>
       </c>
       <c r="F2">
-        <v>1.08278537031645</v>
+        <v>1.05307844348342</v>
       </c>
       <c r="G2">
-        <v>-0.9432208836866045</v>
+        <v>-0.6504019707362143</v>
       </c>
       <c r="H2">
-        <v>-0.928579184308906</v>
+        <v>-0.7360841467267152</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1606,25 +1606,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>39.5</v>
+        <v>39</v>
       </c>
       <c r="C3">
-        <v>1.796601730428249</v>
+        <v>3.0840089349921</v>
       </c>
       <c r="D3">
-        <v>0.039636</v>
+        <v>0.047857</v>
       </c>
       <c r="E3">
-        <v>0.002826119915675514</v>
+        <v>0.005268825939218126</v>
       </c>
       <c r="F3">
-        <v>1.59659709562646</v>
+        <v>1.591064607026499</v>
       </c>
       <c r="G3">
-        <v>-1.401910180260961</v>
+        <v>-1.320054529380785</v>
       </c>
       <c r="H3">
-        <v>-1.410745692789158</v>
+        <v>-1.299983122420791</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1632,25 +1632,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>80.09999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="C4">
-        <v>3.572891763761611</v>
+        <v>2.478574859336174</v>
       </c>
       <c r="D4">
-        <v>0.019578</v>
+        <v>0.01952</v>
       </c>
       <c r="E4">
-        <v>0.001783419810987369</v>
+        <v>0.001232376205187</v>
       </c>
       <c r="F4">
-        <v>1.903632516084238</v>
+        <v>1.898176483497676</v>
       </c>
       <c r="G4">
-        <v>-1.708231675828481</v>
+        <v>-1.709520186669327</v>
       </c>
       <c r="H4">
-        <v>-1.698871069010518</v>
+        <v>-1.621887446920606</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1658,25 +1658,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>137.2</v>
+        <v>130.9</v>
       </c>
       <c r="C5">
-        <v>4.304519588628781</v>
+        <v>4.787599723359411</v>
       </c>
       <c r="D5">
-        <v>0.012534</v>
+        <v>0.012653</v>
       </c>
       <c r="E5">
-        <v>0.0009046155721262668</v>
+        <v>0.001167132335636747</v>
       </c>
       <c r="F5">
-        <v>2.137354111370733</v>
+        <v>2.116939646550756</v>
       </c>
       <c r="G5">
-        <v>-1.901910309636048</v>
+        <v>-1.897806491960256</v>
       </c>
       <c r="H5">
-        <v>-1.918197954724794</v>
+        <v>-1.851187625856062</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1684,25 +1684,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>203.4</v>
+        <v>214.1</v>
       </c>
       <c r="C6">
-        <v>4.77772609791171</v>
+        <v>4.670117771534247</v>
       </c>
       <c r="D6">
-        <v>0.008934000000000001</v>
+        <v>0.007606</v>
       </c>
       <c r="E6">
-        <v>0.000431483745026649</v>
+        <v>0.000416579190817571</v>
       </c>
       <c r="F6">
-        <v>2.308350948586726</v>
+        <v>2.330616667294438</v>
       </c>
       <c r="G6">
-        <v>-2.04895405186418</v>
+        <v>-2.118843678924436</v>
       </c>
       <c r="H6">
-        <v>-2.07866324560903</v>
+        <v>-2.075156681738808</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1710,25 +1710,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>290.4</v>
+        <v>288.1</v>
       </c>
       <c r="C7">
-        <v>4.742713709821976</v>
+        <v>5.685165882462103</v>
       </c>
       <c r="D7">
-        <v>0.005514</v>
+        <v>0.00615</v>
       </c>
       <c r="E7">
-        <v>0.0003042593922589372</v>
+        <v>0.0003635351121663185</v>
       </c>
       <c r="F7">
-        <v>2.462996612028056</v>
+        <v>2.459543258280413</v>
       </c>
       <c r="G7">
-        <v>-2.258533238230245</v>
+        <v>-2.211124884224583</v>
       </c>
       <c r="H7">
-        <v>-2.22378441727581</v>
+        <v>-2.210293191789403</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1736,25 +1736,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>397.9</v>
+        <v>394</v>
       </c>
       <c r="C8">
-        <v>4.958606435055898</v>
+        <v>3.346640106136302</v>
       </c>
       <c r="D8">
-        <v>0.004329999999999999</v>
+        <v>0.004235000000000001</v>
       </c>
       <c r="E8">
-        <v>0.0001732114956410868</v>
+        <v>0.0001603347193287288</v>
       </c>
       <c r="F8">
-        <v>2.599773939146388</v>
+        <v>2.595496221825574</v>
       </c>
       <c r="G8">
-        <v>-2.363512103646635</v>
+        <v>-2.373146585333274</v>
       </c>
       <c r="H8">
-        <v>-2.352137747897287</v>
+        <v>-2.352794508887963</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1762,25 +1762,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>515.9</v>
+        <v>515.2</v>
       </c>
       <c r="C9">
-        <v>5.700779673771728</v>
+        <v>3.805843460317889</v>
       </c>
       <c r="D9">
-        <v>0.003257</v>
+        <v>0.003294</v>
       </c>
       <c r="E9">
-        <v>0.0001395711686241507</v>
+        <v>0.0001124000790826136</v>
       </c>
       <c r="F9">
-        <v>2.712565527873308</v>
+        <v>2.711975854351756</v>
       </c>
       <c r="G9">
-        <v>-2.487182241435127</v>
+        <v>-2.482276405166265</v>
       </c>
       <c r="H9">
-        <v>-2.457982600872541</v>
+        <v>-2.474884536330605</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1788,25 +1788,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>667</v>
+        <v>662.5</v>
       </c>
       <c r="C10">
-        <v>4.695151163109069</v>
+        <v>6.057593948462082</v>
       </c>
       <c r="D10">
-        <v>0.002504999999999999</v>
+        <v>0.002638000000000001</v>
       </c>
       <c r="E10">
-        <v>7.528095524249295E-05</v>
+        <v>7.209253313161726E-05</v>
       </c>
       <c r="F10">
-        <v>2.824125833916549</v>
+        <v>2.821185882608845</v>
       </c>
       <c r="G10">
-        <v>-2.601192269796736</v>
+        <v>-2.578725208789654</v>
       </c>
       <c r="H10">
-        <v>-2.56267200479263</v>
+        <v>-2.589354809439706</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1814,25 +1814,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>811.5</v>
+        <v>812.9</v>
       </c>
       <c r="C11">
-        <v>8.364275886836296</v>
+        <v>9.599131905195039</v>
       </c>
       <c r="D11">
-        <v>0.002171</v>
+        <v>0.00213</v>
       </c>
       <c r="E11">
-        <v>6.04510821518799E-05</v>
+        <v>6.881537295950343E-05</v>
       </c>
       <c r="F11">
-        <v>2.909288524162251</v>
+        <v>2.910037123553051</v>
       </c>
       <c r="G11">
-        <v>-2.66334017654558</v>
+        <v>-2.671620396561262</v>
       </c>
       <c r="H11">
-        <v>-2.642589599089996</v>
+        <v>-2.68248568743035</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1858,7 +1858,7 @@
         <v>-2.338187314462739</v>
       </c>
       <c r="H12">
-        <v>-2.441950929022662</v>
+        <v>-2.457595894667791</v>
       </c>
     </row>
   </sheetData>
@@ -1881,290 +1881,290 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>12.1</v>
+        <v>11.3</v>
       </c>
       <c r="B2">
-        <v>0.114118894657337</v>
+        <v>0.2234229411226657</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>20.17474747474747</v>
+        <v>19.3969696969697</v>
       </c>
       <c r="B3">
-        <v>0.07153840198621657</v>
+        <v>0.1156212373834673</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>28.24949494949495</v>
+        <v>27.4939393939394</v>
       </c>
       <c r="B4">
-        <v>0.05259964516128546</v>
+        <v>0.07556595810281702</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>36.32424242424242</v>
+        <v>35.59090909090909</v>
       </c>
       <c r="B5">
-        <v>0.04180625295572488</v>
+        <v>0.05516354196624016</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>44.3989898989899</v>
+        <v>43.68787878787879</v>
       </c>
       <c r="B6">
-        <v>0.03480208572938091</v>
+        <v>0.04296524975839557</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>52.47373737373737</v>
+        <v>51.78484848484848</v>
       </c>
       <c r="B7">
-        <v>0.02987537705570119</v>
+        <v>0.03492127028347099</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>60.54848484848484</v>
+        <v>59.88181818181819</v>
       </c>
       <c r="B8">
-        <v>0.02621373526820083</v>
+        <v>0.02925286548600948</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>68.62323232323232</v>
+        <v>67.97878787878788</v>
       </c>
       <c r="B9">
-        <v>0.02338103360402072</v>
+        <v>0.02506208489084306</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>76.69797979797978</v>
+        <v>76.07575757575758</v>
       </c>
       <c r="B10">
-        <v>0.02112174936903392</v>
+        <v>0.02184900993129131</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>84.77272727272725</v>
+        <v>84.17272727272727</v>
       </c>
       <c r="B11">
-        <v>0.01927604335909764</v>
+        <v>0.01931428318245793</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>92.84747474747473</v>
+        <v>92.26969696969697</v>
       </c>
       <c r="B12">
-        <v>0.01773870091217781</v>
+        <v>0.01726822968450587</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>100.9222222222222</v>
+        <v>100.3666666666667</v>
       </c>
       <c r="B13">
-        <v>0.01643757540808223</v>
+        <v>0.01558512248656729</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>108.9969696969697</v>
+        <v>108.4636363636364</v>
       </c>
       <c r="B14">
-        <v>0.01532150915408134</v>
+        <v>0.01417848879016148</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>117.0717171717172</v>
+        <v>116.5606060606061</v>
       </c>
       <c r="B15">
-        <v>0.01435319723341663</v>
+        <v>0.01298699511530168</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>125.1464646464646</v>
+        <v>124.6575757575758</v>
       </c>
       <c r="B16">
-        <v>0.0135047825124472</v>
+        <v>0.01196599002919759</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>133.2212121212121</v>
+        <v>132.7545454545455</v>
       </c>
       <c r="B17">
-        <v>0.01275503402534345</v>
+        <v>0.0110822316650582</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>141.2959595959596</v>
+        <v>140.8515151515152</v>
       </c>
       <c r="B18">
-        <v>0.01208748145851442</v>
+        <v>0.01031048744007662</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>149.3707070707071</v>
+        <v>148.9484848484849</v>
       </c>
       <c r="B19">
-        <v>0.01148914749613198</v>
+        <v>0.009631275999786809</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>157.4454545454545</v>
+        <v>157.0454545454546</v>
       </c>
       <c r="B20">
-        <v>0.01094966553484734</v>
+        <v>0.009029328839544866</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>165.520202020202</v>
+        <v>165.1424242424243</v>
       </c>
       <c r="B21">
-        <v>0.01046065249826879</v>
+        <v>0.008492518339989152</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>173.5949494949495</v>
+        <v>173.2393939393939</v>
       </c>
       <c r="B22">
-        <v>0.01001525453838841</v>
+        <v>0.008011095705198019</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>181.6696969696969</v>
+        <v>181.3363636363637</v>
       </c>
       <c r="B23">
-        <v>0.009607812388484292</v>
+        <v>0.007577139428687919</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>189.7444444444444</v>
+        <v>189.4333333333334</v>
       </c>
       <c r="B24">
-        <v>0.009233611095551531</v>
+        <v>0.007184149648374311</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>197.8191919191919</v>
+        <v>197.5303030303031</v>
       </c>
       <c r="B25">
-        <v>0.008888690275485224</v>
+        <v>0.006826745424516108</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>205.8939393939393</v>
+        <v>205.6272727272728</v>
       </c>
       <c r="B26">
-        <v>0.00856969845168928</v>
+        <v>0.006500435816382649</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>213.9686868686868</v>
+        <v>213.7242424242424</v>
       </c>
       <c r="B27">
-        <v>0.008273779955781664</v>
+        <v>0.006201444662158525</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>222.0434343434343</v>
+        <v>221.8212121212121</v>
       </c>
       <c r="B28">
-        <v>0.007998486190224757</v>
+        <v>0.005926574970018011</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>230.1181818181818</v>
+        <v>229.9181818181818</v>
       </c>
       <c r="B29">
-        <v>0.007741705333417221</v>
+        <v>0.00567310289062023</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>238.1929292929293</v>
+        <v>238.0151515151516</v>
       </c>
       <c r="B30">
-        <v>0.007501606158254927</v>
+        <v>0.005438694034608454</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>246.2676767676767</v>
+        <v>246.1121212121213</v>
       </c>
       <c r="B31">
-        <v>0.007276592760105602</v>
+        <v>0.00522133684803717</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>254.3424242424242</v>
+        <v>254.2090909090909</v>
       </c>
       <c r="B32">
-        <v>0.007065267796277352</v>
+        <v>0.005019289137692525</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>262.4171717171717</v>
+        <v>262.3060606060606</v>
       </c>
       <c r="B33">
-        <v>0.006866402423782412</v>
+        <v>0.004831034826267896</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>270.4919191919192</v>
+        <v>270.4030303030303</v>
       </c>
       <c r="B34">
-        <v>0.006678911551119365</v>
+        <v>0.0046552487335509</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>278.5666666666667</v>
+        <v>278.5000000000001</v>
       </c>
       <c r="B35">
-        <v>0.006501833337750171</v>
+        <v>0.004490767704652825</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>286.6414141414141</v>
+        <v>286.5969696969697</v>
       </c>
       <c r="B36">
-        <v>0.006334312112962199</v>
+        <v>0.004336566794921568</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>294.7161616161616</v>
+        <v>294.6939393939394</v>
       </c>
       <c r="B37">
-        <v>0.006175584065620148</v>
+        <v>0.004191739511663775</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2172,511 +2172,511 @@
         <v>302.7909090909091</v>
       </c>
       <c r="B38">
-        <v>0.006024965193333106</v>
+        <v>0.004055481331892936</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>310.8656565656565</v>
+        <v>310.8878787878788</v>
       </c>
       <c r="B39">
-        <v>0.005881841104820782</v>
+        <v>0.003927075881962371</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>318.940404040404</v>
+        <v>318.9848484848485</v>
       </c>
       <c r="B40">
-        <v>0.005745658350741072</v>
+        <v>0.003805883292700867</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>327.0151515151515</v>
+        <v>327.0818181818182</v>
       </c>
       <c r="B41">
-        <v>0.005615917021766245</v>
+        <v>0.003691330342352621</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>335.089898989899</v>
+        <v>335.1787878787879</v>
       </c>
       <c r="B42">
-        <v>0.005492164402560705</v>
+        <v>0.00358290207638999</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>343.1646464646465</v>
+        <v>343.2757575757576</v>
       </c>
       <c r="B43">
-        <v>0.005373989509709177</v>
+        <v>0.003480134653385886</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>351.2393939393939</v>
+        <v>351.3727272727273</v>
       </c>
       <c r="B44">
-        <v>0.005261018372958773</v>
+        <v>0.003382609213512734</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>359.3141414141414</v>
+        <v>359.469696969697</v>
       </c>
       <c r="B45">
-        <v>0.005152909944174143</v>
+        <v>0.003289946603801274</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>367.3888888888889</v>
+        <v>367.5666666666667</v>
       </c>
       <c r="B46">
-        <v>0.005049352538531013</v>
+        <v>0.003201802824248834</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>375.4636363636363</v>
+        <v>375.6636363636364</v>
       </c>
       <c r="B47">
-        <v>0.004950060728737752</v>
+        <v>0.003117865082885064</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>383.5383838383838</v>
+        <v>383.7606060606061</v>
       </c>
       <c r="B48">
-        <v>0.004854772626283929</v>
+        <v>0.003037848367260696</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>391.6131313131313</v>
+        <v>391.8575757575758</v>
       </c>
       <c r="B49">
-        <v>0.004763247494494139</v>
+        <v>0.002961492455503649</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>399.6878787878787</v>
+        <v>399.9545454545455</v>
       </c>
       <c r="B50">
-        <v>0.004675263647001852</v>
+        <v>0.002888559302845906</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>407.7626262626262</v>
+        <v>408.0515151515152</v>
       </c>
       <c r="B51">
-        <v>0.004590616592533375</v>
+        <v>0.002818830749954937</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>415.8373737373737</v>
+        <v>416.1484848484849</v>
       </c>
       <c r="B52">
-        <v>0.004509117392907075</v>
+        <v>0.002752106507966855</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>423.9121212121212</v>
+        <v>424.2454545454546</v>
       </c>
       <c r="B53">
-        <v>0.004430591206145848</v>
+        <v>0.002688202382178486</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>431.9868686868687</v>
+        <v>432.3424242424243</v>
       </c>
       <c r="B54">
-        <v>0.004354875990761184</v>
+        <v>0.002626948702199065</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>440.0616161616161</v>
+        <v>440.439393939394</v>
       </c>
       <c r="B55">
-        <v>0.004281821350746441</v>
+        <v>0.002568188931217557</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>448.1363636363636</v>
+        <v>448.5363636363637</v>
       </c>
       <c r="B56">
-        <v>0.004211287503737038</v>
+        <v>0.00251177843109041</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>456.2111111111111</v>
+        <v>456.6333333333334</v>
       </c>
       <c r="B57">
-        <v>0.00414314435725427</v>
+        <v>0.002457583363342884</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>464.2858585858585</v>
+        <v>464.7303030303031</v>
       </c>
       <c r="B58">
-        <v>0.00407727068002698</v>
+        <v>0.002405479709022215</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>472.360606060606</v>
+        <v>472.8272727272728</v>
       </c>
       <c r="B59">
-        <v>0.004013553357146009</v>
+        <v>0.002355352392737675</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>480.4353535353535</v>
+        <v>480.9242424242425</v>
       </c>
       <c r="B60">
-        <v>0.003951886719303136</v>
+        <v>0.002307094498248114</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>488.510101010101</v>
+        <v>489.0212121212122</v>
       </c>
       <c r="B61">
-        <v>0.003892171937642248</v>
+        <v>0.00226060656467445</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>496.5848484848485</v>
+        <v>497.1181818181819</v>
       </c>
       <c r="B62">
-        <v>0.003834316476841483</v>
+        <v>0.00221579595387411</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>504.6595959595959</v>
+        <v>505.2151515151515</v>
       </c>
       <c r="B63">
-        <v>0.003778233599980349</v>
+        <v>0.002172576280758743</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>512.7343434343434</v>
+        <v>513.3121212121213</v>
       </c>
       <c r="B64">
-        <v>0.003723841919549707</v>
+        <v>0.002130866899400167</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>520.8090909090909</v>
+        <v>521.4090909090909</v>
       </c>
       <c r="B65">
-        <v>0.003671064989655256</v>
+        <v>0.00209059243868117</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>528.8838383838383</v>
+        <v>529.5060606060606</v>
       </c>
       <c r="B66">
-        <v>0.003619830935063521</v>
+        <v>0.002051682382031121</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>536.9585858585858</v>
+        <v>537.6030303030303</v>
       </c>
       <c r="B67">
-        <v>0.003570072113257467</v>
+        <v>0.002014070686461129</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>545.0333333333333</v>
+        <v>545.7</v>
       </c>
       <c r="B68">
-        <v>0.003521724806118537</v>
+        <v>0.001977695436696093</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>553.1080808080808</v>
+        <v>553.7969696969697</v>
       </c>
       <c r="B69">
-        <v>0.003474728938243024</v>
+        <v>0.001942498530705191</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>561.1828282828283</v>
+        <v>561.8939393939394</v>
       </c>
       <c r="B70">
-        <v>0.003429027819241569</v>
+        <v>0.001908425393369704</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>569.2575757575758</v>
+        <v>569.9909090909091</v>
       </c>
       <c r="B71">
-        <v>0.003384567907668399</v>
+        <v>0.001875424715407219</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>577.3323232323232</v>
+        <v>578.0878787878788</v>
       </c>
       <c r="B72">
-        <v>0.003341298594487549</v>
+        <v>0.001843448215002397</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>585.4070707070706</v>
+        <v>586.1848484848484</v>
       </c>
       <c r="B73">
-        <v>0.00329917200421184</v>
+        <v>0.001812450419883519</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>593.4818181818181</v>
+        <v>594.2818181818182</v>
       </c>
       <c r="B74">
-        <v>0.003258142812051314</v>
+        <v>0.001782388467836827</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>601.5565656565656</v>
+        <v>602.3787878787879</v>
       </c>
       <c r="B75">
-        <v>0.003218168075584502</v>
+        <v>0.001753221923872184</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>609.631313131313</v>
+        <v>610.4757575757576</v>
       </c>
       <c r="B76">
-        <v>0.003179207079621927</v>
+        <v>0.001724912612448014</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>617.7060606060605</v>
+        <v>618.5727272727273</v>
       </c>
       <c r="B77">
-        <v>0.003141221193068869</v>
+        <v>0.001697424463334556</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>625.780808080808</v>
+        <v>626.6696969696969</v>
       </c>
       <c r="B78">
-        <v>0.003104173736716384</v>
+        <v>0.00167072336984511</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>633.8555555555555</v>
+        <v>634.7666666666667</v>
       </c>
       <c r="B79">
-        <v>0.003068029860997553</v>
+        <v>0.00164477705829798</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>641.930303030303</v>
+        <v>642.8636363636364</v>
       </c>
       <c r="B80">
-        <v>0.003032756432841862</v>
+        <v>0.001619554967689372</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>650.0050505050505</v>
+        <v>650.9606060606061</v>
       </c>
       <c r="B81">
-        <v>0.002998321930845916</v>
+        <v>0.001595028138661609</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82">
-        <v>658.0797979797979</v>
+        <v>659.0575757575757</v>
       </c>
       <c r="B82">
-        <v>0.002964696348054624</v>
+        <v>0.001571169110943376</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83">
-        <v>666.1545454545454</v>
+        <v>667.1545454545454</v>
       </c>
       <c r="B83">
-        <v>0.002931851101714743</v>
+        <v>0.001547951828520692</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84">
-        <v>674.2292929292929</v>
+        <v>675.2515151515152</v>
       </c>
       <c r="B84">
-        <v>0.002899758949423204</v>
+        <v>0.001525351551870314</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85">
-        <v>682.3040404040404</v>
+        <v>683.3484848484849</v>
       </c>
       <c r="B85">
-        <v>0.002868393911146696</v>
+        <v>0.001503344776652226</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86">
-        <v>690.3787878787878</v>
+        <v>691.4454545454546</v>
       </c>
       <c r="B86">
-        <v>0.002837731196637552</v>
+        <v>0.001481909158315892</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87">
-        <v>698.4535353535352</v>
+        <v>699.5424242424242</v>
       </c>
       <c r="B87">
-        <v>0.002807747137814382</v>
+        <v>0.001461023442126762</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88">
-        <v>706.5282828282827</v>
+        <v>707.6393939393939</v>
       </c>
       <c r="B88">
-        <v>0.002778419125714995</v>
+        <v>0.001440667398165869</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89">
-        <v>714.6030303030302</v>
+        <v>715.7363636363636</v>
       </c>
       <c r="B89">
-        <v>0.002749725551664224</v>
+        <v>0.001420821760896863</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90">
-        <v>722.6777777777777</v>
+        <v>723.8333333333334</v>
       </c>
       <c r="B90">
-        <v>0.002721645752330935</v>
+        <v>0.001401468172932123</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91">
-        <v>730.7525252525252</v>
+        <v>731.9303030303031</v>
       </c>
       <c r="B91">
-        <v>0.00269415995837694</v>
+        <v>0.001382589132662983</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92">
-        <v>738.8272727272727</v>
+        <v>740.0272727272727</v>
       </c>
       <c r="B92">
-        <v>0.002667249246426297</v>
+        <v>0.001364167945449245</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93">
-        <v>746.9020202020201</v>
+        <v>748.1242424242424</v>
       </c>
       <c r="B93">
-        <v>0.00264089549410671</v>
+        <v>0.001346188678090202</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94">
-        <v>754.9767676767676</v>
+        <v>756.2212121212121</v>
       </c>
       <c r="B94">
-        <v>0.002615081337935753</v>
+        <v>0.001328636116323822</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95">
-        <v>763.0515151515151</v>
+        <v>764.3181818181819</v>
       </c>
       <c r="B95">
-        <v>0.002589790133843706</v>
+        <v>0.001311495725122791</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96">
-        <v>771.1262626262626</v>
+        <v>772.4151515151515</v>
       </c>
       <c r="B96">
-        <v>0.002565005920142038</v>
+        <v>0.00129475361157598</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97">
-        <v>779.2010101010101</v>
+        <v>780.5121212121212</v>
       </c>
       <c r="B97">
-        <v>0.002540713382762229</v>
+        <v>0.001278396490161965</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98">
-        <v>787.2757575757574</v>
+        <v>788.6090909090909</v>
       </c>
       <c r="B98">
-        <v>0.002516897822603894</v>
+        <v>0.001262411650237472</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99">
-        <v>795.3505050505049</v>
+        <v>796.7060606060606</v>
       </c>
       <c r="B99">
-        <v>0.002493545124844073</v>
+        <v>0.001246786925578432</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100">
-        <v>803.4252525252524</v>
+        <v>804.8030303030304</v>
       </c>
       <c r="B100">
-        <v>0.002470641730071381</v>
+        <v>0.001231510665824734</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101">
-        <v>811.5</v>
+        <v>812.9</v>
       </c>
       <c r="B101">
-        <v>0.002448174607119392</v>
+        <v>0.001216571709691934</v>
       </c>
     </row>
   </sheetData>
@@ -2720,25 +2720,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>12.1</v>
+        <v>11.3</v>
       </c>
       <c r="C2">
-        <v>1.12989675044522</v>
+        <v>1.3</v>
       </c>
       <c r="D2">
-        <v>0.113967</v>
+        <v>0.223665</v>
       </c>
       <c r="E2">
-        <v>0.0111726845525644</v>
+        <v>0.08689313063566455</v>
       </c>
       <c r="F2">
-        <v>1.08278537031645</v>
+        <v>1.05307844348342</v>
       </c>
       <c r="G2">
-        <v>-0.9432208836866045</v>
+        <v>-0.6504019707362143</v>
       </c>
       <c r="H2">
-        <v>-0.928579184308906</v>
+        <v>-0.7360841467267152</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2746,25 +2746,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>39.5</v>
+        <v>39</v>
       </c>
       <c r="C3">
-        <v>1.796601730428249</v>
+        <v>3.0840089349921</v>
       </c>
       <c r="D3">
-        <v>0.039636</v>
+        <v>0.047857</v>
       </c>
       <c r="E3">
-        <v>0.002826119915675514</v>
+        <v>0.005268825939218126</v>
       </c>
       <c r="F3">
-        <v>1.59659709562646</v>
+        <v>1.591064607026499</v>
       </c>
       <c r="G3">
-        <v>-1.401910180260961</v>
+        <v>-1.320054529380785</v>
       </c>
       <c r="H3">
-        <v>-1.410745692789158</v>
+        <v>-1.299983122420791</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2772,25 +2772,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>80.09999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="C4">
-        <v>3.572891763761611</v>
+        <v>2.478574859336174</v>
       </c>
       <c r="D4">
-        <v>0.019578</v>
+        <v>0.01952</v>
       </c>
       <c r="E4">
-        <v>0.001783419810987369</v>
+        <v>0.001232376205187</v>
       </c>
       <c r="F4">
-        <v>1.903632516084238</v>
+        <v>1.898176483497676</v>
       </c>
       <c r="G4">
-        <v>-1.708231675828481</v>
+        <v>-1.709520186669327</v>
       </c>
       <c r="H4">
-        <v>-1.698871069010518</v>
+        <v>-1.621887446920606</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2798,25 +2798,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>137.2</v>
+        <v>130.9</v>
       </c>
       <c r="C5">
-        <v>4.304519588628781</v>
+        <v>4.787599723359411</v>
       </c>
       <c r="D5">
-        <v>0.012534</v>
+        <v>0.012653</v>
       </c>
       <c r="E5">
-        <v>0.0009046155721262668</v>
+        <v>0.001167132335636747</v>
       </c>
       <c r="F5">
-        <v>2.137354111370733</v>
+        <v>2.116939646550756</v>
       </c>
       <c r="G5">
-        <v>-1.901910309636048</v>
+        <v>-1.897806491960256</v>
       </c>
       <c r="H5">
-        <v>-1.918197954724794</v>
+        <v>-1.851187625856062</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2824,25 +2824,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>203.4</v>
+        <v>214.1</v>
       </c>
       <c r="C6">
-        <v>4.77772609791171</v>
+        <v>4.670117771534247</v>
       </c>
       <c r="D6">
-        <v>0.008934000000000001</v>
+        <v>0.007606</v>
       </c>
       <c r="E6">
-        <v>0.000431483745026649</v>
+        <v>0.000416579190817571</v>
       </c>
       <c r="F6">
-        <v>2.308350948586726</v>
+        <v>2.330616667294438</v>
       </c>
       <c r="G6">
-        <v>-2.04895405186418</v>
+        <v>-2.118843678924436</v>
       </c>
       <c r="H6">
-        <v>-2.07866324560903</v>
+        <v>-2.075156681738808</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2850,25 +2850,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>290.4</v>
+        <v>288.1</v>
       </c>
       <c r="C7">
-        <v>4.742713709821976</v>
+        <v>5.685165882462103</v>
       </c>
       <c r="D7">
-        <v>0.005514</v>
+        <v>0.00615</v>
       </c>
       <c r="E7">
-        <v>0.0003042593922589372</v>
+        <v>0.0003635351121663185</v>
       </c>
       <c r="F7">
-        <v>2.462996612028056</v>
+        <v>2.459543258280413</v>
       </c>
       <c r="G7">
-        <v>-2.258533238230245</v>
+        <v>-2.211124884224583</v>
       </c>
       <c r="H7">
-        <v>-2.22378441727581</v>
+        <v>-2.210293191789403</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2876,25 +2876,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>397.9</v>
+        <v>394</v>
       </c>
       <c r="C8">
-        <v>4.958606435055898</v>
+        <v>3.346640106136302</v>
       </c>
       <c r="D8">
-        <v>0.004329999999999999</v>
+        <v>0.004235000000000001</v>
       </c>
       <c r="E8">
-        <v>0.0001732114956410868</v>
+        <v>0.0001603347193287288</v>
       </c>
       <c r="F8">
-        <v>2.599773939146388</v>
+        <v>2.595496221825574</v>
       </c>
       <c r="G8">
-        <v>-2.363512103646635</v>
+        <v>-2.373146585333274</v>
       </c>
       <c r="H8">
-        <v>-2.352137747897287</v>
+        <v>-2.352794508887963</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2902,25 +2902,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>515.9</v>
+        <v>515.2</v>
       </c>
       <c r="C9">
-        <v>5.700779673771728</v>
+        <v>3.805843460317889</v>
       </c>
       <c r="D9">
-        <v>0.003257</v>
+        <v>0.003294</v>
       </c>
       <c r="E9">
-        <v>0.0001395711686241507</v>
+        <v>0.0001124000790826136</v>
       </c>
       <c r="F9">
-        <v>2.712565527873308</v>
+        <v>2.711975854351756</v>
       </c>
       <c r="G9">
-        <v>-2.487182241435127</v>
+        <v>-2.482276405166265</v>
       </c>
       <c r="H9">
-        <v>-2.457982600872541</v>
+        <v>-2.474884536330605</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2928,25 +2928,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>667</v>
+        <v>662.5</v>
       </c>
       <c r="C10">
-        <v>4.695151163109069</v>
+        <v>6.057593948462082</v>
       </c>
       <c r="D10">
-        <v>0.002504999999999999</v>
+        <v>0.002638000000000001</v>
       </c>
       <c r="E10">
-        <v>7.528095524249295E-05</v>
+        <v>7.209253313161726E-05</v>
       </c>
       <c r="F10">
-        <v>2.824125833916549</v>
+        <v>2.821185882608845</v>
       </c>
       <c r="G10">
-        <v>-2.601192269796736</v>
+        <v>-2.578725208789654</v>
       </c>
       <c r="H10">
-        <v>-2.56267200479263</v>
+        <v>-2.589354809439706</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2954,25 +2954,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>811.5</v>
+        <v>812.9</v>
       </c>
       <c r="C11">
-        <v>8.364275886836296</v>
+        <v>9.599131905195039</v>
       </c>
       <c r="D11">
-        <v>0.002171</v>
+        <v>0.00213</v>
       </c>
       <c r="E11">
-        <v>6.04510821518799E-05</v>
+        <v>6.881537295950343E-05</v>
       </c>
       <c r="F11">
-        <v>2.909288524162251</v>
+        <v>2.910037123553051</v>
       </c>
       <c r="G11">
-        <v>-2.66334017654558</v>
+        <v>-2.671620396561262</v>
       </c>
       <c r="H11">
-        <v>-2.642589599089996</v>
+        <v>-2.68248568743035</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2998,7 +2998,7 @@
         <v>-2.338187314462739</v>
       </c>
       <c r="H12">
-        <v>-2.441950929022662</v>
+        <v>-2.457595894667791</v>
       </c>
     </row>
   </sheetData>
@@ -3021,290 +3021,290 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>12.1</v>
+        <v>11.3</v>
       </c>
       <c r="B2">
-        <v>0.114118894657337</v>
+        <v>0.2234229411226657</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>20.17474747474747</v>
+        <v>19.3969696969697</v>
       </c>
       <c r="B3">
-        <v>0.07153840198621657</v>
+        <v>0.1156212373834673</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>28.24949494949495</v>
+        <v>27.4939393939394</v>
       </c>
       <c r="B4">
-        <v>0.05259964516128546</v>
+        <v>0.07556595810281702</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>36.32424242424242</v>
+        <v>35.59090909090909</v>
       </c>
       <c r="B5">
-        <v>0.04180625295572488</v>
+        <v>0.05516354196624016</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>44.3989898989899</v>
+        <v>43.68787878787879</v>
       </c>
       <c r="B6">
-        <v>0.03480208572938091</v>
+        <v>0.04296524975839557</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>52.47373737373737</v>
+        <v>51.78484848484848</v>
       </c>
       <c r="B7">
-        <v>0.02987537705570119</v>
+        <v>0.03492127028347099</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>60.54848484848484</v>
+        <v>59.88181818181819</v>
       </c>
       <c r="B8">
-        <v>0.02621373526820083</v>
+        <v>0.02925286548600948</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>68.62323232323232</v>
+        <v>67.97878787878788</v>
       </c>
       <c r="B9">
-        <v>0.02338103360402072</v>
+        <v>0.02506208489084306</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>76.69797979797978</v>
+        <v>76.07575757575758</v>
       </c>
       <c r="B10">
-        <v>0.02112174936903392</v>
+        <v>0.02184900993129131</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>84.77272727272725</v>
+        <v>84.17272727272727</v>
       </c>
       <c r="B11">
-        <v>0.01927604335909764</v>
+        <v>0.01931428318245793</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>92.84747474747473</v>
+        <v>92.26969696969697</v>
       </c>
       <c r="B12">
-        <v>0.01773870091217781</v>
+        <v>0.01726822968450587</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>100.9222222222222</v>
+        <v>100.3666666666667</v>
       </c>
       <c r="B13">
-        <v>0.01643757540808223</v>
+        <v>0.01558512248656729</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>108.9969696969697</v>
+        <v>108.4636363636364</v>
       </c>
       <c r="B14">
-        <v>0.01532150915408134</v>
+        <v>0.01417848879016148</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>117.0717171717172</v>
+        <v>116.5606060606061</v>
       </c>
       <c r="B15">
-        <v>0.01435319723341663</v>
+        <v>0.01298699511530168</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>125.1464646464646</v>
+        <v>124.6575757575758</v>
       </c>
       <c r="B16">
-        <v>0.0135047825124472</v>
+        <v>0.01196599002919759</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>133.2212121212121</v>
+        <v>132.7545454545455</v>
       </c>
       <c r="B17">
-        <v>0.01275503402534345</v>
+        <v>0.0110822316650582</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>141.2959595959596</v>
+        <v>140.8515151515152</v>
       </c>
       <c r="B18">
-        <v>0.01208748145851442</v>
+        <v>0.01031048744007662</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>149.3707070707071</v>
+        <v>148.9484848484849</v>
       </c>
       <c r="B19">
-        <v>0.01148914749613198</v>
+        <v>0.009631275999786809</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>157.4454545454545</v>
+        <v>157.0454545454546</v>
       </c>
       <c r="B20">
-        <v>0.01094966553484734</v>
+        <v>0.009029328839544866</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>165.520202020202</v>
+        <v>165.1424242424243</v>
       </c>
       <c r="B21">
-        <v>0.01046065249826879</v>
+        <v>0.008492518339989152</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>173.5949494949495</v>
+        <v>173.2393939393939</v>
       </c>
       <c r="B22">
-        <v>0.01001525453838841</v>
+        <v>0.008011095705198019</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>181.6696969696969</v>
+        <v>181.3363636363637</v>
       </c>
       <c r="B23">
-        <v>0.009607812388484292</v>
+        <v>0.007577139428687919</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>189.7444444444444</v>
+        <v>189.4333333333334</v>
       </c>
       <c r="B24">
-        <v>0.009233611095551531</v>
+        <v>0.007184149648374311</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>197.8191919191919</v>
+        <v>197.5303030303031</v>
       </c>
       <c r="B25">
-        <v>0.008888690275485224</v>
+        <v>0.006826745424516108</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>205.8939393939393</v>
+        <v>205.6272727272728</v>
       </c>
       <c r="B26">
-        <v>0.00856969845168928</v>
+        <v>0.006500435816382649</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>213.9686868686868</v>
+        <v>213.7242424242424</v>
       </c>
       <c r="B27">
-        <v>0.008273779955781664</v>
+        <v>0.006201444662158525</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>222.0434343434343</v>
+        <v>221.8212121212121</v>
       </c>
       <c r="B28">
-        <v>0.007998486190224757</v>
+        <v>0.005926574970018011</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>230.1181818181818</v>
+        <v>229.9181818181818</v>
       </c>
       <c r="B29">
-        <v>0.007741705333417221</v>
+        <v>0.00567310289062023</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>238.1929292929293</v>
+        <v>238.0151515151516</v>
       </c>
       <c r="B30">
-        <v>0.007501606158254927</v>
+        <v>0.005438694034608454</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>246.2676767676767</v>
+        <v>246.1121212121213</v>
       </c>
       <c r="B31">
-        <v>0.007276592760105602</v>
+        <v>0.00522133684803717</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>254.3424242424242</v>
+        <v>254.2090909090909</v>
       </c>
       <c r="B32">
-        <v>0.007065267796277352</v>
+        <v>0.005019289137692525</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>262.4171717171717</v>
+        <v>262.3060606060606</v>
       </c>
       <c r="B33">
-        <v>0.006866402423782412</v>
+        <v>0.004831034826267896</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>270.4919191919192</v>
+        <v>270.4030303030303</v>
       </c>
       <c r="B34">
-        <v>0.006678911551119365</v>
+        <v>0.0046552487335509</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>278.5666666666667</v>
+        <v>278.5000000000001</v>
       </c>
       <c r="B35">
-        <v>0.006501833337750171</v>
+        <v>0.004490767704652825</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>286.6414141414141</v>
+        <v>286.5969696969697</v>
       </c>
       <c r="B36">
-        <v>0.006334312112962199</v>
+        <v>0.004336566794921568</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>294.7161616161616</v>
+        <v>294.6939393939394</v>
       </c>
       <c r="B37">
-        <v>0.006175584065620148</v>
+        <v>0.004191739511663775</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3312,511 +3312,511 @@
         <v>302.7909090909091</v>
       </c>
       <c r="B38">
-        <v>0.006024965193333106</v>
+        <v>0.004055481331892936</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>310.8656565656565</v>
+        <v>310.8878787878788</v>
       </c>
       <c r="B39">
-        <v>0.005881841104820782</v>
+        <v>0.003927075881962371</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>318.940404040404</v>
+        <v>318.9848484848485</v>
       </c>
       <c r="B40">
-        <v>0.005745658350741072</v>
+        <v>0.003805883292700867</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>327.0151515151515</v>
+        <v>327.0818181818182</v>
       </c>
       <c r="B41">
-        <v>0.005615917021766245</v>
+        <v>0.003691330342352621</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>335.089898989899</v>
+        <v>335.1787878787879</v>
       </c>
       <c r="B42">
-        <v>0.005492164402560705</v>
+        <v>0.00358290207638999</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>343.1646464646465</v>
+        <v>343.2757575757576</v>
       </c>
       <c r="B43">
-        <v>0.005373989509709177</v>
+        <v>0.003480134653385886</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>351.2393939393939</v>
+        <v>351.3727272727273</v>
       </c>
       <c r="B44">
-        <v>0.005261018372958773</v>
+        <v>0.003382609213512734</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>359.3141414141414</v>
+        <v>359.469696969697</v>
       </c>
       <c r="B45">
-        <v>0.005152909944174143</v>
+        <v>0.003289946603801274</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>367.3888888888889</v>
+        <v>367.5666666666667</v>
       </c>
       <c r="B46">
-        <v>0.005049352538531013</v>
+        <v>0.003201802824248834</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>375.4636363636363</v>
+        <v>375.6636363636364</v>
       </c>
       <c r="B47">
-        <v>0.004950060728737752</v>
+        <v>0.003117865082885064</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>383.5383838383838</v>
+        <v>383.7606060606061</v>
       </c>
       <c r="B48">
-        <v>0.004854772626283929</v>
+        <v>0.003037848367260696</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>391.6131313131313</v>
+        <v>391.8575757575758</v>
       </c>
       <c r="B49">
-        <v>0.004763247494494139</v>
+        <v>0.002961492455503649</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>399.6878787878787</v>
+        <v>399.9545454545455</v>
       </c>
       <c r="B50">
-        <v>0.004675263647001852</v>
+        <v>0.002888559302845906</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>407.7626262626262</v>
+        <v>408.0515151515152</v>
       </c>
       <c r="B51">
-        <v>0.004590616592533375</v>
+        <v>0.002818830749954937</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>415.8373737373737</v>
+        <v>416.1484848484849</v>
       </c>
       <c r="B52">
-        <v>0.004509117392907075</v>
+        <v>0.002752106507966855</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>423.9121212121212</v>
+        <v>424.2454545454546</v>
       </c>
       <c r="B53">
-        <v>0.004430591206145848</v>
+        <v>0.002688202382178486</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>431.9868686868687</v>
+        <v>432.3424242424243</v>
       </c>
       <c r="B54">
-        <v>0.004354875990761184</v>
+        <v>0.002626948702199065</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>440.0616161616161</v>
+        <v>440.439393939394</v>
       </c>
       <c r="B55">
-        <v>0.004281821350746441</v>
+        <v>0.002568188931217557</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>448.1363636363636</v>
+        <v>448.5363636363637</v>
       </c>
       <c r="B56">
-        <v>0.004211287503737038</v>
+        <v>0.00251177843109041</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>456.2111111111111</v>
+        <v>456.6333333333334</v>
       </c>
       <c r="B57">
-        <v>0.00414314435725427</v>
+        <v>0.002457583363342884</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>464.2858585858585</v>
+        <v>464.7303030303031</v>
       </c>
       <c r="B58">
-        <v>0.00407727068002698</v>
+        <v>0.002405479709022215</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>472.360606060606</v>
+        <v>472.8272727272728</v>
       </c>
       <c r="B59">
-        <v>0.004013553357146009</v>
+        <v>0.002355352392737675</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>480.4353535353535</v>
+        <v>480.9242424242425</v>
       </c>
       <c r="B60">
-        <v>0.003951886719303136</v>
+        <v>0.002307094498248114</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>488.510101010101</v>
+        <v>489.0212121212122</v>
       </c>
       <c r="B61">
-        <v>0.003892171937642248</v>
+        <v>0.00226060656467445</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>496.5848484848485</v>
+        <v>497.1181818181819</v>
       </c>
       <c r="B62">
-        <v>0.003834316476841483</v>
+        <v>0.00221579595387411</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>504.6595959595959</v>
+        <v>505.2151515151515</v>
       </c>
       <c r="B63">
-        <v>0.003778233599980349</v>
+        <v>0.002172576280758743</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>512.7343434343434</v>
+        <v>513.3121212121213</v>
       </c>
       <c r="B64">
-        <v>0.003723841919549707</v>
+        <v>0.002130866899400167</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>520.8090909090909</v>
+        <v>521.4090909090909</v>
       </c>
       <c r="B65">
-        <v>0.003671064989655256</v>
+        <v>0.00209059243868117</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>528.8838383838383</v>
+        <v>529.5060606060606</v>
       </c>
       <c r="B66">
-        <v>0.003619830935063521</v>
+        <v>0.002051682382031121</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>536.9585858585858</v>
+        <v>537.6030303030303</v>
       </c>
       <c r="B67">
-        <v>0.003570072113257467</v>
+        <v>0.002014070686461129</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>545.0333333333333</v>
+        <v>545.7</v>
       </c>
       <c r="B68">
-        <v>0.003521724806118537</v>
+        <v>0.001977695436696093</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>553.1080808080808</v>
+        <v>553.7969696969697</v>
       </c>
       <c r="B69">
-        <v>0.003474728938243024</v>
+        <v>0.001942498530705191</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>561.1828282828283</v>
+        <v>561.8939393939394</v>
       </c>
       <c r="B70">
-        <v>0.003429027819241569</v>
+        <v>0.001908425393369704</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>569.2575757575758</v>
+        <v>569.9909090909091</v>
       </c>
       <c r="B71">
-        <v>0.003384567907668399</v>
+        <v>0.001875424715407219</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>577.3323232323232</v>
+        <v>578.0878787878788</v>
       </c>
       <c r="B72">
-        <v>0.003341298594487549</v>
+        <v>0.001843448215002397</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>585.4070707070706</v>
+        <v>586.1848484848484</v>
       </c>
       <c r="B73">
-        <v>0.00329917200421184</v>
+        <v>0.001812450419883519</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>593.4818181818181</v>
+        <v>594.2818181818182</v>
       </c>
       <c r="B74">
-        <v>0.003258142812051314</v>
+        <v>0.001782388467836827</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>601.5565656565656</v>
+        <v>602.3787878787879</v>
       </c>
       <c r="B75">
-        <v>0.003218168075584502</v>
+        <v>0.001753221923872184</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>609.631313131313</v>
+        <v>610.4757575757576</v>
       </c>
       <c r="B76">
-        <v>0.003179207079621927</v>
+        <v>0.001724912612448014</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>617.7060606060605</v>
+        <v>618.5727272727273</v>
       </c>
       <c r="B77">
-        <v>0.003141221193068869</v>
+        <v>0.001697424463334556</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>625.780808080808</v>
+        <v>626.6696969696969</v>
       </c>
       <c r="B78">
-        <v>0.003104173736716384</v>
+        <v>0.00167072336984511</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>633.8555555555555</v>
+        <v>634.7666666666667</v>
       </c>
       <c r="B79">
-        <v>0.003068029860997553</v>
+        <v>0.00164477705829798</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>641.930303030303</v>
+        <v>642.8636363636364</v>
       </c>
       <c r="B80">
-        <v>0.003032756432841862</v>
+        <v>0.001619554967689372</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>650.0050505050505</v>
+        <v>650.9606060606061</v>
       </c>
       <c r="B81">
-        <v>0.002998321930845916</v>
+        <v>0.001595028138661609</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82">
-        <v>658.0797979797979</v>
+        <v>659.0575757575757</v>
       </c>
       <c r="B82">
-        <v>0.002964696348054624</v>
+        <v>0.001571169110943376</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83">
-        <v>666.1545454545454</v>
+        <v>667.1545454545454</v>
       </c>
       <c r="B83">
-        <v>0.002931851101714743</v>
+        <v>0.001547951828520692</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84">
-        <v>674.2292929292929</v>
+        <v>675.2515151515152</v>
       </c>
       <c r="B84">
-        <v>0.002899758949423204</v>
+        <v>0.001525351551870314</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85">
-        <v>682.3040404040404</v>
+        <v>683.3484848484849</v>
       </c>
       <c r="B85">
-        <v>0.002868393911146696</v>
+        <v>0.001503344776652226</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86">
-        <v>690.3787878787878</v>
+        <v>691.4454545454546</v>
       </c>
       <c r="B86">
-        <v>0.002837731196637552</v>
+        <v>0.001481909158315892</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87">
-        <v>698.4535353535352</v>
+        <v>699.5424242424242</v>
       </c>
       <c r="B87">
-        <v>0.002807747137814382</v>
+        <v>0.001461023442126762</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88">
-        <v>706.5282828282827</v>
+        <v>707.6393939393939</v>
       </c>
       <c r="B88">
-        <v>0.002778419125714995</v>
+        <v>0.001440667398165869</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89">
-        <v>714.6030303030302</v>
+        <v>715.7363636363636</v>
       </c>
       <c r="B89">
-        <v>0.002749725551664224</v>
+        <v>0.001420821760896863</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90">
-        <v>722.6777777777777</v>
+        <v>723.8333333333334</v>
       </c>
       <c r="B90">
-        <v>0.002721645752330935</v>
+        <v>0.001401468172932123</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91">
-        <v>730.7525252525252</v>
+        <v>731.9303030303031</v>
       </c>
       <c r="B91">
-        <v>0.00269415995837694</v>
+        <v>0.001382589132662983</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92">
-        <v>738.8272727272727</v>
+        <v>740.0272727272727</v>
       </c>
       <c r="B92">
-        <v>0.002667249246426297</v>
+        <v>0.001364167945449245</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93">
-        <v>746.9020202020201</v>
+        <v>748.1242424242424</v>
       </c>
       <c r="B93">
-        <v>0.00264089549410671</v>
+        <v>0.001346188678090202</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94">
-        <v>754.9767676767676</v>
+        <v>756.2212121212121</v>
       </c>
       <c r="B94">
-        <v>0.002615081337935753</v>
+        <v>0.001328636116323822</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95">
-        <v>763.0515151515151</v>
+        <v>764.3181818181819</v>
       </c>
       <c r="B95">
-        <v>0.002589790133843706</v>
+        <v>0.001311495725122791</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96">
-        <v>771.1262626262626</v>
+        <v>772.4151515151515</v>
       </c>
       <c r="B96">
-        <v>0.002565005920142038</v>
+        <v>0.00129475361157598</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97">
-        <v>779.2010101010101</v>
+        <v>780.5121212121212</v>
       </c>
       <c r="B97">
-        <v>0.002540713382762229</v>
+        <v>0.001278396490161965</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98">
-        <v>787.2757575757574</v>
+        <v>788.6090909090909</v>
       </c>
       <c r="B98">
-        <v>0.002516897822603894</v>
+        <v>0.001262411650237472</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99">
-        <v>795.3505050505049</v>
+        <v>796.7060606060606</v>
       </c>
       <c r="B99">
-        <v>0.002493545124844073</v>
+        <v>0.001246786925578432</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100">
-        <v>803.4252525252524</v>
+        <v>804.8030303030304</v>
       </c>
       <c r="B100">
-        <v>0.002470641730071381</v>
+        <v>0.001231510665824734</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101">
-        <v>811.5</v>
+        <v>812.9</v>
       </c>
       <c r="B101">
-        <v>0.002448174607119392</v>
+        <v>0.001216571709691934</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sgt_files/InVitroBioFilm_SGT_scaling.xlsx
+++ b/datasets/sgt_files/InVitroBioFilm_SGT_scaling.xlsx
@@ -440,25 +440,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>11.3</v>
+        <v>10.5</v>
       </c>
       <c r="C2">
-        <v>1.3</v>
+        <v>1.408308678285174</v>
       </c>
       <c r="D2">
-        <v>0.223665</v>
+        <v>0.185419</v>
       </c>
       <c r="E2">
-        <v>0.08689313063566455</v>
+        <v>0.02764825308727077</v>
       </c>
       <c r="F2">
-        <v>1.05307844348342</v>
+        <v>1.021189299069938</v>
       </c>
       <c r="G2">
-        <v>-0.6504019707362143</v>
+        <v>-0.7318457654861891</v>
       </c>
       <c r="H2">
-        <v>-0.7360841467267152</v>
+        <v>-0.7956170590946079</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -466,25 +466,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>39</v>
+        <v>38.1</v>
       </c>
       <c r="C3">
-        <v>3.0840089349921</v>
+        <v>1.27758452644912</v>
       </c>
       <c r="D3">
-        <v>0.047857</v>
+        <v>0.03847</v>
       </c>
       <c r="E3">
-        <v>0.005268825939218126</v>
+        <v>0.003421588649865569</v>
       </c>
       <c r="F3">
-        <v>1.591064607026499</v>
+        <v>1.580924975675619</v>
       </c>
       <c r="G3">
-        <v>-1.320054529380785</v>
+        <v>-1.414877813693185</v>
       </c>
       <c r="H3">
-        <v>-1.299983122420791</v>
+        <v>-1.347299254247706</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -492,25 +492,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>79.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="C4">
-        <v>2.478574859336174</v>
+        <v>2.394437999475729</v>
       </c>
       <c r="D4">
-        <v>0.01952</v>
+        <v>0.018984</v>
       </c>
       <c r="E4">
-        <v>0.001232376205187</v>
+        <v>0.00127096481287074</v>
       </c>
       <c r="F4">
-        <v>1.898176483497676</v>
+        <v>1.90848501887865</v>
       </c>
       <c r="G4">
-        <v>-1.709520186669327</v>
+        <v>-1.721612274790717</v>
       </c>
       <c r="H4">
-        <v>-1.621887446920606</v>
+        <v>-1.670146360893718</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -518,25 +518,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>130.9</v>
+        <v>137.5</v>
       </c>
       <c r="C5">
-        <v>4.787599723359411</v>
+        <v>4.185291706281256</v>
       </c>
       <c r="D5">
-        <v>0.012653</v>
+        <v>0.012357</v>
       </c>
       <c r="E5">
-        <v>0.001167132335636747</v>
+        <v>0.0007632111255886026</v>
       </c>
       <c r="F5">
-        <v>2.116939646550756</v>
+        <v>2.138302698166282</v>
       </c>
       <c r="G5">
-        <v>-1.897806491960256</v>
+        <v>-1.90808695332392</v>
       </c>
       <c r="H5">
-        <v>-1.851187625856062</v>
+        <v>-1.896657421548708</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -544,25 +544,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>214.1</v>
+        <v>211.1</v>
       </c>
       <c r="C6">
-        <v>4.670117771534247</v>
+        <v>5.722179072113467</v>
       </c>
       <c r="D6">
-        <v>0.007606</v>
+        <v>0.008705000000000001</v>
       </c>
       <c r="E6">
-        <v>0.000416579190817571</v>
+        <v>0.0005302289861727458</v>
       </c>
       <c r="F6">
-        <v>2.330616667294438</v>
+        <v>2.324488233307656</v>
       </c>
       <c r="G6">
-        <v>-2.118843678924436</v>
+        <v>-2.06023122454665</v>
       </c>
       <c r="H6">
-        <v>-2.075156681738808</v>
+        <v>-2.080164117701128</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -570,25 +570,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>288.1</v>
+        <v>287.4</v>
       </c>
       <c r="C7">
-        <v>5.685165882462103</v>
+        <v>3.679371927079101</v>
       </c>
       <c r="D7">
-        <v>0.00615</v>
+        <v>0.006292000000000001</v>
       </c>
       <c r="E7">
-        <v>0.0003635351121663185</v>
+        <v>0.0001936308056299124</v>
       </c>
       <c r="F7">
-        <v>2.459543258280413</v>
+        <v>2.458486763798207</v>
       </c>
       <c r="G7">
-        <v>-2.211124884224583</v>
+        <v>-2.201211286048751</v>
       </c>
       <c r="H7">
-        <v>-2.210293191789403</v>
+        <v>-2.212234676248701</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -596,25 +596,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>394</v>
+        <v>393.5</v>
       </c>
       <c r="C8">
-        <v>3.346640106136302</v>
+        <v>5.066776314603025</v>
       </c>
       <c r="D8">
-        <v>0.004235000000000001</v>
+        <v>0.004414</v>
       </c>
       <c r="E8">
-        <v>0.0001603347193287288</v>
+        <v>0.0002112144776182626</v>
       </c>
       <c r="F8">
-        <v>2.595496221825574</v>
+        <v>2.594944736695084</v>
       </c>
       <c r="G8">
-        <v>-2.373146585333274</v>
+        <v>-2.355167671174364</v>
       </c>
       <c r="H8">
-        <v>-2.352794508887963</v>
+        <v>-2.346729290725321</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -622,25 +622,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>515.2</v>
+        <v>515.3</v>
       </c>
       <c r="C9">
-        <v>3.805843460317889</v>
+        <v>7.935923946768195</v>
       </c>
       <c r="D9">
-        <v>0.003294</v>
+        <v>0.003261</v>
       </c>
       <c r="E9">
-        <v>0.0001124000790826136</v>
+        <v>0.0001578497879490358</v>
       </c>
       <c r="F9">
-        <v>2.711975854351756</v>
+        <v>2.712060142461075</v>
       </c>
       <c r="G9">
-        <v>-2.482276405166265</v>
+        <v>-2.486649201194043</v>
       </c>
       <c r="H9">
-        <v>-2.474884536330605</v>
+        <v>-2.462159639083738</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -648,25 +648,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>662.5</v>
+        <v>665.3</v>
       </c>
       <c r="C10">
-        <v>6.057593948462082</v>
+        <v>8.203048213926333</v>
       </c>
       <c r="D10">
-        <v>0.002638000000000001</v>
+        <v>0.002514</v>
       </c>
       <c r="E10">
-        <v>7.209253313161726E-05</v>
+        <v>0.0001025367142918954</v>
       </c>
       <c r="F10">
-        <v>2.821185882608845</v>
+        <v>2.823017523446049</v>
       </c>
       <c r="G10">
-        <v>-2.578725208789654</v>
+        <v>-2.599634726650061</v>
       </c>
       <c r="H10">
-        <v>-2.589354809439706</v>
+        <v>-2.571520564371608</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -674,25 +674,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>812.9</v>
+        <v>803.1</v>
       </c>
       <c r="C11">
-        <v>9.599131905195039</v>
+        <v>7.651361534611556</v>
       </c>
       <c r="D11">
-        <v>0.00213</v>
+        <v>0.002173</v>
       </c>
       <c r="E11">
-        <v>6.881537295950343E-05</v>
+        <v>6.824872811187685E-05</v>
       </c>
       <c r="F11">
-        <v>2.910037123553051</v>
+        <v>2.904769625906595</v>
       </c>
       <c r="G11">
-        <v>-2.671620396561262</v>
+        <v>-2.662940273679475</v>
       </c>
       <c r="H11">
-        <v>-2.68248568743035</v>
+        <v>-2.652096416919216</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -718,7 +718,7 @@
         <v>-2.338187314462739</v>
       </c>
       <c r="H12">
-        <v>-2.457595894667791</v>
+        <v>-2.445819704215646</v>
       </c>
     </row>
   </sheetData>
@@ -741,802 +741,802 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>11.3</v>
+        <v>10.5</v>
       </c>
       <c r="B2">
-        <v>0.2234229411226657</v>
+        <v>0.184891647846076</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>19.3969696969697</v>
+        <v>18.50606060606061</v>
       </c>
       <c r="B3">
-        <v>0.1156212373834673</v>
+        <v>0.09699386650165555</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>27.4939393939394</v>
+        <v>26.51212121212121</v>
       </c>
       <c r="B4">
-        <v>0.07556595810281702</v>
+        <v>0.06441915600835781</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>35.59090909090909</v>
+        <v>34.51818181818182</v>
       </c>
       <c r="B5">
-        <v>0.05516354196624016</v>
+        <v>0.04770430921186292</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>43.68787878787879</v>
+        <v>42.52424242424242</v>
       </c>
       <c r="B6">
-        <v>0.04296524975839557</v>
+        <v>0.03762158624308524</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>51.78484848484848</v>
+        <v>50.53030303030303</v>
       </c>
       <c r="B7">
-        <v>0.03492127028347099</v>
+        <v>0.03091421103869369</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>59.88181818181819</v>
+        <v>58.53636363636363</v>
       </c>
       <c r="B8">
-        <v>0.02925286548600948</v>
+        <v>0.02614858339296097</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>67.97878787878788</v>
+        <v>66.54242424242423</v>
       </c>
       <c r="B9">
-        <v>0.02506208489084306</v>
+        <v>0.02259818839391243</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>76.07575757575758</v>
+        <v>74.54848484848485</v>
       </c>
       <c r="B10">
-        <v>0.02184900993129131</v>
+        <v>0.01985673358482553</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>84.17272727272727</v>
+        <v>82.55454545454545</v>
       </c>
       <c r="B11">
-        <v>0.01931428318245793</v>
+        <v>0.01767978487064297</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>92.26969696969697</v>
+        <v>90.56060606060606</v>
       </c>
       <c r="B12">
-        <v>0.01726822968450587</v>
+        <v>0.01591174092637995</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>100.3666666666667</v>
+        <v>98.56666666666666</v>
       </c>
       <c r="B13">
-        <v>0.01558512248656729</v>
+        <v>0.01444898696256113</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>108.4636363636364</v>
+        <v>106.5727272727273</v>
       </c>
       <c r="B14">
-        <v>0.01417848879016148</v>
+        <v>0.01321994121343388</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>116.5606060606061</v>
+        <v>114.5787878787879</v>
       </c>
       <c r="B15">
-        <v>0.01298699511530168</v>
+        <v>0.01217361410153211</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>124.6575757575758</v>
+        <v>122.5848484848485</v>
       </c>
       <c r="B16">
-        <v>0.01196599002919759</v>
+        <v>0.01127273135110265</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>132.7545454545455</v>
+        <v>130.5909090909091</v>
       </c>
       <c r="B17">
-        <v>0.0110822316650582</v>
+        <v>0.01048943309212318</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>140.8515151515152</v>
+        <v>138.5969696969697</v>
       </c>
       <c r="B18">
-        <v>0.01031048744007662</v>
+        <v>0.009802491403436467</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>148.9484848484849</v>
+        <v>146.6030303030303</v>
       </c>
       <c r="B19">
-        <v>0.009631275999786809</v>
+        <v>0.009195456799216902</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>157.0454545454546</v>
+        <v>154.6090909090909</v>
       </c>
       <c r="B20">
-        <v>0.009029328839544866</v>
+        <v>0.008655391614442896</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>165.1424242424243</v>
+        <v>162.6151515151515</v>
       </c>
       <c r="B21">
-        <v>0.008492518339989152</v>
+        <v>0.008171984784864205</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>173.2393939393939</v>
+        <v>170.6212121212121</v>
       </c>
       <c r="B22">
-        <v>0.008011095705198019</v>
+        <v>0.007736920717535016</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>181.3363636363637</v>
+        <v>178.6272727272727</v>
       </c>
       <c r="B23">
-        <v>0.007577139428687919</v>
+        <v>0.007343421227736977</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>189.4333333333334</v>
+        <v>186.6333333333333</v>
       </c>
       <c r="B24">
-        <v>0.007184149648374311</v>
+        <v>0.006985907714317893</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>197.5303030303031</v>
+        <v>194.6393939393939</v>
       </c>
       <c r="B25">
-        <v>0.006826745424516108</v>
+        <v>0.006659748375801701</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>205.6272727272728</v>
+        <v>202.6454545454545</v>
       </c>
       <c r="B26">
-        <v>0.006500435816382649</v>
+        <v>0.006361066553561816</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>213.7242424242424</v>
+        <v>210.6515151515152</v>
       </c>
       <c r="B27">
-        <v>0.006201444662158525</v>
+        <v>0.006086593664304345</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>221.8212121212121</v>
+        <v>218.6575757575758</v>
       </c>
       <c r="B28">
-        <v>0.005926574970018011</v>
+        <v>0.005833555098793225</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>229.9181818181818</v>
+        <v>226.6636363636364</v>
       </c>
       <c r="B29">
-        <v>0.00567310289062023</v>
+        <v>0.005599580796224393</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>238.0151515151516</v>
+        <v>234.669696969697</v>
       </c>
       <c r="B30">
-        <v>0.005438694034608454</v>
+        <v>0.005382634499791695</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>246.1121212121213</v>
+        <v>242.6757575757576</v>
       </c>
       <c r="B31">
-        <v>0.00522133684803717</v>
+        <v>0.005180957304561919</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>254.2090909090909</v>
+        <v>250.6818181818182</v>
       </c>
       <c r="B32">
-        <v>0.005019289137692525</v>
+        <v>0.004993022246858652</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>262.3060606060606</v>
+        <v>258.6878787878788</v>
       </c>
       <c r="B33">
-        <v>0.004831034826267896</v>
+        <v>0.004817497501294103</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>270.4030303030303</v>
+        <v>266.6939393939394</v>
       </c>
       <c r="B34">
-        <v>0.0046552487335509</v>
+        <v>0.004653216344908505</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>278.5000000000001</v>
+        <v>274.7</v>
       </c>
       <c r="B35">
-        <v>0.004490767704652825</v>
+        <v>0.004499152483511465</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>286.5969696969697</v>
+        <v>282.7060606060606</v>
       </c>
       <c r="B36">
-        <v>0.004336566794921568</v>
+        <v>0.00435439965844809</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>294.6939393939394</v>
+        <v>290.7121212121212</v>
       </c>
       <c r="B37">
-        <v>0.004191739511663775</v>
+        <v>0.004218154693983959</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>302.7909090909091</v>
+        <v>298.7181818181818</v>
       </c>
       <c r="B38">
-        <v>0.004055481331892936</v>
+        <v>0.004089703328325833</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>310.8878787878788</v>
+        <v>306.7242424242424</v>
       </c>
       <c r="B39">
-        <v>0.003927075881962371</v>
+        <v>0.003968408310592312</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>318.9848484848485</v>
+        <v>314.730303030303</v>
       </c>
       <c r="B40">
-        <v>0.003805883292700867</v>
+        <v>0.003853699353024394</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>327.0818181818182</v>
+        <v>322.7363636363636</v>
       </c>
       <c r="B41">
-        <v>0.003691330342352621</v>
+        <v>0.003745064610494677</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>335.1787878787879</v>
+        <v>330.7424242424242</v>
       </c>
       <c r="B42">
-        <v>0.00358290207638999</v>
+        <v>0.003642043423865678</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>343.2757575757576</v>
+        <v>338.7484848484848</v>
       </c>
       <c r="B43">
-        <v>0.003480134653385886</v>
+        <v>0.003544220114334572</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>351.3727272727273</v>
+        <v>346.7545454545455</v>
       </c>
       <c r="B44">
-        <v>0.003382609213512734</v>
+        <v>0.003451218655832776</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>359.469696969697</v>
+        <v>354.7606060606061</v>
       </c>
       <c r="B45">
-        <v>0.003289946603801274</v>
+        <v>0.003362698084258411</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>367.5666666666667</v>
+        <v>362.7666666666667</v>
       </c>
       <c r="B46">
-        <v>0.003201802824248834</v>
+        <v>0.003278348527644262</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>375.6636363636364</v>
+        <v>370.7727272727273</v>
       </c>
       <c r="B47">
-        <v>0.003117865082885064</v>
+        <v>0.003197887761699077</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>383.7606060606061</v>
+        <v>378.7787878787879</v>
       </c>
       <c r="B48">
-        <v>0.003037848367260696</v>
+        <v>0.003121058211573426</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>391.8575757575758</v>
+        <v>386.7848484848485</v>
       </c>
       <c r="B49">
-        <v>0.002961492455503649</v>
+        <v>0.003047624334014674</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>399.9545454545455</v>
+        <v>394.7909090909091</v>
       </c>
       <c r="B50">
-        <v>0.002888559302845906</v>
+        <v>0.002977370324925316</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>408.0515151515152</v>
+        <v>402.7969696969697</v>
       </c>
       <c r="B51">
-        <v>0.002818830749954937</v>
+        <v>0.002910098106220766</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>416.1484848484849</v>
+        <v>410.8030303030303</v>
       </c>
       <c r="B52">
-        <v>0.002752106507966855</v>
+        <v>0.002845625553184896</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>424.2454545454546</v>
+        <v>418.8090909090909</v>
       </c>
       <c r="B53">
-        <v>0.002688202382178486</v>
+        <v>0.002783784929549944</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>432.3424242424243</v>
+        <v>426.8151515151515</v>
       </c>
       <c r="B54">
-        <v>0.002626948702199065</v>
+        <v>0.002724421502523833</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>440.439393939394</v>
+        <v>434.8212121212121</v>
       </c>
       <c r="B55">
-        <v>0.002568188931217557</v>
+        <v>0.002667392314144691</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>448.5363636363637</v>
+        <v>442.8272727272727</v>
       </c>
       <c r="B56">
-        <v>0.00251177843109041</v>
+        <v>0.00261256508881331</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>456.6333333333334</v>
+        <v>450.8333333333333</v>
       </c>
       <c r="B57">
-        <v>0.002457583363342884</v>
+        <v>0.00255981725976266</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>464.7303030303031</v>
+        <v>458.8393939393939</v>
       </c>
       <c r="B58">
-        <v>0.002405479709022215</v>
+        <v>0.002509035099668747</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>472.8272727272728</v>
+        <v>466.8454545454545</v>
       </c>
       <c r="B59">
-        <v>0.002355352392737675</v>
+        <v>0.002460112942669601</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>480.9242424242425</v>
+        <v>474.8515151515151</v>
       </c>
       <c r="B60">
-        <v>0.002307094498248114</v>
+        <v>0.002412952486804241</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>489.0212121212122</v>
+        <v>482.8575757575758</v>
       </c>
       <c r="B61">
-        <v>0.00226060656467445</v>
+        <v>0.002367462167364444</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>497.1181818181819</v>
+        <v>490.8636363636364</v>
       </c>
       <c r="B62">
-        <v>0.00221579595387411</v>
+        <v>0.002323556592912663</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>505.2151515151515</v>
+        <v>498.869696969697</v>
       </c>
       <c r="B63">
-        <v>0.002172576280758743</v>
+        <v>0.002281156036795257</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>513.3121212121213</v>
+        <v>506.8757575757576</v>
       </c>
       <c r="B64">
-        <v>0.002130866899400167</v>
+        <v>0.002240185977900962</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>521.4090909090909</v>
+        <v>514.8818181818182</v>
       </c>
       <c r="B65">
-        <v>0.00209059243868117</v>
+        <v>0.002200576685204554</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>529.5060606060606</v>
+        <v>522.8878787878788</v>
       </c>
       <c r="B66">
-        <v>0.002051682382031121</v>
+        <v>0.002162262841315321</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>537.6030303030303</v>
+        <v>530.8939393939394</v>
       </c>
       <c r="B67">
-        <v>0.002014070686461129</v>
+        <v>0.002125183200835971</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>545.7</v>
+        <v>538.9</v>
       </c>
       <c r="B68">
-        <v>0.001977695436696093</v>
+        <v>0.002089280279844253</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>553.7969696969697</v>
+        <v>546.9060606060606</v>
       </c>
       <c r="B69">
-        <v>0.001942498530705191</v>
+        <v>0.002054500073248407</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>561.8939393939394</v>
+        <v>554.9121212121212</v>
       </c>
       <c r="B70">
-        <v>0.001908425393369704</v>
+        <v>0.002020791797148658</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>569.9909090909091</v>
+        <v>562.9181818181818</v>
       </c>
       <c r="B71">
-        <v>0.001875424715407219</v>
+        <v>0.001988107653668595</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>578.0878787878788</v>
+        <v>570.9242424242424</v>
       </c>
       <c r="B72">
-        <v>0.001843448215002397</v>
+        <v>0.001956402616009377</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>586.1848484848484</v>
+        <v>578.930303030303</v>
       </c>
       <c r="B73">
-        <v>0.001812450419883519</v>
+        <v>0.001925634231732409</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>594.2818181818182</v>
+        <v>586.9363636363636</v>
       </c>
       <c r="B74">
-        <v>0.001782388467836827</v>
+        <v>0.00189576244249727</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>602.3787878787879</v>
+        <v>594.9424242424242</v>
       </c>
       <c r="B75">
-        <v>0.001753221923872184</v>
+        <v>0.001866749418675721</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>610.4757575757576</v>
+        <v>602.9484848484848</v>
       </c>
       <c r="B76">
-        <v>0.001724912612448014</v>
+        <v>0.001838559407433083</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>618.5727272727273</v>
+        <v>610.9545454545455</v>
       </c>
       <c r="B77">
-        <v>0.001697424463334556</v>
+        <v>0.00181115859301838</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>626.6696969696969</v>
+        <v>618.9606060606061</v>
       </c>
       <c r="B78">
-        <v>0.00167072336984511</v>
+        <v>0.001784514968137032</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>634.7666666666667</v>
+        <v>626.9666666666667</v>
       </c>
       <c r="B79">
-        <v>0.00164477705829798</v>
+        <v>0.001758598215396764</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>642.8636363636364</v>
+        <v>634.9727272727273</v>
       </c>
       <c r="B80">
-        <v>0.001619554967689372</v>
+        <v>0.001733379597920934</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>650.9606060606061</v>
+        <v>642.9787878787879</v>
       </c>
       <c r="B81">
-        <v>0.001595028138661609</v>
+        <v>0.001708831858315155</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82">
-        <v>659.0575757575757</v>
+        <v>650.9848484848485</v>
       </c>
       <c r="B82">
-        <v>0.001571169110943376</v>
+        <v>0.001684929125254508</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83">
-        <v>667.1545454545454</v>
+        <v>658.9909090909091</v>
       </c>
       <c r="B83">
-        <v>0.001547951828520692</v>
+        <v>0.001661646827031027</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84">
-        <v>675.2515151515152</v>
+        <v>666.9969696969697</v>
       </c>
       <c r="B84">
-        <v>0.001525351551870314</v>
+        <v>0.001638961611465592</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85">
-        <v>683.3484848484849</v>
+        <v>675.0030303030303</v>
       </c>
       <c r="B85">
-        <v>0.001503344776652226</v>
+        <v>0.001616851271645816</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86">
-        <v>691.4454545454546</v>
+        <v>683.0090909090909</v>
       </c>
       <c r="B86">
-        <v>0.001481909158315892</v>
+        <v>0.001595294677002861</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87">
-        <v>699.5424242424242</v>
+        <v>691.0151515151515</v>
       </c>
       <c r="B87">
-        <v>0.001461023442126762</v>
+        <v>0.001574271709285973</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88">
-        <v>707.6393939393939</v>
+        <v>699.0212121212121</v>
       </c>
       <c r="B88">
-        <v>0.001440667398165869</v>
+        <v>0.001553763203034644</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89">
-        <v>715.7363636363636</v>
+        <v>707.0272727272727</v>
       </c>
       <c r="B89">
-        <v>0.001420821760896863</v>
+        <v>0.001533750890185145</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90">
-        <v>723.8333333333334</v>
+        <v>715.0333333333333</v>
       </c>
       <c r="B90">
-        <v>0.001401468172932123</v>
+        <v>0.001514217348481232</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91">
-        <v>731.9303030303031</v>
+        <v>723.0393939393939</v>
       </c>
       <c r="B91">
-        <v>0.001382589132662983</v>
+        <v>0.001495145953388581</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92">
-        <v>740.0272727272727</v>
+        <v>731.0454545454545</v>
       </c>
       <c r="B92">
-        <v>0.001364167945449245</v>
+        <v>0.001476520833239256</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93">
-        <v>748.1242424242424</v>
+        <v>739.0515151515151</v>
       </c>
       <c r="B93">
-        <v>0.001346188678090202</v>
+        <v>0.00145832682735662</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94">
-        <v>756.2212121212121</v>
+        <v>747.0575757575757</v>
       </c>
       <c r="B94">
-        <v>0.001328636116323822</v>
+        <v>0.001440549446932866</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95">
-        <v>764.3181818181819</v>
+        <v>755.0636363636363</v>
       </c>
       <c r="B95">
-        <v>0.001311495725122791</v>
+        <v>0.001423174838450966</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96">
-        <v>772.4151515151515</v>
+        <v>763.0696969696969</v>
       </c>
       <c r="B96">
-        <v>0.00129475361157598</v>
+        <v>0.001406189749460629</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97">
-        <v>780.5121212121212</v>
+        <v>771.0757575757575</v>
       </c>
       <c r="B97">
-        <v>0.001278396490161965</v>
+        <v>0.001389581496533911</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98">
-        <v>788.6090909090909</v>
+        <v>779.0818181818181</v>
       </c>
       <c r="B98">
-        <v>0.001262411650237472</v>
+        <v>0.00137333793524071</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99">
-        <v>796.7060606060606</v>
+        <v>787.0878787878788</v>
       </c>
       <c r="B99">
-        <v>0.001246786925578432</v>
+        <v>0.001357447431997586</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100">
-        <v>804.8030303030304</v>
+        <v>795.0939393939394</v>
       </c>
       <c r="B100">
-        <v>0.001231510665824734</v>
+        <v>0.00134189883765535</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101">
-        <v>812.9</v>
+        <v>803.1</v>
       </c>
       <c r="B101">
-        <v>0.001216571709691934</v>
+        <v>0.00132668146270177</v>
       </c>
     </row>
   </sheetData>
@@ -1580,25 +1580,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>11.3</v>
+        <v>10.5</v>
       </c>
       <c r="C2">
-        <v>1.3</v>
+        <v>1.408308678285174</v>
       </c>
       <c r="D2">
-        <v>0.223665</v>
+        <v>0.185419</v>
       </c>
       <c r="E2">
-        <v>0.08689313063566455</v>
+        <v>0.02764825308727077</v>
       </c>
       <c r="F2">
-        <v>1.05307844348342</v>
+        <v>1.021189299069938</v>
       </c>
       <c r="G2">
-        <v>-0.6504019707362143</v>
+        <v>-0.7318457654861891</v>
       </c>
       <c r="H2">
-        <v>-0.7360841467267152</v>
+        <v>-0.7956170590946079</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1606,25 +1606,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>39</v>
+        <v>38.1</v>
       </c>
       <c r="C3">
-        <v>3.0840089349921</v>
+        <v>1.27758452644912</v>
       </c>
       <c r="D3">
-        <v>0.047857</v>
+        <v>0.03847</v>
       </c>
       <c r="E3">
-        <v>0.005268825939218126</v>
+        <v>0.003421588649865569</v>
       </c>
       <c r="F3">
-        <v>1.591064607026499</v>
+        <v>1.580924975675619</v>
       </c>
       <c r="G3">
-        <v>-1.320054529380785</v>
+        <v>-1.414877813693185</v>
       </c>
       <c r="H3">
-        <v>-1.299983122420791</v>
+        <v>-1.347299254247706</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1632,25 +1632,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>79.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="C4">
-        <v>2.478574859336174</v>
+        <v>2.394437999475729</v>
       </c>
       <c r="D4">
-        <v>0.01952</v>
+        <v>0.018984</v>
       </c>
       <c r="E4">
-        <v>0.001232376205187</v>
+        <v>0.00127096481287074</v>
       </c>
       <c r="F4">
-        <v>1.898176483497676</v>
+        <v>1.90848501887865</v>
       </c>
       <c r="G4">
-        <v>-1.709520186669327</v>
+        <v>-1.721612274790717</v>
       </c>
       <c r="H4">
-        <v>-1.621887446920606</v>
+        <v>-1.670146360893718</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1658,25 +1658,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>130.9</v>
+        <v>137.5</v>
       </c>
       <c r="C5">
-        <v>4.787599723359411</v>
+        <v>4.185291706281256</v>
       </c>
       <c r="D5">
-        <v>0.012653</v>
+        <v>0.012357</v>
       </c>
       <c r="E5">
-        <v>0.001167132335636747</v>
+        <v>0.0007632111255886026</v>
       </c>
       <c r="F5">
-        <v>2.116939646550756</v>
+        <v>2.138302698166282</v>
       </c>
       <c r="G5">
-        <v>-1.897806491960256</v>
+        <v>-1.90808695332392</v>
       </c>
       <c r="H5">
-        <v>-1.851187625856062</v>
+        <v>-1.896657421548708</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1684,25 +1684,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>214.1</v>
+        <v>211.1</v>
       </c>
       <c r="C6">
-        <v>4.670117771534247</v>
+        <v>5.722179072113467</v>
       </c>
       <c r="D6">
-        <v>0.007606</v>
+        <v>0.008705000000000001</v>
       </c>
       <c r="E6">
-        <v>0.000416579190817571</v>
+        <v>0.0005302289861727458</v>
       </c>
       <c r="F6">
-        <v>2.330616667294438</v>
+        <v>2.324488233307656</v>
       </c>
       <c r="G6">
-        <v>-2.118843678924436</v>
+        <v>-2.06023122454665</v>
       </c>
       <c r="H6">
-        <v>-2.075156681738808</v>
+        <v>-2.080164117701128</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1710,25 +1710,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>288.1</v>
+        <v>287.4</v>
       </c>
       <c r="C7">
-        <v>5.685165882462103</v>
+        <v>3.679371927079101</v>
       </c>
       <c r="D7">
-        <v>0.00615</v>
+        <v>0.006292000000000001</v>
       </c>
       <c r="E7">
-        <v>0.0003635351121663185</v>
+        <v>0.0001936308056299124</v>
       </c>
       <c r="F7">
-        <v>2.459543258280413</v>
+        <v>2.458486763798207</v>
       </c>
       <c r="G7">
-        <v>-2.211124884224583</v>
+        <v>-2.201211286048751</v>
       </c>
       <c r="H7">
-        <v>-2.210293191789403</v>
+        <v>-2.212234676248701</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1736,25 +1736,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>394</v>
+        <v>393.5</v>
       </c>
       <c r="C8">
-        <v>3.346640106136302</v>
+        <v>5.066776314603025</v>
       </c>
       <c r="D8">
-        <v>0.004235000000000001</v>
+        <v>0.004414</v>
       </c>
       <c r="E8">
-        <v>0.0001603347193287288</v>
+        <v>0.0002112144776182626</v>
       </c>
       <c r="F8">
-        <v>2.595496221825574</v>
+        <v>2.594944736695084</v>
       </c>
       <c r="G8">
-        <v>-2.373146585333274</v>
+        <v>-2.355167671174364</v>
       </c>
       <c r="H8">
-        <v>-2.352794508887963</v>
+        <v>-2.346729290725321</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1762,25 +1762,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>515.2</v>
+        <v>515.3</v>
       </c>
       <c r="C9">
-        <v>3.805843460317889</v>
+        <v>7.935923946768195</v>
       </c>
       <c r="D9">
-        <v>0.003294</v>
+        <v>0.003261</v>
       </c>
       <c r="E9">
-        <v>0.0001124000790826136</v>
+        <v>0.0001578497879490358</v>
       </c>
       <c r="F9">
-        <v>2.711975854351756</v>
+        <v>2.712060142461075</v>
       </c>
       <c r="G9">
-        <v>-2.482276405166265</v>
+        <v>-2.486649201194043</v>
       </c>
       <c r="H9">
-        <v>-2.474884536330605</v>
+        <v>-2.462159639083738</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1788,25 +1788,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>662.5</v>
+        <v>665.3</v>
       </c>
       <c r="C10">
-        <v>6.057593948462082</v>
+        <v>8.203048213926333</v>
       </c>
       <c r="D10">
-        <v>0.002638000000000001</v>
+        <v>0.002514</v>
       </c>
       <c r="E10">
-        <v>7.209253313161726E-05</v>
+        <v>0.0001025367142918954</v>
       </c>
       <c r="F10">
-        <v>2.821185882608845</v>
+        <v>2.823017523446049</v>
       </c>
       <c r="G10">
-        <v>-2.578725208789654</v>
+        <v>-2.599634726650061</v>
       </c>
       <c r="H10">
-        <v>-2.589354809439706</v>
+        <v>-2.571520564371608</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1814,25 +1814,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>812.9</v>
+        <v>803.1</v>
       </c>
       <c r="C11">
-        <v>9.599131905195039</v>
+        <v>7.651361534611556</v>
       </c>
       <c r="D11">
-        <v>0.00213</v>
+        <v>0.002173</v>
       </c>
       <c r="E11">
-        <v>6.881537295950343E-05</v>
+        <v>6.824872811187685E-05</v>
       </c>
       <c r="F11">
-        <v>2.910037123553051</v>
+        <v>2.904769625906595</v>
       </c>
       <c r="G11">
-        <v>-2.671620396561262</v>
+        <v>-2.662940273679475</v>
       </c>
       <c r="H11">
-        <v>-2.68248568743035</v>
+        <v>-2.652096416919216</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1858,7 +1858,7 @@
         <v>-2.338187314462739</v>
       </c>
       <c r="H12">
-        <v>-2.457595894667791</v>
+        <v>-2.445819704215646</v>
       </c>
     </row>
   </sheetData>
@@ -1881,802 +1881,802 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>11.3</v>
+        <v>10.5</v>
       </c>
       <c r="B2">
-        <v>0.2234229411226657</v>
+        <v>0.184891647846076</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>19.3969696969697</v>
+        <v>18.50606060606061</v>
       </c>
       <c r="B3">
-        <v>0.1156212373834673</v>
+        <v>0.09699386650165555</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>27.4939393939394</v>
+        <v>26.51212121212121</v>
       </c>
       <c r="B4">
-        <v>0.07556595810281702</v>
+        <v>0.06441915600835781</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>35.59090909090909</v>
+        <v>34.51818181818182</v>
       </c>
       <c r="B5">
-        <v>0.05516354196624016</v>
+        <v>0.04770430921186292</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>43.68787878787879</v>
+        <v>42.52424242424242</v>
       </c>
       <c r="B6">
-        <v>0.04296524975839557</v>
+        <v>0.03762158624308524</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>51.78484848484848</v>
+        <v>50.53030303030303</v>
       </c>
       <c r="B7">
-        <v>0.03492127028347099</v>
+        <v>0.03091421103869369</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>59.88181818181819</v>
+        <v>58.53636363636363</v>
       </c>
       <c r="B8">
-        <v>0.02925286548600948</v>
+        <v>0.02614858339296097</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>67.97878787878788</v>
+        <v>66.54242424242423</v>
       </c>
       <c r="B9">
-        <v>0.02506208489084306</v>
+        <v>0.02259818839391243</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>76.07575757575758</v>
+        <v>74.54848484848485</v>
       </c>
       <c r="B10">
-        <v>0.02184900993129131</v>
+        <v>0.01985673358482553</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>84.17272727272727</v>
+        <v>82.55454545454545</v>
       </c>
       <c r="B11">
-        <v>0.01931428318245793</v>
+        <v>0.01767978487064297</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>92.26969696969697</v>
+        <v>90.56060606060606</v>
       </c>
       <c r="B12">
-        <v>0.01726822968450587</v>
+        <v>0.01591174092637995</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>100.3666666666667</v>
+        <v>98.56666666666666</v>
       </c>
       <c r="B13">
-        <v>0.01558512248656729</v>
+        <v>0.01444898696256113</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>108.4636363636364</v>
+        <v>106.5727272727273</v>
       </c>
       <c r="B14">
-        <v>0.01417848879016148</v>
+        <v>0.01321994121343388</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>116.5606060606061</v>
+        <v>114.5787878787879</v>
       </c>
       <c r="B15">
-        <v>0.01298699511530168</v>
+        <v>0.01217361410153211</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>124.6575757575758</v>
+        <v>122.5848484848485</v>
       </c>
       <c r="B16">
-        <v>0.01196599002919759</v>
+        <v>0.01127273135110265</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>132.7545454545455</v>
+        <v>130.5909090909091</v>
       </c>
       <c r="B17">
-        <v>0.0110822316650582</v>
+        <v>0.01048943309212318</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>140.8515151515152</v>
+        <v>138.5969696969697</v>
       </c>
       <c r="B18">
-        <v>0.01031048744007662</v>
+        <v>0.009802491403436467</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>148.9484848484849</v>
+        <v>146.6030303030303</v>
       </c>
       <c r="B19">
-        <v>0.009631275999786809</v>
+        <v>0.009195456799216902</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>157.0454545454546</v>
+        <v>154.6090909090909</v>
       </c>
       <c r="B20">
-        <v>0.009029328839544866</v>
+        <v>0.008655391614442896</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>165.1424242424243</v>
+        <v>162.6151515151515</v>
       </c>
       <c r="B21">
-        <v>0.008492518339989152</v>
+        <v>0.008171984784864205</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>173.2393939393939</v>
+        <v>170.6212121212121</v>
       </c>
       <c r="B22">
-        <v>0.008011095705198019</v>
+        <v>0.007736920717535016</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>181.3363636363637</v>
+        <v>178.6272727272727</v>
       </c>
       <c r="B23">
-        <v>0.007577139428687919</v>
+        <v>0.007343421227736977</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>189.4333333333334</v>
+        <v>186.6333333333333</v>
       </c>
       <c r="B24">
-        <v>0.007184149648374311</v>
+        <v>0.006985907714317893</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>197.5303030303031</v>
+        <v>194.6393939393939</v>
       </c>
       <c r="B25">
-        <v>0.006826745424516108</v>
+        <v>0.006659748375801701</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>205.6272727272728</v>
+        <v>202.6454545454545</v>
       </c>
       <c r="B26">
-        <v>0.006500435816382649</v>
+        <v>0.006361066553561816</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>213.7242424242424</v>
+        <v>210.6515151515152</v>
       </c>
       <c r="B27">
-        <v>0.006201444662158525</v>
+        <v>0.006086593664304345</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>221.8212121212121</v>
+        <v>218.6575757575758</v>
       </c>
       <c r="B28">
-        <v>0.005926574970018011</v>
+        <v>0.005833555098793225</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>229.9181818181818</v>
+        <v>226.6636363636364</v>
       </c>
       <c r="B29">
-        <v>0.00567310289062023</v>
+        <v>0.005599580796224393</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>238.0151515151516</v>
+        <v>234.669696969697</v>
       </c>
       <c r="B30">
-        <v>0.005438694034608454</v>
+        <v>0.005382634499791695</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>246.1121212121213</v>
+        <v>242.6757575757576</v>
       </c>
       <c r="B31">
-        <v>0.00522133684803717</v>
+        <v>0.005180957304561919</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>254.2090909090909</v>
+        <v>250.6818181818182</v>
       </c>
       <c r="B32">
-        <v>0.005019289137692525</v>
+        <v>0.004993022246858652</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>262.3060606060606</v>
+        <v>258.6878787878788</v>
       </c>
       <c r="B33">
-        <v>0.004831034826267896</v>
+        <v>0.004817497501294103</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>270.4030303030303</v>
+        <v>266.6939393939394</v>
       </c>
       <c r="B34">
-        <v>0.0046552487335509</v>
+        <v>0.004653216344908505</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>278.5000000000001</v>
+        <v>274.7</v>
       </c>
       <c r="B35">
-        <v>0.004490767704652825</v>
+        <v>0.004499152483511465</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>286.5969696969697</v>
+        <v>282.7060606060606</v>
       </c>
       <c r="B36">
-        <v>0.004336566794921568</v>
+        <v>0.00435439965844809</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>294.6939393939394</v>
+        <v>290.7121212121212</v>
       </c>
       <c r="B37">
-        <v>0.004191739511663775</v>
+        <v>0.004218154693983959</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>302.7909090909091</v>
+        <v>298.7181818181818</v>
       </c>
       <c r="B38">
-        <v>0.004055481331892936</v>
+        <v>0.004089703328325833</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>310.8878787878788</v>
+        <v>306.7242424242424</v>
       </c>
       <c r="B39">
-        <v>0.003927075881962371</v>
+        <v>0.003968408310592312</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>318.9848484848485</v>
+        <v>314.730303030303</v>
       </c>
       <c r="B40">
-        <v>0.003805883292700867</v>
+        <v>0.003853699353024394</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>327.0818181818182</v>
+        <v>322.7363636363636</v>
       </c>
       <c r="B41">
-        <v>0.003691330342352621</v>
+        <v>0.003745064610494677</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>335.1787878787879</v>
+        <v>330.7424242424242</v>
       </c>
       <c r="B42">
-        <v>0.00358290207638999</v>
+        <v>0.003642043423865678</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>343.2757575757576</v>
+        <v>338.7484848484848</v>
       </c>
       <c r="B43">
-        <v>0.003480134653385886</v>
+        <v>0.003544220114334572</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>351.3727272727273</v>
+        <v>346.7545454545455</v>
       </c>
       <c r="B44">
-        <v>0.003382609213512734</v>
+        <v>0.003451218655832776</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>359.469696969697</v>
+        <v>354.7606060606061</v>
       </c>
       <c r="B45">
-        <v>0.003289946603801274</v>
+        <v>0.003362698084258411</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>367.5666666666667</v>
+        <v>362.7666666666667</v>
       </c>
       <c r="B46">
-        <v>0.003201802824248834</v>
+        <v>0.003278348527644262</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>375.6636363636364</v>
+        <v>370.7727272727273</v>
       </c>
       <c r="B47">
-        <v>0.003117865082885064</v>
+        <v>0.003197887761699077</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>383.7606060606061</v>
+        <v>378.7787878787879</v>
       </c>
       <c r="B48">
-        <v>0.003037848367260696</v>
+        <v>0.003121058211573426</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>391.8575757575758</v>
+        <v>386.7848484848485</v>
       </c>
       <c r="B49">
-        <v>0.002961492455503649</v>
+        <v>0.003047624334014674</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>399.9545454545455</v>
+        <v>394.7909090909091</v>
       </c>
       <c r="B50">
-        <v>0.002888559302845906</v>
+        <v>0.002977370324925316</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>408.0515151515152</v>
+        <v>402.7969696969697</v>
       </c>
       <c r="B51">
-        <v>0.002818830749954937</v>
+        <v>0.002910098106220766</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>416.1484848484849</v>
+        <v>410.8030303030303</v>
       </c>
       <c r="B52">
-        <v>0.002752106507966855</v>
+        <v>0.002845625553184896</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>424.2454545454546</v>
+        <v>418.8090909090909</v>
       </c>
       <c r="B53">
-        <v>0.002688202382178486</v>
+        <v>0.002783784929549944</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>432.3424242424243</v>
+        <v>426.8151515151515</v>
       </c>
       <c r="B54">
-        <v>0.002626948702199065</v>
+        <v>0.002724421502523833</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>440.439393939394</v>
+        <v>434.8212121212121</v>
       </c>
       <c r="B55">
-        <v>0.002568188931217557</v>
+        <v>0.002667392314144691</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>448.5363636363637</v>
+        <v>442.8272727272727</v>
       </c>
       <c r="B56">
-        <v>0.00251177843109041</v>
+        <v>0.00261256508881331</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>456.6333333333334</v>
+        <v>450.8333333333333</v>
       </c>
       <c r="B57">
-        <v>0.002457583363342884</v>
+        <v>0.00255981725976266</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>464.7303030303031</v>
+        <v>458.8393939393939</v>
       </c>
       <c r="B58">
-        <v>0.002405479709022215</v>
+        <v>0.002509035099668747</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>472.8272727272728</v>
+        <v>466.8454545454545</v>
       </c>
       <c r="B59">
-        <v>0.002355352392737675</v>
+        <v>0.002460112942669601</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>480.9242424242425</v>
+        <v>474.8515151515151</v>
       </c>
       <c r="B60">
-        <v>0.002307094498248114</v>
+        <v>0.002412952486804241</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>489.0212121212122</v>
+        <v>482.8575757575758</v>
       </c>
       <c r="B61">
-        <v>0.00226060656467445</v>
+        <v>0.002367462167364444</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>497.1181818181819</v>
+        <v>490.8636363636364</v>
       </c>
       <c r="B62">
-        <v>0.00221579595387411</v>
+        <v>0.002323556592912663</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>505.2151515151515</v>
+        <v>498.869696969697</v>
       </c>
       <c r="B63">
-        <v>0.002172576280758743</v>
+        <v>0.002281156036795257</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>513.3121212121213</v>
+        <v>506.8757575757576</v>
       </c>
       <c r="B64">
-        <v>0.002130866899400167</v>
+        <v>0.002240185977900962</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>521.4090909090909</v>
+        <v>514.8818181818182</v>
       </c>
       <c r="B65">
-        <v>0.00209059243868117</v>
+        <v>0.002200576685204554</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>529.5060606060606</v>
+        <v>522.8878787878788</v>
       </c>
       <c r="B66">
-        <v>0.002051682382031121</v>
+        <v>0.002162262841315321</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>537.6030303030303</v>
+        <v>530.8939393939394</v>
       </c>
       <c r="B67">
-        <v>0.002014070686461129</v>
+        <v>0.002125183200835971</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>545.7</v>
+        <v>538.9</v>
       </c>
       <c r="B68">
-        <v>0.001977695436696093</v>
+        <v>0.002089280279844253</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>553.7969696969697</v>
+        <v>546.9060606060606</v>
       </c>
       <c r="B69">
-        <v>0.001942498530705191</v>
+        <v>0.002054500073248407</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>561.8939393939394</v>
+        <v>554.9121212121212</v>
       </c>
       <c r="B70">
-        <v>0.001908425393369704</v>
+        <v>0.002020791797148658</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>569.9909090909091</v>
+        <v>562.9181818181818</v>
       </c>
       <c r="B71">
-        <v>0.001875424715407219</v>
+        <v>0.001988107653668595</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>578.0878787878788</v>
+        <v>570.9242424242424</v>
       </c>
       <c r="B72">
-        <v>0.001843448215002397</v>
+        <v>0.001956402616009377</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>586.1848484848484</v>
+        <v>578.930303030303</v>
       </c>
       <c r="B73">
-        <v>0.001812450419883519</v>
+        <v>0.001925634231732409</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>594.2818181818182</v>
+        <v>586.9363636363636</v>
       </c>
       <c r="B74">
-        <v>0.001782388467836827</v>
+        <v>0.00189576244249727</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>602.3787878787879</v>
+        <v>594.9424242424242</v>
       </c>
       <c r="B75">
-        <v>0.001753221923872184</v>
+        <v>0.001866749418675721</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>610.4757575757576</v>
+        <v>602.9484848484848</v>
       </c>
       <c r="B76">
-        <v>0.001724912612448014</v>
+        <v>0.001838559407433083</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>618.5727272727273</v>
+        <v>610.9545454545455</v>
       </c>
       <c r="B77">
-        <v>0.001697424463334556</v>
+        <v>0.00181115859301838</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>626.6696969696969</v>
+        <v>618.9606060606061</v>
       </c>
       <c r="B78">
-        <v>0.00167072336984511</v>
+        <v>0.001784514968137032</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>634.7666666666667</v>
+        <v>626.9666666666667</v>
       </c>
       <c r="B79">
-        <v>0.00164477705829798</v>
+        <v>0.001758598215396764</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>642.8636363636364</v>
+        <v>634.9727272727273</v>
       </c>
       <c r="B80">
-        <v>0.001619554967689372</v>
+        <v>0.001733379597920934</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>650.9606060606061</v>
+        <v>642.9787878787879</v>
       </c>
       <c r="B81">
-        <v>0.001595028138661609</v>
+        <v>0.001708831858315155</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82">
-        <v>659.0575757575757</v>
+        <v>650.9848484848485</v>
       </c>
       <c r="B82">
-        <v>0.001571169110943376</v>
+        <v>0.001684929125254508</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83">
-        <v>667.1545454545454</v>
+        <v>658.9909090909091</v>
       </c>
       <c r="B83">
-        <v>0.001547951828520692</v>
+        <v>0.001661646827031027</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84">
-        <v>675.2515151515152</v>
+        <v>666.9969696969697</v>
       </c>
       <c r="B84">
-        <v>0.001525351551870314</v>
+        <v>0.001638961611465592</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85">
-        <v>683.3484848484849</v>
+        <v>675.0030303030303</v>
       </c>
       <c r="B85">
-        <v>0.001503344776652226</v>
+        <v>0.001616851271645816</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86">
-        <v>691.4454545454546</v>
+        <v>683.0090909090909</v>
       </c>
       <c r="B86">
-        <v>0.001481909158315892</v>
+        <v>0.001595294677002861</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87">
-        <v>699.5424242424242</v>
+        <v>691.0151515151515</v>
       </c>
       <c r="B87">
-        <v>0.001461023442126762</v>
+        <v>0.001574271709285973</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88">
-        <v>707.6393939393939</v>
+        <v>699.0212121212121</v>
       </c>
       <c r="B88">
-        <v>0.001440667398165869</v>
+        <v>0.001553763203034644</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89">
-        <v>715.7363636363636</v>
+        <v>707.0272727272727</v>
       </c>
       <c r="B89">
-        <v>0.001420821760896863</v>
+        <v>0.001533750890185145</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90">
-        <v>723.8333333333334</v>
+        <v>715.0333333333333</v>
       </c>
       <c r="B90">
-        <v>0.001401468172932123</v>
+        <v>0.001514217348481232</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91">
-        <v>731.9303030303031</v>
+        <v>723.0393939393939</v>
       </c>
       <c r="B91">
-        <v>0.001382589132662983</v>
+        <v>0.001495145953388581</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92">
-        <v>740.0272727272727</v>
+        <v>731.0454545454545</v>
       </c>
       <c r="B92">
-        <v>0.001364167945449245</v>
+        <v>0.001476520833239256</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93">
-        <v>748.1242424242424</v>
+        <v>739.0515151515151</v>
       </c>
       <c r="B93">
-        <v>0.001346188678090202</v>
+        <v>0.00145832682735662</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94">
-        <v>756.2212121212121</v>
+        <v>747.0575757575757</v>
       </c>
       <c r="B94">
-        <v>0.001328636116323822</v>
+        <v>0.001440549446932866</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95">
-        <v>764.3181818181819</v>
+        <v>755.0636363636363</v>
       </c>
       <c r="B95">
-        <v>0.001311495725122791</v>
+        <v>0.001423174838450966</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96">
-        <v>772.4151515151515</v>
+        <v>763.0696969696969</v>
       </c>
       <c r="B96">
-        <v>0.00129475361157598</v>
+        <v>0.001406189749460629</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97">
-        <v>780.5121212121212</v>
+        <v>771.0757575757575</v>
       </c>
       <c r="B97">
-        <v>0.001278396490161965</v>
+        <v>0.001389581496533911</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98">
-        <v>788.6090909090909</v>
+        <v>779.0818181818181</v>
       </c>
       <c r="B98">
-        <v>0.001262411650237472</v>
+        <v>0.00137333793524071</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99">
-        <v>796.7060606060606</v>
+        <v>787.0878787878788</v>
       </c>
       <c r="B99">
-        <v>0.001246786925578432</v>
+        <v>0.001357447431997586</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100">
-        <v>804.8030303030304</v>
+        <v>795.0939393939394</v>
       </c>
       <c r="B100">
-        <v>0.001231510665824734</v>
+        <v>0.00134189883765535</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101">
-        <v>812.9</v>
+        <v>803.1</v>
       </c>
       <c r="B101">
-        <v>0.001216571709691934</v>
+        <v>0.00132668146270177</v>
       </c>
     </row>
   </sheetData>
@@ -2720,25 +2720,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>11.3</v>
+        <v>10.5</v>
       </c>
       <c r="C2">
-        <v>1.3</v>
+        <v>1.408308678285174</v>
       </c>
       <c r="D2">
-        <v>0.223665</v>
+        <v>0.185419</v>
       </c>
       <c r="E2">
-        <v>0.08689313063566455</v>
+        <v>0.02764825308727077</v>
       </c>
       <c r="F2">
-        <v>1.05307844348342</v>
+        <v>1.021189299069938</v>
       </c>
       <c r="G2">
-        <v>-0.6504019707362143</v>
+        <v>-0.7318457654861891</v>
       </c>
       <c r="H2">
-        <v>-0.7360841467267152</v>
+        <v>-0.7956170590946079</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2746,25 +2746,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>39</v>
+        <v>38.1</v>
       </c>
       <c r="C3">
-        <v>3.0840089349921</v>
+        <v>1.27758452644912</v>
       </c>
       <c r="D3">
-        <v>0.047857</v>
+        <v>0.03847</v>
       </c>
       <c r="E3">
-        <v>0.005268825939218126</v>
+        <v>0.003421588649865569</v>
       </c>
       <c r="F3">
-        <v>1.591064607026499</v>
+        <v>1.580924975675619</v>
       </c>
       <c r="G3">
-        <v>-1.320054529380785</v>
+        <v>-1.414877813693185</v>
       </c>
       <c r="H3">
-        <v>-1.299983122420791</v>
+        <v>-1.347299254247706</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2772,25 +2772,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>79.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="C4">
-        <v>2.478574859336174</v>
+        <v>2.394437999475729</v>
       </c>
       <c r="D4">
-        <v>0.01952</v>
+        <v>0.018984</v>
       </c>
       <c r="E4">
-        <v>0.001232376205187</v>
+        <v>0.00127096481287074</v>
       </c>
       <c r="F4">
-        <v>1.898176483497676</v>
+        <v>1.90848501887865</v>
       </c>
       <c r="G4">
-        <v>-1.709520186669327</v>
+        <v>-1.721612274790717</v>
       </c>
       <c r="H4">
-        <v>-1.621887446920606</v>
+        <v>-1.670146360893718</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2798,25 +2798,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>130.9</v>
+        <v>137.5</v>
       </c>
       <c r="C5">
-        <v>4.787599723359411</v>
+        <v>4.185291706281256</v>
       </c>
       <c r="D5">
-        <v>0.012653</v>
+        <v>0.012357</v>
       </c>
       <c r="E5">
-        <v>0.001167132335636747</v>
+        <v>0.0007632111255886026</v>
       </c>
       <c r="F5">
-        <v>2.116939646550756</v>
+        <v>2.138302698166282</v>
       </c>
       <c r="G5">
-        <v>-1.897806491960256</v>
+        <v>-1.90808695332392</v>
       </c>
       <c r="H5">
-        <v>-1.851187625856062</v>
+        <v>-1.896657421548708</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2824,25 +2824,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>214.1</v>
+        <v>211.1</v>
       </c>
       <c r="C6">
-        <v>4.670117771534247</v>
+        <v>5.722179072113467</v>
       </c>
       <c r="D6">
-        <v>0.007606</v>
+        <v>0.008705000000000001</v>
       </c>
       <c r="E6">
-        <v>0.000416579190817571</v>
+        <v>0.0005302289861727458</v>
       </c>
       <c r="F6">
-        <v>2.330616667294438</v>
+        <v>2.324488233307656</v>
       </c>
       <c r="G6">
-        <v>-2.118843678924436</v>
+        <v>-2.06023122454665</v>
       </c>
       <c r="H6">
-        <v>-2.075156681738808</v>
+        <v>-2.080164117701128</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2850,25 +2850,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>288.1</v>
+        <v>287.4</v>
       </c>
       <c r="C7">
-        <v>5.685165882462103</v>
+        <v>3.679371927079101</v>
       </c>
       <c r="D7">
-        <v>0.00615</v>
+        <v>0.006292000000000001</v>
       </c>
       <c r="E7">
-        <v>0.0003635351121663185</v>
+        <v>0.0001936308056299124</v>
       </c>
       <c r="F7">
-        <v>2.459543258280413</v>
+        <v>2.458486763798207</v>
       </c>
       <c r="G7">
-        <v>-2.211124884224583</v>
+        <v>-2.201211286048751</v>
       </c>
       <c r="H7">
-        <v>-2.210293191789403</v>
+        <v>-2.212234676248701</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2876,25 +2876,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>394</v>
+        <v>393.5</v>
       </c>
       <c r="C8">
-        <v>3.346640106136302</v>
+        <v>5.066776314603025</v>
       </c>
       <c r="D8">
-        <v>0.004235000000000001</v>
+        <v>0.004414</v>
       </c>
       <c r="E8">
-        <v>0.0001603347193287288</v>
+        <v>0.0002112144776182626</v>
       </c>
       <c r="F8">
-        <v>2.595496221825574</v>
+        <v>2.594944736695084</v>
       </c>
       <c r="G8">
-        <v>-2.373146585333274</v>
+        <v>-2.355167671174364</v>
       </c>
       <c r="H8">
-        <v>-2.352794508887963</v>
+        <v>-2.346729290725321</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2902,25 +2902,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>515.2</v>
+        <v>515.3</v>
       </c>
       <c r="C9">
-        <v>3.805843460317889</v>
+        <v>7.935923946768195</v>
       </c>
       <c r="D9">
-        <v>0.003294</v>
+        <v>0.003261</v>
       </c>
       <c r="E9">
-        <v>0.0001124000790826136</v>
+        <v>0.0001578497879490358</v>
       </c>
       <c r="F9">
-        <v>2.711975854351756</v>
+        <v>2.712060142461075</v>
       </c>
       <c r="G9">
-        <v>-2.482276405166265</v>
+        <v>-2.486649201194043</v>
       </c>
       <c r="H9">
-        <v>-2.474884536330605</v>
+        <v>-2.462159639083738</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2928,25 +2928,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>662.5</v>
+        <v>665.3</v>
       </c>
       <c r="C10">
-        <v>6.057593948462082</v>
+        <v>8.203048213926333</v>
       </c>
       <c r="D10">
-        <v>0.002638000000000001</v>
+        <v>0.002514</v>
       </c>
       <c r="E10">
-        <v>7.209253313161726E-05</v>
+        <v>0.0001025367142918954</v>
       </c>
       <c r="F10">
-        <v>2.821185882608845</v>
+        <v>2.823017523446049</v>
       </c>
       <c r="G10">
-        <v>-2.578725208789654</v>
+        <v>-2.599634726650061</v>
       </c>
       <c r="H10">
-        <v>-2.589354809439706</v>
+        <v>-2.571520564371608</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2954,25 +2954,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>812.9</v>
+        <v>803.1</v>
       </c>
       <c r="C11">
-        <v>9.599131905195039</v>
+        <v>7.651361534611556</v>
       </c>
       <c r="D11">
-        <v>0.00213</v>
+        <v>0.002173</v>
       </c>
       <c r="E11">
-        <v>6.881537295950343E-05</v>
+        <v>6.824872811187685E-05</v>
       </c>
       <c r="F11">
-        <v>2.910037123553051</v>
+        <v>2.904769625906595</v>
       </c>
       <c r="G11">
-        <v>-2.671620396561262</v>
+        <v>-2.662940273679475</v>
       </c>
       <c r="H11">
-        <v>-2.68248568743035</v>
+        <v>-2.652096416919216</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2998,7 +2998,7 @@
         <v>-2.338187314462739</v>
       </c>
       <c r="H12">
-        <v>-2.457595894667791</v>
+        <v>-2.445819704215646</v>
       </c>
     </row>
   </sheetData>
@@ -3021,802 +3021,802 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>11.3</v>
+        <v>10.5</v>
       </c>
       <c r="B2">
-        <v>0.2234229411226657</v>
+        <v>0.184891647846076</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>19.3969696969697</v>
+        <v>18.50606060606061</v>
       </c>
       <c r="B3">
-        <v>0.1156212373834673</v>
+        <v>0.09699386650165555</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>27.4939393939394</v>
+        <v>26.51212121212121</v>
       </c>
       <c r="B4">
-        <v>0.07556595810281702</v>
+        <v>0.06441915600835781</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>35.59090909090909</v>
+        <v>34.51818181818182</v>
       </c>
       <c r="B5">
-        <v>0.05516354196624016</v>
+        <v>0.04770430921186292</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>43.68787878787879</v>
+        <v>42.52424242424242</v>
       </c>
       <c r="B6">
-        <v>0.04296524975839557</v>
+        <v>0.03762158624308524</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>51.78484848484848</v>
+        <v>50.53030303030303</v>
       </c>
       <c r="B7">
-        <v>0.03492127028347099</v>
+        <v>0.03091421103869369</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>59.88181818181819</v>
+        <v>58.53636363636363</v>
       </c>
       <c r="B8">
-        <v>0.02925286548600948</v>
+        <v>0.02614858339296097</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>67.97878787878788</v>
+        <v>66.54242424242423</v>
       </c>
       <c r="B9">
-        <v>0.02506208489084306</v>
+        <v>0.02259818839391243</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>76.07575757575758</v>
+        <v>74.54848484848485</v>
       </c>
       <c r="B10">
-        <v>0.02184900993129131</v>
+        <v>0.01985673358482553</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>84.17272727272727</v>
+        <v>82.55454545454545</v>
       </c>
       <c r="B11">
-        <v>0.01931428318245793</v>
+        <v>0.01767978487064297</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>92.26969696969697</v>
+        <v>90.56060606060606</v>
       </c>
       <c r="B12">
-        <v>0.01726822968450587</v>
+        <v>0.01591174092637995</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>100.3666666666667</v>
+        <v>98.56666666666666</v>
       </c>
       <c r="B13">
-        <v>0.01558512248656729</v>
+        <v>0.01444898696256113</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>108.4636363636364</v>
+        <v>106.5727272727273</v>
       </c>
       <c r="B14">
-        <v>0.01417848879016148</v>
+        <v>0.01321994121343388</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>116.5606060606061</v>
+        <v>114.5787878787879</v>
       </c>
       <c r="B15">
-        <v>0.01298699511530168</v>
+        <v>0.01217361410153211</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>124.6575757575758</v>
+        <v>122.5848484848485</v>
       </c>
       <c r="B16">
-        <v>0.01196599002919759</v>
+        <v>0.01127273135110265</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>132.7545454545455</v>
+        <v>130.5909090909091</v>
       </c>
       <c r="B17">
-        <v>0.0110822316650582</v>
+        <v>0.01048943309212318</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>140.8515151515152</v>
+        <v>138.5969696969697</v>
       </c>
       <c r="B18">
-        <v>0.01031048744007662</v>
+        <v>0.009802491403436467</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>148.9484848484849</v>
+        <v>146.6030303030303</v>
       </c>
       <c r="B19">
-        <v>0.009631275999786809</v>
+        <v>0.009195456799216902</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>157.0454545454546</v>
+        <v>154.6090909090909</v>
       </c>
       <c r="B20">
-        <v>0.009029328839544866</v>
+        <v>0.008655391614442896</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>165.1424242424243</v>
+        <v>162.6151515151515</v>
       </c>
       <c r="B21">
-        <v>0.008492518339989152</v>
+        <v>0.008171984784864205</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>173.2393939393939</v>
+        <v>170.6212121212121</v>
       </c>
       <c r="B22">
-        <v>0.008011095705198019</v>
+        <v>0.007736920717535016</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>181.3363636363637</v>
+        <v>178.6272727272727</v>
       </c>
       <c r="B23">
-        <v>0.007577139428687919</v>
+        <v>0.007343421227736977</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>189.4333333333334</v>
+        <v>186.6333333333333</v>
       </c>
       <c r="B24">
-        <v>0.007184149648374311</v>
+        <v>0.006985907714317893</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>197.5303030303031</v>
+        <v>194.6393939393939</v>
       </c>
       <c r="B25">
-        <v>0.006826745424516108</v>
+        <v>0.006659748375801701</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>205.6272727272728</v>
+        <v>202.6454545454545</v>
       </c>
       <c r="B26">
-        <v>0.006500435816382649</v>
+        <v>0.006361066553561816</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>213.7242424242424</v>
+        <v>210.6515151515152</v>
       </c>
       <c r="B27">
-        <v>0.006201444662158525</v>
+        <v>0.006086593664304345</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>221.8212121212121</v>
+        <v>218.6575757575758</v>
       </c>
       <c r="B28">
-        <v>0.005926574970018011</v>
+        <v>0.005833555098793225</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>229.9181818181818</v>
+        <v>226.6636363636364</v>
       </c>
       <c r="B29">
-        <v>0.00567310289062023</v>
+        <v>0.005599580796224393</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>238.0151515151516</v>
+        <v>234.669696969697</v>
       </c>
       <c r="B30">
-        <v>0.005438694034608454</v>
+        <v>0.005382634499791695</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>246.1121212121213</v>
+        <v>242.6757575757576</v>
       </c>
       <c r="B31">
-        <v>0.00522133684803717</v>
+        <v>0.005180957304561919</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>254.2090909090909</v>
+        <v>250.6818181818182</v>
       </c>
       <c r="B32">
-        <v>0.005019289137692525</v>
+        <v>0.004993022246858652</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>262.3060606060606</v>
+        <v>258.6878787878788</v>
       </c>
       <c r="B33">
-        <v>0.004831034826267896</v>
+        <v>0.004817497501294103</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>270.4030303030303</v>
+        <v>266.6939393939394</v>
       </c>
       <c r="B34">
-        <v>0.0046552487335509</v>
+        <v>0.004653216344908505</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>278.5000000000001</v>
+        <v>274.7</v>
       </c>
       <c r="B35">
-        <v>0.004490767704652825</v>
+        <v>0.004499152483511465</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>286.5969696969697</v>
+        <v>282.7060606060606</v>
       </c>
       <c r="B36">
-        <v>0.004336566794921568</v>
+        <v>0.00435439965844809</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>294.6939393939394</v>
+        <v>290.7121212121212</v>
       </c>
       <c r="B37">
-        <v>0.004191739511663775</v>
+        <v>0.004218154693983959</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>302.7909090909091</v>
+        <v>298.7181818181818</v>
       </c>
       <c r="B38">
-        <v>0.004055481331892936</v>
+        <v>0.004089703328325833</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>310.8878787878788</v>
+        <v>306.7242424242424</v>
       </c>
       <c r="B39">
-        <v>0.003927075881962371</v>
+        <v>0.003968408310592312</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>318.9848484848485</v>
+        <v>314.730303030303</v>
       </c>
       <c r="B40">
-        <v>0.003805883292700867</v>
+        <v>0.003853699353024394</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>327.0818181818182</v>
+        <v>322.7363636363636</v>
       </c>
       <c r="B41">
-        <v>0.003691330342352621</v>
+        <v>0.003745064610494677</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>335.1787878787879</v>
+        <v>330.7424242424242</v>
       </c>
       <c r="B42">
-        <v>0.00358290207638999</v>
+        <v>0.003642043423865678</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>343.2757575757576</v>
+        <v>338.7484848484848</v>
       </c>
       <c r="B43">
-        <v>0.003480134653385886</v>
+        <v>0.003544220114334572</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>351.3727272727273</v>
+        <v>346.7545454545455</v>
       </c>
       <c r="B44">
-        <v>0.003382609213512734</v>
+        <v>0.003451218655832776</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>359.469696969697</v>
+        <v>354.7606060606061</v>
       </c>
       <c r="B45">
-        <v>0.003289946603801274</v>
+        <v>0.003362698084258411</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>367.5666666666667</v>
+        <v>362.7666666666667</v>
       </c>
       <c r="B46">
-        <v>0.003201802824248834</v>
+        <v>0.003278348527644262</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>375.6636363636364</v>
+        <v>370.7727272727273</v>
       </c>
       <c r="B47">
-        <v>0.003117865082885064</v>
+        <v>0.003197887761699077</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>383.7606060606061</v>
+        <v>378.7787878787879</v>
       </c>
       <c r="B48">
-        <v>0.003037848367260696</v>
+        <v>0.003121058211573426</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>391.8575757575758</v>
+        <v>386.7848484848485</v>
       </c>
       <c r="B49">
-        <v>0.002961492455503649</v>
+        <v>0.003047624334014674</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>399.9545454545455</v>
+        <v>394.7909090909091</v>
       </c>
       <c r="B50">
-        <v>0.002888559302845906</v>
+        <v>0.002977370324925316</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>408.0515151515152</v>
+        <v>402.7969696969697</v>
       </c>
       <c r="B51">
-        <v>0.002818830749954937</v>
+        <v>0.002910098106220766</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>416.1484848484849</v>
+        <v>410.8030303030303</v>
       </c>
       <c r="B52">
-        <v>0.002752106507966855</v>
+        <v>0.002845625553184896</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>424.2454545454546</v>
+        <v>418.8090909090909</v>
       </c>
       <c r="B53">
-        <v>0.002688202382178486</v>
+        <v>0.002783784929549944</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>432.3424242424243</v>
+        <v>426.8151515151515</v>
       </c>
       <c r="B54">
-        <v>0.002626948702199065</v>
+        <v>0.002724421502523833</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>440.439393939394</v>
+        <v>434.8212121212121</v>
       </c>
       <c r="B55">
-        <v>0.002568188931217557</v>
+        <v>0.002667392314144691</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>448.5363636363637</v>
+        <v>442.8272727272727</v>
       </c>
       <c r="B56">
-        <v>0.00251177843109041</v>
+        <v>0.00261256508881331</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>456.6333333333334</v>
+        <v>450.8333333333333</v>
       </c>
       <c r="B57">
-        <v>0.002457583363342884</v>
+        <v>0.00255981725976266</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>464.7303030303031</v>
+        <v>458.8393939393939</v>
       </c>
       <c r="B58">
-        <v>0.002405479709022215</v>
+        <v>0.002509035099668747</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>472.8272727272728</v>
+        <v>466.8454545454545</v>
       </c>
       <c r="B59">
-        <v>0.002355352392737675</v>
+        <v>0.002460112942669601</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>480.9242424242425</v>
+        <v>474.8515151515151</v>
       </c>
       <c r="B60">
-        <v>0.002307094498248114</v>
+        <v>0.002412952486804241</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>489.0212121212122</v>
+        <v>482.8575757575758</v>
       </c>
       <c r="B61">
-        <v>0.00226060656467445</v>
+        <v>0.002367462167364444</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>497.1181818181819</v>
+        <v>490.8636363636364</v>
       </c>
       <c r="B62">
-        <v>0.00221579595387411</v>
+        <v>0.002323556592912663</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>505.2151515151515</v>
+        <v>498.869696969697</v>
       </c>
       <c r="B63">
-        <v>0.002172576280758743</v>
+        <v>0.002281156036795257</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>513.3121212121213</v>
+        <v>506.8757575757576</v>
       </c>
       <c r="B64">
-        <v>0.002130866899400167</v>
+        <v>0.002240185977900962</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>521.4090909090909</v>
+        <v>514.8818181818182</v>
       </c>
       <c r="B65">
-        <v>0.00209059243868117</v>
+        <v>0.002200576685204554</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>529.5060606060606</v>
+        <v>522.8878787878788</v>
       </c>
       <c r="B66">
-        <v>0.002051682382031121</v>
+        <v>0.002162262841315321</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>537.6030303030303</v>
+        <v>530.8939393939394</v>
       </c>
       <c r="B67">
-        <v>0.002014070686461129</v>
+        <v>0.002125183200835971</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>545.7</v>
+        <v>538.9</v>
       </c>
       <c r="B68">
-        <v>0.001977695436696093</v>
+        <v>0.002089280279844253</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>553.7969696969697</v>
+        <v>546.9060606060606</v>
       </c>
       <c r="B69">
-        <v>0.001942498530705191</v>
+        <v>0.002054500073248407</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>561.8939393939394</v>
+        <v>554.9121212121212</v>
       </c>
       <c r="B70">
-        <v>0.001908425393369704</v>
+        <v>0.002020791797148658</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>569.9909090909091</v>
+        <v>562.9181818181818</v>
       </c>
       <c r="B71">
-        <v>0.001875424715407219</v>
+        <v>0.001988107653668595</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>578.0878787878788</v>
+        <v>570.9242424242424</v>
       </c>
       <c r="B72">
-        <v>0.001843448215002397</v>
+        <v>0.001956402616009377</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>586.1848484848484</v>
+        <v>578.930303030303</v>
       </c>
       <c r="B73">
-        <v>0.001812450419883519</v>
+        <v>0.001925634231732409</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>594.2818181818182</v>
+        <v>586.9363636363636</v>
       </c>
       <c r="B74">
-        <v>0.001782388467836827</v>
+        <v>0.00189576244249727</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>602.3787878787879</v>
+        <v>594.9424242424242</v>
       </c>
       <c r="B75">
-        <v>0.001753221923872184</v>
+        <v>0.001866749418675721</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>610.4757575757576</v>
+        <v>602.9484848484848</v>
       </c>
       <c r="B76">
-        <v>0.001724912612448014</v>
+        <v>0.001838559407433083</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>618.5727272727273</v>
+        <v>610.9545454545455</v>
       </c>
       <c r="B77">
-        <v>0.001697424463334556</v>
+        <v>0.00181115859301838</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>626.6696969696969</v>
+        <v>618.9606060606061</v>
       </c>
       <c r="B78">
-        <v>0.00167072336984511</v>
+        <v>0.001784514968137032</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>634.7666666666667</v>
+        <v>626.9666666666667</v>
       </c>
       <c r="B79">
-        <v>0.00164477705829798</v>
+        <v>0.001758598215396764</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>642.8636363636364</v>
+        <v>634.9727272727273</v>
       </c>
       <c r="B80">
-        <v>0.001619554967689372</v>
+        <v>0.001733379597920934</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>650.9606060606061</v>
+        <v>642.9787878787879</v>
       </c>
       <c r="B81">
-        <v>0.001595028138661609</v>
+        <v>0.001708831858315155</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82">
-        <v>659.0575757575757</v>
+        <v>650.9848484848485</v>
       </c>
       <c r="B82">
-        <v>0.001571169110943376</v>
+        <v>0.001684929125254508</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83">
-        <v>667.1545454545454</v>
+        <v>658.9909090909091</v>
       </c>
       <c r="B83">
-        <v>0.001547951828520692</v>
+        <v>0.001661646827031027</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84">
-        <v>675.2515151515152</v>
+        <v>666.9969696969697</v>
       </c>
       <c r="B84">
-        <v>0.001525351551870314</v>
+        <v>0.001638961611465592</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85">
-        <v>683.3484848484849</v>
+        <v>675.0030303030303</v>
       </c>
       <c r="B85">
-        <v>0.001503344776652226</v>
+        <v>0.001616851271645816</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86">
-        <v>691.4454545454546</v>
+        <v>683.0090909090909</v>
       </c>
       <c r="B86">
-        <v>0.001481909158315892</v>
+        <v>0.001595294677002861</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87">
-        <v>699.5424242424242</v>
+        <v>691.0151515151515</v>
       </c>
       <c r="B87">
-        <v>0.001461023442126762</v>
+        <v>0.001574271709285973</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88">
-        <v>707.6393939393939</v>
+        <v>699.0212121212121</v>
       </c>
       <c r="B88">
-        <v>0.001440667398165869</v>
+        <v>0.001553763203034644</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89">
-        <v>715.7363636363636</v>
+        <v>707.0272727272727</v>
       </c>
       <c r="B89">
-        <v>0.001420821760896863</v>
+        <v>0.001533750890185145</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90">
-        <v>723.8333333333334</v>
+        <v>715.0333333333333</v>
       </c>
       <c r="B90">
-        <v>0.001401468172932123</v>
+        <v>0.001514217348481232</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91">
-        <v>731.9303030303031</v>
+        <v>723.0393939393939</v>
       </c>
       <c r="B91">
-        <v>0.001382589132662983</v>
+        <v>0.001495145953388581</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92">
-        <v>740.0272727272727</v>
+        <v>731.0454545454545</v>
       </c>
       <c r="B92">
-        <v>0.001364167945449245</v>
+        <v>0.001476520833239256</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93">
-        <v>748.1242424242424</v>
+        <v>739.0515151515151</v>
       </c>
       <c r="B93">
-        <v>0.001346188678090202</v>
+        <v>0.00145832682735662</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94">
-        <v>756.2212121212121</v>
+        <v>747.0575757575757</v>
       </c>
       <c r="B94">
-        <v>0.001328636116323822</v>
+        <v>0.001440549446932866</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95">
-        <v>764.3181818181819</v>
+        <v>755.0636363636363</v>
       </c>
       <c r="B95">
-        <v>0.001311495725122791</v>
+        <v>0.001423174838450966</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96">
-        <v>772.4151515151515</v>
+        <v>763.0696969696969</v>
       </c>
       <c r="B96">
-        <v>0.00129475361157598</v>
+        <v>0.001406189749460629</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97">
-        <v>780.5121212121212</v>
+        <v>771.0757575757575</v>
       </c>
       <c r="B97">
-        <v>0.001278396490161965</v>
+        <v>0.001389581496533911</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98">
-        <v>788.6090909090909</v>
+        <v>779.0818181818181</v>
       </c>
       <c r="B98">
-        <v>0.001262411650237472</v>
+        <v>0.00137333793524071</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99">
-        <v>796.7060606060606</v>
+        <v>787.0878787878788</v>
       </c>
       <c r="B99">
-        <v>0.001246786925578432</v>
+        <v>0.001357447431997586</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100">
-        <v>804.8030303030304</v>
+        <v>795.0939393939394</v>
       </c>
       <c r="B100">
-        <v>0.001231510665824734</v>
+        <v>0.00134189883765535</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101">
-        <v>812.9</v>
+        <v>803.1</v>
       </c>
       <c r="B101">
-        <v>0.001216571709691934</v>
+        <v>0.00132668146270177</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sgt_files/InVitroBioFilm_SGT_scaling.xlsx
+++ b/datasets/sgt_files/InVitroBioFilm_SGT_scaling.xlsx
@@ -625,25 +625,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="C2">
-        <v>0.9521904571390467</v>
+        <v>0.8749603165604457</v>
       </c>
       <c r="D2">
-        <v>0.590404</v>
+        <v>0.54381</v>
       </c>
       <c r="E2">
-        <v>0.1001237670996363</v>
+        <v>0.08774793272651941</v>
       </c>
       <c r="F2">
-        <v>0.6812412373755872</v>
+        <v>0.6901960800285137</v>
       </c>
       <c r="G2">
-        <v>-0.2288507088204435</v>
+        <v>-0.2645528105313652</v>
       </c>
       <c r="H2">
-        <v>-0.1513986946015146</v>
+        <v>-0.1883687288611057</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -651,25 +651,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>19.6</v>
+        <v>15.1</v>
       </c>
       <c r="C3">
-        <v>3.584534682338684</v>
+        <v>1.494062322067665</v>
       </c>
       <c r="D3">
-        <v>0.170902</v>
+        <v>0.160176</v>
       </c>
       <c r="E3">
-        <v>0.04535361869183588</v>
+        <v>0.02307557738292924</v>
       </c>
       <c r="F3">
-        <v>1.292256071356476</v>
+        <v>1.178976947293169</v>
       </c>
       <c r="G3">
-        <v>-0.7672528548691906</v>
+        <v>-0.79540255596962</v>
       </c>
       <c r="H3">
-        <v>-0.8081813728620506</v>
+        <v>-0.7028767673401117</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -677,25 +677,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>33</v>
+        <v>38.7</v>
       </c>
       <c r="C4">
-        <v>6.189597007165418</v>
+        <v>7.03964961249256</v>
       </c>
       <c r="D4">
-        <v>0.103301</v>
+        <v>0.096871</v>
       </c>
       <c r="E4">
-        <v>0.02878502382412694</v>
+        <v>0.02955341012284182</v>
       </c>
       <c r="F4">
-        <v>1.518513939877888</v>
+        <v>1.587710965018911</v>
       </c>
       <c r="G4">
-        <v>-0.9858954742947084</v>
+        <v>-1.013806217015109</v>
       </c>
       <c r="H4">
-        <v>-1.05138700487075</v>
+        <v>-1.13312465919519</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -703,25 +703,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>71.7</v>
+        <v>55.9</v>
       </c>
       <c r="C5">
-        <v>11.16248677988517</v>
+        <v>10.85505514597794</v>
       </c>
       <c r="D5">
-        <v>0.03901</v>
+        <v>0.077846</v>
       </c>
       <c r="E5">
-        <v>0.006590887986033781</v>
+        <v>0.03040207913942729</v>
       </c>
       <c r="F5">
-        <v>1.8555191556678</v>
+        <v>1.747411807886423</v>
       </c>
       <c r="G5">
-        <v>-1.408824049688209</v>
+        <v>-1.108763698093395</v>
       </c>
       <c r="H5">
-        <v>-1.4136354739827</v>
+        <v>-1.301231418093175</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -729,25 +729,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>114.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="C6">
-        <v>13.48974919460452</v>
+        <v>14.12755384975678</v>
       </c>
       <c r="D6">
-        <v>0.02455</v>
+        <v>0.039588</v>
       </c>
       <c r="E6">
-        <v>0.005725250503980881</v>
+        <v>0.007898477462284881</v>
       </c>
       <c r="F6">
-        <v>2.057666103909829</v>
+        <v>1.8926510338773</v>
       </c>
       <c r="G6">
-        <v>-1.609948503541013</v>
+        <v>-1.402436438407031</v>
       </c>
       <c r="H6">
-        <v>-1.630924165983173</v>
+        <v>-1.454115367280804</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -755,25 +755,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>152.9</v>
+        <v>167.1</v>
       </c>
       <c r="C7">
-        <v>18.38081729533386</v>
+        <v>13.01405223424109</v>
       </c>
       <c r="D7">
-        <v>0.018458</v>
+        <v>0.013829</v>
       </c>
       <c r="E7">
-        <v>0.003957827911592137</v>
+        <v>0.0009057574485233646</v>
       </c>
       <c r="F7">
-        <v>2.18440748541232</v>
+        <v>2.222976449893391</v>
       </c>
       <c r="G7">
-        <v>-1.733815358349094</v>
+        <v>-1.859209223374698</v>
       </c>
       <c r="H7">
-        <v>-1.76715906464727</v>
+        <v>-1.801827590153425</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -781,25 +781,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>185.7</v>
+        <v>215.3</v>
       </c>
       <c r="C8">
-        <v>24.28627870492582</v>
+        <v>14.01590366532089</v>
       </c>
       <c r="D8">
-        <v>0.014253</v>
+        <v>0.010871</v>
       </c>
       <c r="E8">
-        <v>0.002260750145907819</v>
+        <v>0.0007843078335563005</v>
       </c>
       <c r="F8">
-        <v>2.26881190373978</v>
+        <v>2.333044029823487</v>
       </c>
       <c r="G8">
-        <v>-1.846093714861132</v>
+        <v>-1.963730504257185</v>
       </c>
       <c r="H8">
-        <v>-1.857885765282276</v>
+        <v>-1.917688619998731</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -807,25 +807,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>261.5</v>
+        <v>276.4</v>
       </c>
       <c r="C9">
-        <v>18.55936421324825</v>
+        <v>24.80913810137976</v>
       </c>
       <c r="D9">
-        <v>0.008937</v>
+        <v>0.008915000000000001</v>
       </c>
       <c r="E9">
-        <v>0.0006362669775076077</v>
+        <v>0.001054587070321312</v>
       </c>
       <c r="F9">
-        <v>2.417471693203293</v>
+        <v>2.441538038702161</v>
       </c>
       <c r="G9">
-        <v>-2.048808242065294</v>
+        <v>-2.049878652488626</v>
       </c>
       <c r="H9">
-        <v>-2.017680862297134</v>
+        <v>-2.031893253267785</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -833,25 +833,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>278</v>
+        <v>339.4</v>
       </c>
       <c r="C10">
-        <v>21.19224176700311</v>
+        <v>27.14496065366256</v>
       </c>
       <c r="D10">
-        <v>0.008409</v>
+        <v>0.007071000000000001</v>
       </c>
       <c r="E10">
-        <v>0.0006029362413316281</v>
+        <v>0.0006898702776609526</v>
       </c>
       <c r="F10">
-        <v>2.444044795918076</v>
+        <v>2.530711837981657</v>
       </c>
       <c r="G10">
-        <v>-2.075255647520052</v>
+        <v>-2.150519162756014</v>
       </c>
       <c r="H10">
-        <v>-2.046244413622065</v>
+        <v>-2.125760750184704</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -859,25 +859,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>382</v>
+        <v>312.8</v>
       </c>
       <c r="C11">
-        <v>23.13054738267606</v>
+        <v>30.94719516998089</v>
       </c>
       <c r="D11">
-        <v>0.006128</v>
+        <v>0.007683</v>
       </c>
       <c r="E11">
-        <v>0.0004466935315304118</v>
+        <v>0.0006173546612586461</v>
       </c>
       <c r="F11">
-        <v>2.582063362911709</v>
+        <v>2.49526674438781</v>
       </c>
       <c r="G11">
-        <v>-2.212681243375453</v>
+        <v>-2.114469166811908</v>
       </c>
       <c r="H11">
-        <v>-2.194601211261768</v>
+        <v>-2.088449990291968</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -885,25 +885,25 @@
         <v>638</v>
       </c>
       <c r="B12">
-        <v>496</v>
+        <v>286</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0.004589999999999999</v>
+        <v>0.00851</v>
       </c>
       <c r="E12">
-        <v>2.891205793294678E-19</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>2.695481676490198</v>
+        <v>2.456366033129043</v>
       </c>
       <c r="G12">
-        <v>-2.338187314462739</v>
+        <v>-2.070070439915412</v>
       </c>
       <c r="H12">
-        <v>-2.316515082436625</v>
+        <v>-2.047501724953364</v>
       </c>
     </row>
   </sheetData>
@@ -926,802 +926,802 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="B2">
-        <v>0.5924498304088603</v>
+        <v>0.5398045483159717</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>9.761616161616161</v>
+        <v>8.278787878787879</v>
       </c>
       <c r="B3">
-        <v>0.3058435010807216</v>
+        <v>0.3284083995079981</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>14.72323232323232</v>
+        <v>11.65757575757576</v>
       </c>
       <c r="B4">
-        <v>0.2085691820389627</v>
+        <v>0.2374489201543626</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>19.68484848484848</v>
+        <v>15.03636363636364</v>
       </c>
       <c r="B5">
-        <v>0.1591349376280704</v>
+        <v>0.1865666643680177</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>24.64646464646465</v>
+        <v>18.41515151515151</v>
       </c>
       <c r="B6">
-        <v>0.1290724626557771</v>
+        <v>0.1539641388384904</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>29.60808080808081</v>
+        <v>21.7939393939394</v>
       </c>
       <c r="B7">
-        <v>0.108802083286604</v>
+        <v>0.1312492966062286</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>34.56969696969697</v>
+        <v>25.17272727272727</v>
       </c>
       <c r="B8">
-        <v>0.09418100717880147</v>
+        <v>0.1144948720744534</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>39.53131313131313</v>
+        <v>28.55151515151515</v>
       </c>
       <c r="B9">
-        <v>0.08312077044674787</v>
+        <v>0.1016147002929615</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>44.49292929292929</v>
+        <v>31.93030303030303</v>
       </c>
       <c r="B10">
-        <v>0.07445246553257689</v>
+        <v>0.0913967491010062</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>49.45454545454545</v>
+        <v>35.30909090909091</v>
       </c>
       <c r="B11">
-        <v>0.06746999728410076</v>
+        <v>0.08308809485423957</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>54.41616161616162</v>
+        <v>38.68787878787879</v>
       </c>
       <c r="B12">
-        <v>0.0617212501107028</v>
+        <v>0.07619603829433115</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>59.37777777777777</v>
+        <v>42.06666666666667</v>
       </c>
       <c r="B13">
-        <v>0.05690309688298167</v>
+        <v>0.07038445451469259</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>64.33939393939394</v>
+        <v>45.44545454545455</v>
       </c>
       <c r="B14">
-        <v>0.05280457456085561</v>
+        <v>0.06541607560131416</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>69.30101010101009</v>
+        <v>48.82424242424242</v>
       </c>
       <c r="B15">
-        <v>0.04927425686139162</v>
+        <v>0.06111857673102275</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>74.26262626262626</v>
+        <v>52.2030303030303</v>
       </c>
       <c r="B16">
-        <v>0.04620058946241919</v>
+        <v>0.05736374168613149</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>79.22424242424242</v>
+        <v>55.58181818181819</v>
       </c>
       <c r="B17">
-        <v>0.04349954728063713</v>
+        <v>0.05405417411447415</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>84.18585858585858</v>
+        <v>58.96060606060606</v>
       </c>
       <c r="B18">
-        <v>0.04110661597844825</v>
+        <v>0.05111454534972518</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>89.14747474747475</v>
+        <v>62.33939393939394</v>
       </c>
       <c r="B19">
-        <v>0.03897142601586922</v>
+        <v>0.0484856678716831</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>94.10909090909091</v>
+        <v>65.71818181818182</v>
       </c>
       <c r="B20">
-        <v>0.03705406799320808</v>
+        <v>0.04612038362129586</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>99.07070707070707</v>
+        <v>69.09696969696971</v>
       </c>
       <c r="B21">
-        <v>0.03532250455840226</v>
+        <v>0.04398064975636115</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>104.0323232323232</v>
+        <v>72.47575757575758</v>
       </c>
       <c r="B22">
-        <v>0.03375071573494694</v>
+        <v>0.04203543349690217</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>108.9939393939394</v>
+        <v>75.85454545454546</v>
       </c>
       <c r="B23">
-        <v>0.03231734586368994</v>
+        <v>0.04025916536229642</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>113.9555555555555</v>
+        <v>79.23333333333335</v>
       </c>
       <c r="B24">
-        <v>0.03100470053197421</v>
+        <v>0.0386305851690889</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>118.9171717171717</v>
+        <v>82.61212121212122</v>
       </c>
       <c r="B25">
-        <v>0.0297979921181669</v>
+        <v>0.03713186905886506</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>123.8787878787879</v>
+        <v>85.9909090909091</v>
       </c>
       <c r="B26">
-        <v>0.02868476483013806</v>
+        <v>0.03574796075508859</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>128.8404040404041</v>
+        <v>89.36969696969697</v>
       </c>
       <c r="B27">
-        <v>0.02765445125844361</v>
+        <v>0.03446605334880411</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>133.8020202020202</v>
+        <v>92.74848484848485</v>
       </c>
       <c r="B28">
-        <v>0.02669802659540598</v>
+        <v>0.03327518347648203</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>138.7636363636364</v>
+        <v>96.12727272727274</v>
       </c>
       <c r="B29">
-        <v>0.02580773628320412</v>
+        <v>0.03216591041717451</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>143.7252525252525</v>
+        <v>99.50606060606061</v>
       </c>
       <c r="B30">
-        <v>0.02497687949863043</v>
+        <v>0.03113006005706683</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>148.6868686868687</v>
+        <v>102.8848484848485</v>
       </c>
       <c r="B31">
-        <v>0.02419963554396714</v>
+        <v>0.03016051890784841</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>153.6484848484849</v>
+        <v>106.2636363636364</v>
       </c>
       <c r="B32">
-        <v>0.02347092352911663</v>
+        <v>0.02925106711204735</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>158.610101010101</v>
+        <v>109.6424242424243</v>
       </c>
       <c r="B33">
-        <v>0.02278628811836855</v>
+        <v>0.02839624208121811</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>163.5717171717172</v>
+        <v>113.0212121212121</v>
       </c>
       <c r="B34">
-        <v>0.02214180585570508</v>
+        <v>0.02759122639938759</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>168.5333333333333</v>
+        <v>116.4</v>
       </c>
       <c r="B35">
-        <v>0.02153400786491867</v>
+        <v>0.02683175509432052</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>173.4949494949495</v>
+        <v>119.7787878787879</v>
       </c>
       <c r="B36">
-        <v>0.02095981567530501</v>
+        <v>0.02611403847796769</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>178.4565656565657</v>
+        <v>123.1575757575758</v>
       </c>
       <c r="B37">
-        <v>0.02041648764092429</v>
+        <v>0.0254346975863321</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>183.4181818181818</v>
+        <v>126.5363636363636</v>
       </c>
       <c r="B38">
-        <v>0.01990157396520017</v>
+        <v>0.02479070987968223</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>188.379797979798</v>
+        <v>129.9151515151515</v>
       </c>
       <c r="B39">
-        <v>0.01941287875836224</v>
+        <v>0.02417936334786408</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>193.3414141414142</v>
+        <v>133.2939393939394</v>
       </c>
       <c r="B40">
-        <v>0.01894842787559876</v>
+        <v>0.02359821753947685</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>198.3030303030303</v>
+        <v>136.6727272727273</v>
       </c>
       <c r="B41">
-        <v>0.01850644153249176</v>
+        <v>0.02304507032490236</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>203.2646464646465</v>
+        <v>140.0515151515152</v>
       </c>
       <c r="B42">
-        <v>0.01808531088874405</v>
+        <v>0.02251792943149735</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>208.2262626262626</v>
+        <v>143.430303030303</v>
       </c>
       <c r="B43">
-        <v>0.01768357794422913</v>
+        <v>0.02201498796942169</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>213.1878787878788</v>
+        <v>146.8090909090909</v>
       </c>
       <c r="B44">
-        <v>0.01729991821258228</v>
+        <v>0.02153460330961525</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>218.149494949495</v>
+        <v>150.1878787878788</v>
       </c>
       <c r="B45">
-        <v>0.01693312573410098</v>
+        <v>0.02107527878966524</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>223.1111111111111</v>
+        <v>153.5666666666667</v>
       </c>
       <c r="B46">
-        <v>0.01658210006707991</v>
+        <v>0.02063564781503395</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>228.0727272727273</v>
+        <v>156.9454545454546</v>
       </c>
       <c r="B47">
-        <v>0.01624583495902135</v>
+        <v>0.02021445999716518</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>233.0343434343434</v>
+        <v>160.3242424242424</v>
       </c>
       <c r="B48">
-        <v>0.01592340844961805</v>
+        <v>0.0198105690300645</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>237.9959595959596</v>
+        <v>163.7030303030303</v>
       </c>
       <c r="B49">
-        <v>0.01561397419846001</v>
+        <v>0.01942292205592545</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>242.9575757575758</v>
+        <v>167.0818181818182</v>
       </c>
       <c r="B50">
-        <v>0.01531675386397739</v>
+        <v>0.01905055031048268</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>247.9191919191919</v>
+        <v>170.4606060606061</v>
       </c>
       <c r="B51">
-        <v>0.01503103038768949</v>
+        <v>0.01869256087176563</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>252.8808080808081</v>
+        <v>173.8393939393939</v>
       </c>
       <c r="B52">
-        <v>0.01475614206055503</v>
+        <v>0.01834812936317774</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>257.8424242424242</v>
+        <v>177.2181818181818</v>
       </c>
       <c r="B53">
-        <v>0.01449147726703538</v>
+        <v>0.01801649348442664</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>262.8040404040404</v>
+        <v>180.5969696969697</v>
       </c>
       <c r="B54">
-        <v>0.01423646981812463</v>
+        <v>0.01769694726264558</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>267.7656565656566</v>
+        <v>183.9757575757576</v>
       </c>
       <c r="B55">
-        <v>0.0139905947976513</v>
+        <v>0.01738883593176847</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>272.7272727272727</v>
+        <v>187.3545454545455</v>
       </c>
       <c r="B56">
-        <v>0.0137533648570862</v>
+        <v>0.01709155136140432</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>277.6888888888889</v>
+        <v>190.7333333333333</v>
       </c>
       <c r="B57">
-        <v>0.01352432690327473</v>
+        <v>0.01680452796754974</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>282.650505050505</v>
+        <v>194.1121212121212</v>
       </c>
       <c r="B58">
-        <v>0.01330305913125553</v>
+        <v>0.0165272390468431</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>287.6121212121212</v>
+        <v>197.4909090909091</v>
       </c>
       <c r="B59">
-        <v>0.01308916836087662</v>
+        <v>0.01625919348399371</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>292.5737373737374</v>
+        <v>200.869696969697</v>
       </c>
       <c r="B60">
-        <v>0.01288228764147714</v>
+        <v>0.01599993278875608</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>297.5353535353535</v>
+        <v>204.2484848484848</v>
       </c>
       <c r="B61">
-        <v>0.01268207409363181</v>
+        <v>0.01574902842455767</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>302.4969696969697</v>
+        <v>207.6272727272728</v>
       </c>
       <c r="B62">
-        <v>0.0124882069609904</v>
+        <v>0.01550607939579167</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>307.4585858585859</v>
+        <v>211.0060606060606</v>
       </c>
       <c r="B63">
-        <v>0.01230038584869856</v>
+        <v>0.01527071006498598</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>312.4202020202021</v>
+        <v>214.3848484848485</v>
       </c>
       <c r="B64">
-        <v>0.01211832912784966</v>
+        <v>0.0150425681746673</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>317.3818181818182</v>
+        <v>217.7636363636364</v>
       </c>
       <c r="B65">
-        <v>0.01194177248796671</v>
+        <v>0.01482132305184568</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>322.3434343434344</v>
+        <v>221.1424242424243</v>
       </c>
       <c r="B66">
-        <v>0.01177046762171235</v>
+        <v>0.01460666397572636</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>327.3050505050505</v>
+        <v>224.5212121212121</v>
       </c>
       <c r="B67">
-        <v>0.01160418102792583</v>
+        <v>0.01439829869157622</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>332.2666666666667</v>
+        <v>227.9</v>
       </c>
       <c r="B68">
-        <v>0.01144269292073312</v>
+        <v>0.01419595205568452</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>337.2282828282828</v>
+        <v>231.2787878787879</v>
       </c>
       <c r="B69">
-        <v>0.01128579623390697</v>
+        <v>0.01399936479810706</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>342.189898989899</v>
+        <v>234.6575757575758</v>
       </c>
       <c r="B70">
-        <v>0.01113329571089922</v>
+        <v>0.01380829239140649</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>347.1515151515152</v>
+        <v>238.0363636363637</v>
       </c>
       <c r="B71">
-        <v>0.01098500707205367</v>
+        <v>0.01362250401493192</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>352.1131313131313</v>
+        <v>241.4151515151515</v>
       </c>
       <c r="B72">
-        <v>0.01084075625145765</v>
+        <v>0.01344178160534442</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>357.0747474747475</v>
+        <v>244.7939393939394</v>
       </c>
       <c r="B73">
-        <v>0.01070037869672178</v>
+        <v>0.01326591898511502</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>362.0363636363637</v>
+        <v>248.1727272727273</v>
       </c>
       <c r="B74">
-        <v>0.01056371872570723</v>
+        <v>0.013094721061617</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>366.9979797979798</v>
+        <v>251.5515151515152</v>
       </c>
       <c r="B75">
-        <v>0.0104306289348615</v>
+        <v>0.01292800309022271</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>371.959595959596</v>
+        <v>254.930303030303</v>
       </c>
       <c r="B76">
-        <v>0.0103009696543887</v>
+        <v>0.01276558999550886</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>376.9212121212121</v>
+        <v>258.3090909090909</v>
       </c>
       <c r="B77">
-        <v>0.01017460844597923</v>
+        <v>0.01260731574528809</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>381.8828282828283</v>
+        <v>261.6878787878788</v>
       </c>
       <c r="B78">
-        <v>0.01005141963926408</v>
+        <v>0.01245302277272614</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>386.8444444444444</v>
+        <v>265.0666666666667</v>
       </c>
       <c r="B79">
-        <v>0.009931283903549807</v>
+        <v>0.01230256144228506</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>391.8060606060606</v>
+        <v>268.4454545454545</v>
       </c>
       <c r="B80">
-        <v>0.009814087851735777</v>
+        <v>0.01215578955565855</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>396.7676767676768</v>
+        <v>271.8242424242424</v>
       </c>
       <c r="B81">
-        <v>0.009699723673623097</v>
+        <v>0.01201257189424466</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82">
-        <v>401.729292929293</v>
+        <v>275.2030303030303</v>
       </c>
       <c r="B82">
-        <v>0.009588088796097901</v>
+        <v>0.01187277979503844</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83">
-        <v>406.6909090909091</v>
+        <v>278.5818181818182</v>
       </c>
       <c r="B83">
-        <v>0.009479085567915465</v>
+        <v>0.01173629075712732</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84">
-        <v>411.6525252525253</v>
+        <v>281.960606060606</v>
       </c>
       <c r="B84">
-        <v>0.009372620967029011</v>
+        <v>0.0116029880762408</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85">
-        <v>416.6141414141414</v>
+        <v>285.3393939393939</v>
       </c>
       <c r="B85">
-        <v>0.009268606328601416</v>
+        <v>0.01147276050504557</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86">
-        <v>421.5757575757576</v>
+        <v>288.7181818181818</v>
       </c>
       <c r="B86">
-        <v>0.009166957092011792</v>
+        <v>0.01134550193709238</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87">
-        <v>426.5373737373737</v>
+        <v>292.0969696969697</v>
       </c>
       <c r="B87">
-        <v>0.009067592565324854</v>
+        <v>0.01122111111251317</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88">
-        <v>431.4989898989899</v>
+        <v>295.4757575757575</v>
       </c>
       <c r="B88">
-        <v>0.008970435705830657</v>
+        <v>0.01109949134373992</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89">
-        <v>436.4606060606061</v>
+        <v>298.8545454545454</v>
       </c>
       <c r="B89">
-        <v>0.00887541291538794</v>
+        <v>0.01098055025967232</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90">
-        <v>441.4222222222222</v>
+        <v>302.2333333333333</v>
       </c>
       <c r="B90">
-        <v>0.008782453849417272</v>
+        <v>0.01086419956686064</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91">
-        <v>446.3838383838384</v>
+        <v>305.6121212121212</v>
       </c>
       <c r="B91">
-        <v>0.008691491238491958</v>
+        <v>0.01075035482639666</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92">
-        <v>451.3454545454546</v>
+        <v>308.9909090909091</v>
       </c>
       <c r="B92">
-        <v>0.00860246072156641</v>
+        <v>0.01063893524531896</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93">
-        <v>456.3070707070707</v>
+        <v>312.369696969697</v>
       </c>
       <c r="B93">
-        <v>0.008515300689964578</v>
+        <v>0.01052986348144133</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94">
-        <v>461.2686868686869</v>
+        <v>315.7484848484848</v>
       </c>
       <c r="B94">
-        <v>0.008429952141325862</v>
+        <v>0.01042306546060632</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95">
-        <v>466.230303030303</v>
+        <v>319.1272727272727</v>
       </c>
       <c r="B95">
-        <v>0.008346358542773744</v>
+        <v>0.01031847020544955</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96">
-        <v>471.1919191919192</v>
+        <v>322.5060606060606</v>
       </c>
       <c r="B96">
-        <v>0.008264465702633741</v>
+        <v>0.01021600967483671</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97">
-        <v>476.1535353535353</v>
+        <v>325.8848484848485</v>
       </c>
       <c r="B97">
-        <v>0.00818422165008296</v>
+        <v>0.01011561861320442</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98">
-        <v>481.1151515151515</v>
+        <v>329.2636363636364</v>
       </c>
       <c r="B98">
-        <v>0.008105576522164084</v>
+        <v>0.01001723440909843</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99">
-        <v>486.0767676767677</v>
+        <v>332.6424242424242</v>
       </c>
       <c r="B99">
-        <v>0.008028482457642554</v>
+        <v>0.009920796962260125</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100">
-        <v>491.0383838383838</v>
+        <v>336.0212121212121</v>
       </c>
       <c r="B100">
-        <v>0.00795289349722748</v>
+        <v>0.009826248558663993</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101">
-        <v>496</v>
+        <v>339.4</v>
       </c>
       <c r="B101">
-        <v>0.007878765489714909</v>
+        <v>0.009733533752955834</v>
       </c>
     </row>
   </sheetData>
@@ -1765,25 +1765,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="C2">
-        <v>0.9521904571390467</v>
+        <v>0.8749603165604457</v>
       </c>
       <c r="D2">
-        <v>0.590404</v>
+        <v>0.54381</v>
       </c>
       <c r="E2">
-        <v>0.1001237670996363</v>
+        <v>0.08774793272651941</v>
       </c>
       <c r="F2">
-        <v>0.6812412373755872</v>
+        <v>0.6901960800285137</v>
       </c>
       <c r="G2">
-        <v>-0.2288507088204435</v>
+        <v>-0.2645528105313652</v>
       </c>
       <c r="H2">
-        <v>-0.1513986946015146</v>
+        <v>-0.1883687288611057</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1791,25 +1791,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>19.6</v>
+        <v>15.1</v>
       </c>
       <c r="C3">
-        <v>3.584534682338684</v>
+        <v>1.494062322067665</v>
       </c>
       <c r="D3">
-        <v>0.170902</v>
+        <v>0.160176</v>
       </c>
       <c r="E3">
-        <v>0.04535361869183588</v>
+        <v>0.02307557738292924</v>
       </c>
       <c r="F3">
-        <v>1.292256071356476</v>
+        <v>1.178976947293169</v>
       </c>
       <c r="G3">
-        <v>-0.7672528548691906</v>
+        <v>-0.79540255596962</v>
       </c>
       <c r="H3">
-        <v>-0.8081813728620506</v>
+        <v>-0.7028767673401117</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1817,25 +1817,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>33</v>
+        <v>38.7</v>
       </c>
       <c r="C4">
-        <v>6.189597007165418</v>
+        <v>7.03964961249256</v>
       </c>
       <c r="D4">
-        <v>0.103301</v>
+        <v>0.096871</v>
       </c>
       <c r="E4">
-        <v>0.02878502382412694</v>
+        <v>0.02955341012284182</v>
       </c>
       <c r="F4">
-        <v>1.518513939877888</v>
+        <v>1.587710965018911</v>
       </c>
       <c r="G4">
-        <v>-0.9858954742947084</v>
+        <v>-1.013806217015109</v>
       </c>
       <c r="H4">
-        <v>-1.05138700487075</v>
+        <v>-1.13312465919519</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1843,25 +1843,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>71.7</v>
+        <v>55.9</v>
       </c>
       <c r="C5">
-        <v>11.16248677988517</v>
+        <v>10.85505514597794</v>
       </c>
       <c r="D5">
-        <v>0.03901</v>
+        <v>0.077846</v>
       </c>
       <c r="E5">
-        <v>0.006590887986033781</v>
+        <v>0.03040207913942729</v>
       </c>
       <c r="F5">
-        <v>1.8555191556678</v>
+        <v>1.747411807886423</v>
       </c>
       <c r="G5">
-        <v>-1.408824049688209</v>
+        <v>-1.108763698093395</v>
       </c>
       <c r="H5">
-        <v>-1.4136354739827</v>
+        <v>-1.301231418093175</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1869,25 +1869,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>114.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="C6">
-        <v>13.48974919460452</v>
+        <v>14.12755384975678</v>
       </c>
       <c r="D6">
-        <v>0.02455</v>
+        <v>0.039588</v>
       </c>
       <c r="E6">
-        <v>0.005725250503980881</v>
+        <v>0.007898477462284881</v>
       </c>
       <c r="F6">
-        <v>2.057666103909829</v>
+        <v>1.8926510338773</v>
       </c>
       <c r="G6">
-        <v>-1.609948503541013</v>
+        <v>-1.402436438407031</v>
       </c>
       <c r="H6">
-        <v>-1.630924165983173</v>
+        <v>-1.454115367280804</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1895,25 +1895,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>152.9</v>
+        <v>167.1</v>
       </c>
       <c r="C7">
-        <v>18.38081729533386</v>
+        <v>13.01405223424109</v>
       </c>
       <c r="D7">
-        <v>0.018458</v>
+        <v>0.013829</v>
       </c>
       <c r="E7">
-        <v>0.003957827911592137</v>
+        <v>0.0009057574485233646</v>
       </c>
       <c r="F7">
-        <v>2.18440748541232</v>
+        <v>2.222976449893391</v>
       </c>
       <c r="G7">
-        <v>-1.733815358349094</v>
+        <v>-1.859209223374698</v>
       </c>
       <c r="H7">
-        <v>-1.76715906464727</v>
+        <v>-1.801827590153425</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1921,25 +1921,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>185.7</v>
+        <v>215.3</v>
       </c>
       <c r="C8">
-        <v>24.28627870492582</v>
+        <v>14.01590366532089</v>
       </c>
       <c r="D8">
-        <v>0.014253</v>
+        <v>0.010871</v>
       </c>
       <c r="E8">
-        <v>0.002260750145907819</v>
+        <v>0.0007843078335563005</v>
       </c>
       <c r="F8">
-        <v>2.26881190373978</v>
+        <v>2.333044029823487</v>
       </c>
       <c r="G8">
-        <v>-1.846093714861132</v>
+        <v>-1.963730504257185</v>
       </c>
       <c r="H8">
-        <v>-1.857885765282276</v>
+        <v>-1.917688619998731</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1947,25 +1947,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>261.5</v>
+        <v>276.4</v>
       </c>
       <c r="C9">
-        <v>18.55936421324825</v>
+        <v>24.80913810137976</v>
       </c>
       <c r="D9">
-        <v>0.008937</v>
+        <v>0.008915000000000001</v>
       </c>
       <c r="E9">
-        <v>0.0006362669775076077</v>
+        <v>0.001054587070321312</v>
       </c>
       <c r="F9">
-        <v>2.417471693203293</v>
+        <v>2.441538038702161</v>
       </c>
       <c r="G9">
-        <v>-2.048808242065294</v>
+        <v>-2.049878652488626</v>
       </c>
       <c r="H9">
-        <v>-2.017680862297134</v>
+        <v>-2.031893253267785</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1973,25 +1973,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>278</v>
+        <v>339.4</v>
       </c>
       <c r="C10">
-        <v>21.19224176700311</v>
+        <v>27.14496065366256</v>
       </c>
       <c r="D10">
-        <v>0.008409</v>
+        <v>0.007071000000000001</v>
       </c>
       <c r="E10">
-        <v>0.0006029362413316281</v>
+        <v>0.0006898702776609526</v>
       </c>
       <c r="F10">
-        <v>2.444044795918076</v>
+        <v>2.530711837981657</v>
       </c>
       <c r="G10">
-        <v>-2.075255647520052</v>
+        <v>-2.150519162756014</v>
       </c>
       <c r="H10">
-        <v>-2.046244413622065</v>
+        <v>-2.125760750184704</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1999,25 +1999,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>382</v>
+        <v>312.8</v>
       </c>
       <c r="C11">
-        <v>23.13054738267606</v>
+        <v>30.94719516998089</v>
       </c>
       <c r="D11">
-        <v>0.006128</v>
+        <v>0.007683</v>
       </c>
       <c r="E11">
-        <v>0.0004466935315304118</v>
+        <v>0.0006173546612586461</v>
       </c>
       <c r="F11">
-        <v>2.582063362911709</v>
+        <v>2.49526674438781</v>
       </c>
       <c r="G11">
-        <v>-2.212681243375453</v>
+        <v>-2.114469166811908</v>
       </c>
       <c r="H11">
-        <v>-2.194601211261768</v>
+        <v>-2.088449990291968</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2025,25 +2025,25 @@
         <v>638</v>
       </c>
       <c r="B12">
-        <v>496</v>
+        <v>286</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0.004589999999999999</v>
+        <v>0.00851</v>
       </c>
       <c r="E12">
-        <v>2.891205793294678E-19</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>2.695481676490198</v>
+        <v>2.456366033129043</v>
       </c>
       <c r="G12">
-        <v>-2.338187314462739</v>
+        <v>-2.070070439915412</v>
       </c>
       <c r="H12">
-        <v>-2.316515082436625</v>
+        <v>-2.047501724953364</v>
       </c>
     </row>
   </sheetData>
@@ -2066,802 +2066,802 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="B2">
-        <v>0.5924498304088603</v>
+        <v>0.5398045483159717</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>9.761616161616161</v>
+        <v>8.278787878787879</v>
       </c>
       <c r="B3">
-        <v>0.3058435010807216</v>
+        <v>0.3284083995079981</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>14.72323232323232</v>
+        <v>11.65757575757576</v>
       </c>
       <c r="B4">
-        <v>0.2085691820389627</v>
+        <v>0.2374489201543626</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>19.68484848484848</v>
+        <v>15.03636363636364</v>
       </c>
       <c r="B5">
-        <v>0.1591349376280704</v>
+        <v>0.1865666643680177</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>24.64646464646465</v>
+        <v>18.41515151515151</v>
       </c>
       <c r="B6">
-        <v>0.1290724626557771</v>
+        <v>0.1539641388384904</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>29.60808080808081</v>
+        <v>21.7939393939394</v>
       </c>
       <c r="B7">
-        <v>0.108802083286604</v>
+        <v>0.1312492966062286</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>34.56969696969697</v>
+        <v>25.17272727272727</v>
       </c>
       <c r="B8">
-        <v>0.09418100717880147</v>
+        <v>0.1144948720744534</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>39.53131313131313</v>
+        <v>28.55151515151515</v>
       </c>
       <c r="B9">
-        <v>0.08312077044674787</v>
+        <v>0.1016147002929615</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>44.49292929292929</v>
+        <v>31.93030303030303</v>
       </c>
       <c r="B10">
-        <v>0.07445246553257689</v>
+        <v>0.0913967491010062</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>49.45454545454545</v>
+        <v>35.30909090909091</v>
       </c>
       <c r="B11">
-        <v>0.06746999728410076</v>
+        <v>0.08308809485423957</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>54.41616161616162</v>
+        <v>38.68787878787879</v>
       </c>
       <c r="B12">
-        <v>0.0617212501107028</v>
+        <v>0.07619603829433115</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>59.37777777777777</v>
+        <v>42.06666666666667</v>
       </c>
       <c r="B13">
-        <v>0.05690309688298167</v>
+        <v>0.07038445451469259</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>64.33939393939394</v>
+        <v>45.44545454545455</v>
       </c>
       <c r="B14">
-        <v>0.05280457456085561</v>
+        <v>0.06541607560131416</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>69.30101010101009</v>
+        <v>48.82424242424242</v>
       </c>
       <c r="B15">
-        <v>0.04927425686139162</v>
+        <v>0.06111857673102275</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>74.26262626262626</v>
+        <v>52.2030303030303</v>
       </c>
       <c r="B16">
-        <v>0.04620058946241919</v>
+        <v>0.05736374168613149</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>79.22424242424242</v>
+        <v>55.58181818181819</v>
       </c>
       <c r="B17">
-        <v>0.04349954728063713</v>
+        <v>0.05405417411447415</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>84.18585858585858</v>
+        <v>58.96060606060606</v>
       </c>
       <c r="B18">
-        <v>0.04110661597844825</v>
+        <v>0.05111454534972518</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>89.14747474747475</v>
+        <v>62.33939393939394</v>
       </c>
       <c r="B19">
-        <v>0.03897142601586922</v>
+        <v>0.0484856678716831</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>94.10909090909091</v>
+        <v>65.71818181818182</v>
       </c>
       <c r="B20">
-        <v>0.03705406799320808</v>
+        <v>0.04612038362129586</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>99.07070707070707</v>
+        <v>69.09696969696971</v>
       </c>
       <c r="B21">
-        <v>0.03532250455840226</v>
+        <v>0.04398064975636115</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>104.0323232323232</v>
+        <v>72.47575757575758</v>
       </c>
       <c r="B22">
-        <v>0.03375071573494694</v>
+        <v>0.04203543349690217</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>108.9939393939394</v>
+        <v>75.85454545454546</v>
       </c>
       <c r="B23">
-        <v>0.03231734586368994</v>
+        <v>0.04025916536229642</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>113.9555555555555</v>
+        <v>79.23333333333335</v>
       </c>
       <c r="B24">
-        <v>0.03100470053197421</v>
+        <v>0.0386305851690889</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>118.9171717171717</v>
+        <v>82.61212121212122</v>
       </c>
       <c r="B25">
-        <v>0.0297979921181669</v>
+        <v>0.03713186905886506</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>123.8787878787879</v>
+        <v>85.9909090909091</v>
       </c>
       <c r="B26">
-        <v>0.02868476483013806</v>
+        <v>0.03574796075508859</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>128.8404040404041</v>
+        <v>89.36969696969697</v>
       </c>
       <c r="B27">
-        <v>0.02765445125844361</v>
+        <v>0.03446605334880411</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>133.8020202020202</v>
+        <v>92.74848484848485</v>
       </c>
       <c r="B28">
-        <v>0.02669802659540598</v>
+        <v>0.03327518347648203</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>138.7636363636364</v>
+        <v>96.12727272727274</v>
       </c>
       <c r="B29">
-        <v>0.02580773628320412</v>
+        <v>0.03216591041717451</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>143.7252525252525</v>
+        <v>99.50606060606061</v>
       </c>
       <c r="B30">
-        <v>0.02497687949863043</v>
+        <v>0.03113006005706683</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>148.6868686868687</v>
+        <v>102.8848484848485</v>
       </c>
       <c r="B31">
-        <v>0.02419963554396714</v>
+        <v>0.03016051890784841</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>153.6484848484849</v>
+        <v>106.2636363636364</v>
       </c>
       <c r="B32">
-        <v>0.02347092352911663</v>
+        <v>0.02925106711204735</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>158.610101010101</v>
+        <v>109.6424242424243</v>
       </c>
       <c r="B33">
-        <v>0.02278628811836855</v>
+        <v>0.02839624208121811</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>163.5717171717172</v>
+        <v>113.0212121212121</v>
       </c>
       <c r="B34">
-        <v>0.02214180585570508</v>
+        <v>0.02759122639938759</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>168.5333333333333</v>
+        <v>116.4</v>
       </c>
       <c r="B35">
-        <v>0.02153400786491867</v>
+        <v>0.02683175509432052</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>173.4949494949495</v>
+        <v>119.7787878787879</v>
       </c>
       <c r="B36">
-        <v>0.02095981567530501</v>
+        <v>0.02611403847796769</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>178.4565656565657</v>
+        <v>123.1575757575758</v>
       </c>
       <c r="B37">
-        <v>0.02041648764092429</v>
+        <v>0.0254346975863321</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>183.4181818181818</v>
+        <v>126.5363636363636</v>
       </c>
       <c r="B38">
-        <v>0.01990157396520017</v>
+        <v>0.02479070987968223</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>188.379797979798</v>
+        <v>129.9151515151515</v>
       </c>
       <c r="B39">
-        <v>0.01941287875836224</v>
+        <v>0.02417936334786408</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>193.3414141414142</v>
+        <v>133.2939393939394</v>
       </c>
       <c r="B40">
-        <v>0.01894842787559876</v>
+        <v>0.02359821753947685</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>198.3030303030303</v>
+        <v>136.6727272727273</v>
       </c>
       <c r="B41">
-        <v>0.01850644153249176</v>
+        <v>0.02304507032490236</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>203.2646464646465</v>
+        <v>140.0515151515152</v>
       </c>
       <c r="B42">
-        <v>0.01808531088874405</v>
+        <v>0.02251792943149735</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>208.2262626262626</v>
+        <v>143.430303030303</v>
       </c>
       <c r="B43">
-        <v>0.01768357794422913</v>
+        <v>0.02201498796942169</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>213.1878787878788</v>
+        <v>146.8090909090909</v>
       </c>
       <c r="B44">
-        <v>0.01729991821258228</v>
+        <v>0.02153460330961525</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>218.149494949495</v>
+        <v>150.1878787878788</v>
       </c>
       <c r="B45">
-        <v>0.01693312573410098</v>
+        <v>0.02107527878966524</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>223.1111111111111</v>
+        <v>153.5666666666667</v>
       </c>
       <c r="B46">
-        <v>0.01658210006707991</v>
+        <v>0.02063564781503395</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>228.0727272727273</v>
+        <v>156.9454545454546</v>
       </c>
       <c r="B47">
-        <v>0.01624583495902135</v>
+        <v>0.02021445999716518</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>233.0343434343434</v>
+        <v>160.3242424242424</v>
       </c>
       <c r="B48">
-        <v>0.01592340844961805</v>
+        <v>0.0198105690300645</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>237.9959595959596</v>
+        <v>163.7030303030303</v>
       </c>
       <c r="B49">
-        <v>0.01561397419846001</v>
+        <v>0.01942292205592545</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>242.9575757575758</v>
+        <v>167.0818181818182</v>
       </c>
       <c r="B50">
-        <v>0.01531675386397739</v>
+        <v>0.01905055031048268</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>247.9191919191919</v>
+        <v>170.4606060606061</v>
       </c>
       <c r="B51">
-        <v>0.01503103038768949</v>
+        <v>0.01869256087176563</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>252.8808080808081</v>
+        <v>173.8393939393939</v>
       </c>
       <c r="B52">
-        <v>0.01475614206055503</v>
+        <v>0.01834812936317774</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>257.8424242424242</v>
+        <v>177.2181818181818</v>
       </c>
       <c r="B53">
-        <v>0.01449147726703538</v>
+        <v>0.01801649348442664</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>262.8040404040404</v>
+        <v>180.5969696969697</v>
       </c>
       <c r="B54">
-        <v>0.01423646981812463</v>
+        <v>0.01769694726264558</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>267.7656565656566</v>
+        <v>183.9757575757576</v>
       </c>
       <c r="B55">
-        <v>0.0139905947976513</v>
+        <v>0.01738883593176847</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>272.7272727272727</v>
+        <v>187.3545454545455</v>
       </c>
       <c r="B56">
-        <v>0.0137533648570862</v>
+        <v>0.01709155136140432</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>277.6888888888889</v>
+        <v>190.7333333333333</v>
       </c>
       <c r="B57">
-        <v>0.01352432690327473</v>
+        <v>0.01680452796754974</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>282.650505050505</v>
+        <v>194.1121212121212</v>
       </c>
       <c r="B58">
-        <v>0.01330305913125553</v>
+        <v>0.0165272390468431</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>287.6121212121212</v>
+        <v>197.4909090909091</v>
       </c>
       <c r="B59">
-        <v>0.01308916836087662</v>
+        <v>0.01625919348399371</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>292.5737373737374</v>
+        <v>200.869696969697</v>
       </c>
       <c r="B60">
-        <v>0.01288228764147714</v>
+        <v>0.01599993278875608</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>297.5353535353535</v>
+        <v>204.2484848484848</v>
       </c>
       <c r="B61">
-        <v>0.01268207409363181</v>
+        <v>0.01574902842455767</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>302.4969696969697</v>
+        <v>207.6272727272728</v>
       </c>
       <c r="B62">
-        <v>0.0124882069609904</v>
+        <v>0.01550607939579167</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>307.4585858585859</v>
+        <v>211.0060606060606</v>
       </c>
       <c r="B63">
-        <v>0.01230038584869856</v>
+        <v>0.01527071006498598</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>312.4202020202021</v>
+        <v>214.3848484848485</v>
       </c>
       <c r="B64">
-        <v>0.01211832912784966</v>
+        <v>0.0150425681746673</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>317.3818181818182</v>
+        <v>217.7636363636364</v>
       </c>
       <c r="B65">
-        <v>0.01194177248796671</v>
+        <v>0.01482132305184568</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>322.3434343434344</v>
+        <v>221.1424242424243</v>
       </c>
       <c r="B66">
-        <v>0.01177046762171235</v>
+        <v>0.01460666397572636</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>327.3050505050505</v>
+        <v>224.5212121212121</v>
       </c>
       <c r="B67">
-        <v>0.01160418102792583</v>
+        <v>0.01439829869157622</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>332.2666666666667</v>
+        <v>227.9</v>
       </c>
       <c r="B68">
-        <v>0.01144269292073312</v>
+        <v>0.01419595205568452</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>337.2282828282828</v>
+        <v>231.2787878787879</v>
       </c>
       <c r="B69">
-        <v>0.01128579623390697</v>
+        <v>0.01399936479810706</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>342.189898989899</v>
+        <v>234.6575757575758</v>
       </c>
       <c r="B70">
-        <v>0.01113329571089922</v>
+        <v>0.01380829239140649</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>347.1515151515152</v>
+        <v>238.0363636363637</v>
       </c>
       <c r="B71">
-        <v>0.01098500707205367</v>
+        <v>0.01362250401493192</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>352.1131313131313</v>
+        <v>241.4151515151515</v>
       </c>
       <c r="B72">
-        <v>0.01084075625145765</v>
+        <v>0.01344178160534442</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>357.0747474747475</v>
+        <v>244.7939393939394</v>
       </c>
       <c r="B73">
-        <v>0.01070037869672178</v>
+        <v>0.01326591898511502</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>362.0363636363637</v>
+        <v>248.1727272727273</v>
       </c>
       <c r="B74">
-        <v>0.01056371872570723</v>
+        <v>0.013094721061617</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>366.9979797979798</v>
+        <v>251.5515151515152</v>
       </c>
       <c r="B75">
-        <v>0.0104306289348615</v>
+        <v>0.01292800309022271</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>371.959595959596</v>
+        <v>254.930303030303</v>
       </c>
       <c r="B76">
-        <v>0.0103009696543887</v>
+        <v>0.01276558999550886</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>376.9212121212121</v>
+        <v>258.3090909090909</v>
       </c>
       <c r="B77">
-        <v>0.01017460844597923</v>
+        <v>0.01260731574528809</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>381.8828282828283</v>
+        <v>261.6878787878788</v>
       </c>
       <c r="B78">
-        <v>0.01005141963926408</v>
+        <v>0.01245302277272614</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>386.8444444444444</v>
+        <v>265.0666666666667</v>
       </c>
       <c r="B79">
-        <v>0.009931283903549807</v>
+        <v>0.01230256144228506</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>391.8060606060606</v>
+        <v>268.4454545454545</v>
       </c>
       <c r="B80">
-        <v>0.009814087851735777</v>
+        <v>0.01215578955565855</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>396.7676767676768</v>
+        <v>271.8242424242424</v>
       </c>
       <c r="B81">
-        <v>0.009699723673623097</v>
+        <v>0.01201257189424466</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82">
-        <v>401.729292929293</v>
+        <v>275.2030303030303</v>
       </c>
       <c r="B82">
-        <v>0.009588088796097901</v>
+        <v>0.01187277979503844</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83">
-        <v>406.6909090909091</v>
+        <v>278.5818181818182</v>
       </c>
       <c r="B83">
-        <v>0.009479085567915465</v>
+        <v>0.01173629075712732</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84">
-        <v>411.6525252525253</v>
+        <v>281.960606060606</v>
       </c>
       <c r="B84">
-        <v>0.009372620967029011</v>
+        <v>0.0116029880762408</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85">
-        <v>416.6141414141414</v>
+        <v>285.3393939393939</v>
       </c>
       <c r="B85">
-        <v>0.009268606328601416</v>
+        <v>0.01147276050504557</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86">
-        <v>421.5757575757576</v>
+        <v>288.7181818181818</v>
       </c>
       <c r="B86">
-        <v>0.009166957092011792</v>
+        <v>0.01134550193709238</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87">
-        <v>426.5373737373737</v>
+        <v>292.0969696969697</v>
       </c>
       <c r="B87">
-        <v>0.009067592565324854</v>
+        <v>0.01122111111251317</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88">
-        <v>431.4989898989899</v>
+        <v>295.4757575757575</v>
       </c>
       <c r="B88">
-        <v>0.008970435705830657</v>
+        <v>0.01109949134373992</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89">
-        <v>436.4606060606061</v>
+        <v>298.8545454545454</v>
       </c>
       <c r="B89">
-        <v>0.00887541291538794</v>
+        <v>0.01098055025967232</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90">
-        <v>441.4222222222222</v>
+        <v>302.2333333333333</v>
       </c>
       <c r="B90">
-        <v>0.008782453849417272</v>
+        <v>0.01086419956686064</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91">
-        <v>446.3838383838384</v>
+        <v>305.6121212121212</v>
       </c>
       <c r="B91">
-        <v>0.008691491238491958</v>
+        <v>0.01075035482639666</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92">
-        <v>451.3454545454546</v>
+        <v>308.9909090909091</v>
       </c>
       <c r="B92">
-        <v>0.00860246072156641</v>
+        <v>0.01063893524531896</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93">
-        <v>456.3070707070707</v>
+        <v>312.369696969697</v>
       </c>
       <c r="B93">
-        <v>0.008515300689964578</v>
+        <v>0.01052986348144133</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94">
-        <v>461.2686868686869</v>
+        <v>315.7484848484848</v>
       </c>
       <c r="B94">
-        <v>0.008429952141325862</v>
+        <v>0.01042306546060632</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95">
-        <v>466.230303030303</v>
+        <v>319.1272727272727</v>
       </c>
       <c r="B95">
-        <v>0.008346358542773744</v>
+        <v>0.01031847020544955</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96">
-        <v>471.1919191919192</v>
+        <v>322.5060606060606</v>
       </c>
       <c r="B96">
-        <v>0.008264465702633741</v>
+        <v>0.01021600967483671</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97">
-        <v>476.1535353535353</v>
+        <v>325.8848484848485</v>
       </c>
       <c r="B97">
-        <v>0.00818422165008296</v>
+        <v>0.01011561861320442</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98">
-        <v>481.1151515151515</v>
+        <v>329.2636363636364</v>
       </c>
       <c r="B98">
-        <v>0.008105576522164084</v>
+        <v>0.01001723440909843</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99">
-        <v>486.0767676767677</v>
+        <v>332.6424242424242</v>
       </c>
       <c r="B99">
-        <v>0.008028482457642554</v>
+        <v>0.009920796962260125</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100">
-        <v>491.0383838383838</v>
+        <v>336.0212121212121</v>
       </c>
       <c r="B100">
-        <v>0.00795289349722748</v>
+        <v>0.009826248558663993</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101">
-        <v>496</v>
+        <v>339.4</v>
       </c>
       <c r="B101">
-        <v>0.007878765489714909</v>
+        <v>0.009733533752955834</v>
       </c>
     </row>
   </sheetData>
@@ -2905,25 +2905,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="C2">
-        <v>0.9521904571390467</v>
+        <v>0.8749603165604457</v>
       </c>
       <c r="D2">
-        <v>0.590404</v>
+        <v>0.54381</v>
       </c>
       <c r="E2">
-        <v>0.1001237670996363</v>
+        <v>0.08774793272651941</v>
       </c>
       <c r="F2">
-        <v>0.6812412373755872</v>
+        <v>0.6901960800285137</v>
       </c>
       <c r="G2">
-        <v>-0.2288507088204435</v>
+        <v>-0.2645528105313652</v>
       </c>
       <c r="H2">
-        <v>-0.1513986946015146</v>
+        <v>-0.1883687288611057</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2931,25 +2931,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>19.6</v>
+        <v>15.1</v>
       </c>
       <c r="C3">
-        <v>3.584534682338684</v>
+        <v>1.494062322067665</v>
       </c>
       <c r="D3">
-        <v>0.170902</v>
+        <v>0.160176</v>
       </c>
       <c r="E3">
-        <v>0.04535361869183588</v>
+        <v>0.02307557738292924</v>
       </c>
       <c r="F3">
-        <v>1.292256071356476</v>
+        <v>1.178976947293169</v>
       </c>
       <c r="G3">
-        <v>-0.7672528548691906</v>
+        <v>-0.79540255596962</v>
       </c>
       <c r="H3">
-        <v>-0.8081813728620506</v>
+        <v>-0.7028767673401117</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2957,25 +2957,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>33</v>
+        <v>38.7</v>
       </c>
       <c r="C4">
-        <v>6.189597007165418</v>
+        <v>7.03964961249256</v>
       </c>
       <c r="D4">
-        <v>0.103301</v>
+        <v>0.096871</v>
       </c>
       <c r="E4">
-        <v>0.02878502382412694</v>
+        <v>0.02955341012284182</v>
       </c>
       <c r="F4">
-        <v>1.518513939877888</v>
+        <v>1.587710965018911</v>
       </c>
       <c r="G4">
-        <v>-0.9858954742947084</v>
+        <v>-1.013806217015109</v>
       </c>
       <c r="H4">
-        <v>-1.05138700487075</v>
+        <v>-1.13312465919519</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2983,25 +2983,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>71.7</v>
+        <v>55.9</v>
       </c>
       <c r="C5">
-        <v>11.16248677988517</v>
+        <v>10.85505514597794</v>
       </c>
       <c r="D5">
-        <v>0.03901</v>
+        <v>0.077846</v>
       </c>
       <c r="E5">
-        <v>0.006590887986033781</v>
+        <v>0.03040207913942729</v>
       </c>
       <c r="F5">
-        <v>1.8555191556678</v>
+        <v>1.747411807886423</v>
       </c>
       <c r="G5">
-        <v>-1.408824049688209</v>
+        <v>-1.108763698093395</v>
       </c>
       <c r="H5">
-        <v>-1.4136354739827</v>
+        <v>-1.301231418093175</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3009,25 +3009,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>114.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="C6">
-        <v>13.48974919460452</v>
+        <v>14.12755384975678</v>
       </c>
       <c r="D6">
-        <v>0.02455</v>
+        <v>0.039588</v>
       </c>
       <c r="E6">
-        <v>0.005725250503980881</v>
+        <v>0.007898477462284881</v>
       </c>
       <c r="F6">
-        <v>2.057666103909829</v>
+        <v>1.8926510338773</v>
       </c>
       <c r="G6">
-        <v>-1.609948503541013</v>
+        <v>-1.402436438407031</v>
       </c>
       <c r="H6">
-        <v>-1.630924165983173</v>
+        <v>-1.454115367280804</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3035,25 +3035,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>152.9</v>
+        <v>167.1</v>
       </c>
       <c r="C7">
-        <v>18.38081729533386</v>
+        <v>13.01405223424109</v>
       </c>
       <c r="D7">
-        <v>0.018458</v>
+        <v>0.013829</v>
       </c>
       <c r="E7">
-        <v>0.003957827911592137</v>
+        <v>0.0009057574485233646</v>
       </c>
       <c r="F7">
-        <v>2.18440748541232</v>
+        <v>2.222976449893391</v>
       </c>
       <c r="G7">
-        <v>-1.733815358349094</v>
+        <v>-1.859209223374698</v>
       </c>
       <c r="H7">
-        <v>-1.76715906464727</v>
+        <v>-1.801827590153425</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -3061,25 +3061,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>185.7</v>
+        <v>215.3</v>
       </c>
       <c r="C8">
-        <v>24.28627870492582</v>
+        <v>14.01590366532089</v>
       </c>
       <c r="D8">
-        <v>0.014253</v>
+        <v>0.010871</v>
       </c>
       <c r="E8">
-        <v>0.002260750145907819</v>
+        <v>0.0007843078335563005</v>
       </c>
       <c r="F8">
-        <v>2.26881190373978</v>
+        <v>2.333044029823487</v>
       </c>
       <c r="G8">
-        <v>-1.846093714861132</v>
+        <v>-1.963730504257185</v>
       </c>
       <c r="H8">
-        <v>-1.857885765282276</v>
+        <v>-1.917688619998731</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3087,25 +3087,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>261.5</v>
+        <v>276.4</v>
       </c>
       <c r="C9">
-        <v>18.55936421324825</v>
+        <v>24.80913810137976</v>
       </c>
       <c r="D9">
-        <v>0.008937</v>
+        <v>0.008915000000000001</v>
       </c>
       <c r="E9">
-        <v>0.0006362669775076077</v>
+        <v>0.001054587070321312</v>
       </c>
       <c r="F9">
-        <v>2.417471693203293</v>
+        <v>2.441538038702161</v>
       </c>
       <c r="G9">
-        <v>-2.048808242065294</v>
+        <v>-2.049878652488626</v>
       </c>
       <c r="H9">
-        <v>-2.017680862297134</v>
+        <v>-2.031893253267785</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -3113,25 +3113,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>278</v>
+        <v>339.4</v>
       </c>
       <c r="C10">
-        <v>21.19224176700311</v>
+        <v>27.14496065366256</v>
       </c>
       <c r="D10">
-        <v>0.008409</v>
+        <v>0.007071000000000001</v>
       </c>
       <c r="E10">
-        <v>0.0006029362413316281</v>
+        <v>0.0006898702776609526</v>
       </c>
       <c r="F10">
-        <v>2.444044795918076</v>
+        <v>2.530711837981657</v>
       </c>
       <c r="G10">
-        <v>-2.075255647520052</v>
+        <v>-2.150519162756014</v>
       </c>
       <c r="H10">
-        <v>-2.046244413622065</v>
+        <v>-2.125760750184704</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3139,25 +3139,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>382</v>
+        <v>312.8</v>
       </c>
       <c r="C11">
-        <v>23.13054738267606</v>
+        <v>30.94719516998089</v>
       </c>
       <c r="D11">
-        <v>0.006128</v>
+        <v>0.007683</v>
       </c>
       <c r="E11">
-        <v>0.0004466935315304118</v>
+        <v>0.0006173546612586461</v>
       </c>
       <c r="F11">
-        <v>2.582063362911709</v>
+        <v>2.49526674438781</v>
       </c>
       <c r="G11">
-        <v>-2.212681243375453</v>
+        <v>-2.114469166811908</v>
       </c>
       <c r="H11">
-        <v>-2.194601211261768</v>
+        <v>-2.088449990291968</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -3165,25 +3165,25 @@
         <v>638</v>
       </c>
       <c r="B12">
-        <v>496</v>
+        <v>286</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0.004589999999999999</v>
+        <v>0.00851</v>
       </c>
       <c r="E12">
-        <v>2.891205793294678E-19</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>2.695481676490198</v>
+        <v>2.456366033129043</v>
       </c>
       <c r="G12">
-        <v>-2.338187314462739</v>
+        <v>-2.070070439915412</v>
       </c>
       <c r="H12">
-        <v>-2.316515082436625</v>
+        <v>-2.047501724953364</v>
       </c>
     </row>
   </sheetData>
@@ -3206,802 +3206,802 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="B2">
-        <v>0.5924498304088603</v>
+        <v>0.5398045483159717</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>9.761616161616161</v>
+        <v>8.278787878787879</v>
       </c>
       <c r="B3">
-        <v>0.3058435010807216</v>
+        <v>0.3284083995079981</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>14.72323232323232</v>
+        <v>11.65757575757576</v>
       </c>
       <c r="B4">
-        <v>0.2085691820389627</v>
+        <v>0.2374489201543626</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>19.68484848484848</v>
+        <v>15.03636363636364</v>
       </c>
       <c r="B5">
-        <v>0.1591349376280704</v>
+        <v>0.1865666643680177</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>24.64646464646465</v>
+        <v>18.41515151515151</v>
       </c>
       <c r="B6">
-        <v>0.1290724626557771</v>
+        <v>0.1539641388384904</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>29.60808080808081</v>
+        <v>21.7939393939394</v>
       </c>
       <c r="B7">
-        <v>0.108802083286604</v>
+        <v>0.1312492966062286</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>34.56969696969697</v>
+        <v>25.17272727272727</v>
       </c>
       <c r="B8">
-        <v>0.09418100717880147</v>
+        <v>0.1144948720744534</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>39.53131313131313</v>
+        <v>28.55151515151515</v>
       </c>
       <c r="B9">
-        <v>0.08312077044674787</v>
+        <v>0.1016147002929615</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>44.49292929292929</v>
+        <v>31.93030303030303</v>
       </c>
       <c r="B10">
-        <v>0.07445246553257689</v>
+        <v>0.0913967491010062</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>49.45454545454545</v>
+        <v>35.30909090909091</v>
       </c>
       <c r="B11">
-        <v>0.06746999728410076</v>
+        <v>0.08308809485423957</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>54.41616161616162</v>
+        <v>38.68787878787879</v>
       </c>
       <c r="B12">
-        <v>0.0617212501107028</v>
+        <v>0.07619603829433115</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>59.37777777777777</v>
+        <v>42.06666666666667</v>
       </c>
       <c r="B13">
-        <v>0.05690309688298167</v>
+        <v>0.07038445451469259</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>64.33939393939394</v>
+        <v>45.44545454545455</v>
       </c>
       <c r="B14">
-        <v>0.05280457456085561</v>
+        <v>0.06541607560131416</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>69.30101010101009</v>
+        <v>48.82424242424242</v>
       </c>
       <c r="B15">
-        <v>0.04927425686139162</v>
+        <v>0.06111857673102275</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>74.26262626262626</v>
+        <v>52.2030303030303</v>
       </c>
       <c r="B16">
-        <v>0.04620058946241919</v>
+        <v>0.05736374168613149</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>79.22424242424242</v>
+        <v>55.58181818181819</v>
       </c>
       <c r="B17">
-        <v>0.04349954728063713</v>
+        <v>0.05405417411447415</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>84.18585858585858</v>
+        <v>58.96060606060606</v>
       </c>
       <c r="B18">
-        <v>0.04110661597844825</v>
+        <v>0.05111454534972518</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>89.14747474747475</v>
+        <v>62.33939393939394</v>
       </c>
       <c r="B19">
-        <v>0.03897142601586922</v>
+        <v>0.0484856678716831</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>94.10909090909091</v>
+        <v>65.71818181818182</v>
       </c>
       <c r="B20">
-        <v>0.03705406799320808</v>
+        <v>0.04612038362129586</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>99.07070707070707</v>
+        <v>69.09696969696971</v>
       </c>
       <c r="B21">
-        <v>0.03532250455840226</v>
+        <v>0.04398064975636115</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>104.0323232323232</v>
+        <v>72.47575757575758</v>
       </c>
       <c r="B22">
-        <v>0.03375071573494694</v>
+        <v>0.04203543349690217</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>108.9939393939394</v>
+        <v>75.85454545454546</v>
       </c>
       <c r="B23">
-        <v>0.03231734586368994</v>
+        <v>0.04025916536229642</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>113.9555555555555</v>
+        <v>79.23333333333335</v>
       </c>
       <c r="B24">
-        <v>0.03100470053197421</v>
+        <v>0.0386305851690889</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>118.9171717171717</v>
+        <v>82.61212121212122</v>
       </c>
       <c r="B25">
-        <v>0.0297979921181669</v>
+        <v>0.03713186905886506</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>123.8787878787879</v>
+        <v>85.9909090909091</v>
       </c>
       <c r="B26">
-        <v>0.02868476483013806</v>
+        <v>0.03574796075508859</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>128.8404040404041</v>
+        <v>89.36969696969697</v>
       </c>
       <c r="B27">
-        <v>0.02765445125844361</v>
+        <v>0.03446605334880411</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>133.8020202020202</v>
+        <v>92.74848484848485</v>
       </c>
       <c r="B28">
-        <v>0.02669802659540598</v>
+        <v>0.03327518347648203</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>138.7636363636364</v>
+        <v>96.12727272727274</v>
       </c>
       <c r="B29">
-        <v>0.02580773628320412</v>
+        <v>0.03216591041717451</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>143.7252525252525</v>
+        <v>99.50606060606061</v>
       </c>
       <c r="B30">
-        <v>0.02497687949863043</v>
+        <v>0.03113006005706683</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>148.6868686868687</v>
+        <v>102.8848484848485</v>
       </c>
       <c r="B31">
-        <v>0.02419963554396714</v>
+        <v>0.03016051890784841</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>153.6484848484849</v>
+        <v>106.2636363636364</v>
       </c>
       <c r="B32">
-        <v>0.02347092352911663</v>
+        <v>0.02925106711204735</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>158.610101010101</v>
+        <v>109.6424242424243</v>
       </c>
       <c r="B33">
-        <v>0.02278628811836855</v>
+        <v>0.02839624208121811</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>163.5717171717172</v>
+        <v>113.0212121212121</v>
       </c>
       <c r="B34">
-        <v>0.02214180585570508</v>
+        <v>0.02759122639938759</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>168.5333333333333</v>
+        <v>116.4</v>
       </c>
       <c r="B35">
-        <v>0.02153400786491867</v>
+        <v>0.02683175509432052</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>173.4949494949495</v>
+        <v>119.7787878787879</v>
       </c>
       <c r="B36">
-        <v>0.02095981567530501</v>
+        <v>0.02611403847796769</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>178.4565656565657</v>
+        <v>123.1575757575758</v>
       </c>
       <c r="B37">
-        <v>0.02041648764092429</v>
+        <v>0.0254346975863321</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>183.4181818181818</v>
+        <v>126.5363636363636</v>
       </c>
       <c r="B38">
-        <v>0.01990157396520017</v>
+        <v>0.02479070987968223</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>188.379797979798</v>
+        <v>129.9151515151515</v>
       </c>
       <c r="B39">
-        <v>0.01941287875836224</v>
+        <v>0.02417936334786408</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>193.3414141414142</v>
+        <v>133.2939393939394</v>
       </c>
       <c r="B40">
-        <v>0.01894842787559876</v>
+        <v>0.02359821753947685</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>198.3030303030303</v>
+        <v>136.6727272727273</v>
       </c>
       <c r="B41">
-        <v>0.01850644153249176</v>
+        <v>0.02304507032490236</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>203.2646464646465</v>
+        <v>140.0515151515152</v>
       </c>
       <c r="B42">
-        <v>0.01808531088874405</v>
+        <v>0.02251792943149735</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>208.2262626262626</v>
+        <v>143.430303030303</v>
       </c>
       <c r="B43">
-        <v>0.01768357794422913</v>
+        <v>0.02201498796942169</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>213.1878787878788</v>
+        <v>146.8090909090909</v>
       </c>
       <c r="B44">
-        <v>0.01729991821258228</v>
+        <v>0.02153460330961525</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>218.149494949495</v>
+        <v>150.1878787878788</v>
       </c>
       <c r="B45">
-        <v>0.01693312573410098</v>
+        <v>0.02107527878966524</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>223.1111111111111</v>
+        <v>153.5666666666667</v>
       </c>
       <c r="B46">
-        <v>0.01658210006707991</v>
+        <v>0.02063564781503395</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>228.0727272727273</v>
+        <v>156.9454545454546</v>
       </c>
       <c r="B47">
-        <v>0.01624583495902135</v>
+        <v>0.02021445999716518</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>233.0343434343434</v>
+        <v>160.3242424242424</v>
       </c>
       <c r="B48">
-        <v>0.01592340844961805</v>
+        <v>0.0198105690300645</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>237.9959595959596</v>
+        <v>163.7030303030303</v>
       </c>
       <c r="B49">
-        <v>0.01561397419846001</v>
+        <v>0.01942292205592545</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>242.9575757575758</v>
+        <v>167.0818181818182</v>
       </c>
       <c r="B50">
-        <v>0.01531675386397739</v>
+        <v>0.01905055031048268</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>247.9191919191919</v>
+        <v>170.4606060606061</v>
       </c>
       <c r="B51">
-        <v>0.01503103038768949</v>
+        <v>0.01869256087176563</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>252.8808080808081</v>
+        <v>173.8393939393939</v>
       </c>
       <c r="B52">
-        <v>0.01475614206055503</v>
+        <v>0.01834812936317774</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>257.8424242424242</v>
+        <v>177.2181818181818</v>
       </c>
       <c r="B53">
-        <v>0.01449147726703538</v>
+        <v>0.01801649348442664</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>262.8040404040404</v>
+        <v>180.5969696969697</v>
       </c>
       <c r="B54">
-        <v>0.01423646981812463</v>
+        <v>0.01769694726264558</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>267.7656565656566</v>
+        <v>183.9757575757576</v>
       </c>
       <c r="B55">
-        <v>0.0139905947976513</v>
+        <v>0.01738883593176847</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>272.7272727272727</v>
+        <v>187.3545454545455</v>
       </c>
       <c r="B56">
-        <v>0.0137533648570862</v>
+        <v>0.01709155136140432</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>277.6888888888889</v>
+        <v>190.7333333333333</v>
       </c>
       <c r="B57">
-        <v>0.01352432690327473</v>
+        <v>0.01680452796754974</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>282.650505050505</v>
+        <v>194.1121212121212</v>
       </c>
       <c r="B58">
-        <v>0.01330305913125553</v>
+        <v>0.0165272390468431</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>287.6121212121212</v>
+        <v>197.4909090909091</v>
       </c>
       <c r="B59">
-        <v>0.01308916836087662</v>
+        <v>0.01625919348399371</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>292.5737373737374</v>
+        <v>200.869696969697</v>
       </c>
       <c r="B60">
-        <v>0.01288228764147714</v>
+        <v>0.01599993278875608</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>297.5353535353535</v>
+        <v>204.2484848484848</v>
       </c>
       <c r="B61">
-        <v>0.01268207409363181</v>
+        <v>0.01574902842455767</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>302.4969696969697</v>
+        <v>207.6272727272728</v>
       </c>
       <c r="B62">
-        <v>0.0124882069609904</v>
+        <v>0.01550607939579167</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>307.4585858585859</v>
+        <v>211.0060606060606</v>
       </c>
       <c r="B63">
-        <v>0.01230038584869856</v>
+        <v>0.01527071006498598</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>312.4202020202021</v>
+        <v>214.3848484848485</v>
       </c>
       <c r="B64">
-        <v>0.01211832912784966</v>
+        <v>0.0150425681746673</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>317.3818181818182</v>
+        <v>217.7636363636364</v>
       </c>
       <c r="B65">
-        <v>0.01194177248796671</v>
+        <v>0.01482132305184568</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>322.3434343434344</v>
+        <v>221.1424242424243</v>
       </c>
       <c r="B66">
-        <v>0.01177046762171235</v>
+        <v>0.01460666397572636</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>327.3050505050505</v>
+        <v>224.5212121212121</v>
       </c>
       <c r="B67">
-        <v>0.01160418102792583</v>
+        <v>0.01439829869157622</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>332.2666666666667</v>
+        <v>227.9</v>
       </c>
       <c r="B68">
-        <v>0.01144269292073312</v>
+        <v>0.01419595205568452</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>337.2282828282828</v>
+        <v>231.2787878787879</v>
       </c>
       <c r="B69">
-        <v>0.01128579623390697</v>
+        <v>0.01399936479810706</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>342.189898989899</v>
+        <v>234.6575757575758</v>
       </c>
       <c r="B70">
-        <v>0.01113329571089922</v>
+        <v>0.01380829239140649</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>347.1515151515152</v>
+        <v>238.0363636363637</v>
       </c>
       <c r="B71">
-        <v>0.01098500707205367</v>
+        <v>0.01362250401493192</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>352.1131313131313</v>
+        <v>241.4151515151515</v>
       </c>
       <c r="B72">
-        <v>0.01084075625145765</v>
+        <v>0.01344178160534442</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>357.0747474747475</v>
+        <v>244.7939393939394</v>
       </c>
       <c r="B73">
-        <v>0.01070037869672178</v>
+        <v>0.01326591898511502</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>362.0363636363637</v>
+        <v>248.1727272727273</v>
       </c>
       <c r="B74">
-        <v>0.01056371872570723</v>
+        <v>0.013094721061617</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>366.9979797979798</v>
+        <v>251.5515151515152</v>
       </c>
       <c r="B75">
-        <v>0.0104306289348615</v>
+        <v>0.01292800309022271</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>371.959595959596</v>
+        <v>254.930303030303</v>
       </c>
       <c r="B76">
-        <v>0.0103009696543887</v>
+        <v>0.01276558999550886</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>376.9212121212121</v>
+        <v>258.3090909090909</v>
       </c>
       <c r="B77">
-        <v>0.01017460844597923</v>
+        <v>0.01260731574528809</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>381.8828282828283</v>
+        <v>261.6878787878788</v>
       </c>
       <c r="B78">
-        <v>0.01005141963926408</v>
+        <v>0.01245302277272614</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>386.8444444444444</v>
+        <v>265.0666666666667</v>
       </c>
       <c r="B79">
-        <v>0.009931283903549807</v>
+        <v>0.01230256144228506</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>391.8060606060606</v>
+        <v>268.4454545454545</v>
       </c>
       <c r="B80">
-        <v>0.009814087851735777</v>
+        <v>0.01215578955565855</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>396.7676767676768</v>
+        <v>271.8242424242424</v>
       </c>
       <c r="B81">
-        <v>0.009699723673623097</v>
+        <v>0.01201257189424466</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82">
-        <v>401.729292929293</v>
+        <v>275.2030303030303</v>
       </c>
       <c r="B82">
-        <v>0.009588088796097901</v>
+        <v>0.01187277979503844</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83">
-        <v>406.6909090909091</v>
+        <v>278.5818181818182</v>
       </c>
       <c r="B83">
-        <v>0.009479085567915465</v>
+        <v>0.01173629075712732</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84">
-        <v>411.6525252525253</v>
+        <v>281.960606060606</v>
       </c>
       <c r="B84">
-        <v>0.009372620967029011</v>
+        <v>0.0116029880762408</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85">
-        <v>416.6141414141414</v>
+        <v>285.3393939393939</v>
       </c>
       <c r="B85">
-        <v>0.009268606328601416</v>
+        <v>0.01147276050504557</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86">
-        <v>421.5757575757576</v>
+        <v>288.7181818181818</v>
       </c>
       <c r="B86">
-        <v>0.009166957092011792</v>
+        <v>0.01134550193709238</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87">
-        <v>426.5373737373737</v>
+        <v>292.0969696969697</v>
       </c>
       <c r="B87">
-        <v>0.009067592565324854</v>
+        <v>0.01122111111251317</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88">
-        <v>431.4989898989899</v>
+        <v>295.4757575757575</v>
       </c>
       <c r="B88">
-        <v>0.008970435705830657</v>
+        <v>0.01109949134373992</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89">
-        <v>436.4606060606061</v>
+        <v>298.8545454545454</v>
       </c>
       <c r="B89">
-        <v>0.00887541291538794</v>
+        <v>0.01098055025967232</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90">
-        <v>441.4222222222222</v>
+        <v>302.2333333333333</v>
       </c>
       <c r="B90">
-        <v>0.008782453849417272</v>
+        <v>0.01086419956686064</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91">
-        <v>446.3838383838384</v>
+        <v>305.6121212121212</v>
       </c>
       <c r="B91">
-        <v>0.008691491238491958</v>
+        <v>0.01075035482639666</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92">
-        <v>451.3454545454546</v>
+        <v>308.9909090909091</v>
       </c>
       <c r="B92">
-        <v>0.00860246072156641</v>
+        <v>0.01063893524531896</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93">
-        <v>456.3070707070707</v>
+        <v>312.369696969697</v>
       </c>
       <c r="B93">
-        <v>0.008515300689964578</v>
+        <v>0.01052986348144133</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94">
-        <v>461.2686868686869</v>
+        <v>315.7484848484848</v>
       </c>
       <c r="B94">
-        <v>0.008429952141325862</v>
+        <v>0.01042306546060632</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95">
-        <v>466.230303030303</v>
+        <v>319.1272727272727</v>
       </c>
       <c r="B95">
-        <v>0.008346358542773744</v>
+        <v>0.01031847020544955</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96">
-        <v>471.1919191919192</v>
+        <v>322.5060606060606</v>
       </c>
       <c r="B96">
-        <v>0.008264465702633741</v>
+        <v>0.01021600967483671</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97">
-        <v>476.1535353535353</v>
+        <v>325.8848484848485</v>
       </c>
       <c r="B97">
-        <v>0.00818422165008296</v>
+        <v>0.01011561861320442</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98">
-        <v>481.1151515151515</v>
+        <v>329.2636363636364</v>
       </c>
       <c r="B98">
-        <v>0.008105576522164084</v>
+        <v>0.01001723440909843</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99">
-        <v>486.0767676767677</v>
+        <v>332.6424242424242</v>
       </c>
       <c r="B99">
-        <v>0.008028482457642554</v>
+        <v>0.009920796962260125</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100">
-        <v>491.0383838383838</v>
+        <v>336.0212121212121</v>
       </c>
       <c r="B100">
-        <v>0.00795289349722748</v>
+        <v>0.009826248558663993</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101">
-        <v>496</v>
+        <v>339.4</v>
       </c>
       <c r="B101">
-        <v>0.007878765489714909</v>
+        <v>0.009733533752955834</v>
       </c>
     </row>
   </sheetData>
@@ -4045,25 +4045,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="C2">
-        <v>0.9521904571390467</v>
+        <v>0.8749603165604457</v>
       </c>
       <c r="D2">
-        <v>0.590404</v>
+        <v>0.54381</v>
       </c>
       <c r="E2">
-        <v>0.1001237670996363</v>
+        <v>0.08774793272651941</v>
       </c>
       <c r="F2">
-        <v>0.6812412373755872</v>
+        <v>0.6901960800285137</v>
       </c>
       <c r="G2">
-        <v>-0.2288507088204435</v>
+        <v>-0.2645528105313652</v>
       </c>
       <c r="H2">
-        <v>-0.1513986946015146</v>
+        <v>-0.1883687288611057</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4071,25 +4071,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>19.6</v>
+        <v>15.1</v>
       </c>
       <c r="C3">
-        <v>3.584534682338684</v>
+        <v>1.494062322067665</v>
       </c>
       <c r="D3">
-        <v>0.170902</v>
+        <v>0.160176</v>
       </c>
       <c r="E3">
-        <v>0.04535361869183588</v>
+        <v>0.02307557738292924</v>
       </c>
       <c r="F3">
-        <v>1.292256071356476</v>
+        <v>1.178976947293169</v>
       </c>
       <c r="G3">
-        <v>-0.7672528548691906</v>
+        <v>-0.79540255596962</v>
       </c>
       <c r="H3">
-        <v>-0.8081813728620506</v>
+        <v>-0.7028767673401117</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4097,25 +4097,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>33</v>
+        <v>38.7</v>
       </c>
       <c r="C4">
-        <v>6.189597007165418</v>
+        <v>7.03964961249256</v>
       </c>
       <c r="D4">
-        <v>0.103301</v>
+        <v>0.096871</v>
       </c>
       <c r="E4">
-        <v>0.02878502382412694</v>
+        <v>0.02955341012284182</v>
       </c>
       <c r="F4">
-        <v>1.518513939877888</v>
+        <v>1.587710965018911</v>
       </c>
       <c r="G4">
-        <v>-0.9858954742947084</v>
+        <v>-1.013806217015109</v>
       </c>
       <c r="H4">
-        <v>-1.05138700487075</v>
+        <v>-1.13312465919519</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4123,25 +4123,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>71.7</v>
+        <v>55.9</v>
       </c>
       <c r="C5">
-        <v>11.16248677988517</v>
+        <v>10.85505514597794</v>
       </c>
       <c r="D5">
-        <v>0.03901</v>
+        <v>0.077846</v>
       </c>
       <c r="E5">
-        <v>0.006590887986033781</v>
+        <v>0.03040207913942729</v>
       </c>
       <c r="F5">
-        <v>1.8555191556678</v>
+        <v>1.747411807886423</v>
       </c>
       <c r="G5">
-        <v>-1.408824049688209</v>
+        <v>-1.108763698093395</v>
       </c>
       <c r="H5">
-        <v>-1.4136354739827</v>
+        <v>-1.301231418093175</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -4149,25 +4149,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>114.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="C6">
-        <v>13.48974919460452</v>
+        <v>14.12755384975678</v>
       </c>
       <c r="D6">
-        <v>0.02455</v>
+        <v>0.039588</v>
       </c>
       <c r="E6">
-        <v>0.005725250503980881</v>
+        <v>0.007898477462284881</v>
       </c>
       <c r="F6">
-        <v>2.057666103909829</v>
+        <v>1.8926510338773</v>
       </c>
       <c r="G6">
-        <v>-1.609948503541013</v>
+        <v>-1.402436438407031</v>
       </c>
       <c r="H6">
-        <v>-1.630924165983173</v>
+        <v>-1.454115367280804</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4175,25 +4175,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>152.9</v>
+        <v>167.1</v>
       </c>
       <c r="C7">
-        <v>18.38081729533386</v>
+        <v>13.01405223424109</v>
       </c>
       <c r="D7">
-        <v>0.018458</v>
+        <v>0.013829</v>
       </c>
       <c r="E7">
-        <v>0.003957827911592137</v>
+        <v>0.0009057574485233646</v>
       </c>
       <c r="F7">
-        <v>2.18440748541232</v>
+        <v>2.222976449893391</v>
       </c>
       <c r="G7">
-        <v>-1.733815358349094</v>
+        <v>-1.859209223374698</v>
       </c>
       <c r="H7">
-        <v>-1.76715906464727</v>
+        <v>-1.801827590153425</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -4201,25 +4201,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>185.7</v>
+        <v>215.3</v>
       </c>
       <c r="C8">
-        <v>24.28627870492582</v>
+        <v>14.01590366532089</v>
       </c>
       <c r="D8">
-        <v>0.014253</v>
+        <v>0.010871</v>
       </c>
       <c r="E8">
-        <v>0.002260750145907819</v>
+        <v>0.0007843078335563005</v>
       </c>
       <c r="F8">
-        <v>2.26881190373978</v>
+        <v>2.333044029823487</v>
       </c>
       <c r="G8">
-        <v>-1.846093714861132</v>
+        <v>-1.963730504257185</v>
       </c>
       <c r="H8">
-        <v>-1.857885765282276</v>
+        <v>-1.917688619998731</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -4227,25 +4227,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>261.5</v>
+        <v>276.4</v>
       </c>
       <c r="C9">
-        <v>18.55936421324825</v>
+        <v>24.80913810137976</v>
       </c>
       <c r="D9">
-        <v>0.008937</v>
+        <v>0.008915000000000001</v>
       </c>
       <c r="E9">
-        <v>0.0006362669775076077</v>
+        <v>0.001054587070321312</v>
       </c>
       <c r="F9">
-        <v>2.417471693203293</v>
+        <v>2.441538038702161</v>
       </c>
       <c r="G9">
-        <v>-2.048808242065294</v>
+        <v>-2.049878652488626</v>
       </c>
       <c r="H9">
-        <v>-2.017680862297134</v>
+        <v>-2.031893253267785</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -4253,25 +4253,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>278</v>
+        <v>339.4</v>
       </c>
       <c r="C10">
-        <v>21.19224176700311</v>
+        <v>27.14496065366256</v>
       </c>
       <c r="D10">
-        <v>0.008409</v>
+        <v>0.007071000000000001</v>
       </c>
       <c r="E10">
-        <v>0.0006029362413316281</v>
+        <v>0.0006898702776609526</v>
       </c>
       <c r="F10">
-        <v>2.444044795918076</v>
+        <v>2.530711837981657</v>
       </c>
       <c r="G10">
-        <v>-2.075255647520052</v>
+        <v>-2.150519162756014</v>
       </c>
       <c r="H10">
-        <v>-2.046244413622065</v>
+        <v>-2.125760750184704</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -4279,25 +4279,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>382</v>
+        <v>312.8</v>
       </c>
       <c r="C11">
-        <v>23.13054738267606</v>
+        <v>30.94719516998089</v>
       </c>
       <c r="D11">
-        <v>0.006128</v>
+        <v>0.007683</v>
       </c>
       <c r="E11">
-        <v>0.0004466935315304118</v>
+        <v>0.0006173546612586461</v>
       </c>
       <c r="F11">
-        <v>2.582063362911709</v>
+        <v>2.49526674438781</v>
       </c>
       <c r="G11">
-        <v>-2.212681243375453</v>
+        <v>-2.114469166811908</v>
       </c>
       <c r="H11">
-        <v>-2.194601211261768</v>
+        <v>-2.088449990291968</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -4305,25 +4305,25 @@
         <v>638</v>
       </c>
       <c r="B12">
-        <v>496</v>
+        <v>286</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0.004589999999999999</v>
+        <v>0.00851</v>
       </c>
       <c r="E12">
-        <v>2.891205793294678E-19</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>2.695481676490198</v>
+        <v>2.456366033129043</v>
       </c>
       <c r="G12">
-        <v>-2.338187314462739</v>
+        <v>-2.070070439915412</v>
       </c>
       <c r="H12">
-        <v>-2.316515082436625</v>
+        <v>-2.047501724953364</v>
       </c>
     </row>
   </sheetData>
@@ -4346,802 +4346,802 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="B2">
-        <v>0.5924498304088603</v>
+        <v>0.5398045483159717</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>9.761616161616161</v>
+        <v>8.278787878787879</v>
       </c>
       <c r="B3">
-        <v>0.3058435010807216</v>
+        <v>0.3284083995079981</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>14.72323232323232</v>
+        <v>11.65757575757576</v>
       </c>
       <c r="B4">
-        <v>0.2085691820389627</v>
+        <v>0.2374489201543626</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>19.68484848484848</v>
+        <v>15.03636363636364</v>
       </c>
       <c r="B5">
-        <v>0.1591349376280704</v>
+        <v>0.1865666643680177</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>24.64646464646465</v>
+        <v>18.41515151515151</v>
       </c>
       <c r="B6">
-        <v>0.1290724626557771</v>
+        <v>0.1539641388384904</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>29.60808080808081</v>
+        <v>21.7939393939394</v>
       </c>
       <c r="B7">
-        <v>0.108802083286604</v>
+        <v>0.1312492966062286</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>34.56969696969697</v>
+        <v>25.17272727272727</v>
       </c>
       <c r="B8">
-        <v>0.09418100717880147</v>
+        <v>0.1144948720744534</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>39.53131313131313</v>
+        <v>28.55151515151515</v>
       </c>
       <c r="B9">
-        <v>0.08312077044674787</v>
+        <v>0.1016147002929615</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>44.49292929292929</v>
+        <v>31.93030303030303</v>
       </c>
       <c r="B10">
-        <v>0.07445246553257689</v>
+        <v>0.0913967491010062</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>49.45454545454545</v>
+        <v>35.30909090909091</v>
       </c>
       <c r="B11">
-        <v>0.06746999728410076</v>
+        <v>0.08308809485423957</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>54.41616161616162</v>
+        <v>38.68787878787879</v>
       </c>
       <c r="B12">
-        <v>0.0617212501107028</v>
+        <v>0.07619603829433115</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>59.37777777777777</v>
+        <v>42.06666666666667</v>
       </c>
       <c r="B13">
-        <v>0.05690309688298167</v>
+        <v>0.07038445451469259</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>64.33939393939394</v>
+        <v>45.44545454545455</v>
       </c>
       <c r="B14">
-        <v>0.05280457456085561</v>
+        <v>0.06541607560131416</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>69.30101010101009</v>
+        <v>48.82424242424242</v>
       </c>
       <c r="B15">
-        <v>0.04927425686139162</v>
+        <v>0.06111857673102275</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>74.26262626262626</v>
+        <v>52.2030303030303</v>
       </c>
       <c r="B16">
-        <v>0.04620058946241919</v>
+        <v>0.05736374168613149</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>79.22424242424242</v>
+        <v>55.58181818181819</v>
       </c>
       <c r="B17">
-        <v>0.04349954728063713</v>
+        <v>0.05405417411447415</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>84.18585858585858</v>
+        <v>58.96060606060606</v>
       </c>
       <c r="B18">
-        <v>0.04110661597844825</v>
+        <v>0.05111454534972518</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>89.14747474747475</v>
+        <v>62.33939393939394</v>
       </c>
       <c r="B19">
-        <v>0.03897142601586922</v>
+        <v>0.0484856678716831</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>94.10909090909091</v>
+        <v>65.71818181818182</v>
       </c>
       <c r="B20">
-        <v>0.03705406799320808</v>
+        <v>0.04612038362129586</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>99.07070707070707</v>
+        <v>69.09696969696971</v>
       </c>
       <c r="B21">
-        <v>0.03532250455840226</v>
+        <v>0.04398064975636115</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>104.0323232323232</v>
+        <v>72.47575757575758</v>
       </c>
       <c r="B22">
-        <v>0.03375071573494694</v>
+        <v>0.04203543349690217</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>108.9939393939394</v>
+        <v>75.85454545454546</v>
       </c>
       <c r="B23">
-        <v>0.03231734586368994</v>
+        <v>0.04025916536229642</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>113.9555555555555</v>
+        <v>79.23333333333335</v>
       </c>
       <c r="B24">
-        <v>0.03100470053197421</v>
+        <v>0.0386305851690889</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>118.9171717171717</v>
+        <v>82.61212121212122</v>
       </c>
       <c r="B25">
-        <v>0.0297979921181669</v>
+        <v>0.03713186905886506</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>123.8787878787879</v>
+        <v>85.9909090909091</v>
       </c>
       <c r="B26">
-        <v>0.02868476483013806</v>
+        <v>0.03574796075508859</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>128.8404040404041</v>
+        <v>89.36969696969697</v>
       </c>
       <c r="B27">
-        <v>0.02765445125844361</v>
+        <v>0.03446605334880411</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>133.8020202020202</v>
+        <v>92.74848484848485</v>
       </c>
       <c r="B28">
-        <v>0.02669802659540598</v>
+        <v>0.03327518347648203</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>138.7636363636364</v>
+        <v>96.12727272727274</v>
       </c>
       <c r="B29">
-        <v>0.02580773628320412</v>
+        <v>0.03216591041717451</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>143.7252525252525</v>
+        <v>99.50606060606061</v>
       </c>
       <c r="B30">
-        <v>0.02497687949863043</v>
+        <v>0.03113006005706683</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>148.6868686868687</v>
+        <v>102.8848484848485</v>
       </c>
       <c r="B31">
-        <v>0.02419963554396714</v>
+        <v>0.03016051890784841</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>153.6484848484849</v>
+        <v>106.2636363636364</v>
       </c>
       <c r="B32">
-        <v>0.02347092352911663</v>
+        <v>0.02925106711204735</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>158.610101010101</v>
+        <v>109.6424242424243</v>
       </c>
       <c r="B33">
-        <v>0.02278628811836855</v>
+        <v>0.02839624208121811</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>163.5717171717172</v>
+        <v>113.0212121212121</v>
       </c>
       <c r="B34">
-        <v>0.02214180585570508</v>
+        <v>0.02759122639938759</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>168.5333333333333</v>
+        <v>116.4</v>
       </c>
       <c r="B35">
-        <v>0.02153400786491867</v>
+        <v>0.02683175509432052</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>173.4949494949495</v>
+        <v>119.7787878787879</v>
       </c>
       <c r="B36">
-        <v>0.02095981567530501</v>
+        <v>0.02611403847796769</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>178.4565656565657</v>
+        <v>123.1575757575758</v>
       </c>
       <c r="B37">
-        <v>0.02041648764092429</v>
+        <v>0.0254346975863321</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>183.4181818181818</v>
+        <v>126.5363636363636</v>
       </c>
       <c r="B38">
-        <v>0.01990157396520017</v>
+        <v>0.02479070987968223</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>188.379797979798</v>
+        <v>129.9151515151515</v>
       </c>
       <c r="B39">
-        <v>0.01941287875836224</v>
+        <v>0.02417936334786408</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>193.3414141414142</v>
+        <v>133.2939393939394</v>
       </c>
       <c r="B40">
-        <v>0.01894842787559876</v>
+        <v>0.02359821753947685</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>198.3030303030303</v>
+        <v>136.6727272727273</v>
       </c>
       <c r="B41">
-        <v>0.01850644153249176</v>
+        <v>0.02304507032490236</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>203.2646464646465</v>
+        <v>140.0515151515152</v>
       </c>
       <c r="B42">
-        <v>0.01808531088874405</v>
+        <v>0.02251792943149735</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>208.2262626262626</v>
+        <v>143.430303030303</v>
       </c>
       <c r="B43">
-        <v>0.01768357794422913</v>
+        <v>0.02201498796942169</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>213.1878787878788</v>
+        <v>146.8090909090909</v>
       </c>
       <c r="B44">
-        <v>0.01729991821258228</v>
+        <v>0.02153460330961525</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>218.149494949495</v>
+        <v>150.1878787878788</v>
       </c>
       <c r="B45">
-        <v>0.01693312573410098</v>
+        <v>0.02107527878966524</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>223.1111111111111</v>
+        <v>153.5666666666667</v>
       </c>
       <c r="B46">
-        <v>0.01658210006707991</v>
+        <v>0.02063564781503395</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>228.0727272727273</v>
+        <v>156.9454545454546</v>
       </c>
       <c r="B47">
-        <v>0.01624583495902135</v>
+        <v>0.02021445999716518</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>233.0343434343434</v>
+        <v>160.3242424242424</v>
       </c>
       <c r="B48">
-        <v>0.01592340844961805</v>
+        <v>0.0198105690300645</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>237.9959595959596</v>
+        <v>163.7030303030303</v>
       </c>
       <c r="B49">
-        <v>0.01561397419846001</v>
+        <v>0.01942292205592545</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>242.9575757575758</v>
+        <v>167.0818181818182</v>
       </c>
       <c r="B50">
-        <v>0.01531675386397739</v>
+        <v>0.01905055031048268</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>247.9191919191919</v>
+        <v>170.4606060606061</v>
       </c>
       <c r="B51">
-        <v>0.01503103038768949</v>
+        <v>0.01869256087176563</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>252.8808080808081</v>
+        <v>173.8393939393939</v>
       </c>
       <c r="B52">
-        <v>0.01475614206055503</v>
+        <v>0.01834812936317774</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>257.8424242424242</v>
+        <v>177.2181818181818</v>
       </c>
       <c r="B53">
-        <v>0.01449147726703538</v>
+        <v>0.01801649348442664</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>262.8040404040404</v>
+        <v>180.5969696969697</v>
       </c>
       <c r="B54">
-        <v>0.01423646981812463</v>
+        <v>0.01769694726264558</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>267.7656565656566</v>
+        <v>183.9757575757576</v>
       </c>
       <c r="B55">
-        <v>0.0139905947976513</v>
+        <v>0.01738883593176847</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>272.7272727272727</v>
+        <v>187.3545454545455</v>
       </c>
       <c r="B56">
-        <v>0.0137533648570862</v>
+        <v>0.01709155136140432</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>277.6888888888889</v>
+        <v>190.7333333333333</v>
       </c>
       <c r="B57">
-        <v>0.01352432690327473</v>
+        <v>0.01680452796754974</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>282.650505050505</v>
+        <v>194.1121212121212</v>
       </c>
       <c r="B58">
-        <v>0.01330305913125553</v>
+        <v>0.0165272390468431</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>287.6121212121212</v>
+        <v>197.4909090909091</v>
       </c>
       <c r="B59">
-        <v>0.01308916836087662</v>
+        <v>0.01625919348399371</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>292.5737373737374</v>
+        <v>200.869696969697</v>
       </c>
       <c r="B60">
-        <v>0.01288228764147714</v>
+        <v>0.01599993278875608</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>297.5353535353535</v>
+        <v>204.2484848484848</v>
       </c>
       <c r="B61">
-        <v>0.01268207409363181</v>
+        <v>0.01574902842455767</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>302.4969696969697</v>
+        <v>207.6272727272728</v>
       </c>
       <c r="B62">
-        <v>0.0124882069609904</v>
+        <v>0.01550607939579167</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>307.4585858585859</v>
+        <v>211.0060606060606</v>
       </c>
       <c r="B63">
-        <v>0.01230038584869856</v>
+        <v>0.01527071006498598</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>312.4202020202021</v>
+        <v>214.3848484848485</v>
       </c>
       <c r="B64">
-        <v>0.01211832912784966</v>
+        <v>0.0150425681746673</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>317.3818181818182</v>
+        <v>217.7636363636364</v>
       </c>
       <c r="B65">
-        <v>0.01194177248796671</v>
+        <v>0.01482132305184568</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>322.3434343434344</v>
+        <v>221.1424242424243</v>
       </c>
       <c r="B66">
-        <v>0.01177046762171235</v>
+        <v>0.01460666397572636</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>327.3050505050505</v>
+        <v>224.5212121212121</v>
       </c>
       <c r="B67">
-        <v>0.01160418102792583</v>
+        <v>0.01439829869157622</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>332.2666666666667</v>
+        <v>227.9</v>
       </c>
       <c r="B68">
-        <v>0.01144269292073312</v>
+        <v>0.01419595205568452</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>337.2282828282828</v>
+        <v>231.2787878787879</v>
       </c>
       <c r="B69">
-        <v>0.01128579623390697</v>
+        <v>0.01399936479810706</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>342.189898989899</v>
+        <v>234.6575757575758</v>
       </c>
       <c r="B70">
-        <v>0.01113329571089922</v>
+        <v>0.01380829239140649</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>347.1515151515152</v>
+        <v>238.0363636363637</v>
       </c>
       <c r="B71">
-        <v>0.01098500707205367</v>
+        <v>0.01362250401493192</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>352.1131313131313</v>
+        <v>241.4151515151515</v>
       </c>
       <c r="B72">
-        <v>0.01084075625145765</v>
+        <v>0.01344178160534442</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>357.0747474747475</v>
+        <v>244.7939393939394</v>
       </c>
       <c r="B73">
-        <v>0.01070037869672178</v>
+        <v>0.01326591898511502</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>362.0363636363637</v>
+        <v>248.1727272727273</v>
       </c>
       <c r="B74">
-        <v>0.01056371872570723</v>
+        <v>0.013094721061617</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>366.9979797979798</v>
+        <v>251.5515151515152</v>
       </c>
       <c r="B75">
-        <v>0.0104306289348615</v>
+        <v>0.01292800309022271</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>371.959595959596</v>
+        <v>254.930303030303</v>
       </c>
       <c r="B76">
-        <v>0.0103009696543887</v>
+        <v>0.01276558999550886</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>376.9212121212121</v>
+        <v>258.3090909090909</v>
       </c>
       <c r="B77">
-        <v>0.01017460844597923</v>
+        <v>0.01260731574528809</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>381.8828282828283</v>
+        <v>261.6878787878788</v>
       </c>
       <c r="B78">
-        <v>0.01005141963926408</v>
+        <v>0.01245302277272614</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>386.8444444444444</v>
+        <v>265.0666666666667</v>
       </c>
       <c r="B79">
-        <v>0.009931283903549807</v>
+        <v>0.01230256144228506</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>391.8060606060606</v>
+        <v>268.4454545454545</v>
       </c>
       <c r="B80">
-        <v>0.009814087851735777</v>
+        <v>0.01215578955565855</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>396.7676767676768</v>
+        <v>271.8242424242424</v>
       </c>
       <c r="B81">
-        <v>0.009699723673623097</v>
+        <v>0.01201257189424466</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82">
-        <v>401.729292929293</v>
+        <v>275.2030303030303</v>
       </c>
       <c r="B82">
-        <v>0.009588088796097901</v>
+        <v>0.01187277979503844</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83">
-        <v>406.6909090909091</v>
+        <v>278.5818181818182</v>
       </c>
       <c r="B83">
-        <v>0.009479085567915465</v>
+        <v>0.01173629075712732</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84">
-        <v>411.6525252525253</v>
+        <v>281.960606060606</v>
       </c>
       <c r="B84">
-        <v>0.009372620967029011</v>
+        <v>0.0116029880762408</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85">
-        <v>416.6141414141414</v>
+        <v>285.3393939393939</v>
       </c>
       <c r="B85">
-        <v>0.009268606328601416</v>
+        <v>0.01147276050504557</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86">
-        <v>421.5757575757576</v>
+        <v>288.7181818181818</v>
       </c>
       <c r="B86">
-        <v>0.009166957092011792</v>
+        <v>0.01134550193709238</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87">
-        <v>426.5373737373737</v>
+        <v>292.0969696969697</v>
       </c>
       <c r="B87">
-        <v>0.009067592565324854</v>
+        <v>0.01122111111251317</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88">
-        <v>431.4989898989899</v>
+        <v>295.4757575757575</v>
       </c>
       <c r="B88">
-        <v>0.008970435705830657</v>
+        <v>0.01109949134373992</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89">
-        <v>436.4606060606061</v>
+        <v>298.8545454545454</v>
       </c>
       <c r="B89">
-        <v>0.00887541291538794</v>
+        <v>0.01098055025967232</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90">
-        <v>441.4222222222222</v>
+        <v>302.2333333333333</v>
       </c>
       <c r="B90">
-        <v>0.008782453849417272</v>
+        <v>0.01086419956686064</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91">
-        <v>446.3838383838384</v>
+        <v>305.6121212121212</v>
       </c>
       <c r="B91">
-        <v>0.008691491238491958</v>
+        <v>0.01075035482639666</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92">
-        <v>451.3454545454546</v>
+        <v>308.9909090909091</v>
       </c>
       <c r="B92">
-        <v>0.00860246072156641</v>
+        <v>0.01063893524531896</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93">
-        <v>456.3070707070707</v>
+        <v>312.369696969697</v>
       </c>
       <c r="B93">
-        <v>0.008515300689964578</v>
+        <v>0.01052986348144133</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94">
-        <v>461.2686868686869</v>
+        <v>315.7484848484848</v>
       </c>
       <c r="B94">
-        <v>0.008429952141325862</v>
+        <v>0.01042306546060632</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95">
-        <v>466.230303030303</v>
+        <v>319.1272727272727</v>
       </c>
       <c r="B95">
-        <v>0.008346358542773744</v>
+        <v>0.01031847020544955</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96">
-        <v>471.1919191919192</v>
+        <v>322.5060606060606</v>
       </c>
       <c r="B96">
-        <v>0.008264465702633741</v>
+        <v>0.01021600967483671</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97">
-        <v>476.1535353535353</v>
+        <v>325.8848484848485</v>
       </c>
       <c r="B97">
-        <v>0.00818422165008296</v>
+        <v>0.01011561861320442</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98">
-        <v>481.1151515151515</v>
+        <v>329.2636363636364</v>
       </c>
       <c r="B98">
-        <v>0.008105576522164084</v>
+        <v>0.01001723440909843</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99">
-        <v>486.0767676767677</v>
+        <v>332.6424242424242</v>
       </c>
       <c r="B99">
-        <v>0.008028482457642554</v>
+        <v>0.009920796962260125</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100">
-        <v>491.0383838383838</v>
+        <v>336.0212121212121</v>
       </c>
       <c r="B100">
-        <v>0.00795289349722748</v>
+        <v>0.009826248558663993</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101">
-        <v>496</v>
+        <v>339.4</v>
       </c>
       <c r="B101">
-        <v>0.007878765489714909</v>
+        <v>0.009733533752955834</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sgt_files/InVitroBioFilm_SGT_scaling.xlsx
+++ b/datasets/sgt_files/InVitroBioFilm_SGT_scaling.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Image GT" sheetId="1" r:id="rId1"/>
+    <sheet name="SGT Descriptors" sheetId="1" r:id="rId1"/>
     <sheet name="Nodes-Number of edge." sheetId="2" r:id="rId2"/>
     <sheet name="Nodes-Number of edge. (Fitting)" sheetId="3" r:id="rId3"/>
     <sheet name="Nodes-Average degree" sheetId="4" r:id="rId4"/>
@@ -625,25 +625,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>0.8749603165604457</v>
+        <v>1.273664878302853</v>
       </c>
       <c r="D2">
-        <v>0.54381</v>
+        <v>5.1</v>
       </c>
       <c r="E2">
-        <v>0.08774793272651941</v>
+        <v>1.268857754044952</v>
       </c>
       <c r="F2">
-        <v>0.6901960800285137</v>
+        <v>0.7781512503836436</v>
       </c>
       <c r="G2">
-        <v>-0.2645528105313652</v>
+        <v>0.7075701760979364</v>
       </c>
       <c r="H2">
-        <v>-0.1883687288611057</v>
+        <v>0.7485654903230231</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -651,25 +651,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>15.1</v>
+        <v>16.5</v>
       </c>
       <c r="C3">
-        <v>1.494062322067665</v>
+        <v>2.944863701807305</v>
       </c>
       <c r="D3">
-        <v>0.160176</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>0.02307557738292924</v>
+        <v>3.396076167186674</v>
       </c>
       <c r="F3">
-        <v>1.178976947293169</v>
+        <v>1.217483944213906</v>
       </c>
       <c r="G3">
-        <v>-0.79540255596962</v>
+        <v>1.230448921378274</v>
       </c>
       <c r="H3">
-        <v>-0.7028767673401117</v>
+        <v>1.209361370100398</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -677,25 +677,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>38.7</v>
+        <v>31.4</v>
       </c>
       <c r="C4">
-        <v>7.03964961249256</v>
+        <v>6.491361781458322</v>
       </c>
       <c r="D4">
-        <v>0.096871</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>0.02955341012284182</v>
+        <v>7.428174592575068</v>
       </c>
       <c r="F4">
-        <v>1.587710965018911</v>
+        <v>1.496929648073215</v>
       </c>
       <c r="G4">
-        <v>-1.013806217015109</v>
+        <v>1.531478917042255</v>
       </c>
       <c r="H4">
-        <v>-1.13312465919519</v>
+        <v>1.502459131246322</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -703,25 +703,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>55.9</v>
+        <v>50</v>
       </c>
       <c r="C5">
-        <v>10.85505514597794</v>
+        <v>7.049034606872695</v>
       </c>
       <c r="D5">
-        <v>0.077846</v>
+        <v>53.5</v>
       </c>
       <c r="E5">
-        <v>0.03040207913942729</v>
+        <v>8.112062349091971</v>
       </c>
       <c r="F5">
-        <v>1.747411807886423</v>
+        <v>1.698970004336019</v>
       </c>
       <c r="G5">
-        <v>-1.108763698093395</v>
+        <v>1.728353782021228</v>
       </c>
       <c r="H5">
-        <v>-1.301231418093175</v>
+        <v>1.714369979271263</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -729,25 +729,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>78.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="C6">
-        <v>14.12755384975678</v>
+        <v>12.8</v>
       </c>
       <c r="D6">
-        <v>0.039588</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="E6">
-        <v>0.007898477462284881</v>
+        <v>13.919171431279</v>
       </c>
       <c r="F6">
-        <v>1.8926510338773</v>
+        <v>1.887617300335736</v>
       </c>
       <c r="G6">
-        <v>-1.402436438407031</v>
+        <v>1.913283901760418</v>
       </c>
       <c r="H6">
-        <v>-1.454115367280804</v>
+        <v>1.91223346165848</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -755,25 +755,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>167.1</v>
+        <v>156.8</v>
       </c>
       <c r="C7">
-        <v>13.01405223424109</v>
+        <v>19.21214893411631</v>
       </c>
       <c r="D7">
-        <v>0.013829</v>
+        <v>175.6</v>
       </c>
       <c r="E7">
-        <v>0.0009057574485233646</v>
+        <v>23.36768899332771</v>
       </c>
       <c r="F7">
-        <v>2.222976449893391</v>
+        <v>2.19534605834842</v>
       </c>
       <c r="G7">
-        <v>-1.859209223374698</v>
+        <v>2.244524511570084</v>
       </c>
       <c r="H7">
-        <v>-1.801827590153425</v>
+        <v>2.23499601899285</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -781,25 +781,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>215.3</v>
+        <v>157.3</v>
       </c>
       <c r="C8">
-        <v>14.01590366532089</v>
+        <v>17.51002887236658</v>
       </c>
       <c r="D8">
-        <v>0.010871</v>
+        <v>170</v>
       </c>
       <c r="E8">
-        <v>0.0007843078335563005</v>
+        <v>20.03108695114782</v>
       </c>
       <c r="F8">
-        <v>2.333044029823487</v>
+        <v>2.196728722623287</v>
       </c>
       <c r="G8">
-        <v>-1.963730504257185</v>
+        <v>2.230448921378274</v>
       </c>
       <c r="H8">
-        <v>-1.917688619998731</v>
+        <v>2.236446232031673</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -807,25 +807,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>276.4</v>
+        <v>268.4</v>
       </c>
       <c r="C9">
-        <v>24.80913810137976</v>
+        <v>15.93751688452264</v>
       </c>
       <c r="D9">
-        <v>0.008915000000000001</v>
+        <v>297.4</v>
       </c>
       <c r="E9">
-        <v>0.001054587070321312</v>
+        <v>18.39939612535634</v>
       </c>
       <c r="F9">
-        <v>2.441538038702161</v>
+        <v>2.428782511496955</v>
       </c>
       <c r="G9">
-        <v>-2.049878652488626</v>
+        <v>2.473340964185935</v>
       </c>
       <c r="H9">
-        <v>-2.031893253267785</v>
+        <v>2.479836790716175</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -833,25 +833,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>339.4</v>
+        <v>311.6</v>
       </c>
       <c r="C10">
-        <v>27.14496065366256</v>
+        <v>26.19847323795797</v>
       </c>
       <c r="D10">
-        <v>0.007071000000000001</v>
+        <v>348.5</v>
       </c>
       <c r="E10">
-        <v>0.0006898702776609526</v>
+        <v>31.04450210763753</v>
       </c>
       <c r="F10">
-        <v>2.530711837981657</v>
+        <v>2.493597449000527</v>
       </c>
       <c r="G10">
-        <v>-2.150519162756014</v>
+        <v>2.542202782434028</v>
       </c>
       <c r="H10">
-        <v>-2.125760750184704</v>
+        <v>2.547818201089456</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -859,25 +859,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>312.8</v>
+        <v>343.4</v>
       </c>
       <c r="C11">
-        <v>30.94719516998089</v>
+        <v>28.52297319705644</v>
       </c>
       <c r="D11">
-        <v>0.007683</v>
+        <v>385.1</v>
       </c>
       <c r="E11">
-        <v>0.0006173546612586461</v>
+        <v>33.37678834160052</v>
       </c>
       <c r="F11">
-        <v>2.49526674438781</v>
+        <v>2.535800290824898</v>
       </c>
       <c r="G11">
-        <v>-2.114469166811908</v>
+        <v>2.585573518622731</v>
       </c>
       <c r="H11">
-        <v>-2.088449990291968</v>
+        <v>2.592082823096121</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -885,25 +885,25 @@
         <v>638</v>
       </c>
       <c r="B12">
-        <v>286</v>
+        <v>496</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0.00851</v>
+        <v>563</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>2.456366033129043</v>
+        <v>2.695481676490198</v>
       </c>
       <c r="G12">
-        <v>-2.070070439915412</v>
+        <v>2.750508394851346</v>
       </c>
       <c r="H12">
-        <v>-2.047501724953364</v>
+        <v>2.759565292816756</v>
       </c>
     </row>
   </sheetData>
@@ -926,802 +926,802 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>0.5398045483159717</v>
+        <v>5.964762332057422</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>8.278787878787879</v>
+        <v>10.94949494949495</v>
       </c>
       <c r="B3">
-        <v>0.3284083995079981</v>
+        <v>11.0823649503327</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>11.65757575757576</v>
+        <v>15.8989898989899</v>
       </c>
       <c r="B4">
-        <v>0.2374489201543626</v>
+        <v>16.27203421343469</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>15.03636363636364</v>
+        <v>20.84848484848485</v>
       </c>
       <c r="B5">
-        <v>0.1865666643680177</v>
+        <v>21.51094904735587</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>18.41515151515151</v>
+        <v>25.7979797979798</v>
       </c>
       <c r="B6">
-        <v>0.1539641388384904</v>
+        <v>26.78746724132179</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>21.7939393939394</v>
+        <v>30.74747474747475</v>
       </c>
       <c r="B7">
-        <v>0.1312492966062286</v>
+        <v>32.09447020666597</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>25.17272727272727</v>
+        <v>35.6969696969697</v>
       </c>
       <c r="B8">
-        <v>0.1144948720744534</v>
+        <v>37.42713957760572</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>28.55151515151515</v>
+        <v>40.64646464646465</v>
       </c>
       <c r="B9">
-        <v>0.1016147002929615</v>
+        <v>42.78199134326086</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>31.93030303030303</v>
+        <v>45.5959595959596</v>
       </c>
       <c r="B10">
-        <v>0.0913967491010062</v>
+        <v>48.15638616568128</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>35.30909090909091</v>
+        <v>50.54545454545455</v>
       </c>
       <c r="B11">
-        <v>0.08308809485423957</v>
+        <v>53.54825392267355</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>38.68787878787879</v>
+        <v>55.49494949494949</v>
       </c>
       <c r="B12">
-        <v>0.07619603829433115</v>
+        <v>58.95592662293612</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>42.06666666666667</v>
+        <v>60.44444444444445</v>
       </c>
       <c r="B13">
-        <v>0.07038445451469259</v>
+        <v>64.37803106413091</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>45.44545454545455</v>
+        <v>65.39393939393941</v>
       </c>
       <c r="B14">
-        <v>0.06541607560131416</v>
+        <v>69.81341667303326</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>48.82424242424242</v>
+        <v>70.34343434343435</v>
       </c>
       <c r="B15">
-        <v>0.06111857673102275</v>
+        <v>75.26110517996189</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>52.2030303030303</v>
+        <v>75.2929292929293</v>
       </c>
       <c r="B16">
-        <v>0.05736374168613149</v>
+        <v>80.720254435976</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>55.58181818181819</v>
+        <v>80.24242424242425</v>
       </c>
       <c r="B17">
-        <v>0.05405417411447415</v>
+        <v>86.19013172276803</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>58.96060606060606</v>
+        <v>85.1919191919192</v>
       </c>
       <c r="B18">
-        <v>0.05111454534972518</v>
+        <v>91.67009362887831</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>62.33939393939394</v>
+        <v>90.14141414141415</v>
       </c>
       <c r="B19">
-        <v>0.0484856678716831</v>
+        <v>97.15957058679552</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>65.71818181818182</v>
+        <v>95.09090909090909</v>
       </c>
       <c r="B20">
-        <v>0.04612038362129586</v>
+        <v>102.6580547933645</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>69.09696969696971</v>
+        <v>100.040404040404</v>
       </c>
       <c r="B21">
-        <v>0.04398064975636115</v>
+        <v>108.1650906347704</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>72.47575757575758</v>
+        <v>104.989898989899</v>
       </c>
       <c r="B22">
-        <v>0.04203543349690217</v>
+        <v>113.6802669980107</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>75.85454545454546</v>
+        <v>109.939393939394</v>
       </c>
       <c r="B23">
-        <v>0.04025916536229642</v>
+        <v>119.2032110253892</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>79.23333333333335</v>
+        <v>114.8888888888889</v>
       </c>
       <c r="B24">
-        <v>0.0386305851690889</v>
+        <v>124.7335829881737</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>82.61212121212122</v>
+        <v>119.8383838383838</v>
       </c>
       <c r="B25">
-        <v>0.03713186905886506</v>
+        <v>130.2710720391229</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>85.9909090909091</v>
+        <v>124.7878787878788</v>
       </c>
       <c r="B26">
-        <v>0.03574796075508859</v>
+        <v>135.8153926630103</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>89.36969696969697</v>
+        <v>129.7373737373737</v>
       </c>
       <c r="B27">
-        <v>0.03446605334880411</v>
+        <v>141.3662816872214</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>92.74848484848485</v>
+        <v>134.6868686868687</v>
       </c>
       <c r="B28">
-        <v>0.03327518347648203</v>
+        <v>146.9234957459932</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>96.12727272727274</v>
+        <v>139.6363636363637</v>
       </c>
       <c r="B29">
-        <v>0.03216591041717451</v>
+        <v>152.4868091152699</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>99.50606060606061</v>
+        <v>144.5858585858586</v>
       </c>
       <c r="B30">
-        <v>0.03113006005706683</v>
+        <v>158.0560118527572</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>102.8848484848485</v>
+        <v>149.5353535353536</v>
       </c>
       <c r="B31">
-        <v>0.03016051890784841</v>
+        <v>163.6309081911545</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>106.2636363636364</v>
+        <v>154.4848484848485</v>
       </c>
       <c r="B32">
-        <v>0.02925106711204735</v>
+        <v>169.2113151428445</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>109.6424242424243</v>
+        <v>159.4343434343434</v>
       </c>
       <c r="B33">
-        <v>0.02839624208121811</v>
+        <v>174.7970612823134</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>113.0212121212121</v>
+        <v>164.3838383838384</v>
       </c>
       <c r="B34">
-        <v>0.02759122639938759</v>
+        <v>180.3879856788375</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>116.4</v>
+        <v>169.3333333333333</v>
       </c>
       <c r="B35">
-        <v>0.02683175509432052</v>
+        <v>185.9839369569168</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>119.7787878787879</v>
+        <v>174.2828282828283</v>
       </c>
       <c r="B36">
-        <v>0.02611403847796769</v>
+        <v>191.5847724658714</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>123.1575757575758</v>
+        <v>179.2323232323232</v>
       </c>
       <c r="B37">
-        <v>0.0254346975863321</v>
+        <v>197.1903575431725</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>126.5363636363636</v>
+        <v>184.1818181818182</v>
       </c>
       <c r="B38">
-        <v>0.02479070987968223</v>
+        <v>202.800564858627</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>129.9151515151515</v>
+        <v>189.1313131313131</v>
       </c>
       <c r="B39">
-        <v>0.02417936334786408</v>
+        <v>208.4152738286039</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>133.2939393939394</v>
+        <v>194.0808080808081</v>
       </c>
       <c r="B40">
-        <v>0.02359821753947685</v>
+        <v>214.034370091182</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>136.6727272727273</v>
+        <v>199.030303030303</v>
       </c>
       <c r="B41">
-        <v>0.02304507032490236</v>
+        <v>219.6577450344884</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>140.0515151515152</v>
+        <v>203.979797979798</v>
       </c>
       <c r="B42">
-        <v>0.02251792943149735</v>
+        <v>225.2852953716474</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>143.430303030303</v>
+        <v>208.929292929293</v>
       </c>
       <c r="B43">
-        <v>0.02201498796942169</v>
+        <v>230.9169227567126</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>146.8090909090909</v>
+        <v>213.8787878787879</v>
       </c>
       <c r="B44">
-        <v>0.02153460330961525</v>
+        <v>236.5525334367514</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>150.1878787878788</v>
+        <v>218.8282828282829</v>
       </c>
       <c r="B45">
-        <v>0.02107527878966524</v>
+        <v>242.1920379359224</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>153.5666666666667</v>
+        <v>223.7777777777778</v>
       </c>
       <c r="B46">
-        <v>0.02063564781503395</v>
+        <v>247.8353507679419</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>156.9454545454546</v>
+        <v>228.7272727272727</v>
       </c>
       <c r="B47">
-        <v>0.02021445999716518</v>
+        <v>253.4823901738206</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>160.3242424242424</v>
+        <v>233.6767676767677</v>
       </c>
       <c r="B48">
-        <v>0.0198105690300645</v>
+        <v>259.1330778821469</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>163.7030303030303</v>
+        <v>238.6262626262626</v>
       </c>
       <c r="B49">
-        <v>0.01942292205592545</v>
+        <v>264.7873388895433</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>167.0818181818182</v>
+        <v>243.5757575757576</v>
       </c>
       <c r="B50">
-        <v>0.01905055031048268</v>
+        <v>270.4451012592135</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>170.4606060606061</v>
+        <v>248.5252525252525</v>
       </c>
       <c r="B51">
-        <v>0.01869256087176563</v>
+        <v>276.1062959357533</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>173.8393939393939</v>
+        <v>253.4747474747475</v>
       </c>
       <c r="B52">
-        <v>0.01834812936317774</v>
+        <v>281.770856574613</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>177.2181818181818</v>
+        <v>258.4242424242424</v>
       </c>
       <c r="B53">
-        <v>0.01801649348442664</v>
+        <v>287.4387193847877</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>180.5969696969697</v>
+        <v>263.3737373737374</v>
       </c>
       <c r="B54">
-        <v>0.01769694726264558</v>
+        <v>293.1098229834785</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>183.9757575757576</v>
+        <v>268.3232323232323</v>
       </c>
       <c r="B55">
-        <v>0.01738883593176847</v>
+        <v>298.7841082616019</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>187.3545454545455</v>
+        <v>273.2727272727273</v>
       </c>
       <c r="B56">
-        <v>0.01709155136140432</v>
+        <v>304.4615182591557</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>190.7333333333333</v>
+        <v>278.2222222222222</v>
       </c>
       <c r="B57">
-        <v>0.01680452796754974</v>
+        <v>310.1419980495502</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>194.1121212121212</v>
+        <v>283.1717171717172</v>
       </c>
       <c r="B58">
-        <v>0.0165272390468431</v>
+        <v>315.8254946321151</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>197.4909090909091</v>
+        <v>288.1212121212121</v>
       </c>
       <c r="B59">
-        <v>0.01625919348399371</v>
+        <v>321.5119568320683</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>200.869696969697</v>
+        <v>293.0707070707071</v>
       </c>
       <c r="B60">
-        <v>0.01599993278875608</v>
+        <v>327.2013352073111</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>204.2484848484848</v>
+        <v>298.020202020202</v>
       </c>
       <c r="B61">
-        <v>0.01574902842455767</v>
+        <v>332.8935819614759</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>207.6272727272728</v>
+        <v>302.969696969697</v>
       </c>
       <c r="B62">
-        <v>0.01550607939579167</v>
+        <v>338.5886508627097</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>211.0060606060606</v>
+        <v>307.9191919191919</v>
       </c>
       <c r="B63">
-        <v>0.01527071006498598</v>
+        <v>344.2864971677276</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>214.3848484848485</v>
+        <v>312.8686868686869</v>
       </c>
       <c r="B64">
-        <v>0.0150425681746673</v>
+        <v>349.9870775507161</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>217.7636363636364</v>
+        <v>317.8181818181818</v>
       </c>
       <c r="B65">
-        <v>0.01482132305184568</v>
+        <v>355.6903500367021</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>221.1424242424243</v>
+        <v>322.7676767676768</v>
       </c>
       <c r="B66">
-        <v>0.01460666397572636</v>
+        <v>361.3962739390456</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>224.5212121212121</v>
+        <v>327.7171717171718</v>
       </c>
       <c r="B67">
-        <v>0.01439829869157622</v>
+        <v>367.1048098007374</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>227.9</v>
+        <v>332.6666666666667</v>
       </c>
       <c r="B68">
-        <v>0.01419595205568452</v>
+        <v>372.8159193392195</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>231.2787878787879</v>
+        <v>337.6161616161617</v>
       </c>
       <c r="B69">
-        <v>0.01399936479810706</v>
+        <v>378.5295653944661</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>234.6575757575758</v>
+        <v>342.5656565656566</v>
       </c>
       <c r="B70">
-        <v>0.01380829239140649</v>
+        <v>384.2457118800868</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>238.0363636363637</v>
+        <v>347.5151515151516</v>
       </c>
       <c r="B71">
-        <v>0.01362250401493192</v>
+        <v>389.964323737237</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>241.4151515151515</v>
+        <v>352.4646464646465</v>
       </c>
       <c r="B72">
-        <v>0.01344178160534442</v>
+        <v>395.6853668911342</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>244.7939393939394</v>
+        <v>357.4141414141415</v>
       </c>
       <c r="B73">
-        <v>0.01326591898511502</v>
+        <v>401.4088082100006</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>248.1727272727273</v>
+        <v>362.3636363636364</v>
       </c>
       <c r="B74">
-        <v>0.013094721061617</v>
+        <v>407.134615466263</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>251.5515151515152</v>
+        <v>367.3131313131314</v>
       </c>
       <c r="B75">
-        <v>0.01292800309022271</v>
+        <v>412.8627572998581</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>254.930303030303</v>
+        <v>372.2626262626263</v>
       </c>
       <c r="B76">
-        <v>0.01276558999550886</v>
+        <v>418.5932031835009</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>258.3090909090909</v>
+        <v>377.2121212121212</v>
       </c>
       <c r="B77">
-        <v>0.01260731574528809</v>
+        <v>424.3259233897883</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>261.6878787878788</v>
+        <v>382.1616161616162</v>
       </c>
       <c r="B78">
-        <v>0.01245302277272614</v>
+        <v>430.0608889600148</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>265.0666666666667</v>
+        <v>387.1111111111111</v>
       </c>
       <c r="B79">
-        <v>0.01230256144228506</v>
+        <v>435.7980716745953</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>268.4454545454545</v>
+        <v>392.0606060606061</v>
       </c>
       <c r="B80">
-        <v>0.01215578955565855</v>
+        <v>441.5374440249866</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>271.8242424242424</v>
+        <v>397.010101010101</v>
       </c>
       <c r="B81">
-        <v>0.01201257189424466</v>
+        <v>447.278979187019</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82">
-        <v>275.2030303030303</v>
+        <v>401.959595959596</v>
       </c>
       <c r="B82">
-        <v>0.01187277979503844</v>
+        <v>453.0226509955469</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83">
-        <v>278.5818181818182</v>
+        <v>406.9090909090909</v>
       </c>
       <c r="B83">
-        <v>0.01173629075712732</v>
+        <v>458.7684339203399</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84">
-        <v>281.960606060606</v>
+        <v>411.8585858585859</v>
       </c>
       <c r="B84">
-        <v>0.0116029880762408</v>
+        <v>464.5163030431381</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85">
-        <v>285.3393939393939</v>
+        <v>416.8080808080808</v>
       </c>
       <c r="B85">
-        <v>0.01147276050504557</v>
+        <v>470.266234035802</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86">
-        <v>288.7181818181818</v>
+        <v>421.7575757575758</v>
       </c>
       <c r="B86">
-        <v>0.01134550193709238</v>
+        <v>476.0182031394944</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87">
-        <v>292.0969696969697</v>
+        <v>426.7070707070707</v>
       </c>
       <c r="B87">
-        <v>0.01122111111251317</v>
+        <v>481.7721871448301</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88">
-        <v>295.4757575757575</v>
+        <v>431.6565656565657</v>
       </c>
       <c r="B88">
-        <v>0.01109949134373992</v>
+        <v>487.5281633729426</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89">
-        <v>298.8545454545454</v>
+        <v>436.6060606060606</v>
       </c>
       <c r="B89">
-        <v>0.01098055025967232</v>
+        <v>493.2861096574107</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90">
-        <v>302.2333333333333</v>
+        <v>441.5555555555556</v>
       </c>
       <c r="B90">
-        <v>0.01086419956686064</v>
+        <v>499.0460043270007</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91">
-        <v>305.6121212121212</v>
+        <v>446.5050505050505</v>
       </c>
       <c r="B91">
-        <v>0.01075035482639666</v>
+        <v>504.8078261891748</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92">
-        <v>308.9909090909091</v>
+        <v>451.4545454545455</v>
       </c>
       <c r="B92">
-        <v>0.01063893524531896</v>
+        <v>510.5715545143277</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93">
-        <v>312.369696969697</v>
+        <v>456.4040404040404</v>
       </c>
       <c r="B93">
-        <v>0.01052986348144133</v>
+        <v>516.3371690207069</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94">
-        <v>315.7484848484848</v>
+        <v>461.3535353535354</v>
       </c>
       <c r="B94">
-        <v>0.01042306546060632</v>
+        <v>522.1046498599859</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95">
-        <v>319.1272727272727</v>
+        <v>466.3030303030303</v>
       </c>
       <c r="B95">
-        <v>0.01031847020544955</v>
+        <v>527.8739776034479</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96">
-        <v>322.5060606060606</v>
+        <v>471.2525252525253</v>
       </c>
       <c r="B96">
-        <v>0.01021600967483671</v>
+        <v>533.6451332287552</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97">
-        <v>325.8848484848485</v>
+        <v>476.2020202020202</v>
       </c>
       <c r="B97">
-        <v>0.01011561861320442</v>
+        <v>539.4180981072691</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98">
-        <v>329.2636363636364</v>
+        <v>481.1515151515152</v>
       </c>
       <c r="B98">
-        <v>0.01001723440909843</v>
+        <v>545.1928539918933</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99">
-        <v>332.6424242424242</v>
+        <v>486.1010101010102</v>
       </c>
       <c r="B99">
-        <v>0.009920796962260125</v>
+        <v>550.9693830054133</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100">
-        <v>336.0212121212121</v>
+        <v>491.0505050505051</v>
       </c>
       <c r="B100">
-        <v>0.009826248558663993</v>
+        <v>556.7476676293085</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101">
-        <v>339.4</v>
+        <v>496</v>
       </c>
       <c r="B101">
-        <v>0.009733533752955834</v>
+        <v>562.5276906930112</v>
       </c>
     </row>
   </sheetData>
@@ -1765,25 +1765,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>0.8749603165604457</v>
+        <v>1.273664878302853</v>
       </c>
       <c r="D2">
-        <v>0.54381</v>
+        <v>1.567263</v>
       </c>
       <c r="E2">
-        <v>0.08774793272651941</v>
+        <v>0.1059014148583483</v>
       </c>
       <c r="F2">
-        <v>0.6901960800285137</v>
+        <v>0.7781512503836436</v>
       </c>
       <c r="G2">
-        <v>-0.2645528105313652</v>
+        <v>0.1951418808749138</v>
       </c>
       <c r="H2">
-        <v>-0.1883687288611057</v>
+        <v>0.2388171056877338</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1791,25 +1791,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>15.1</v>
+        <v>16.5</v>
       </c>
       <c r="C3">
-        <v>1.494062322067665</v>
+        <v>2.944863701807305</v>
       </c>
       <c r="D3">
-        <v>0.160176</v>
+        <v>1.927077</v>
       </c>
       <c r="E3">
-        <v>0.02307557738292924</v>
+        <v>0.08889780622277595</v>
       </c>
       <c r="F3">
-        <v>1.178976947293169</v>
+        <v>1.217483944213906</v>
       </c>
       <c r="G3">
-        <v>-0.79540255596962</v>
+        <v>0.284899068058154</v>
       </c>
       <c r="H3">
-        <v>-0.7028767673401117</v>
+        <v>0.268703766341072</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1817,25 +1817,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>38.7</v>
+        <v>31.4</v>
       </c>
       <c r="C4">
-        <v>7.03964961249256</v>
+        <v>6.491361781458322</v>
       </c>
       <c r="D4">
-        <v>0.096871</v>
+        <v>2.06712</v>
       </c>
       <c r="E4">
-        <v>0.02955341012284182</v>
+        <v>0.06553245891244361</v>
       </c>
       <c r="F4">
-        <v>1.587710965018911</v>
+        <v>1.496929648073215</v>
       </c>
       <c r="G4">
-        <v>-1.013806217015109</v>
+        <v>0.3153656889277745</v>
       </c>
       <c r="H4">
-        <v>-1.13312465919519</v>
+        <v>0.2877137308612701</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1843,25 +1843,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>55.9</v>
+        <v>50</v>
       </c>
       <c r="C5">
-        <v>10.85505514597794</v>
+        <v>7.049034606872695</v>
       </c>
       <c r="D5">
-        <v>0.077846</v>
+        <v>2.105783</v>
       </c>
       <c r="E5">
-        <v>0.03040207913942729</v>
+        <v>0.03783272134747321</v>
       </c>
       <c r="F5">
-        <v>1.747411807886423</v>
+        <v>1.698970004336019</v>
       </c>
       <c r="G5">
-        <v>-1.108763698093395</v>
+        <v>0.3234136153023646</v>
       </c>
       <c r="H5">
-        <v>-1.301231418093175</v>
+        <v>0.3014580108811834</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1869,25 +1869,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>78.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="C6">
-        <v>14.12755384975678</v>
+        <v>12.8</v>
       </c>
       <c r="D6">
-        <v>0.039588</v>
+        <v>2.101004</v>
       </c>
       <c r="E6">
-        <v>0.007898477462284881</v>
+        <v>0.02090798652296399</v>
       </c>
       <c r="F6">
-        <v>1.8926510338773</v>
+        <v>1.887617300335736</v>
       </c>
       <c r="G6">
-        <v>-1.402436438407031</v>
+        <v>0.3224268792390197</v>
       </c>
       <c r="H6">
-        <v>-1.454115367280804</v>
+        <v>0.3142911958407613</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1895,25 +1895,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>167.1</v>
+        <v>156.8</v>
       </c>
       <c r="C7">
-        <v>13.01405223424109</v>
+        <v>19.21214893411631</v>
       </c>
       <c r="D7">
-        <v>0.013829</v>
+        <v>2.208656</v>
       </c>
       <c r="E7">
-        <v>0.0009057574485233646</v>
+        <v>0.03128599239986554</v>
       </c>
       <c r="F7">
-        <v>2.222976449893391</v>
+        <v>2.19534605834842</v>
       </c>
       <c r="G7">
-        <v>-1.859209223374698</v>
+        <v>0.3441280794135139</v>
       </c>
       <c r="H7">
-        <v>-1.801827590153425</v>
+        <v>0.3352251829834335</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1921,25 +1921,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>215.3</v>
+        <v>157.3</v>
       </c>
       <c r="C8">
-        <v>14.01590366532089</v>
+        <v>17.51002887236658</v>
       </c>
       <c r="D8">
-        <v>0.010871</v>
+        <v>2.148046</v>
       </c>
       <c r="E8">
-        <v>0.0007843078335563005</v>
+        <v>0.015994988395675</v>
       </c>
       <c r="F8">
-        <v>2.333044029823487</v>
+        <v>2.196728722623287</v>
       </c>
       <c r="G8">
-        <v>-1.963730504257185</v>
+        <v>0.3320435774615302</v>
       </c>
       <c r="H8">
-        <v>-1.917688619998731</v>
+        <v>0.3353192420383611</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1947,25 +1947,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>276.4</v>
+        <v>268.4</v>
       </c>
       <c r="C9">
-        <v>24.80913810137976</v>
+        <v>15.93751688452264</v>
       </c>
       <c r="D9">
-        <v>0.008915000000000001</v>
+        <v>2.213014</v>
       </c>
       <c r="E9">
-        <v>0.001054587070321312</v>
+        <v>0.008185803048910686</v>
       </c>
       <c r="F9">
-        <v>2.441538038702161</v>
+        <v>2.428782511496955</v>
       </c>
       <c r="G9">
-        <v>-2.049878652488626</v>
+        <v>0.3449841613757507</v>
       </c>
       <c r="H9">
-        <v>-2.031893253267785</v>
+        <v>0.3511052578272706</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1973,25 +1973,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>339.4</v>
+        <v>311.6</v>
       </c>
       <c r="C10">
-        <v>27.14496065366256</v>
+        <v>26.19847323795797</v>
       </c>
       <c r="D10">
-        <v>0.007071000000000001</v>
+        <v>2.226885</v>
       </c>
       <c r="E10">
-        <v>0.0006898702776609526</v>
+        <v>0.01392093501409539</v>
       </c>
       <c r="F10">
-        <v>2.530711837981657</v>
+        <v>2.493597449000527</v>
       </c>
       <c r="G10">
-        <v>-2.150519162756014</v>
+        <v>0.3476977899325617</v>
       </c>
       <c r="H10">
-        <v>-2.125760750184704</v>
+        <v>0.3555144494709614</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1999,25 +1999,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>312.8</v>
+        <v>343.4</v>
       </c>
       <c r="C11">
-        <v>30.94719516998089</v>
+        <v>28.52297319705644</v>
       </c>
       <c r="D11">
-        <v>0.007683</v>
+        <v>2.236785</v>
       </c>
       <c r="E11">
-        <v>0.0006173546612586461</v>
+        <v>0.009397004871529828</v>
       </c>
       <c r="F11">
-        <v>2.49526674438781</v>
+        <v>2.535800290824898</v>
       </c>
       <c r="G11">
-        <v>-2.114469166811908</v>
+        <v>0.3496242416732986</v>
       </c>
       <c r="H11">
-        <v>-2.088449990291968</v>
+        <v>0.3583853990495484</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2025,25 +2025,25 @@
         <v>638</v>
       </c>
       <c r="B12">
-        <v>286</v>
+        <v>496</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0.00851</v>
+        <v>2.27016</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>2.456366033129043</v>
+        <v>2.695481676490198</v>
       </c>
       <c r="G12">
-        <v>-2.070070439915412</v>
+        <v>0.3560564671791732</v>
       </c>
       <c r="H12">
-        <v>-2.047501724953364</v>
+        <v>0.3692481084564596</v>
       </c>
     </row>
   </sheetData>
@@ -2066,802 +2066,802 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>0.5398045483159717</v>
+        <v>1.760677699531628</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>8.278787878787879</v>
+        <v>10.94949494949495</v>
       </c>
       <c r="B3">
-        <v>0.3284083995079981</v>
+        <v>1.828422796121607</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>11.65757575757576</v>
+        <v>15.8989898989899</v>
       </c>
       <c r="B4">
-        <v>0.2374489201543626</v>
+        <v>1.871728820147263</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>15.03636363636364</v>
+        <v>20.84848484848485</v>
       </c>
       <c r="B5">
-        <v>0.1865666643680177</v>
+        <v>1.903840736599299</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>18.41515151515151</v>
+        <v>25.7979797979798</v>
       </c>
       <c r="B6">
-        <v>0.1539641388384904</v>
+        <v>1.92946555562133</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>21.7939393939394</v>
+        <v>30.74747474747475</v>
       </c>
       <c r="B7">
-        <v>0.1312492966062286</v>
+        <v>1.950837846333064</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>25.17272727272727</v>
+        <v>35.6969696969697</v>
       </c>
       <c r="B8">
-        <v>0.1144948720744534</v>
+        <v>1.969199347648592</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>28.55151515151515</v>
+        <v>40.64646464646465</v>
       </c>
       <c r="B9">
-        <v>0.1016147002929615</v>
+        <v>1.985313337755314</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>31.93030303030303</v>
+        <v>45.5959595959596</v>
       </c>
       <c r="B10">
-        <v>0.0913967491010062</v>
+        <v>1.999683353636969</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>35.30909090909091</v>
+        <v>50.54545454545455</v>
       </c>
       <c r="B11">
-        <v>0.08308809485423957</v>
+        <v>2.012659470909559</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>38.68787878787879</v>
+        <v>55.49494949494949</v>
       </c>
       <c r="B12">
-        <v>0.07619603829433115</v>
+        <v>2.024495147255233</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>42.06666666666667</v>
+        <v>60.44444444444445</v>
       </c>
       <c r="B13">
-        <v>0.07038445451469259</v>
+        <v>2.035379917654685</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>45.44545454545455</v>
+        <v>65.39393939393941</v>
       </c>
       <c r="B14">
-        <v>0.06541607560131416</v>
+        <v>2.045459306643067</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>48.82424242424242</v>
+        <v>70.34343434343435</v>
       </c>
       <c r="B15">
-        <v>0.06111857673102275</v>
+        <v>2.054847529263604</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>52.2030303030303</v>
+        <v>75.2929292929293</v>
       </c>
       <c r="B16">
-        <v>0.05736374168613149</v>
+        <v>2.063635907850051</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>55.58181818181819</v>
+        <v>80.24242424242425</v>
       </c>
       <c r="B17">
-        <v>0.05405417411447415</v>
+        <v>2.071898631878178</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>58.96060606060606</v>
+        <v>85.1919191919192</v>
       </c>
       <c r="B18">
-        <v>0.05111454534972518</v>
+        <v>2.079696809165901</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>62.33939393939394</v>
+        <v>90.14141414141415</v>
       </c>
       <c r="B19">
-        <v>0.0484856678716831</v>
+        <v>2.087081383568123</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>65.71818181818182</v>
+        <v>95.09090909090909</v>
       </c>
       <c r="B20">
-        <v>0.04612038362129586</v>
+        <v>2.094095280188565</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>69.09696969696971</v>
+        <v>100.040404040404</v>
       </c>
       <c r="B21">
-        <v>0.04398064975636115</v>
+        <v>2.100775011589487</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>72.47575757575758</v>
+        <v>104.989898989899</v>
       </c>
       <c r="B22">
-        <v>0.04203543349690217</v>
+        <v>2.107151900003449</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>75.85454545454546</v>
+        <v>109.939393939394</v>
       </c>
       <c r="B23">
-        <v>0.04025916536229642</v>
+        <v>2.113253020864831</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>79.23333333333335</v>
+        <v>114.8888888888889</v>
       </c>
       <c r="B24">
-        <v>0.0386305851690889</v>
+        <v>2.119101940713338</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>82.61212121212122</v>
+        <v>119.8383838383838</v>
       </c>
       <c r="B25">
-        <v>0.03713186905886506</v>
+        <v>2.124719301089494</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>85.9909090909091</v>
+        <v>124.7878787878788</v>
       </c>
       <c r="B26">
-        <v>0.03574796075508859</v>
+        <v>2.130123285513141</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>89.36969696969697</v>
+        <v>129.7373737373737</v>
       </c>
       <c r="B27">
-        <v>0.03446605334880411</v>
+        <v>2.135329996604065</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>92.74848484848485</v>
+        <v>134.6868686868687</v>
       </c>
       <c r="B28">
-        <v>0.03327518347648203</v>
+        <v>2.140353763360163</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>96.12727272727274</v>
+        <v>139.6363636363637</v>
       </c>
       <c r="B29">
-        <v>0.03216591041717451</v>
+        <v>2.145207393587139</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>99.50606060606061</v>
+        <v>144.5858585858586</v>
       </c>
       <c r="B30">
-        <v>0.03113006005706683</v>
+        <v>2.149902382843427</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>102.8848484848485</v>
+        <v>149.5353535353536</v>
       </c>
       <c r="B31">
-        <v>0.03016051890784841</v>
+        <v>2.15444908860566</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>106.2636363636364</v>
+        <v>154.4848484848485</v>
       </c>
       <c r="B32">
-        <v>0.02925106711204735</v>
+        <v>2.158856876389921</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>109.6424242424243</v>
+        <v>159.4343434343434</v>
       </c>
       <c r="B33">
-        <v>0.02839624208121811</v>
+        <v>2.16313424308807</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>113.0212121212121</v>
+        <v>164.3838383838384</v>
       </c>
       <c r="B34">
-        <v>0.02759122639938759</v>
+        <v>2.167288921661169</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>116.4</v>
+        <v>169.3333333333333</v>
       </c>
       <c r="B35">
-        <v>0.02683175509432052</v>
+        <v>2.171327970478336</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>119.7787878787879</v>
+        <v>174.2828282828283</v>
       </c>
       <c r="B36">
-        <v>0.02611403847796769</v>
+        <v>2.175257849931133</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>123.1575757575758</v>
+        <v>179.2323232323232</v>
       </c>
       <c r="B37">
-        <v>0.0254346975863321</v>
+        <v>2.179084488441947</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>126.5363636363636</v>
+        <v>184.1818181818182</v>
       </c>
       <c r="B38">
-        <v>0.02479070987968223</v>
+        <v>2.182813339583932</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>129.9151515151515</v>
+        <v>189.1313131313131</v>
       </c>
       <c r="B39">
-        <v>0.02417936334786408</v>
+        <v>2.18644943171367</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>133.2939393939394</v>
+        <v>194.0808080808081</v>
       </c>
       <c r="B40">
-        <v>0.02359821753947685</v>
+        <v>2.189997411266342</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>136.6727272727273</v>
+        <v>199.030303030303</v>
       </c>
       <c r="B41">
-        <v>0.02304507032490236</v>
+        <v>2.193461580662015</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>140.0515151515152</v>
+        <v>203.979797979798</v>
       </c>
       <c r="B42">
-        <v>0.02251792943149735</v>
+        <v>2.196845931609889</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>143.430303030303</v>
+        <v>208.929292929293</v>
       </c>
       <c r="B43">
-        <v>0.02201498796942169</v>
+        <v>2.200154174466262</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>146.8090909090909</v>
+        <v>213.8787878787879</v>
       </c>
       <c r="B44">
-        <v>0.02153460330961525</v>
+        <v>2.203389764195388</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>150.1878787878788</v>
+        <v>218.8282828282829</v>
       </c>
       <c r="B45">
-        <v>0.02107527878966524</v>
+        <v>2.206555923395126</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>153.5666666666667</v>
+        <v>223.7777777777778</v>
       </c>
       <c r="B46">
-        <v>0.02063564781503395</v>
+        <v>2.209655662777549</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>156.9454545454546</v>
+        <v>228.7272727272727</v>
       </c>
       <c r="B47">
-        <v>0.02021445999716518</v>
+        <v>2.212691799435388</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>160.3242424242424</v>
+        <v>233.6767676767677</v>
       </c>
       <c r="B48">
-        <v>0.0198105690300645</v>
+        <v>2.215666973176025</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>163.7030303030303</v>
+        <v>238.6262626262626</v>
       </c>
       <c r="B49">
-        <v>0.01942292205592545</v>
+        <v>2.21858366116373</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>167.0818181818182</v>
+        <v>243.5757575757576</v>
       </c>
       <c r="B50">
-        <v>0.01905055031048268</v>
+        <v>2.221444191076524</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>170.4606060606061</v>
+        <v>248.5252525252525</v>
       </c>
       <c r="B51">
-        <v>0.01869256087176563</v>
+        <v>2.22425075295523</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>173.8393939393939</v>
+        <v>253.4747474747475</v>
       </c>
       <c r="B52">
-        <v>0.01834812936317774</v>
+        <v>2.227005409897973</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>177.2181818181818</v>
+        <v>258.4242424242424</v>
       </c>
       <c r="B53">
-        <v>0.01801649348442664</v>
+        <v>2.229710107732774</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>180.5969696969697</v>
+        <v>263.3737373737374</v>
       </c>
       <c r="B54">
-        <v>0.01769694726264558</v>
+        <v>2.232366683783468</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>183.9757575757576</v>
+        <v>268.3232323232323</v>
       </c>
       <c r="B55">
-        <v>0.01738883593176847</v>
+        <v>2.234976874829218</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>187.3545454545455</v>
+        <v>273.2727272727273</v>
       </c>
       <c r="B56">
-        <v>0.01709155136140432</v>
+        <v>2.237542324345223</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>190.7333333333333</v>
+        <v>278.2222222222222</v>
       </c>
       <c r="B57">
-        <v>0.01680452796754974</v>
+        <v>2.24006458910128</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>194.1121212121212</v>
+        <v>283.1717171717172</v>
       </c>
       <c r="B58">
-        <v>0.0165272390468431</v>
+        <v>2.242545145185469</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>197.4909090909091</v>
+        <v>288.1212121212121</v>
       </c>
       <c r="B59">
-        <v>0.01625919348399371</v>
+        <v>2.244985393512151</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>200.869696969697</v>
+        <v>293.0707070707071</v>
       </c>
       <c r="B60">
-        <v>0.01599993278875608</v>
+        <v>2.247386664866469</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>204.2484848484848</v>
+        <v>298.020202020202</v>
       </c>
       <c r="B61">
-        <v>0.01574902842455767</v>
+        <v>2.249750224531466</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>207.6272727272728</v>
+        <v>302.969696969697</v>
       </c>
       <c r="B62">
-        <v>0.01550607939579167</v>
+        <v>2.252077276538662</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>211.0060606060606</v>
+        <v>307.9191919191919</v>
       </c>
       <c r="B63">
-        <v>0.01527071006498598</v>
+        <v>2.254368967578351</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>214.3848484848485</v>
+        <v>312.8686868686869</v>
       </c>
       <c r="B64">
-        <v>0.0150425681746673</v>
+        <v>2.256626390601844</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>217.7636363636364</v>
+        <v>317.8181818181818</v>
       </c>
       <c r="B65">
-        <v>0.01482132305184568</v>
+        <v>2.258850588144396</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>221.1424242424243</v>
+        <v>322.7676767676768</v>
       </c>
       <c r="B66">
-        <v>0.01460666397572636</v>
+        <v>2.261042555394444</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>224.5212121212121</v>
+        <v>327.7171717171718</v>
       </c>
       <c r="B67">
-        <v>0.01439829869157622</v>
+        <v>2.26320324303211</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>227.9</v>
+        <v>332.6666666666667</v>
       </c>
       <c r="B68">
-        <v>0.01419595205568452</v>
+        <v>2.265333559857502</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>231.2787878787879</v>
+        <v>337.6161616161617</v>
       </c>
       <c r="B69">
-        <v>0.01399936479810706</v>
+        <v>2.267434375227262</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>234.6575757575758</v>
+        <v>342.5656565656566</v>
       </c>
       <c r="B70">
-        <v>0.01380829239140649</v>
+        <v>2.26950652131594</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>238.0363636363637</v>
+        <v>347.5151515151516</v>
       </c>
       <c r="B71">
-        <v>0.01362250401493192</v>
+        <v>2.271550795217121</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>241.4151515151515</v>
+        <v>352.4646464646465</v>
       </c>
       <c r="B72">
-        <v>0.01344178160534442</v>
+        <v>2.27356796089776</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>244.7939393939394</v>
+        <v>357.4141414141415</v>
       </c>
       <c r="B73">
-        <v>0.01326591898511502</v>
+        <v>2.275558751017902</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>248.1727272727273</v>
+        <v>362.3636363636364</v>
       </c>
       <c r="B74">
-        <v>0.013094721061617</v>
+        <v>2.27752386862677</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>251.5515151515152</v>
+        <v>367.3131313131314</v>
       </c>
       <c r="B75">
-        <v>0.01292800309022271</v>
+        <v>2.279463988745188</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>254.930303030303</v>
+        <v>372.2626262626263</v>
       </c>
       <c r="B76">
-        <v>0.01276558999550886</v>
+        <v>2.281379759843382</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>258.3090909090909</v>
+        <v>377.2121212121212</v>
       </c>
       <c r="B77">
-        <v>0.01260731574528809</v>
+        <v>2.283271805222359</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>261.6878787878788</v>
+        <v>382.1616161616162</v>
       </c>
       <c r="B78">
-        <v>0.01245302277272614</v>
+        <v>2.28514072430634</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>265.0666666666667</v>
+        <v>387.1111111111111</v>
       </c>
       <c r="B79">
-        <v>0.01230256144228506</v>
+        <v>2.286987093853039</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>268.4454545454545</v>
+        <v>392.0606060606061</v>
       </c>
       <c r="B80">
-        <v>0.01215578955565855</v>
+        <v>2.28881146908799</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>271.8242424242424</v>
+        <v>397.010101010101</v>
       </c>
       <c r="B81">
-        <v>0.01201257189424466</v>
+        <v>2.290614384768581</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82">
-        <v>275.2030303030303</v>
+        <v>401.959595959596</v>
       </c>
       <c r="B82">
-        <v>0.01187277979503844</v>
+        <v>2.292396356182973</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83">
-        <v>278.5818181818182</v>
+        <v>406.9090909090909</v>
       </c>
       <c r="B83">
-        <v>0.01173629075712732</v>
+        <v>2.294157880088628</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84">
-        <v>281.960606060606</v>
+        <v>411.8585858585859</v>
       </c>
       <c r="B84">
-        <v>0.0116029880762408</v>
+        <v>2.2958994355948</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85">
-        <v>285.3393939393939</v>
+        <v>416.8080808080808</v>
       </c>
       <c r="B85">
-        <v>0.01147276050504557</v>
+        <v>2.297621484992936</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86">
-        <v>288.7181818181818</v>
+        <v>421.7575757575758</v>
       </c>
       <c r="B86">
-        <v>0.01134550193709238</v>
+        <v>2.29932447453868</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87">
-        <v>292.0969696969697</v>
+        <v>426.7070707070707</v>
       </c>
       <c r="B87">
-        <v>0.01122111111251317</v>
+        <v>2.301008835188793</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88">
-        <v>295.4757575757575</v>
+        <v>431.6565656565657</v>
       </c>
       <c r="B88">
-        <v>0.01109949134373992</v>
+        <v>2.302674983296105</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89">
-        <v>298.8545454545454</v>
+        <v>436.6060606060606</v>
       </c>
       <c r="B89">
-        <v>0.01098055025967232</v>
+        <v>2.304323321265331</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90">
-        <v>302.2333333333333</v>
+        <v>441.5555555555556</v>
       </c>
       <c r="B90">
-        <v>0.01086419956686064</v>
+        <v>2.305954238172375</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91">
-        <v>305.6121212121212</v>
+        <v>446.5050505050505</v>
       </c>
       <c r="B91">
-        <v>0.01075035482639666</v>
+        <v>2.307568110349527</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92">
-        <v>308.9909090909091</v>
+        <v>451.4545454545455</v>
       </c>
       <c r="B92">
-        <v>0.01063893524531896</v>
+        <v>2.309165301938808</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93">
-        <v>312.369696969697</v>
+        <v>456.4040404040404</v>
       </c>
       <c r="B93">
-        <v>0.01052986348144133</v>
+        <v>2.310746165415508</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94">
-        <v>315.7484848484848</v>
+        <v>461.3535353535354</v>
       </c>
       <c r="B94">
-        <v>0.01042306546060632</v>
+        <v>2.312311042083833</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95">
-        <v>319.1272727272727</v>
+        <v>466.3030303030303</v>
       </c>
       <c r="B95">
-        <v>0.01031847020544955</v>
+        <v>2.31386026254643</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96">
-        <v>322.5060606060606</v>
+        <v>471.2525252525253</v>
       </c>
       <c r="B96">
-        <v>0.01021600967483671</v>
+        <v>2.315394147149425</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97">
-        <v>325.8848484848485</v>
+        <v>476.2020202020202</v>
       </c>
       <c r="B97">
-        <v>0.01011561861320442</v>
+        <v>2.316913006404496</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98">
-        <v>329.2636363636364</v>
+        <v>481.1515151515152</v>
       </c>
       <c r="B98">
-        <v>0.01001723440909843</v>
+        <v>2.318417141389393</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99">
-        <v>332.6424242424242</v>
+        <v>486.1010101010102</v>
       </c>
       <c r="B99">
-        <v>0.009920796962260125</v>
+        <v>2.319906844128206</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100">
-        <v>336.0212121212121</v>
+        <v>491.0505050505051</v>
       </c>
       <c r="B100">
-        <v>0.009826248558663993</v>
+        <v>2.321382397952612</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101">
-        <v>339.4</v>
+        <v>496</v>
       </c>
       <c r="B101">
-        <v>0.009733533752955834</v>
+        <v>2.322844077845233</v>
       </c>
     </row>
   </sheetData>
@@ -2905,25 +2905,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>0.8749603165604457</v>
+        <v>1.273664878302853</v>
       </c>
       <c r="D2">
-        <v>0.54381</v>
+        <v>3.1</v>
       </c>
       <c r="E2">
-        <v>0.08774793272651941</v>
+        <v>0.5666666666666665</v>
       </c>
       <c r="F2">
-        <v>0.6901960800285137</v>
+        <v>0.7781512503836436</v>
       </c>
       <c r="G2">
-        <v>-0.2645528105313652</v>
+        <v>0.4913616938342727</v>
       </c>
       <c r="H2">
-        <v>-0.1883687288611057</v>
+        <v>0.5814355492798631</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2931,25 +2931,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>15.1</v>
+        <v>16.5</v>
       </c>
       <c r="C3">
-        <v>1.494062322067665</v>
+        <v>2.944863701807305</v>
       </c>
       <c r="D3">
-        <v>0.160176</v>
+        <v>6.6</v>
       </c>
       <c r="E3">
-        <v>0.02307557738292924</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="F3">
-        <v>1.178976947293169</v>
+        <v>1.217483944213906</v>
       </c>
       <c r="G3">
-        <v>-0.79540255596962</v>
+        <v>0.8195439355418687</v>
       </c>
       <c r="H3">
-        <v>-0.7028767673401117</v>
+        <v>0.835477306763505</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2957,25 +2957,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>38.7</v>
+        <v>31.4</v>
       </c>
       <c r="C4">
-        <v>7.03964961249256</v>
+        <v>6.491361781458322</v>
       </c>
       <c r="D4">
-        <v>0.096871</v>
+        <v>11.3</v>
       </c>
       <c r="E4">
-        <v>0.02955341012284182</v>
+        <v>2.022374841615668</v>
       </c>
       <c r="F4">
-        <v>1.587710965018911</v>
+        <v>1.496929648073215</v>
       </c>
       <c r="G4">
-        <v>-1.013806217015109</v>
+        <v>1.05307844348342</v>
       </c>
       <c r="H4">
-        <v>-1.13312465919519</v>
+        <v>0.9970652758052525</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2983,25 +2983,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>55.9</v>
+        <v>50</v>
       </c>
       <c r="C5">
-        <v>10.85505514597794</v>
+        <v>7.049034606872695</v>
       </c>
       <c r="D5">
-        <v>0.077846</v>
+        <v>14.9</v>
       </c>
       <c r="E5">
-        <v>0.03040207913942729</v>
+        <v>1.394034911088432</v>
       </c>
       <c r="F5">
-        <v>1.747411807886423</v>
+        <v>1.698970004336019</v>
       </c>
       <c r="G5">
-        <v>-1.108763698093395</v>
+        <v>1.173186268412274</v>
       </c>
       <c r="H5">
-        <v>-1.301231418093175</v>
+        <v>1.11389402064584</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3009,25 +3009,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>78.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="C6">
-        <v>14.12755384975678</v>
+        <v>12.8</v>
       </c>
       <c r="D6">
-        <v>0.039588</v>
+        <v>18.8</v>
       </c>
       <c r="E6">
-        <v>0.007898477462284881</v>
+        <v>2.230097157823697</v>
       </c>
       <c r="F6">
-        <v>1.8926510338773</v>
+        <v>1.887617300335736</v>
       </c>
       <c r="G6">
-        <v>-1.402436438407031</v>
+        <v>1.27415784926368</v>
       </c>
       <c r="H6">
-        <v>-1.454115367280804</v>
+        <v>1.222978300721797</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3035,25 +3035,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>167.1</v>
+        <v>156.8</v>
       </c>
       <c r="C7">
-        <v>13.01405223424109</v>
+        <v>19.21214893411631</v>
       </c>
       <c r="D7">
-        <v>0.013829</v>
+        <v>26.5</v>
       </c>
       <c r="E7">
-        <v>0.0009057574485233646</v>
+        <v>1.035481637800604</v>
       </c>
       <c r="F7">
-        <v>2.222976449893391</v>
+        <v>2.19534605834842</v>
       </c>
       <c r="G7">
-        <v>-1.859209223374698</v>
+        <v>1.423245873936808</v>
       </c>
       <c r="H7">
-        <v>-1.801827590153425</v>
+        <v>1.40092079307818</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -3061,25 +3061,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>215.3</v>
+        <v>157.3</v>
       </c>
       <c r="C8">
-        <v>14.01590366532089</v>
+        <v>17.51002887236658</v>
       </c>
       <c r="D8">
-        <v>0.010871</v>
+        <v>28.5</v>
       </c>
       <c r="E8">
-        <v>0.0007843078335563005</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="F8">
-        <v>2.333044029823487</v>
+        <v>2.196728722623287</v>
       </c>
       <c r="G8">
-        <v>-1.963730504257185</v>
+        <v>1.45484486000851</v>
       </c>
       <c r="H8">
-        <v>-1.917688619998731</v>
+        <v>1.401720311227705</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3087,25 +3087,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>276.4</v>
+        <v>268.4</v>
       </c>
       <c r="C9">
-        <v>24.80913810137976</v>
+        <v>15.93751688452264</v>
       </c>
       <c r="D9">
-        <v>0.008915000000000001</v>
+        <v>34.2</v>
       </c>
       <c r="E9">
-        <v>0.001054587070321312</v>
+        <v>1.093414631123782</v>
       </c>
       <c r="F9">
-        <v>2.441538038702161</v>
+        <v>2.428782511496955</v>
       </c>
       <c r="G9">
-        <v>-2.049878652488626</v>
+        <v>1.534026106056135</v>
       </c>
       <c r="H9">
-        <v>-2.031893253267785</v>
+        <v>1.535904161380638</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -3113,25 +3113,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>339.4</v>
+        <v>311.6</v>
       </c>
       <c r="C10">
-        <v>27.14496065366256</v>
+        <v>26.19847323795797</v>
       </c>
       <c r="D10">
-        <v>0.007071000000000001</v>
+        <v>35.2</v>
       </c>
       <c r="E10">
-        <v>0.0006898702776609526</v>
+        <v>0.7118052168020874</v>
       </c>
       <c r="F10">
-        <v>2.530711837981657</v>
+        <v>2.493597449000527</v>
       </c>
       <c r="G10">
-        <v>-2.150519162756014</v>
+        <v>1.546542663478131</v>
       </c>
       <c r="H10">
-        <v>-2.125760750184704</v>
+        <v>1.57338304894315</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3139,25 +3139,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>312.8</v>
+        <v>343.4</v>
       </c>
       <c r="C11">
-        <v>30.94719516998089</v>
+        <v>28.52297319705644</v>
       </c>
       <c r="D11">
-        <v>0.007683</v>
+        <v>37.9</v>
       </c>
       <c r="E11">
-        <v>0.0006173546612586461</v>
+        <v>0.7810249675906654</v>
       </c>
       <c r="F11">
-        <v>2.49526674438781</v>
+        <v>2.535800290824898</v>
       </c>
       <c r="G11">
-        <v>-2.114469166811908</v>
+        <v>1.578639209968072</v>
       </c>
       <c r="H11">
-        <v>-2.088449990291968</v>
+        <v>1.597786614301319</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -3165,25 +3165,25 @@
         <v>638</v>
       </c>
       <c r="B12">
-        <v>286</v>
+        <v>496</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0.00851</v>
+        <v>40</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>2.456366033129043</v>
+        <v>2.695481676490198</v>
       </c>
       <c r="G12">
-        <v>-2.070070439915412</v>
+        <v>1.602059991327962</v>
       </c>
       <c r="H12">
-        <v>-2.047501724953364</v>
+        <v>1.690121513163885</v>
       </c>
     </row>
   </sheetData>
@@ -3206,802 +3206,802 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>0.5398045483159717</v>
+        <v>5.66198792140861</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>8.278787878787879</v>
+        <v>10.94949494949495</v>
       </c>
       <c r="B3">
-        <v>0.3284083995079981</v>
+        <v>7.474959053098556</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>11.65757575757576</v>
+        <v>15.8989898989899</v>
       </c>
       <c r="B4">
-        <v>0.2374489201543626</v>
+        <v>8.879894374116928</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>15.03636363636364</v>
+        <v>20.84848484848485</v>
       </c>
       <c r="B5">
-        <v>0.1865666643680177</v>
+        <v>10.06382377374156</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>18.41515151515151</v>
+        <v>25.7979797979798</v>
       </c>
       <c r="B6">
-        <v>0.1539641388384904</v>
+        <v>11.10411535929186</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>21.7939393939394</v>
+        <v>30.74747474747475</v>
       </c>
       <c r="B7">
-        <v>0.1312492966062286</v>
+        <v>12.0415804968403</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>25.17272727272727</v>
+        <v>35.6969696969697</v>
       </c>
       <c r="B8">
-        <v>0.1144948720744534</v>
+        <v>12.90083240864015</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>28.55151515151515</v>
+        <v>40.64646464646465</v>
       </c>
       <c r="B9">
-        <v>0.1016147002929615</v>
+        <v>13.69805321732124</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>31.93030303030303</v>
+        <v>45.5959595959596</v>
       </c>
       <c r="B10">
-        <v>0.0913967491010062</v>
+        <v>14.44454710712743</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>35.30909090909091</v>
+        <v>50.54545454545455</v>
       </c>
       <c r="B11">
-        <v>0.08308809485423957</v>
+        <v>15.14857494310264</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>38.68787878787879</v>
+        <v>55.49494949494949</v>
       </c>
       <c r="B12">
-        <v>0.07619603829433115</v>
+        <v>15.81638801519555</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>42.06666666666667</v>
+        <v>60.44444444444445</v>
       </c>
       <c r="B13">
-        <v>0.07038445451469259</v>
+        <v>16.45285047275812</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>45.44545454545455</v>
+        <v>65.39393939393941</v>
       </c>
       <c r="B14">
-        <v>0.06541607560131416</v>
+        <v>17.0618342083371</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>48.82424242424242</v>
+        <v>70.34343434343435</v>
       </c>
       <c r="B15">
-        <v>0.06111857673102275</v>
+        <v>17.64648020420153</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>52.2030303030303</v>
+        <v>75.2929292929293</v>
       </c>
       <c r="B16">
-        <v>0.05736374168613149</v>
+        <v>18.20937765834915</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>55.58181818181819</v>
+        <v>80.24242424242425</v>
       </c>
       <c r="B17">
-        <v>0.05405417411447415</v>
+        <v>18.7526904251764</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>58.96060606060606</v>
+        <v>85.1919191919192</v>
       </c>
       <c r="B18">
-        <v>0.05111454534972518</v>
+        <v>19.27824853836678</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>62.33939393939394</v>
+        <v>90.14141414141415</v>
       </c>
       <c r="B19">
-        <v>0.0484856678716831</v>
+        <v>19.78761591309307</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>65.71818181818182</v>
+        <v>95.09090909090909</v>
       </c>
       <c r="B20">
-        <v>0.04612038362129586</v>
+        <v>20.28214138565716</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>69.09696969696971</v>
+        <v>100.040404040404</v>
       </c>
       <c r="B21">
-        <v>0.04398064975636115</v>
+        <v>20.76299783920173</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>72.47575757575758</v>
+        <v>104.989898989899</v>
       </c>
       <c r="B22">
-        <v>0.04203543349690217</v>
+        <v>21.23121264421505</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>75.85454545454546</v>
+        <v>109.939393939394</v>
       </c>
       <c r="B23">
-        <v>0.04025916536229642</v>
+        <v>21.68769165749161</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>79.23333333333335</v>
+        <v>114.8888888888889</v>
       </c>
       <c r="B24">
-        <v>0.0386305851690889</v>
+        <v>22.13323836928446</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>82.61212121212122</v>
+        <v>119.8383838383838</v>
       </c>
       <c r="B25">
-        <v>0.03713186905886506</v>
+        <v>22.56856934486709</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>85.9909090909091</v>
+        <v>124.7878787878788</v>
       </c>
       <c r="B26">
-        <v>0.03574796075508859</v>
+        <v>22.99432680005626</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>89.36969696969697</v>
+        <v>129.7373737373737</v>
       </c>
       <c r="B27">
-        <v>0.03446605334880411</v>
+        <v>23.41108893447495</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>92.74848484848485</v>
+        <v>134.6868686868687</v>
       </c>
       <c r="B28">
-        <v>0.03327518347648203</v>
+        <v>23.81937849209228</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>96.12727272727274</v>
+        <v>139.6363636363637</v>
       </c>
       <c r="B29">
-        <v>0.03216591041717451</v>
+        <v>24.21966990671201</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>99.50606060606061</v>
+        <v>144.5858585858586</v>
       </c>
       <c r="B30">
-        <v>0.03113006005706683</v>
+        <v>24.61239530786796</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>102.8848484848485</v>
+        <v>149.5353535353536</v>
       </c>
       <c r="B31">
-        <v>0.03016051890784841</v>
+        <v>24.99794960142191</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>106.2636363636364</v>
+        <v>154.4848484848485</v>
       </c>
       <c r="B32">
-        <v>0.02925106711204735</v>
+        <v>25.3766947931423</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>109.6424242424243</v>
+        <v>159.4343434343434</v>
       </c>
       <c r="B33">
-        <v>0.02839624208121811</v>
+        <v>25.74896368855654</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>113.0212121212121</v>
+        <v>164.3838383838384</v>
       </c>
       <c r="B34">
-        <v>0.02759122639938759</v>
+        <v>26.11506307551329</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>116.4</v>
+        <v>169.3333333333333</v>
       </c>
       <c r="B35">
-        <v>0.02683175509432052</v>
+        <v>26.47527647508695</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>119.7787878787879</v>
+        <v>174.2828282828283</v>
       </c>
       <c r="B36">
-        <v>0.02611403847796769</v>
+        <v>26.82986653020564</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>123.1575757575758</v>
+        <v>179.2323232323232</v>
       </c>
       <c r="B37">
-        <v>0.0254346975863321</v>
+        <v>27.1790770885887</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>126.5363636363636</v>
+        <v>184.1818181818182</v>
       </c>
       <c r="B38">
-        <v>0.02479070987968223</v>
+        <v>27.52313502643036</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>129.9151515151515</v>
+        <v>189.1313131313131</v>
       </c>
       <c r="B39">
-        <v>0.02417936334786408</v>
+        <v>27.86225185116032</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>133.2939393939394</v>
+        <v>194.0808080808081</v>
       </c>
       <c r="B40">
-        <v>0.02359821753947685</v>
+        <v>28.19662511509476</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>136.6727272727273</v>
+        <v>199.030303030303</v>
       </c>
       <c r="B41">
-        <v>0.02304507032490236</v>
+        <v>28.52643966651966</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>140.0515151515152</v>
+        <v>203.979797979798</v>
       </c>
       <c r="B42">
-        <v>0.02251792943149735</v>
+        <v>28.85186876045853</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>143.430303030303</v>
+        <v>208.929292929293</v>
       </c>
       <c r="B43">
-        <v>0.02201498796942169</v>
+        <v>29.17307504786788</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>146.8090909090909</v>
+        <v>213.8787878787879</v>
       </c>
       <c r="B44">
-        <v>0.02153460330961525</v>
+        <v>29.4902114591167</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>150.1878787878788</v>
+        <v>218.8282828282829</v>
       </c>
       <c r="B45">
-        <v>0.02107527878966524</v>
+        <v>29.80342199522129</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>153.5666666666667</v>
+        <v>223.7777777777778</v>
       </c>
       <c r="B46">
-        <v>0.02063564781503395</v>
+        <v>30.1128424383253</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>156.9454545454546</v>
+        <v>228.7272727272727</v>
       </c>
       <c r="B47">
-        <v>0.02021445999716518</v>
+        <v>30.41860099126242</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>160.3242424242424</v>
+        <v>233.6767676767677</v>
       </c>
       <c r="B48">
-        <v>0.0198105690300645</v>
+        <v>30.72081885465492</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>163.7030303030303</v>
+        <v>238.6262626262626</v>
       </c>
       <c r="B49">
-        <v>0.01942292205592545</v>
+        <v>31.01961074883639</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>167.0818181818182</v>
+        <v>243.5757575757576</v>
       </c>
       <c r="B50">
-        <v>0.01905055031048268</v>
+        <v>31.31508538690397</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>170.4606060606061</v>
+        <v>248.5252525252525</v>
       </c>
       <c r="B51">
-        <v>0.01869256087176563</v>
+        <v>31.60734590437189</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>173.8393939393939</v>
+        <v>253.4747474747475</v>
       </c>
       <c r="B52">
-        <v>0.01834812936317774</v>
+        <v>31.89649025018883</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>177.2181818181818</v>
+        <v>258.4242424242424</v>
       </c>
       <c r="B53">
-        <v>0.01801649348442664</v>
+        <v>32.18261154327715</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>180.5969696969697</v>
+        <v>263.3737373737374</v>
       </c>
       <c r="B54">
-        <v>0.01769694726264558</v>
+        <v>32.46579839823307</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>183.9757575757576</v>
+        <v>268.3232323232323</v>
       </c>
       <c r="B55">
-        <v>0.01738883593176847</v>
+        <v>32.74613522338262</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>187.3545454545455</v>
+        <v>273.2727272727273</v>
       </c>
       <c r="B56">
-        <v>0.01709155136140432</v>
+        <v>33.02370249400405</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>190.7333333333333</v>
+        <v>278.2222222222222</v>
       </c>
       <c r="B57">
-        <v>0.01680452796754974</v>
+        <v>33.29857700319631</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>194.1121212121212</v>
+        <v>283.1717171717172</v>
       </c>
       <c r="B58">
-        <v>0.0165272390468431</v>
+        <v>33.57083209258622</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>197.4909090909091</v>
+        <v>288.1212121212121</v>
       </c>
       <c r="B59">
-        <v>0.01625919348399371</v>
+        <v>33.84053786481708</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>200.869696969697</v>
+        <v>293.0707070707071</v>
       </c>
       <c r="B60">
-        <v>0.01599993278875608</v>
+        <v>34.10776137954467</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>204.2484848484848</v>
+        <v>298.020202020202</v>
       </c>
       <c r="B61">
-        <v>0.01574902842455767</v>
+        <v>34.37256683447649</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>207.6272727272728</v>
+        <v>302.969696969697</v>
       </c>
       <c r="B62">
-        <v>0.01550607939579167</v>
+        <v>34.63501573282411</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>211.0060606060606</v>
+        <v>307.9191919191919</v>
       </c>
       <c r="B63">
-        <v>0.01527071006498598</v>
+        <v>34.89516703839288</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>214.3848484848485</v>
+        <v>312.8686868686869</v>
       </c>
       <c r="B64">
-        <v>0.0150425681746673</v>
+        <v>35.15307731940494</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>217.7636363636364</v>
+        <v>317.8181818181818</v>
       </c>
       <c r="B65">
-        <v>0.01482132305184568</v>
+        <v>35.40880088203876</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>221.1424242424243</v>
+        <v>322.7676767676768</v>
       </c>
       <c r="B66">
-        <v>0.01460666397572636</v>
+        <v>35.66238989456853</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>224.5212121212121</v>
+        <v>327.7171717171718</v>
       </c>
       <c r="B67">
-        <v>0.01439829869157622</v>
+        <v>35.91389450289861</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>227.9</v>
+        <v>332.6666666666667</v>
       </c>
       <c r="B68">
-        <v>0.01419595205568452</v>
+        <v>36.16336293821002</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>231.2787878787879</v>
+        <v>337.6161616161617</v>
       </c>
       <c r="B69">
-        <v>0.01399936479810706</v>
+        <v>36.41084161736654</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>234.6575757575758</v>
+        <v>342.5656565656566</v>
       </c>
       <c r="B70">
-        <v>0.01380829239140649</v>
+        <v>36.65637523666582</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>238.0363636363637</v>
+        <v>347.5151515151516</v>
       </c>
       <c r="B71">
-        <v>0.01362250401493192</v>
+        <v>36.90000685946637</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>241.4151515151515</v>
+        <v>352.4646464646465</v>
       </c>
       <c r="B72">
-        <v>0.01344178160534442</v>
+        <v>37.14177799817146</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>244.7939393939394</v>
+        <v>357.4141414141415</v>
       </c>
       <c r="B73">
-        <v>0.01326591898511502</v>
+        <v>37.38172869100734</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>248.1727272727273</v>
+        <v>362.3636363636364</v>
       </c>
       <c r="B74">
-        <v>0.013094721061617</v>
+        <v>37.61989757399358</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>251.5515151515152</v>
+        <v>367.3131313131314</v>
       </c>
       <c r="B75">
-        <v>0.01292800309022271</v>
+        <v>37.85632194846798</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>254.930303030303</v>
+        <v>372.2626262626263</v>
       </c>
       <c r="B76">
-        <v>0.01276558999550886</v>
+        <v>38.09103784449657</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>258.3090909090909</v>
+        <v>377.2121212121212</v>
       </c>
       <c r="B77">
-        <v>0.01260731574528809</v>
+        <v>38.32408008047075</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>261.6878787878788</v>
+        <v>382.1616161616162</v>
       </c>
       <c r="B78">
-        <v>0.01245302277272614</v>
+        <v>38.5554823191676</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>265.0666666666667</v>
+        <v>387.1111111111111</v>
       </c>
       <c r="B79">
-        <v>0.01230256144228506</v>
+        <v>38.78527712052637</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>268.4454545454545</v>
+        <v>392.0606060606061</v>
       </c>
       <c r="B80">
-        <v>0.01215578955565855</v>
+        <v>39.01349599137271</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>271.8242424242424</v>
+        <v>397.010101010101</v>
       </c>
       <c r="B81">
-        <v>0.01201257189424466</v>
+        <v>39.2401694323035</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82">
-        <v>275.2030303030303</v>
+        <v>401.959595959596</v>
       </c>
       <c r="B82">
-        <v>0.01187277979503844</v>
+        <v>39.46532698192765</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83">
-        <v>278.5818181818182</v>
+        <v>406.9090909090909</v>
       </c>
       <c r="B83">
-        <v>0.01173629075712732</v>
+        <v>39.68899725864252</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84">
-        <v>281.960606060606</v>
+        <v>411.8585858585859</v>
       </c>
       <c r="B84">
-        <v>0.0116029880762408</v>
+        <v>39.91120800011161</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85">
-        <v>285.3393939393939</v>
+        <v>416.8080808080808</v>
       </c>
       <c r="B85">
-        <v>0.01147276050504557</v>
+        <v>40.13198610059595</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86">
-        <v>288.7181818181818</v>
+        <v>421.7575757575758</v>
       </c>
       <c r="B86">
-        <v>0.01134550193709238</v>
+        <v>40.35135764627979</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87">
-        <v>292.0969696969697</v>
+        <v>426.7070707070707</v>
       </c>
       <c r="B87">
-        <v>0.01122111111251317</v>
+        <v>40.56934794872086</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88">
-        <v>295.4757575757575</v>
+        <v>431.6565656565657</v>
       </c>
       <c r="B88">
-        <v>0.01109949134373992</v>
+        <v>40.78598157654493</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89">
-        <v>298.8545454545454</v>
+        <v>436.6060606060606</v>
       </c>
       <c r="B89">
-        <v>0.01098055025967232</v>
+        <v>41.00128238549618</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90">
-        <v>302.2333333333333</v>
+        <v>441.5555555555556</v>
       </c>
       <c r="B90">
-        <v>0.01086419956686064</v>
+        <v>41.21527354694609</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91">
-        <v>305.6121212121212</v>
+        <v>446.5050505050505</v>
       </c>
       <c r="B91">
-        <v>0.01075035482639666</v>
+        <v>41.42797757495629</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92">
-        <v>308.9909090909091</v>
+        <v>451.4545454545455</v>
       </c>
       <c r="B92">
-        <v>0.01063893524531896</v>
+        <v>41.63941635198401</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93">
-        <v>312.369696969697</v>
+        <v>456.4040404040404</v>
       </c>
       <c r="B93">
-        <v>0.01052986348144133</v>
+        <v>41.8496111533121</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94">
-        <v>315.7484848484848</v>
+        <v>461.3535353535354</v>
       </c>
       <c r="B94">
-        <v>0.01042306546060632</v>
+        <v>42.05858267028029</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95">
-        <v>319.1272727272727</v>
+        <v>466.3030303030303</v>
       </c>
       <c r="B95">
-        <v>0.01031847020544955</v>
+        <v>42.26635103238843</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96">
-        <v>322.5060606060606</v>
+        <v>471.2525252525253</v>
       </c>
       <c r="B96">
-        <v>0.01021600967483671</v>
+        <v>42.47293582833804</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97">
-        <v>325.8848484848485</v>
+        <v>476.2020202020202</v>
       </c>
       <c r="B97">
-        <v>0.01011561861320442</v>
+        <v>42.67835612607366</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98">
-        <v>329.2636363636364</v>
+        <v>481.1515151515152</v>
       </c>
       <c r="B98">
-        <v>0.01001723440909843</v>
+        <v>42.8826304918814</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99">
-        <v>332.6424242424242</v>
+        <v>486.1010101010102</v>
       </c>
       <c r="B99">
-        <v>0.009920796962260125</v>
+        <v>43.08577700859843</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100">
-        <v>336.0212121212121</v>
+        <v>491.0505050505051</v>
       </c>
       <c r="B100">
-        <v>0.009826248558663993</v>
+        <v>43.28781329298308</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101">
-        <v>339.4</v>
+        <v>496</v>
       </c>
       <c r="B101">
-        <v>0.009733533752955834</v>
+        <v>43.48875651229272</v>
       </c>
     </row>
   </sheetData>
@@ -4045,25 +4045,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>0.8749603165604457</v>
+        <v>1.273664878302853</v>
       </c>
       <c r="D2">
-        <v>0.54381</v>
+        <v>0.482737</v>
       </c>
       <c r="E2">
-        <v>0.08774793272651941</v>
+        <v>0.09437648425381776</v>
       </c>
       <c r="F2">
-        <v>0.6901960800285137</v>
+        <v>0.7781512503836436</v>
       </c>
       <c r="G2">
-        <v>-0.2645528105313652</v>
+        <v>-0.3162894128448587</v>
       </c>
       <c r="H2">
-        <v>-0.1883687288611057</v>
+        <v>-0.2209149646077408</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4071,25 +4071,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>15.1</v>
+        <v>16.5</v>
       </c>
       <c r="C3">
-        <v>1.494062322067665</v>
+        <v>2.944863701807305</v>
       </c>
       <c r="D3">
-        <v>0.160176</v>
+        <v>0.207871</v>
       </c>
       <c r="E3">
-        <v>0.02307557738292924</v>
+        <v>0.05391448311807216</v>
       </c>
       <c r="F3">
-        <v>1.178976947293169</v>
+        <v>1.217483944213906</v>
       </c>
       <c r="G3">
-        <v>-0.79540255596962</v>
+        <v>-0.6822060946919265</v>
       </c>
       <c r="H3">
-        <v>-0.7028767673401117</v>
+        <v>-0.7032441531724856</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4097,25 +4097,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>38.7</v>
+        <v>31.4</v>
       </c>
       <c r="C4">
-        <v>7.03964961249256</v>
+        <v>6.491361781458322</v>
       </c>
       <c r="D4">
-        <v>0.096871</v>
+        <v>0.130971</v>
       </c>
       <c r="E4">
-        <v>0.02955341012284182</v>
+        <v>0.03730612852393617</v>
       </c>
       <c r="F4">
-        <v>1.587710965018911</v>
+        <v>1.496929648073215</v>
       </c>
       <c r="G4">
-        <v>-1.013806217015109</v>
+        <v>-0.882824856513954</v>
       </c>
       <c r="H4">
-        <v>-1.13312465919519</v>
+        <v>-1.010038574537445</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4123,25 +4123,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>55.9</v>
+        <v>50</v>
       </c>
       <c r="C5">
-        <v>10.85505514597794</v>
+        <v>7.049034606872695</v>
       </c>
       <c r="D5">
-        <v>0.077846</v>
+        <v>0.054354</v>
       </c>
       <c r="E5">
-        <v>0.03040207913942729</v>
+        <v>0.01008088490383877</v>
       </c>
       <c r="F5">
-        <v>1.747411807886423</v>
+        <v>1.698970004336019</v>
       </c>
       <c r="G5">
-        <v>-1.108763698093395</v>
+        <v>-1.264768489958457</v>
       </c>
       <c r="H5">
-        <v>-1.301231418093175</v>
+        <v>-1.231852162422211</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -4149,25 +4149,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>78.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="C6">
-        <v>14.12755384975678</v>
+        <v>12.8</v>
       </c>
       <c r="D6">
-        <v>0.039588</v>
+        <v>0.042733</v>
       </c>
       <c r="E6">
-        <v>0.007898477462284881</v>
+        <v>0.01217511743498007</v>
       </c>
       <c r="F6">
-        <v>1.8926510338773</v>
+        <v>1.887617300335736</v>
       </c>
       <c r="G6">
-        <v>-1.402436438407031</v>
+        <v>-1.36923661718254</v>
       </c>
       <c r="H6">
-        <v>-1.454115367280804</v>
+        <v>-1.438961941599336</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4175,25 +4175,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>167.1</v>
+        <v>156.8</v>
       </c>
       <c r="C7">
-        <v>13.01405223424109</v>
+        <v>19.21214893411631</v>
       </c>
       <c r="D7">
-        <v>0.013829</v>
+        <v>0.016318</v>
       </c>
       <c r="E7">
-        <v>0.0009057574485233646</v>
+        <v>0.002021445467426163</v>
       </c>
       <c r="F7">
-        <v>2.222976449893391</v>
+        <v>2.19534605834842</v>
       </c>
       <c r="G7">
-        <v>-1.859209223374698</v>
+        <v>-1.787333071206577</v>
       </c>
       <c r="H7">
-        <v>-1.801827590153425</v>
+        <v>-1.776807415507179</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -4201,25 +4201,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>215.3</v>
+        <v>157.3</v>
       </c>
       <c r="C8">
-        <v>14.01590366532089</v>
+        <v>17.51002887236658</v>
       </c>
       <c r="D8">
-        <v>0.010871</v>
+        <v>0.016206</v>
       </c>
       <c r="E8">
-        <v>0.0007843078335563005</v>
+        <v>0.00285167288134916</v>
       </c>
       <c r="F8">
-        <v>2.333044029823487</v>
+        <v>2.196728722623287</v>
       </c>
       <c r="G8">
-        <v>-1.963730504257185</v>
+        <v>-1.790324165428905</v>
       </c>
       <c r="H8">
-        <v>-1.917688619998731</v>
+        <v>-1.778325397999991</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -4227,25 +4227,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>276.4</v>
+        <v>268.4</v>
       </c>
       <c r="C9">
-        <v>24.80913810137976</v>
+        <v>15.93751688452264</v>
       </c>
       <c r="D9">
-        <v>0.008915000000000001</v>
+        <v>0.008544999999999999</v>
       </c>
       <c r="E9">
-        <v>0.001054587070321312</v>
+        <v>0.0005071428683210371</v>
       </c>
       <c r="F9">
-        <v>2.441538038702161</v>
+        <v>2.428782511496955</v>
       </c>
       <c r="G9">
-        <v>-2.049878652488626</v>
+        <v>-2.068287932943245</v>
       </c>
       <c r="H9">
-        <v>-2.031893253267785</v>
+        <v>-2.033089765101825</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -4253,25 +4253,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>339.4</v>
+        <v>311.6</v>
       </c>
       <c r="C10">
-        <v>27.14496065366256</v>
+        <v>26.19847323795797</v>
       </c>
       <c r="D10">
-        <v>0.007071000000000001</v>
+        <v>0.007674</v>
       </c>
       <c r="E10">
-        <v>0.0006898702776609526</v>
+        <v>0.0006741384625332295</v>
       </c>
       <c r="F10">
-        <v>2.530711837981657</v>
+        <v>2.493597449000527</v>
       </c>
       <c r="G10">
-        <v>-2.150519162756014</v>
+        <v>-2.114978205137703</v>
       </c>
       <c r="H10">
-        <v>-2.125760750184704</v>
+        <v>-2.104247993596996</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -4279,25 +4279,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>312.8</v>
+        <v>343.4</v>
       </c>
       <c r="C11">
-        <v>30.94719516998089</v>
+        <v>28.52297319705644</v>
       </c>
       <c r="D11">
-        <v>0.007683</v>
+        <v>0.006926</v>
       </c>
       <c r="E11">
-        <v>0.0006173546612586461</v>
+        <v>0.0005297173250370847</v>
       </c>
       <c r="F11">
-        <v>2.49526674438781</v>
+        <v>2.535800290824898</v>
       </c>
       <c r="G11">
-        <v>-2.114469166811908</v>
+        <v>-2.159517512786558</v>
       </c>
       <c r="H11">
-        <v>-2.088449990291968</v>
+        <v>-2.150581131872699</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -4305,25 +4305,25 @@
         <v>638</v>
       </c>
       <c r="B12">
-        <v>286</v>
+        <v>496</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0.00851</v>
+        <v>0.004589999999999999</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>2.891205793294678E-19</v>
       </c>
       <c r="F12">
-        <v>2.456366033129043</v>
+        <v>2.695481676490198</v>
       </c>
       <c r="G12">
-        <v>-2.070070439915412</v>
+        <v>-2.338187314462739</v>
       </c>
       <c r="H12">
-        <v>-2.047501724953364</v>
+        <v>-2.325890172739562</v>
       </c>
     </row>
   </sheetData>
@@ -4346,802 +4346,802 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>0.5398045483159717</v>
+        <v>0.4875477315086367</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>8.278787878787879</v>
+        <v>10.94949494949495</v>
       </c>
       <c r="B3">
-        <v>0.3284083995079981</v>
+        <v>0.2834110796830337</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>11.65757575757576</v>
+        <v>15.8989898989899</v>
       </c>
       <c r="B4">
-        <v>0.2374489201543626</v>
+        <v>0.2024604612236869</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>15.03636363636364</v>
+        <v>20.84848484848485</v>
       </c>
       <c r="B5">
-        <v>0.1865666643680177</v>
+        <v>0.1585581945027434</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>18.41515151515151</v>
+        <v>25.7979797979798</v>
       </c>
       <c r="B6">
-        <v>0.1539641388384904</v>
+        <v>0.1308452648313374</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>21.7939393939394</v>
+        <v>30.74747474747475</v>
       </c>
       <c r="B7">
-        <v>0.1312492966062286</v>
+        <v>0.1116904563683539</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>25.17272727272727</v>
+        <v>35.6969696969697</v>
       </c>
       <c r="B8">
-        <v>0.1144948720744534</v>
+        <v>0.09762404962657725</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>28.55151515151515</v>
+        <v>40.64646464646465</v>
       </c>
       <c r="B9">
-        <v>0.1016147002929615</v>
+        <v>0.08683614647417781</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>31.93030303030303</v>
+        <v>45.5959595959596</v>
       </c>
       <c r="B10">
-        <v>0.0913967491010062</v>
+        <v>0.07828801653308547</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>35.30909090909091</v>
+        <v>50.54545454545455</v>
       </c>
       <c r="B11">
-        <v>0.08308809485423957</v>
+        <v>0.07133991436893462</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>38.68787878787879</v>
+        <v>55.49494949494949</v>
       </c>
       <c r="B12">
-        <v>0.07619603829433115</v>
+        <v>0.06557579233850865</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>42.06666666666667</v>
+        <v>60.44444444444445</v>
       </c>
       <c r="B13">
-        <v>0.07038445451469259</v>
+        <v>0.06071311110798542</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>45.44545454545455</v>
+        <v>65.39393939393941</v>
       </c>
       <c r="B14">
-        <v>0.06541607560131416</v>
+        <v>0.05655310503935577</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>48.82424242424242</v>
+        <v>70.34343434343435</v>
       </c>
       <c r="B15">
-        <v>0.06111857673102275</v>
+        <v>0.05295177971504177</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>52.2030303030303</v>
+        <v>75.2929292929293</v>
       </c>
       <c r="B16">
-        <v>0.05736374168613149</v>
+        <v>0.04980220138445488</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>55.58181818181819</v>
+        <v>80.24242424242425</v>
       </c>
       <c r="B17">
-        <v>0.05405417411447415</v>
+        <v>0.04702325500791905</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>58.96060606060606</v>
+        <v>85.1919191919192</v>
       </c>
       <c r="B18">
-        <v>0.05111454534972518</v>
+        <v>0.0445522689441346</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>62.33939393939394</v>
+        <v>90.14141414141415</v>
       </c>
       <c r="B19">
-        <v>0.0484856678716831</v>
+        <v>0.04234003662875545</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>65.71818181818182</v>
+        <v>95.09090909090909</v>
       </c>
       <c r="B20">
-        <v>0.04612038362129586</v>
+        <v>0.04034737175077859</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>69.09696969696971</v>
+        <v>100.040404040404</v>
       </c>
       <c r="B21">
-        <v>0.04398064975636115</v>
+        <v>0.03854267190896647</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>72.47575757575758</v>
+        <v>104.989898989899</v>
       </c>
       <c r="B22">
-        <v>0.04203543349690217</v>
+        <v>0.03690016180004265</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>75.85454545454546</v>
+        <v>109.939393939394</v>
       </c>
       <c r="B23">
-        <v>0.04025916536229642</v>
+        <v>0.03539860429195095</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>79.23333333333335</v>
+        <v>114.8888888888889</v>
       </c>
       <c r="B24">
-        <v>0.0386305851690889</v>
+        <v>0.03402033994824714</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>82.61212121212122</v>
+        <v>119.8383838383838</v>
       </c>
       <c r="B25">
-        <v>0.03713186905886506</v>
+        <v>0.0327505611742873</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>85.9909090909091</v>
+        <v>124.7878787878788</v>
       </c>
       <c r="B26">
-        <v>0.03574796075508859</v>
+        <v>0.03157675662462606</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>89.36969696969697</v>
+        <v>129.7373737373737</v>
       </c>
       <c r="B27">
-        <v>0.03446605334880411</v>
+        <v>0.03048828095179117</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>92.74848484848485</v>
+        <v>134.6868686868687</v>
       </c>
       <c r="B28">
-        <v>0.03327518347648203</v>
+        <v>0.0294760180454342</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>96.12727272727274</v>
+        <v>139.6363636363637</v>
       </c>
       <c r="B29">
-        <v>0.03216591041717451</v>
+        <v>0.02853211484837238</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>99.50606060606061</v>
+        <v>144.5858585858586</v>
       </c>
       <c r="B30">
-        <v>0.03113006005706683</v>
+        <v>0.0276497690451309</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>102.8848484848485</v>
+        <v>149.5353535353536</v>
       </c>
       <c r="B31">
-        <v>0.03016051890784841</v>
+        <v>0.02682305829505003</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>106.2636363636364</v>
+        <v>154.4848484848485</v>
       </c>
       <c r="B32">
-        <v>0.02925106711204735</v>
+        <v>0.02604680180820675</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>109.6424242424243</v>
+        <v>159.4343434343434</v>
       </c>
       <c r="B33">
-        <v>0.02839624208121811</v>
+        <v>0.02531644732326848</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>113.0212121212121</v>
+        <v>164.3838383838384</v>
       </c>
       <c r="B34">
-        <v>0.02759122639938759</v>
+        <v>0.02462797820033746</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>116.4</v>
+        <v>169.3333333333333</v>
       </c>
       <c r="B35">
-        <v>0.02683175509432052</v>
+        <v>0.02397783656478548</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>119.7787878787879</v>
+        <v>174.2828282828283</v>
       </c>
       <c r="B36">
-        <v>0.02611403847796769</v>
+        <v>0.02336285935139925</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>123.1575757575758</v>
+        <v>179.2323232323232</v>
       </c>
       <c r="B37">
-        <v>0.0254346975863321</v>
+        <v>0.02278022478664015</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>126.5363636363636</v>
+        <v>184.1818181818182</v>
       </c>
       <c r="B38">
-        <v>0.02479070987968223</v>
+        <v>0.02222740737037925</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>129.9151515151515</v>
+        <v>189.1313131313131</v>
       </c>
       <c r="B39">
-        <v>0.02417936334786408</v>
+        <v>0.02170213981989436</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>133.2939393939394</v>
+        <v>194.0808080808081</v>
       </c>
       <c r="B40">
-        <v>0.02359821753947685</v>
+        <v>0.02120238074909173</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>136.6727272727273</v>
+        <v>199.030303030303</v>
       </c>
       <c r="B41">
-        <v>0.02304507032490236</v>
+        <v>0.02072628709733862</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>140.0515151515152</v>
+        <v>203.979797979798</v>
       </c>
       <c r="B42">
-        <v>0.02251792943149735</v>
+        <v>0.02027219051150431</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>143.430303030303</v>
+        <v>208.929292929293</v>
       </c>
       <c r="B43">
-        <v>0.02201498796942169</v>
+        <v>0.01983857703406896</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>146.8090909090909</v>
+        <v>213.8787878787879</v>
       </c>
       <c r="B44">
-        <v>0.02153460330961525</v>
+        <v>0.01942406956863548</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>150.1878787878788</v>
+        <v>218.8282828282829</v>
       </c>
       <c r="B45">
-        <v>0.02107527878966524</v>
+        <v>0.01902741268877517</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>153.5666666666667</v>
+        <v>223.7777777777778</v>
       </c>
       <c r="B46">
-        <v>0.02063564781503395</v>
+        <v>0.01864745943208572</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>156.9454545454546</v>
+        <v>228.7272727272727</v>
       </c>
       <c r="B47">
-        <v>0.02021445999716518</v>
+        <v>0.01828315978264344</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>160.3242424242424</v>
+        <v>233.6767676767677</v>
       </c>
       <c r="B48">
-        <v>0.0198105690300645</v>
+        <v>0.01793355059476268</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>163.7030303030303</v>
+        <v>238.6262626262626</v>
       </c>
       <c r="B49">
-        <v>0.01942292205592545</v>
+        <v>0.01759774675151514</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>167.0818181818182</v>
+        <v>243.5757575757576</v>
       </c>
       <c r="B50">
-        <v>0.01905055031048268</v>
+        <v>0.01727493338466043</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>170.4606060606061</v>
+        <v>248.5252525252525</v>
       </c>
       <c r="B51">
-        <v>0.01869256087176563</v>
+        <v>0.01696435900994654</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>173.8393939393939</v>
+        <v>253.4747474747475</v>
       </c>
       <c r="B52">
-        <v>0.01834812936317774</v>
+        <v>0.01666532945429469</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>177.2181818181818</v>
+        <v>258.4242424242424</v>
       </c>
       <c r="B53">
-        <v>0.01801649348442664</v>
+        <v>0.01637720247008973</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>180.5969696969697</v>
+        <v>263.3737373737374</v>
       </c>
       <c r="B54">
-        <v>0.01769694726264558</v>
+        <v>0.01609938294737109</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>183.9757575757576</v>
+        <v>268.3232323232323</v>
       </c>
       <c r="B55">
-        <v>0.01738883593176847</v>
+        <v>0.01583131864773404</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>187.3545454545455</v>
+        <v>273.2727272727273</v>
       </c>
       <c r="B56">
-        <v>0.01709155136140432</v>
+        <v>0.01557249639466486</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>190.7333333333333</v>
+        <v>278.2222222222222</v>
       </c>
       <c r="B57">
-        <v>0.01680452796754974</v>
+        <v>0.01532243866421807</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>194.1121212121212</v>
+        <v>283.1717171717172</v>
       </c>
       <c r="B58">
-        <v>0.0165272390468431</v>
+        <v>0.01508070052769744</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>197.4909090909091</v>
+        <v>288.1212121212121</v>
       </c>
       <c r="B59">
-        <v>0.01625919348399371</v>
+        <v>0.01484686690457024</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>200.869696969697</v>
+        <v>293.0707070707071</v>
       </c>
       <c r="B60">
-        <v>0.01599993278875608</v>
+        <v>0.01462055008942256</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>204.2484848484848</v>
+        <v>298.020202020202</v>
       </c>
       <c r="B61">
-        <v>0.01574902842455767</v>
+        <v>0.0144013875215177</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>207.6272727272728</v>
+        <v>302.969696969697</v>
       </c>
       <c r="B62">
-        <v>0.01550607939579167</v>
+        <v>0.01418903976958098</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>211.0060606060606</v>
+        <v>307.9191919191919</v>
       </c>
       <c r="B63">
-        <v>0.01527071006498598</v>
+        <v>0.01398318870791426</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>214.3848484848485</v>
+        <v>312.8686868686869</v>
       </c>
       <c r="B64">
-        <v>0.0150425681746673</v>
+        <v>0.01378353586293347</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>217.7636363636364</v>
+        <v>317.8181818181818</v>
       </c>
       <c r="B65">
-        <v>0.01482132305184568</v>
+        <v>0.0135898009117967</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>221.1424242424243</v>
+        <v>322.7676767676768</v>
       </c>
       <c r="B66">
-        <v>0.01460666397572636</v>
+        <v>0.01340172031701382</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>224.5212121212121</v>
+        <v>327.7171717171718</v>
       </c>
       <c r="B67">
-        <v>0.01439829869157622</v>
+        <v>0.01321904608285247</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>227.9</v>
+        <v>332.6666666666667</v>
       </c>
       <c r="B68">
-        <v>0.01419595205568452</v>
+        <v>0.01304154462102402</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>231.2787878787879</v>
+        <v>337.6161616161617</v>
       </c>
       <c r="B69">
-        <v>0.01399936479810706</v>
+        <v>0.01286899571458437</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>234.6575757575758</v>
+        <v>342.5656565656566</v>
       </c>
       <c r="B70">
-        <v>0.01380829239140649</v>
+        <v>0.01270119157024843</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>238.0363636363637</v>
+        <v>347.5151515151516</v>
       </c>
       <c r="B71">
-        <v>0.01362250401493192</v>
+        <v>0.01253793595042098</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>241.4151515151515</v>
+        <v>352.4646464646465</v>
       </c>
       <c r="B72">
-        <v>0.01344178160534442</v>
+        <v>0.01237904337721266</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>244.7939393939394</v>
+        <v>357.4141414141415</v>
       </c>
       <c r="B73">
-        <v>0.01326591898511502</v>
+        <v>0.01222433840155585</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>248.1727272727273</v>
+        <v>362.3636363636364</v>
       </c>
       <c r="B74">
-        <v>0.013094721061617</v>
+        <v>0.01207365493127947</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>251.5515151515152</v>
+        <v>367.3131313131314</v>
       </c>
       <c r="B75">
-        <v>0.01292800309022271</v>
+        <v>0.01192683561265549</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>254.930303030303</v>
+        <v>372.2626262626263</v>
       </c>
       <c r="B76">
-        <v>0.01276558999550886</v>
+        <v>0.01178373126050731</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>258.3090909090909</v>
+        <v>377.2121212121212</v>
       </c>
       <c r="B77">
-        <v>0.01260731574528809</v>
+        <v>0.01164420033247908</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>261.6878787878788</v>
+        <v>382.1616161616162</v>
       </c>
       <c r="B78">
-        <v>0.01245302277272614</v>
+        <v>0.0115081084435161</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>265.0666666666667</v>
+        <v>387.1111111111111</v>
       </c>
       <c r="B79">
-        <v>0.01230256144228506</v>
+        <v>0.0113753279170056</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>268.4454545454545</v>
+        <v>392.0606060606061</v>
       </c>
       <c r="B80">
-        <v>0.01215578955565855</v>
+        <v>0.01124573736938153</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>271.8242424242424</v>
+        <v>397.010101010101</v>
       </c>
       <c r="B81">
-        <v>0.01201257189424466</v>
+        <v>0.01111922132531227</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82">
-        <v>275.2030303030303</v>
+        <v>401.959595959596</v>
       </c>
       <c r="B82">
-        <v>0.01187277979503844</v>
+        <v>0.01099566986087049</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83">
-        <v>278.5818181818182</v>
+        <v>406.9090909090909</v>
       </c>
       <c r="B83">
-        <v>0.01173629075712732</v>
+        <v>0.01087497827233463</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84">
-        <v>281.960606060606</v>
+        <v>411.8585858585859</v>
       </c>
       <c r="B84">
-        <v>0.0116029880762408</v>
+        <v>0.01075704676849478</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85">
-        <v>285.3393939393939</v>
+        <v>416.8080808080808</v>
       </c>
       <c r="B85">
-        <v>0.01147276050504557</v>
+        <v>0.01064178018453541</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86">
-        <v>288.7181818181818</v>
+        <v>421.7575757575758</v>
       </c>
       <c r="B86">
-        <v>0.01134550193709238</v>
+        <v>0.01052908771574629</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87">
-        <v>292.0969696969697</v>
+        <v>426.7070707070707</v>
       </c>
       <c r="B87">
-        <v>0.01122111111251317</v>
+        <v>0.01041888266947336</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88">
-        <v>295.4757575757575</v>
+        <v>431.6565656565657</v>
       </c>
       <c r="B88">
-        <v>0.01109949134373992</v>
+        <v>0.01031108223386522</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89">
-        <v>298.8545454545454</v>
+        <v>436.6060606060606</v>
       </c>
       <c r="B89">
-        <v>0.01098055025967232</v>
+        <v>0.01020560726210032</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90">
-        <v>302.2333333333333</v>
+        <v>441.5555555555556</v>
       </c>
       <c r="B90">
-        <v>0.01086419956686064</v>
+        <v>0.01010238207089663</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91">
-        <v>305.6121212121212</v>
+        <v>446.5050505050505</v>
       </c>
       <c r="B91">
-        <v>0.01075035482639666</v>
+        <v>0.01000133425221042</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92">
-        <v>308.9909090909091</v>
+        <v>451.4545454545455</v>
       </c>
       <c r="B92">
-        <v>0.01063893524531896</v>
+        <v>0.009902394497125629</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93">
-        <v>312.369696969697</v>
+        <v>456.4040404040404</v>
       </c>
       <c r="B93">
-        <v>0.01052986348144133</v>
+        <v>0.009805496431020874</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94">
-        <v>315.7484848484848</v>
+        <v>461.3535353535354</v>
       </c>
       <c r="B94">
-        <v>0.01042306546060632</v>
+        <v>0.009710576459178636</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95">
-        <v>319.1272727272727</v>
+        <v>466.3030303030303</v>
       </c>
       <c r="B95">
-        <v>0.01031847020544955</v>
+        <v>0.009617573622071237</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96">
-        <v>322.5060606060606</v>
+        <v>471.2525252525253</v>
       </c>
       <c r="B96">
-        <v>0.01021600967483671</v>
+        <v>0.009526429459621746</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97">
-        <v>325.8848484848485</v>
+        <v>476.2020202020202</v>
       </c>
       <c r="B97">
-        <v>0.01011561861320442</v>
+        <v>0.009437087883795719</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98">
-        <v>329.2636363636364</v>
+        <v>481.1515151515152</v>
       </c>
       <c r="B98">
-        <v>0.01001723440909843</v>
+        <v>0.009349495058931932</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99">
-        <v>332.6424242424242</v>
+        <v>486.1010101010102</v>
       </c>
       <c r="B99">
-        <v>0.009920796962260125</v>
+        <v>0.009263599289268032</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100">
-        <v>336.0212121212121</v>
+        <v>491.0505050505051</v>
       </c>
       <c r="B100">
-        <v>0.009826248558663993</v>
+        <v>0.009179350913160295</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101">
-        <v>339.4</v>
+        <v>496</v>
       </c>
       <c r="B101">
-        <v>0.009733533752955834</v>
+        <v>0.00909670220353624</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sgt_files/InVitroBioFilm_SGT_scaling.xlsx
+++ b/datasets/sgt_files/InVitroBioFilm_SGT_scaling.xlsx
@@ -16,13 +16,19 @@
     <sheet name="Nodes-Network diamet. (Fitting)" sheetId="7" r:id="rId7"/>
     <sheet name="Nodes-Graph density" sheetId="8" r:id="rId8"/>
     <sheet name="Nodes-Graph density (Fitting)" sheetId="9" r:id="rId9"/>
+    <sheet name="Nodes-Assortativity ." sheetId="10" r:id="rId10"/>
+    <sheet name="Nodes-Assortativity . (Fitting)" sheetId="11" r:id="rId11"/>
+    <sheet name="Nodes-Average cluste." sheetId="12" r:id="rId12"/>
+    <sheet name="Nodes-Average cluste. (Fitting)" sheetId="13" r:id="rId13"/>
+    <sheet name="Nodes-Average betwee." sheetId="14" r:id="rId14"/>
+    <sheet name="Nodes-Average betwee. (Fitting)" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="26">
   <si>
     <t>parameter</t>
   </si>
@@ -60,6 +66,15 @@
     <t>Graph density</t>
   </si>
   <si>
+    <t>Assortativity coefficient</t>
+  </si>
+  <si>
+    <t>Average clustering coefficient</t>
+  </si>
+  <si>
+    <t>Average betweenness centrality</t>
+  </si>
+  <si>
     <t>kernel-dim</t>
   </si>
   <si>
@@ -88,6 +103,9 @@
   </si>
   <si>
     <t>Pwr. Law y-fit</t>
+  </si>
+  <si>
+    <t>-inf</t>
   </si>
 </sst>
 </file>
@@ -445,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -582,6 +600,3378 @@
       </c>
       <c r="E8">
         <v>0.00511</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
+        <v>-0.14857</v>
+      </c>
+      <c r="C9">
+        <v>-0.14647</v>
+      </c>
+      <c r="D9">
+        <v>-0.19162</v>
+      </c>
+      <c r="E9">
+        <v>-0.19167</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
+        <v>0.03095</v>
+      </c>
+      <c r="C10">
+        <v>0.0304</v>
+      </c>
+      <c r="D10">
+        <v>0.03082</v>
+      </c>
+      <c r="E10">
+        <v>0.0301</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11">
+        <v>0.03612</v>
+      </c>
+      <c r="C11">
+        <v>0.03708</v>
+      </c>
+      <c r="D11">
+        <v>0.03699</v>
+      </c>
+      <c r="E11">
+        <v>0.03798</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2">
+        <v>62</v>
+      </c>
+      <c r="B2">
+        <v>5.4</v>
+      </c>
+      <c r="C2">
+        <v>0.9451631252505217</v>
+      </c>
+      <c r="D2">
+        <v>-0.77777875</v>
+      </c>
+      <c r="E2">
+        <v>0.07686514451459776</v>
+      </c>
+      <c r="F2">
+        <v>0.7323937598229685</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3">
+        <v>125</v>
+      </c>
+      <c r="B3">
+        <v>17.2</v>
+      </c>
+      <c r="C3">
+        <v>3.349295116554792</v>
+      </c>
+      <c r="D3">
+        <v>-0.378052</v>
+      </c>
+      <c r="E3">
+        <v>0.08763542592658138</v>
+      </c>
+      <c r="F3">
+        <v>1.235528446907549</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4">
+        <v>188</v>
+      </c>
+      <c r="B4">
+        <v>39.6</v>
+      </c>
+      <c r="C4">
+        <v>6.899597411765735</v>
+      </c>
+      <c r="D4">
+        <v>-0.220879</v>
+      </c>
+      <c r="E4">
+        <v>0.0270971627645569</v>
+      </c>
+      <c r="F4">
+        <v>1.597695185925512</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>251</v>
+      </c>
+      <c r="B5">
+        <v>70.5</v>
+      </c>
+      <c r="C5">
+        <v>11.99837952021485</v>
+      </c>
+      <c r="D5">
+        <v>-0.245407</v>
+      </c>
+      <c r="E5">
+        <v>0.02501852789212204</v>
+      </c>
+      <c r="F5">
+        <v>1.848189116991399</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>314</v>
+      </c>
+      <c r="B6">
+        <v>103</v>
+      </c>
+      <c r="C6">
+        <v>13.03755259923341</v>
+      </c>
+      <c r="D6">
+        <v>-0.234321</v>
+      </c>
+      <c r="E6">
+        <v>0.018438916842736</v>
+      </c>
+      <c r="F6">
+        <v>2.012837224705172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>376</v>
+      </c>
+      <c r="B7">
+        <v>135.6</v>
+      </c>
+      <c r="C7">
+        <v>17.64224727433806</v>
+      </c>
+      <c r="D7">
+        <v>-0.239467</v>
+      </c>
+      <c r="E7">
+        <v>0.01348972226466423</v>
+      </c>
+      <c r="F7">
+        <v>2.132259689531045</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>439</v>
+      </c>
+      <c r="B8">
+        <v>199.5</v>
+      </c>
+      <c r="C8">
+        <v>22.33743743384883</v>
+      </c>
+      <c r="D8">
+        <v>-0.210851</v>
+      </c>
+      <c r="E8">
+        <v>0.01196161940448607</v>
+      </c>
+      <c r="F8">
+        <v>2.299942900022767</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>502</v>
+      </c>
+      <c r="B9">
+        <v>246</v>
+      </c>
+      <c r="C9">
+        <v>25.42527176736651</v>
+      </c>
+      <c r="D9">
+        <v>-0.218914</v>
+      </c>
+      <c r="E9">
+        <v>0.01480630775491761</v>
+      </c>
+      <c r="F9">
+        <v>2.390935107103379</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>565</v>
+      </c>
+      <c r="B10">
+        <v>301.9</v>
+      </c>
+      <c r="C10">
+        <v>22.93587679694073</v>
+      </c>
+      <c r="D10">
+        <v>-0.207767</v>
+      </c>
+      <c r="E10">
+        <v>0.007432863370793848</v>
+      </c>
+      <c r="F10">
+        <v>2.479863113023098</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
+        <v>628</v>
+      </c>
+      <c r="B11">
+        <v>333.9</v>
+      </c>
+      <c r="C11">
+        <v>28.02516726087464</v>
+      </c>
+      <c r="D11">
+        <v>-0.195964</v>
+      </c>
+      <c r="E11">
+        <v>0.01112456353201229</v>
+      </c>
+      <c r="F11">
+        <v>2.523616419054371</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12">
+        <v>638</v>
+      </c>
+      <c r="B12">
+        <v>496</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>-0.14739</v>
+      </c>
+      <c r="E12">
+        <v>9.251858538542971E-18</v>
+      </c>
+      <c r="F12">
+        <v>2.695481676490198</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>5.4</v>
+      </c>
+      <c r="B2">
+        <v>-0.7111132316000609</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>10.35555555555556</v>
+      </c>
+      <c r="B3">
+        <v>-0.5568152553445983</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>15.31111111111111</v>
+      </c>
+      <c r="B4">
+        <v>-0.4807423328619749</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>20.26666666666667</v>
+      </c>
+      <c r="B5">
+        <v>-0.4326799063146136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>25.22222222222222</v>
+      </c>
+      <c r="B6">
+        <v>-0.398546593747234</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>30.17777777777778</v>
+      </c>
+      <c r="B7">
+        <v>-0.372575330974093</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>35.13333333333333</v>
+      </c>
+      <c r="B8">
+        <v>-0.3518915160687886</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>40.08888888888889</v>
+      </c>
+      <c r="B9">
+        <v>-0.3348744423796015</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>45.04444444444444</v>
+      </c>
+      <c r="B10">
+        <v>-0.3205290415241885</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>50</v>
+      </c>
+      <c r="B11">
+        <v>-0.3082048001684985</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>54.95555555555556</v>
+      </c>
+      <c r="B12">
+        <v>-0.2974554359051564</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>59.91111111111111</v>
+      </c>
+      <c r="B13">
+        <v>-0.2879628277385431</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>64.86666666666667</v>
+      </c>
+      <c r="B14">
+        <v>-0.2794930347742406</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>69.82222222222222</v>
+      </c>
+      <c r="B15">
+        <v>-0.2718695135427197</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>74.77777777777779</v>
+      </c>
+      <c r="B16">
+        <v>-0.2649560965938083</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>79.73333333333335</v>
+      </c>
+      <c r="B17">
+        <v>-0.2586457800400951</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>84.6888888888889</v>
+      </c>
+      <c r="B18">
+        <v>-0.2528531087827487</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>89.64444444444445</v>
+      </c>
+      <c r="B19">
+        <v>-0.2475088672164817</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>94.60000000000001</v>
+      </c>
+      <c r="B20">
+        <v>-0.2425562915757599</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>99.55555555555557</v>
+      </c>
+      <c r="B21">
+        <v>-0.2379483128103947</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>104.5111111111111</v>
+      </c>
+      <c r="B22">
+        <v>-0.2336455134325338</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>109.4666666666667</v>
+      </c>
+      <c r="B23">
+        <v>-0.2296145891100579</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>114.4222222222222</v>
+      </c>
+      <c r="B24">
+        <v>-0.2258271736000239</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>119.3777777777778</v>
+      </c>
+      <c r="B25">
+        <v>-0.2222589295197932</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>124.3333333333333</v>
+      </c>
+      <c r="B26">
+        <v>-0.2188888365020201</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>129.2888888888889</v>
+      </c>
+      <c r="B27">
+        <v>-0.21569862788134</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>134.2444444444444</v>
+      </c>
+      <c r="B28">
+        <v>-0.2126723405261162</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>139.2</v>
+      </c>
+      <c r="B29">
+        <v>-0.2097959518308515</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>144.1555555555556</v>
+      </c>
+      <c r="B30">
+        <v>-0.2070570845487055</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>149.1111111111111</v>
+      </c>
+      <c r="B31">
+        <v>-0.2044447649318122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>154.0666666666667</v>
+      </c>
+      <c r="B32">
+        <v>-0.2019492231315089</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>159.0222222222222</v>
+      </c>
+      <c r="B33">
+        <v>-0.199561727376095</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>163.9777777777778</v>
+      </c>
+      <c r="B34">
+        <v>-0.1972744453533393</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>168.9333333333333</v>
+      </c>
+      <c r="B35">
+        <v>-0.1950803276608019</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>173.8888888888889</v>
+      </c>
+      <c r="B36">
+        <v>-0.1929730092769292</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>178.8444444444445</v>
+      </c>
+      <c r="B37">
+        <v>-0.1909467258405066</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>183.8</v>
+      </c>
+      <c r="B38">
+        <v>-0.1889962421705293</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>188.7555555555556</v>
+      </c>
+      <c r="B39">
+        <v>-0.1871167909600875</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>193.7111111111111</v>
+      </c>
+      <c r="B40">
+        <v>-0.1853040199710229</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>198.6666666666667</v>
+      </c>
+      <c r="B41">
+        <v>-0.1835539463664701</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>203.6222222222222</v>
+      </c>
+      <c r="B42">
+        <v>-0.1818629170649775</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>208.5777777777778</v>
+      </c>
+      <c r="B43">
+        <v>-0.1802275741970363</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>213.5333333333333</v>
+      </c>
+      <c r="B44">
+        <v>-0.1786448249033724</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>218.4888888888889</v>
+      </c>
+      <c r="B45">
+        <v>-0.1771118148425378</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>223.4444444444445</v>
+      </c>
+      <c r="B46">
+        <v>-0.1756259048795451</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>228.4</v>
+      </c>
+      <c r="B47">
+        <v>-0.1741846505124172</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>233.3555555555556</v>
+      </c>
+      <c r="B48">
+        <v>-0.1727857836634113</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>238.3111111111111</v>
+      </c>
+      <c r="B49">
+        <v>-0.1714271965193075</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>243.2666666666667</v>
+      </c>
+      <c r="B50">
+        <v>-0.1701069271528842</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>248.2222222222222</v>
+      </c>
+      <c r="B51">
+        <v>-0.168823146697403</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>253.1777777777778</v>
+      </c>
+      <c r="B52">
+        <v>-0.1675741478790744</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>258.1333333333333</v>
+      </c>
+      <c r="B53">
+        <v>-0.1663583347402649</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>263.0888888888888</v>
+      </c>
+      <c r="B54">
+        <v>-0.1651742134095776</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>268.0444444444444</v>
+      </c>
+      <c r="B55">
+        <v>-0.1640203837946765</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>273</v>
+      </c>
+      <c r="B56">
+        <v>-0.1628955320904413</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>277.9555555555555</v>
+      </c>
+      <c r="B57">
+        <v>-0.1617984240092409</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>282.9111111111111</v>
+      </c>
+      <c r="B58">
+        <v>-0.1607278986522307</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>287.8666666666667</v>
+      </c>
+      <c r="B59">
+        <v>-0.1596828629509272</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>292.8222222222222</v>
+      </c>
+      <c r="B60">
+        <v>-0.1586622866171939</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>297.7777777777778</v>
+      </c>
+      <c r="B61">
+        <v>-0.1576651975474085</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>302.7333333333333</v>
+      </c>
+      <c r="B62">
+        <v>-0.1566906776331604</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>307.6888888888889</v>
+      </c>
+      <c r="B63">
+        <v>-0.1557378589365197</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>312.6444444444444</v>
+      </c>
+      <c r="B64">
+        <v>-0.1548059201928469</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>317.6</v>
+      </c>
+      <c r="B65">
+        <v>-0.1538940836083989</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>322.5555555555555</v>
+      </c>
+      <c r="B66">
+        <v>-0.1530016119237109</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>327.5111111111111</v>
+      </c>
+      <c r="B67">
+        <v>-0.1521278057169927</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>332.4666666666666</v>
+      </c>
+      <c r="B68">
+        <v>-0.1512720009246218</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>337.4222222222222</v>
+      </c>
+      <c r="B69">
+        <v>-0.1504335665583069</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>342.3777777777777</v>
+      </c>
+      <c r="B70">
+        <v>-0.1496119026006937</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>347.3333333333333</v>
+      </c>
+      <c r="B71">
+        <v>-0.1488064380631029</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>352.2888888888889</v>
+      </c>
+      <c r="B72">
+        <v>-0.1480166291907962</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73">
+        <v>357.2444444444444</v>
+      </c>
+      <c r="B73">
+        <v>-0.1472419578026656</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>362.2</v>
+      </c>
+      <c r="B74">
+        <v>-0.1464819297535671</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75">
+        <v>367.1555555555556</v>
+      </c>
+      <c r="B75">
+        <v>-0.145736073508702</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>372.1111111111111</v>
+      </c>
+      <c r="B76">
+        <v>-0.1450039388204889</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77">
+        <v>377.0666666666667</v>
+      </c>
+      <c r="B77">
+        <v>-0.144285095499305</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78">
+        <v>382.0222222222222</v>
+      </c>
+      <c r="B78">
+        <v>-0.1435791322702996</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79">
+        <v>386.9777777777778</v>
+      </c>
+      <c r="B79">
+        <v>-0.1428856557092246</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80">
+        <v>391.9333333333333</v>
+      </c>
+      <c r="B80">
+        <v>-0.1422042892508867</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81">
+        <v>396.8888888888889</v>
+      </c>
+      <c r="B81">
+        <v>-0.1415346722644157</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
+        <v>401.8444444444444</v>
+      </c>
+      <c r="B82">
+        <v>-0.140876459190077</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83">
+        <v>406.8</v>
+      </c>
+      <c r="B83">
+        <v>-0.1402293187328281</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84">
+        <v>411.7555555555555</v>
+      </c>
+      <c r="B84">
+        <v>-0.1395929331082495</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85">
+        <v>416.7111111111111</v>
+      </c>
+      <c r="B85">
+        <v>-0.1389669973368625</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>421.6666666666666</v>
+      </c>
+      <c r="B86">
+        <v>-0.1383512185831972</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87">
+        <v>426.6222222222222</v>
+      </c>
+      <c r="B87">
+        <v>-0.1377453155362811</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>431.5777777777778</v>
+      </c>
+      <c r="B88">
+        <v>-0.1371490178285084</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89">
+        <v>436.5333333333333</v>
+      </c>
+      <c r="B89">
+        <v>-0.136562065490099</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>441.4888888888889</v>
+      </c>
+      <c r="B90">
+        <v>-0.1359842084365934</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91">
+        <v>446.4444444444445</v>
+      </c>
+      <c r="B91">
+        <v>-0.135415205987036</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>451.4</v>
+      </c>
+      <c r="B92">
+        <v>-0.1348548264106922</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>456.3555555555556</v>
+      </c>
+      <c r="B93">
+        <v>-0.1343028465003155</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
+        <v>461.3111111111111</v>
+      </c>
+      <c r="B94">
+        <v>-0.1337590511701429</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>466.2666666666667</v>
+      </c>
+      <c r="B95">
+        <v>-0.1332232330769336</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>471.2222222222222</v>
+      </c>
+      <c r="B96">
+        <v>-0.1326951922625039</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97">
+        <v>476.1777777777777</v>
+      </c>
+      <c r="B97">
+        <v>-0.1321747358163258</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>481.1333333333333</v>
+      </c>
+      <c r="B98">
+        <v>-0.1316616775568676</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>486.0888888888889</v>
+      </c>
+      <c r="B99">
+        <v>-0.1311558377304544</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>491.0444444444444</v>
+      </c>
+      <c r="B100">
+        <v>-0.1306570427265187</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>496</v>
+      </c>
+      <c r="B101">
+        <v>-0.1301651248081911</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2">
+        <v>62</v>
+      </c>
+      <c r="B2">
+        <v>5.4</v>
+      </c>
+      <c r="C2">
+        <v>0.9451631252505217</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0.7323937598229685</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3">
+        <v>125</v>
+      </c>
+      <c r="B3">
+        <v>17.2</v>
+      </c>
+      <c r="C3">
+        <v>3.349295116554792</v>
+      </c>
+      <c r="D3">
+        <v>0.025621</v>
+      </c>
+      <c r="E3">
+        <v>0.007506537809728855</v>
+      </c>
+      <c r="F3">
+        <v>1.235528446907549</v>
+      </c>
+      <c r="G3">
+        <v>-1.591403923537217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4">
+        <v>188</v>
+      </c>
+      <c r="B4">
+        <v>39.6</v>
+      </c>
+      <c r="C4">
+        <v>6.899597411765735</v>
+      </c>
+      <c r="D4">
+        <v>0.05449</v>
+      </c>
+      <c r="E4">
+        <v>0.009010240963604815</v>
+      </c>
+      <c r="F4">
+        <v>1.597695185925512</v>
+      </c>
+      <c r="G4">
+        <v>-1.263683192095891</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>251</v>
+      </c>
+      <c r="B5">
+        <v>70.5</v>
+      </c>
+      <c r="C5">
+        <v>11.99837952021485</v>
+      </c>
+      <c r="D5">
+        <v>0.023809</v>
+      </c>
+      <c r="E5">
+        <v>0.005649652388520121</v>
+      </c>
+      <c r="F5">
+        <v>1.848189116991399</v>
+      </c>
+      <c r="G5">
+        <v>-1.623258844981603</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>314</v>
+      </c>
+      <c r="B6">
+        <v>103</v>
+      </c>
+      <c r="C6">
+        <v>13.03755259923341</v>
+      </c>
+      <c r="D6">
+        <v>0.031006</v>
+      </c>
+      <c r="E6">
+        <v>0.004530309089283472</v>
+      </c>
+      <c r="F6">
+        <v>2.012837224705172</v>
+      </c>
+      <c r="G6">
+        <v>-1.508554257302728</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>376</v>
+      </c>
+      <c r="B7">
+        <v>135.6</v>
+      </c>
+      <c r="C7">
+        <v>17.64224727433806</v>
+      </c>
+      <c r="D7">
+        <v>0.027943</v>
+      </c>
+      <c r="E7">
+        <v>0.002246629599100741</v>
+      </c>
+      <c r="F7">
+        <v>2.132259689531045</v>
+      </c>
+      <c r="G7">
+        <v>-1.553726969248913</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>439</v>
+      </c>
+      <c r="B8">
+        <v>199.5</v>
+      </c>
+      <c r="C8">
+        <v>22.33743743384883</v>
+      </c>
+      <c r="D8">
+        <v>0.03033</v>
+      </c>
+      <c r="E8">
+        <v>0.002650681673331095</v>
+      </c>
+      <c r="F8">
+        <v>2.299942900022767</v>
+      </c>
+      <c r="G8">
+        <v>-1.518127589689336</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>502</v>
+      </c>
+      <c r="B9">
+        <v>246</v>
+      </c>
+      <c r="C9">
+        <v>25.42527176736651</v>
+      </c>
+      <c r="D9">
+        <v>0.031399</v>
+      </c>
+      <c r="E9">
+        <v>0.001026063080148801</v>
+      </c>
+      <c r="F9">
+        <v>2.390935107103379</v>
+      </c>
+      <c r="G9">
+        <v>-1.503084183181485</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>565</v>
+      </c>
+      <c r="B10">
+        <v>301.9</v>
+      </c>
+      <c r="C10">
+        <v>22.93587679694073</v>
+      </c>
+      <c r="D10">
+        <v>0.030516</v>
+      </c>
+      <c r="E10">
+        <v>0.0009899160458229667</v>
+      </c>
+      <c r="F10">
+        <v>2.479863113023098</v>
+      </c>
+      <c r="G10">
+        <v>-1.515472393776666</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
+        <v>628</v>
+      </c>
+      <c r="B11">
+        <v>333.9</v>
+      </c>
+      <c r="C11">
+        <v>28.02516726087464</v>
+      </c>
+      <c r="D11">
+        <v>0.029857</v>
+      </c>
+      <c r="E11">
+        <v>0.0006752481848262248</v>
+      </c>
+      <c r="F11">
+        <v>2.523616419054371</v>
+      </c>
+      <c r="G11">
+        <v>-1.524953831872202</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12">
+        <v>638</v>
+      </c>
+      <c r="B12">
+        <v>496</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0.03058</v>
+      </c>
+      <c r="E12">
+        <v>1.156482317317871E-18</v>
+      </c>
+      <c r="F12">
+        <v>2.695481676490198</v>
+      </c>
+      <c r="G12">
+        <v>-1.514562518923699</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>5.4</v>
+      </c>
+      <c r="B2">
+        <v>0.02014481677596097</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>10.35555555555556</v>
+      </c>
+      <c r="B3">
+        <v>0.02176060811780119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>15.31111111111111</v>
+      </c>
+      <c r="B4">
+        <v>0.02279267325462529</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>20.26666666666667</v>
+      </c>
+      <c r="B5">
+        <v>0.02356269442698468</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>25.22222222222222</v>
+      </c>
+      <c r="B6">
+        <v>0.02418143153868638</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>30.17777777777778</v>
+      </c>
+      <c r="B7">
+        <v>0.02470092160858785</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>35.13333333333333</v>
+      </c>
+      <c r="B8">
+        <v>0.02514997563167066</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>40.08888888888889</v>
+      </c>
+      <c r="B9">
+        <v>0.02554628955828847</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>45.04444444444444</v>
+      </c>
+      <c r="B10">
+        <v>0.02590154496608103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>50</v>
+      </c>
+      <c r="B11">
+        <v>0.02622387457927782</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>54.95555555555556</v>
+      </c>
+      <c r="B12">
+        <v>0.02651917715259363</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>59.91111111111111</v>
+      </c>
+      <c r="B13">
+        <v>0.0267918726650495</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>64.86666666666667</v>
+      </c>
+      <c r="B14">
+        <v>0.02704536199659073</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>69.82222222222222</v>
+      </c>
+      <c r="B15">
+        <v>0.02728232014152185</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>74.77777777777779</v>
+      </c>
+      <c r="B16">
+        <v>0.02750489060286505</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>79.73333333333335</v>
+      </c>
+      <c r="B17">
+        <v>0.02771481851721175</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>84.6888888888889</v>
+      </c>
+      <c r="B18">
+        <v>0.02791354437329624</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>89.64444444444445</v>
+      </c>
+      <c r="B19">
+        <v>0.02810227157898975</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>94.60000000000001</v>
+      </c>
+      <c r="B20">
+        <v>0.02828201619588744</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>99.55555555555557</v>
+      </c>
+      <c r="B21">
+        <v>0.02845364422242765</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>104.5111111111111</v>
+      </c>
+      <c r="B22">
+        <v>0.02861789999902625</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>109.4666666666667</v>
+      </c>
+      <c r="B23">
+        <v>0.02877542816437205</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>114.4222222222222</v>
+      </c>
+      <c r="B24">
+        <v>0.02892679084880653</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>119.3777777777778</v>
+      </c>
+      <c r="B25">
+        <v>0.02907248129688445</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>124.3333333333333</v>
+      </c>
+      <c r="B26">
+        <v>0.02921293477631378</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>129.2888888888889</v>
+      </c>
+      <c r="B27">
+        <v>0.02934853739911862</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>134.2444444444444</v>
+      </c>
+      <c r="B28">
+        <v>0.0294796333183402</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>139.2</v>
+      </c>
+      <c r="B29">
+        <v>0.02960653064765116</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>144.1555555555556</v>
+      </c>
+      <c r="B30">
+        <v>0.02972950636738547</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>149.1111111111111</v>
+      </c>
+      <c r="B31">
+        <v>0.02984881041902276</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>154.0666666666667</v>
+      </c>
+      <c r="B32">
+        <v>0.02996466914458631</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>159.0222222222222</v>
+      </c>
+      <c r="B33">
+        <v>0.030077288193238</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>163.9777777777778</v>
+      </c>
+      <c r="B34">
+        <v>0.03018685499146561</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>168.9333333333333</v>
+      </c>
+      <c r="B35">
+        <v>0.03029354085345979</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>173.8888888888889</v>
+      </c>
+      <c r="B36">
+        <v>0.03039750279300293</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>178.8444444444445</v>
+      </c>
+      <c r="B37">
+        <v>0.03049888508630719</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>183.8</v>
+      </c>
+      <c r="B38">
+        <v>0.03059782062592076</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>188.7555555555556</v>
+      </c>
+      <c r="B39">
+        <v>0.03069443209846092</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>193.7111111111111</v>
+      </c>
+      <c r="B40">
+        <v>0.03078883301307846</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>198.6666666666667</v>
+      </c>
+      <c r="B41">
+        <v>0.03088112860287232</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>203.6222222222222</v>
+      </c>
+      <c r="B42">
+        <v>0.03097141661769877</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>208.5777777777778</v>
+      </c>
+      <c r="B43">
+        <v>0.03105978802376184</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>213.5333333333333</v>
+      </c>
+      <c r="B44">
+        <v>0.03114632762288128</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>218.4888888888889</v>
+      </c>
+      <c r="B45">
+        <v>0.03123111460229436</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>223.4444444444445</v>
+      </c>
+      <c r="B46">
+        <v>0.03131422302416981</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>228.4</v>
+      </c>
+      <c r="B47">
+        <v>0.03139572226262426</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>233.3555555555556</v>
+      </c>
+      <c r="B48">
+        <v>0.031475677394879</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>238.3111111111111</v>
+      </c>
+      <c r="B49">
+        <v>0.03155414955223362</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>243.2666666666667</v>
+      </c>
+      <c r="B50">
+        <v>0.03163119623572778</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>248.2222222222222</v>
+      </c>
+      <c r="B51">
+        <v>0.03170687160068538</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>253.1777777777778</v>
+      </c>
+      <c r="B52">
+        <v>0.03178122671376406</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>258.1333333333333</v>
+      </c>
+      <c r="B53">
+        <v>0.031854309785649</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>263.0888888888888</v>
+      </c>
+      <c r="B54">
+        <v>0.03192616638211861</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>268.0444444444444</v>
+      </c>
+      <c r="B55">
+        <v>0.03199683961585902</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>273</v>
+      </c>
+      <c r="B56">
+        <v>0.03206637032110424</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>277.9555555555555</v>
+      </c>
+      <c r="B57">
+        <v>0.0321347972129214</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>282.9111111111111</v>
+      </c>
+      <c r="B58">
+        <v>0.0322021570327389</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>287.8666666666667</v>
+      </c>
+      <c r="B59">
+        <v>0.03226848468152434</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>292.8222222222222</v>
+      </c>
+      <c r="B60">
+        <v>0.03233381334185327</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>297.7777777777778</v>
+      </c>
+      <c r="B61">
+        <v>0.03239817458996679</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>302.7333333333333</v>
+      </c>
+      <c r="B62">
+        <v>0.03246159849879071</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>307.6888888888889</v>
+      </c>
+      <c r="B63">
+        <v>0.03252411373278052</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>312.6444444444444</v>
+      </c>
+      <c r="B64">
+        <v>0.03258574763536109</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>317.6</v>
+      </c>
+      <c r="B65">
+        <v>0.03264652630964678</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>322.5555555555555</v>
+      </c>
+      <c r="B66">
+        <v>0.03270647469305456</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>327.5111111111111</v>
+      </c>
+      <c r="B67">
+        <v>0.03276561662635823</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>332.4666666666666</v>
+      </c>
+      <c r="B68">
+        <v>0.03282397491767535</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>337.4222222222222</v>
+      </c>
+      <c r="B69">
+        <v>0.03288157140182823</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>342.3777777777777</v>
+      </c>
+      <c r="B70">
+        <v>0.03293842699547604</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>347.3333333333333</v>
+      </c>
+      <c r="B71">
+        <v>0.03299456174837585</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>352.2888888888889</v>
+      </c>
+      <c r="B72">
+        <v>0.03304999489109535</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73">
+        <v>357.2444444444444</v>
+      </c>
+      <c r="B73">
+        <v>0.03310474487946918</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>362.2</v>
+      </c>
+      <c r="B74">
+        <v>0.03315882943606292</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75">
+        <v>367.1555555555556</v>
+      </c>
+      <c r="B75">
+        <v>0.03321226558888395</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>372.1111111111111</v>
+      </c>
+      <c r="B76">
+        <v>0.03326506970755685</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77">
+        <v>377.0666666666667</v>
+      </c>
+      <c r="B77">
+        <v>0.03331725753716032</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78">
+        <v>382.0222222222222</v>
+      </c>
+      <c r="B78">
+        <v>0.03336884422990578</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79">
+        <v>386.9777777777778</v>
+      </c>
+      <c r="B79">
+        <v>0.03341984437482112</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80">
+        <v>391.9333333333333</v>
+      </c>
+      <c r="B80">
+        <v>0.03347027202558917</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81">
+        <v>396.8888888888889</v>
+      </c>
+      <c r="B81">
+        <v>0.03352014072667727</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
+        <v>401.8444444444444</v>
+      </c>
+      <c r="B82">
+        <v>0.03356946353788287</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83">
+        <v>406.8</v>
+      </c>
+      <c r="B83">
+        <v>0.0336182530574093</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84">
+        <v>411.7555555555555</v>
+      </c>
+      <c r="B84">
+        <v>0.03366652144357662</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85">
+        <v>416.7111111111111</v>
+      </c>
+      <c r="B85">
+        <v>0.03371428043526352</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>421.6666666666666</v>
+      </c>
+      <c r="B86">
+        <v>0.03376154137116872</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87">
+        <v>426.6222222222222</v>
+      </c>
+      <c r="B87">
+        <v>0.03380831520797284</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>431.5777777777778</v>
+      </c>
+      <c r="B88">
+        <v>0.03385461253747578</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89">
+        <v>436.5333333333333</v>
+      </c>
+      <c r="B89">
+        <v>0.03390044360277816</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>441.4888888888889</v>
+      </c>
+      <c r="B90">
+        <v>0.03394581831357053</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91">
+        <v>446.4444444444445</v>
+      </c>
+      <c r="B91">
+        <v>0.03399074626058885</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>451.4</v>
+      </c>
+      <c r="B92">
+        <v>0.03403523672929055</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>456.3555555555556</v>
+      </c>
+      <c r="B93">
+        <v>0.03407929871280104</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
+        <v>461.3111111111111</v>
+      </c>
+      <c r="B94">
+        <v>0.03412294092417731</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>466.2666666666667</v>
+      </c>
+      <c r="B95">
+        <v>0.0341661718080313</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>471.2222222222222</v>
+      </c>
+      <c r="B96">
+        <v>0.03420899955155314</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97">
+        <v>476.1777777777777</v>
+      </c>
+      <c r="B97">
+        <v>0.03425143209497094</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>481.1333333333333</v>
+      </c>
+      <c r="B98">
+        <v>0.03429347714148173</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>486.0888888888889</v>
+      </c>
+      <c r="B99">
+        <v>0.03433514216668523</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>491.0444444444444</v>
+      </c>
+      <c r="B100">
+        <v>0.03437643442755026</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>496</v>
+      </c>
+      <c r="B101">
+        <v>0.03441736097094129</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2">
+        <v>62</v>
+      </c>
+      <c r="B2">
+        <v>5.4</v>
+      </c>
+      <c r="C2">
+        <v>0.9451631252505217</v>
+      </c>
+      <c r="D2">
+        <v>0.187579</v>
+      </c>
+      <c r="E2">
+        <v>0.0316622099126949</v>
+      </c>
+      <c r="F2">
+        <v>0.7323937598229685</v>
+      </c>
+      <c r="G2">
+        <v>-0.7268157837320937</v>
+      </c>
+      <c r="H2">
+        <v>-0.5919958034743413</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3">
+        <v>125</v>
+      </c>
+      <c r="B3">
+        <v>17.2</v>
+      </c>
+      <c r="C3">
+        <v>3.349295116554792</v>
+      </c>
+      <c r="D3">
+        <v>0.181216</v>
+      </c>
+      <c r="E3">
+        <v>0.01271017975220387</v>
+      </c>
+      <c r="F3">
+        <v>1.235528446907549</v>
+      </c>
+      <c r="G3">
+        <v>-0.7418034600535649</v>
+      </c>
+      <c r="H3">
+        <v>-0.7845677009834586</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4">
+        <v>188</v>
+      </c>
+      <c r="B4">
+        <v>39.6</v>
+      </c>
+      <c r="C4">
+        <v>6.899597411765735</v>
+      </c>
+      <c r="D4">
+        <v>0.13762</v>
+      </c>
+      <c r="E4">
+        <v>0.01202706253967831</v>
+      </c>
+      <c r="F4">
+        <v>1.597695185925512</v>
+      </c>
+      <c r="G4">
+        <v>-0.8613184464896263</v>
+      </c>
+      <c r="H4">
+        <v>-0.9231849300031986</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>251</v>
+      </c>
+      <c r="B5">
+        <v>70.5</v>
+      </c>
+      <c r="C5">
+        <v>11.99837952021485</v>
+      </c>
+      <c r="D5">
+        <v>0.114383</v>
+      </c>
+      <c r="E5">
+        <v>0.00987378370005924</v>
+      </c>
+      <c r="F5">
+        <v>1.848189116991399</v>
+      </c>
+      <c r="G5">
+        <v>-0.9416385171060124</v>
+      </c>
+      <c r="H5">
+        <v>-1.019060036327893</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>314</v>
+      </c>
+      <c r="B6">
+        <v>103</v>
+      </c>
+      <c r="C6">
+        <v>13.03755259923341</v>
+      </c>
+      <c r="D6">
+        <v>0.094348</v>
+      </c>
+      <c r="E6">
+        <v>0.008953303152096064</v>
+      </c>
+      <c r="F6">
+        <v>2.012837224705172</v>
+      </c>
+      <c r="G6">
+        <v>-1.025267301626977</v>
+      </c>
+      <c r="H6">
+        <v>-1.082078149246028</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>376</v>
+      </c>
+      <c r="B7">
+        <v>135.6</v>
+      </c>
+      <c r="C7">
+        <v>17.64224727433806</v>
+      </c>
+      <c r="D7">
+        <v>0.08692699999999999</v>
+      </c>
+      <c r="E7">
+        <v>0.008279545351178542</v>
+      </c>
+      <c r="F7">
+        <v>2.132259689531045</v>
+      </c>
+      <c r="G7">
+        <v>-1.060845308364329</v>
+      </c>
+      <c r="H7">
+        <v>-1.127786408380362</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>439</v>
+      </c>
+      <c r="B8">
+        <v>199.5</v>
+      </c>
+      <c r="C8">
+        <v>22.33743743384883</v>
+      </c>
+      <c r="D8">
+        <v>0.06759799999999999</v>
+      </c>
+      <c r="E8">
+        <v>0.006511552264160129</v>
+      </c>
+      <c r="F8">
+        <v>2.299942900022767</v>
+      </c>
+      <c r="G8">
+        <v>-1.17006615319761</v>
+      </c>
+      <c r="H8">
+        <v>-1.191966189368874</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>502</v>
+      </c>
+      <c r="B9">
+        <v>246</v>
+      </c>
+      <c r="C9">
+        <v>25.42527176736651</v>
+      </c>
+      <c r="D9">
+        <v>0.060385</v>
+      </c>
+      <c r="E9">
+        <v>0.005778461396523394</v>
+      </c>
+      <c r="F9">
+        <v>2.390935107103379</v>
+      </c>
+      <c r="G9">
+        <v>-1.219070929363503</v>
+      </c>
+      <c r="H9">
+        <v>-1.226792931443825</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>565</v>
+      </c>
+      <c r="B10">
+        <v>301.9</v>
+      </c>
+      <c r="C10">
+        <v>22.93587679694073</v>
+      </c>
+      <c r="D10">
+        <v>0.04918399999999999</v>
+      </c>
+      <c r="E10">
+        <v>0.002513177360323868</v>
+      </c>
+      <c r="F10">
+        <v>2.479863113023098</v>
+      </c>
+      <c r="G10">
+        <v>-1.308176154180349</v>
+      </c>
+      <c r="H10">
+        <v>-1.260829612438517</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
+        <v>628</v>
+      </c>
+      <c r="B11">
+        <v>333.9</v>
+      </c>
+      <c r="C11">
+        <v>28.02516726087464</v>
+      </c>
+      <c r="D11">
+        <v>0.047047</v>
+      </c>
+      <c r="E11">
+        <v>0.002401744296686611</v>
+      </c>
+      <c r="F11">
+        <v>2.523616419054371</v>
+      </c>
+      <c r="G11">
+        <v>-1.327468064584964</v>
+      </c>
+      <c r="H11">
+        <v>-1.277575937788419</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12">
+        <v>638</v>
+      </c>
+      <c r="B12">
+        <v>496</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0.03575</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>2.695481676490198</v>
+      </c>
+      <c r="G12">
+        <v>-1.446723953862901</v>
+      </c>
+      <c r="H12">
+        <v>-1.343356373107017</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>5.4</v>
+      </c>
+      <c r="B2">
+        <v>0.2124990074521142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>10.35555555555556</v>
+      </c>
+      <c r="B3">
+        <v>0.1752363756296192</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>15.31111111111111</v>
+      </c>
+      <c r="B4">
+        <v>0.1560758341745588</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>20.26666666666667</v>
+      </c>
+      <c r="B5">
+        <v>0.1436406029451742</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>25.22222222222222</v>
+      </c>
+      <c r="B6">
+        <v>0.1346315611741109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>30.17777777777778</v>
+      </c>
+      <c r="B7">
+        <v>0.1276671302233918</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>35.13333333333333</v>
+      </c>
+      <c r="B8">
+        <v>0.1220468626176719</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>40.08888888888889</v>
+      </c>
+      <c r="B9">
+        <v>0.1173703464387646</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>45.04444444444444</v>
+      </c>
+      <c r="B10">
+        <v>0.1133888482922741</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>50</v>
+      </c>
+      <c r="B11">
+        <v>0.1099381033886597</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>54.95555555555556</v>
+      </c>
+      <c r="B12">
+        <v>0.1069044029085363</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>59.91111111111111</v>
+      </c>
+      <c r="B13">
+        <v>0.1042060378262222</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>64.86666666666667</v>
+      </c>
+      <c r="B14">
+        <v>0.1017824808765443</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>69.82222222222222</v>
+      </c>
+      <c r="B15">
+        <v>0.09958774939887208</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>74.77777777777779</v>
+      </c>
+      <c r="B16">
+        <v>0.09758615833478147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>79.73333333333335</v>
+      </c>
+      <c r="B17">
+        <v>0.09574950504590743</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>84.6888888888889</v>
+      </c>
+      <c r="B18">
+        <v>0.09405514631963133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>89.64444444444445</v>
+      </c>
+      <c r="B19">
+        <v>0.09248465034207966</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>94.60000000000001</v>
+      </c>
+      <c r="B20">
+        <v>0.09102283015476478</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>99.55555555555557</v>
+      </c>
+      <c r="B21">
+        <v>0.08965703674472082</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>104.5111111111111</v>
+      </c>
+      <c r="B22">
+        <v>0.08837663284811878</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>109.4666666666667</v>
+      </c>
+      <c r="B23">
+        <v>0.08717259506954181</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>114.4222222222222</v>
+      </c>
+      <c r="B24">
+        <v>0.0860372087516746</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>119.3777777777778</v>
+      </c>
+      <c r="B25">
+        <v>0.08496383097290332</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>124.3333333333333</v>
+      </c>
+      <c r="B26">
+        <v>0.08394670431929244</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>129.2888888888889</v>
+      </c>
+      <c r="B27">
+        <v>0.08298080900101996</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>134.2444444444444</v>
+      </c>
+      <c r="B28">
+        <v>0.08206174427788709</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>139.2</v>
+      </c>
+      <c r="B29">
+        <v>0.08118563253692167</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>144.1555555555556</v>
+      </c>
+      <c r="B30">
+        <v>0.08034904105635884</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>149.1111111111111</v>
+      </c>
+      <c r="B31">
+        <v>0.07954891770938194</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>154.0666666666667</v>
+      </c>
+      <c r="B32">
+        <v>0.07878253775085113</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>159.0222222222222</v>
+      </c>
+      <c r="B33">
+        <v>0.07804745948734432</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>163.9777777777778</v>
+      </c>
+      <c r="B34">
+        <v>0.07734148712131766</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>168.9333333333333</v>
+      </c>
+      <c r="B35">
+        <v>0.07666263943000069</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>173.8888888888889</v>
+      </c>
+      <c r="B36">
+        <v>0.07600912322108468</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>178.8444444444445</v>
+      </c>
+      <c r="B37">
+        <v>0.07537931072334106</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>183.8</v>
+      </c>
+      <c r="B38">
+        <v>0.07477172023756778</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>188.7555555555556</v>
+      </c>
+      <c r="B39">
+        <v>0.0741849995037365</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>193.7111111111111</v>
+      </c>
+      <c r="B40">
+        <v>0.07361791134273486</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>198.6666666666667</v>
+      </c>
+      <c r="B41">
+        <v>0.07306932121220736</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>203.6222222222222</v>
+      </c>
+      <c r="B42">
+        <v>0.07253818638058344</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>208.5777777777778</v>
+      </c>
+      <c r="B43">
+        <v>0.0720235464751261</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>213.5333333333333</v>
+      </c>
+      <c r="B44">
+        <v>0.07152451520152893</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>218.4888888888889</v>
+      </c>
+      <c r="B45">
+        <v>0.07104027306637531</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>223.4444444444445</v>
+      </c>
+      <c r="B46">
+        <v>0.07057006096129056</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>228.4</v>
+      </c>
+      <c r="B47">
+        <v>0.07011317449014322</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>233.3555555555556</v>
+      </c>
+      <c r="B48">
+        <v>0.06966895893917717</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>238.3111111111111</v>
+      </c>
+      <c r="B49">
+        <v>0.06923680480526166</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>243.2666666666667</v>
+      </c>
+      <c r="B50">
+        <v>0.06881614381014589</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>248.2222222222222</v>
+      </c>
+      <c r="B51">
+        <v>0.06840644533918519</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>253.1777777777778</v>
+      </c>
+      <c r="B52">
+        <v>0.06800721325185645</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>258.1333333333333</v>
+      </c>
+      <c r="B53">
+        <v>0.06761798301881079</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>263.0888888888888</v>
+      </c>
+      <c r="B54">
+        <v>0.06723831914647375</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>268.0444444444444</v>
+      </c>
+      <c r="B55">
+        <v>0.06686781285549712</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>273</v>
+      </c>
+      <c r="B56">
+        <v>0.06650607998385955</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>277.9555555555555</v>
+      </c>
+      <c r="B57">
+        <v>0.06615275908923592</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>282.9111111111111</v>
+      </c>
+      <c r="B58">
+        <v>0.06580750972851961</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>287.8666666666667</v>
+      </c>
+      <c r="B59">
+        <v>0.06547001089517733</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>292.8222222222222</v>
+      </c>
+      <c r="B60">
+        <v>0.06513995959751624</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>297.7777777777778</v>
+      </c>
+      <c r="B61">
+        <v>0.06481706956300952</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>302.7333333333333</v>
+      </c>
+      <c r="B62">
+        <v>0.06450107005561209</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>307.6888888888889</v>
+      </c>
+      <c r="B63">
+        <v>0.0641917047945417</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>312.6444444444444</v>
+      </c>
+      <c r="B64">
+        <v>0.06388873096434183</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>317.6</v>
+      </c>
+      <c r="B65">
+        <v>0.06359191830720855</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>322.5555555555555</v>
+      </c>
+      <c r="B66">
+        <v>0.06330104828957936</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>327.5111111111111</v>
+      </c>
+      <c r="B67">
+        <v>0.06301591333587146</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>332.4666666666666</v>
+      </c>
+      <c r="B68">
+        <v>0.06273631612303326</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>337.4222222222222</v>
+      </c>
+      <c r="B69">
+        <v>0.0624620689302564</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>342.3777777777777</v>
+      </c>
+      <c r="B70">
+        <v>0.0621929930387952</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>347.3333333333333</v>
+      </c>
+      <c r="B71">
+        <v>0.06192891817736937</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>352.2888888888889</v>
+      </c>
+      <c r="B72">
+        <v>0.06166968200909234</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73">
+        <v>357.2444444444444</v>
+      </c>
+      <c r="B73">
+        <v>0.0614151296562805</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>362.2</v>
+      </c>
+      <c r="B74">
+        <v>0.06116511325986388</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75">
+        <v>367.1555555555556</v>
+      </c>
+      <c r="B75">
+        <v>0.06091949157044395</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>372.1111111111111</v>
+      </c>
+      <c r="B76">
+        <v>0.06067812956833186</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77">
+        <v>377.0666666666667</v>
+      </c>
+      <c r="B77">
+        <v>0.06044089811015828</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78">
+        <v>382.0222222222222</v>
+      </c>
+      <c r="B78">
+        <v>0.06020767359987401</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79">
+        <v>386.9777777777778</v>
+      </c>
+      <c r="B79">
+        <v>0.05997833768216621</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80">
+        <v>391.9333333333333</v>
+      </c>
+      <c r="B80">
+        <v>0.05975277695649744</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81">
+        <v>396.8888888888889</v>
+      </c>
+      <c r="B81">
+        <v>0.05953088271013916</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
+        <v>401.8444444444444</v>
+      </c>
+      <c r="B82">
+        <v>0.05931255066871823</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83">
+        <v>406.8</v>
+      </c>
+      <c r="B83">
+        <v>0.05909768076292744</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84">
+        <v>411.7555555555555</v>
+      </c>
+      <c r="B84">
+        <v>0.05888617691016994</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85">
+        <v>416.7111111111111</v>
+      </c>
+      <c r="B85">
+        <v>0.05867794681001452</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>421.6666666666666</v>
+      </c>
+      <c r="B86">
+        <v>0.05847290175243567</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87">
+        <v>426.6222222222222</v>
+      </c>
+      <c r="B87">
+        <v>0.05827095643789949</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>431.5777777777778</v>
+      </c>
+      <c r="B88">
+        <v>0.05807202880843542</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89">
+        <v>436.5333333333333</v>
+      </c>
+      <c r="B89">
+        <v>0.05787603988890552</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>441.4888888888889</v>
+      </c>
+      <c r="B90">
+        <v>0.05768291363774769</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91">
+        <v>446.4444444444445</v>
+      </c>
+      <c r="B91">
+        <v>0.05749257680652805</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>451.4</v>
+      </c>
+      <c r="B92">
+        <v>0.05730495880769128</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>456.3555555555556</v>
+      </c>
+      <c r="B93">
+        <v>0.05711999158994618</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
+        <v>461.3111111111111</v>
+      </c>
+      <c r="B94">
+        <v>0.05693760952076803</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>466.2666666666667</v>
+      </c>
+      <c r="B95">
+        <v>0.0567577492755398</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>471.2222222222222</v>
+      </c>
+      <c r="B96">
+        <v>0.05658034973289101</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97">
+        <v>476.1777777777777</v>
+      </c>
+      <c r="B97">
+        <v>0.0564053518758264</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>481.1333333333333</v>
+      </c>
+      <c r="B98">
+        <v>0.05623269869826793</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>486.0888888888889</v>
+      </c>
+      <c r="B99">
+        <v>0.056062335116661</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>491.0444444444444</v>
+      </c>
+      <c r="B100">
+        <v>0.05589420788632224</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>496</v>
+      </c>
+      <c r="B101">
+        <v>0.05572826552222942</v>
       </c>
     </row>
   </sheetData>
@@ -596,28 +3986,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -625,25 +4015,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="C2">
-        <v>1.273664878302853</v>
+        <v>0.9451631252505217</v>
       </c>
       <c r="D2">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="E2">
-        <v>1.268857754044952</v>
+        <v>0.9451631252505217</v>
       </c>
       <c r="F2">
-        <v>0.7781512503836436</v>
+        <v>0.7323937598229685</v>
       </c>
       <c r="G2">
-        <v>0.7075701760979364</v>
+        <v>0.6434526764861874</v>
       </c>
       <c r="H2">
-        <v>0.7485654903230231</v>
+        <v>0.6891307489727133</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -651,25 +4041,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>16.5</v>
+        <v>17.2</v>
       </c>
       <c r="C3">
-        <v>2.944863701807305</v>
+        <v>3.349295116554792</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>17.7</v>
       </c>
       <c r="E3">
-        <v>3.396076167186674</v>
+        <v>3.636390151418483</v>
       </c>
       <c r="F3">
-        <v>1.217483944213906</v>
+        <v>1.235528446907549</v>
       </c>
       <c r="G3">
-        <v>1.230448921378274</v>
+        <v>1.247973266361807</v>
       </c>
       <c r="H3">
-        <v>1.209361370100398</v>
+        <v>1.221126898456717</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -677,25 +4067,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>31.4</v>
+        <v>39.6</v>
       </c>
       <c r="C4">
-        <v>6.491361781458322</v>
+        <v>6.899597411765735</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>42.7</v>
       </c>
       <c r="E4">
-        <v>7.428174592575068</v>
+        <v>7.906467113839292</v>
       </c>
       <c r="F4">
-        <v>1.496929648073215</v>
+        <v>1.597695185925512</v>
       </c>
       <c r="G4">
-        <v>1.531478917042255</v>
+        <v>1.630427875025024</v>
       </c>
       <c r="H4">
-        <v>1.502459131246322</v>
+        <v>1.60406871418636</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -703,25 +4093,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>50</v>
+        <v>70.5</v>
       </c>
       <c r="C5">
-        <v>7.049034606872695</v>
+        <v>11.99837952021485</v>
       </c>
       <c r="D5">
-        <v>53.5</v>
+        <v>77.7</v>
       </c>
       <c r="E5">
-        <v>8.112062349091971</v>
+        <v>13.66589428711735</v>
       </c>
       <c r="F5">
-        <v>1.698970004336019</v>
+        <v>1.848189116991399</v>
       </c>
       <c r="G5">
-        <v>1.728353782021228</v>
+        <v>1.890421018800914</v>
       </c>
       <c r="H5">
-        <v>1.714369979271263</v>
+        <v>1.868931801977723</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -729,25 +4119,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>77.2</v>
+        <v>103</v>
       </c>
       <c r="C6">
-        <v>12.8</v>
+        <v>13.03755259923341</v>
       </c>
       <c r="D6">
-        <v>81.90000000000001</v>
+        <v>114.2</v>
       </c>
       <c r="E6">
-        <v>13.919171431279</v>
+        <v>15.62462443993099</v>
       </c>
       <c r="F6">
-        <v>1.887617300335736</v>
+        <v>2.012837224705172</v>
       </c>
       <c r="G6">
-        <v>1.913283901760418</v>
+        <v>2.057666103909829</v>
       </c>
       <c r="H6">
-        <v>1.91223346165848</v>
+        <v>2.043024667311871</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -755,25 +4145,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>156.8</v>
+        <v>135.6</v>
       </c>
       <c r="C7">
-        <v>19.21214893411631</v>
+        <v>17.64224727433806</v>
       </c>
       <c r="D7">
-        <v>175.6</v>
+        <v>147.9</v>
       </c>
       <c r="E7">
-        <v>23.36768899332771</v>
+        <v>20.52989689858833</v>
       </c>
       <c r="F7">
-        <v>2.19534605834842</v>
+        <v>2.132259689531045</v>
       </c>
       <c r="G7">
-        <v>2.244524511570084</v>
+        <v>2.169968173996892</v>
       </c>
       <c r="H7">
-        <v>2.23499601899285</v>
+        <v>2.169297597960703</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -781,25 +4171,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>157.3</v>
+        <v>199.5</v>
       </c>
       <c r="C8">
-        <v>17.51002887236658</v>
+        <v>22.33743743384883</v>
       </c>
       <c r="D8">
-        <v>170</v>
+        <v>220.8</v>
       </c>
       <c r="E8">
-        <v>20.03108695114782</v>
+        <v>26.42885628332116</v>
       </c>
       <c r="F8">
-        <v>2.196728722623287</v>
+        <v>2.299942900022767</v>
       </c>
       <c r="G8">
-        <v>2.230448921378274</v>
+        <v>2.343999069057161</v>
       </c>
       <c r="H8">
-        <v>2.236446232031673</v>
+        <v>2.34659966956229</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -807,25 +4197,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>268.4</v>
+        <v>246</v>
       </c>
       <c r="C9">
-        <v>15.93751688452264</v>
+        <v>25.42527176736651</v>
       </c>
       <c r="D9">
-        <v>297.4</v>
+        <v>273</v>
       </c>
       <c r="E9">
-        <v>18.39939612535634</v>
+        <v>30.42111839568763</v>
       </c>
       <c r="F9">
-        <v>2.428782511496955</v>
+        <v>2.390935107103379</v>
       </c>
       <c r="G9">
-        <v>2.473340964185935</v>
+        <v>2.436162647040756</v>
       </c>
       <c r="H9">
-        <v>2.479836790716175</v>
+        <v>2.442811489264952</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -833,25 +4223,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>311.6</v>
+        <v>301.9</v>
       </c>
       <c r="C10">
-        <v>26.19847323795797</v>
+        <v>22.93587679694073</v>
       </c>
       <c r="D10">
-        <v>348.5</v>
+        <v>336.7</v>
       </c>
       <c r="E10">
-        <v>31.04450210763753</v>
+        <v>26.78392967599954</v>
       </c>
       <c r="F10">
-        <v>2.493597449000527</v>
+        <v>2.479863113023098</v>
       </c>
       <c r="G10">
-        <v>2.542202782434028</v>
+        <v>2.527243116388088</v>
       </c>
       <c r="H10">
-        <v>2.547818201089456</v>
+        <v>2.536840698431022</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -859,25 +4249,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>343.4</v>
+        <v>333.9</v>
       </c>
       <c r="C11">
-        <v>28.52297319705644</v>
+        <v>28.02516726087464</v>
       </c>
       <c r="D11">
-        <v>385.1</v>
+        <v>373.2</v>
       </c>
       <c r="E11">
-        <v>33.37678834160052</v>
+        <v>32.64175921185077</v>
       </c>
       <c r="F11">
-        <v>2.535800290824898</v>
+        <v>2.523616419054371</v>
       </c>
       <c r="G11">
-        <v>2.585573518622731</v>
+        <v>2.571941635074462</v>
       </c>
       <c r="H11">
-        <v>2.592082823096121</v>
+        <v>2.583103838169426</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -903,7 +4293,7 @@
         <v>2.750508394851346</v>
       </c>
       <c r="H12">
-        <v>2.759565292816756</v>
+        <v>2.764827852698694</v>
       </c>
     </row>
   </sheetData>
@@ -918,802 +4308,802 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="B2">
-        <v>5.964762332057422</v>
+        <v>5.460967995199836</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>10.94949494949495</v>
+        <v>10.35555555555556</v>
       </c>
       <c r="B3">
-        <v>11.0823649503327</v>
+        <v>10.64460182001643</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>15.8989898989899</v>
+        <v>15.31111111111111</v>
       </c>
       <c r="B4">
-        <v>16.27203421343469</v>
+        <v>15.89333207605451</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>20.84848484848485</v>
+        <v>20.26666666666667</v>
       </c>
       <c r="B5">
-        <v>21.51094904735587</v>
+        <v>21.18554071788424</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>25.7979797979798</v>
+        <v>25.22222222222222</v>
       </c>
       <c r="B6">
-        <v>26.78746724132179</v>
+        <v>26.51057707003659</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>30.74747474747475</v>
+        <v>30.17777777777778</v>
       </c>
       <c r="B7">
-        <v>32.09447020666597</v>
+        <v>31.86204325565161</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>35.6969696969697</v>
+        <v>35.13333333333333</v>
       </c>
       <c r="B8">
-        <v>37.42713957760572</v>
+        <v>37.23565634336442</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>40.64646464646465</v>
+        <v>40.08888888888889</v>
       </c>
       <c r="B9">
-        <v>42.78199134326086</v>
+        <v>42.62834309289884</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>45.5959595959596</v>
+        <v>45.04444444444444</v>
       </c>
       <c r="B10">
-        <v>48.15638616568128</v>
+        <v>48.03778849180213</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>50.54545454545455</v>
+        <v>50</v>
       </c>
       <c r="B11">
-        <v>53.54825392267355</v>
+        <v>53.46218473795459</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>55.49494949494949</v>
+        <v>54.95555555555556</v>
       </c>
       <c r="B12">
-        <v>58.95592662293612</v>
+        <v>58.90008030610847</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>60.44444444444445</v>
+        <v>59.91111111111111</v>
       </c>
       <c r="B13">
-        <v>64.37803106413091</v>
+        <v>64.3502836447241</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>65.39393939393941</v>
+        <v>64.86666666666667</v>
       </c>
       <c r="B14">
-        <v>69.81341667303326</v>
+        <v>69.81179879421782</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>70.34343434343435</v>
+        <v>69.82222222222222</v>
       </c>
       <c r="B15">
-        <v>75.26110517996189</v>
+        <v>75.28378069098808</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>75.2929292929293</v>
+        <v>74.77777777777779</v>
       </c>
       <c r="B16">
-        <v>80.720254435976</v>
+        <v>80.76550315580583</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>80.24242424242425</v>
+        <v>79.73333333333335</v>
       </c>
       <c r="B17">
-        <v>86.19013172276803</v>
+        <v>86.2563353583365</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>85.1919191919192</v>
+        <v>84.6888888888889</v>
       </c>
       <c r="B18">
-        <v>91.67009362887831</v>
+        <v>91.75572412254094</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>90.14141414141415</v>
+        <v>89.64444444444445</v>
       </c>
       <c r="B19">
-        <v>97.15957058679552</v>
+        <v>97.26318036435617</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>95.09090909090909</v>
+        <v>94.60000000000001</v>
       </c>
       <c r="B20">
-        <v>102.6580547933645</v>
+        <v>102.7782685202859</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>100.040404040404</v>
+        <v>99.55555555555557</v>
       </c>
       <c r="B21">
-        <v>108.1650906347704</v>
+        <v>108.3005981844062</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>104.989898989899</v>
+        <v>104.5111111111111</v>
       </c>
       <c r="B22">
-        <v>113.6802669980107</v>
+        <v>113.8298174049763</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>109.939393939394</v>
+        <v>109.4666666666667</v>
       </c>
       <c r="B23">
-        <v>119.2032110253892</v>
+        <v>119.3656072479073</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>114.8888888888889</v>
+        <v>114.4222222222222</v>
       </c>
       <c r="B24">
-        <v>124.7335829881737</v>
+        <v>124.9076773409377</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>119.8383838383838</v>
+        <v>119.3777777777778</v>
       </c>
       <c r="B25">
-        <v>130.2710720391229</v>
+        <v>130.4557621866426</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>124.7878787878788</v>
+        <v>124.3333333333333</v>
       </c>
       <c r="B26">
-        <v>135.8153926630103</v>
+        <v>136.009618085105</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>129.7373737373737</v>
+        <v>129.2888888888889</v>
       </c>
       <c r="B27">
-        <v>141.3662816872214</v>
+        <v>141.5690205450825</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>134.6868686868687</v>
+        <v>134.2444444444444</v>
       </c>
       <c r="B28">
-        <v>146.9234957459932</v>
+        <v>147.1337620903234</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>139.6363636363637</v>
+        <v>139.2</v>
       </c>
       <c r="B29">
-        <v>152.4868091152699</v>
+        <v>152.703650388317</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>144.5858585858586</v>
+        <v>144.1555555555556</v>
       </c>
       <c r="B30">
-        <v>158.0560118527572</v>
+        <v>158.2785066442674</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>149.5353535353536</v>
+        <v>149.1111111111111</v>
       </c>
       <c r="B31">
-        <v>163.6309081911545</v>
+        <v>163.8581642148528</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>154.4848484848485</v>
+        <v>154.0666666666667</v>
       </c>
       <c r="B32">
-        <v>169.2113151428445</v>
+        <v>169.4424674053707</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>159.4343434343434</v>
+        <v>159.0222222222222</v>
       </c>
       <c r="B33">
-        <v>174.7970612823134</v>
+        <v>175.0312704208795</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>164.3838383838384</v>
+        <v>163.9777777777778</v>
       </c>
       <c r="B34">
-        <v>180.3879856788375</v>
+        <v>180.6244364474268</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>169.3333333333333</v>
+        <v>168.9333333333333</v>
       </c>
       <c r="B35">
-        <v>185.9839369569168</v>
+        <v>186.221836843779</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>174.2828282828283</v>
+        <v>173.8888888888889</v>
       </c>
       <c r="B36">
-        <v>191.5847724658714</v>
+        <v>191.8233504275046</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>179.2323232323232</v>
+        <v>178.8444444444445</v>
       </c>
       <c r="B37">
-        <v>197.1903575431725</v>
+        <v>197.4288628420186</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>184.1818181818182</v>
+        <v>183.8</v>
       </c>
       <c r="B38">
-        <v>202.800564858627</v>
+        <v>203.038265993412</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>189.1313131313131</v>
+        <v>188.7555555555556</v>
       </c>
       <c r="B39">
-        <v>208.4152738286039</v>
+        <v>208.6514575476977</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>194.0808080808081</v>
+        <v>193.7111111111111</v>
       </c>
       <c r="B40">
-        <v>214.034370091182</v>
+        <v>214.2683404805717</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>199.030303030303</v>
+        <v>198.6666666666667</v>
       </c>
       <c r="B41">
-        <v>219.6577450344884</v>
+        <v>219.8888226729995</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>203.979797979798</v>
+        <v>203.6222222222222</v>
       </c>
       <c r="B42">
-        <v>225.2852953716474</v>
+        <v>225.512816546936</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>208.929292929293</v>
+        <v>208.5777777777778</v>
       </c>
       <c r="B43">
-        <v>230.9169227567126</v>
+        <v>231.1402387363136</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>213.8787878787879</v>
+        <v>213.5333333333333</v>
       </c>
       <c r="B44">
-        <v>236.5525334367514</v>
+        <v>236.7710097891282</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>218.8282828282829</v>
+        <v>218.4888888888889</v>
       </c>
       <c r="B45">
-        <v>242.1920379359224</v>
+        <v>242.4050538970273</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>223.7777777777778</v>
+        <v>223.4444444444445</v>
       </c>
       <c r="B46">
-        <v>247.8353507679419</v>
+        <v>248.0422986492962</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>228.7272727272727</v>
+        <v>228.4</v>
       </c>
       <c r="B47">
-        <v>253.4823901738206</v>
+        <v>253.6826748085472</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>233.6767676767677</v>
+        <v>233.3555555555556</v>
       </c>
       <c r="B48">
-        <v>259.1330778821469</v>
+        <v>259.3261161057673</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>238.6262626262626</v>
+        <v>238.3111111111111</v>
       </c>
       <c r="B49">
-        <v>264.7873388895433</v>
+        <v>264.9725590526777</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>243.5757575757576</v>
+        <v>243.2666666666667</v>
       </c>
       <c r="B50">
-        <v>270.4451012592135</v>
+        <v>270.6219427696142</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>248.5252525252525</v>
+        <v>248.2222222222222</v>
       </c>
       <c r="B51">
-        <v>276.1062959357533</v>
+        <v>276.2742088273522</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>253.4747474747475</v>
+        <v>253.1777777777778</v>
       </c>
       <c r="B52">
-        <v>281.770856574613</v>
+        <v>281.9293011014918</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>258.4242424242424</v>
+        <v>258.1333333333333</v>
       </c>
       <c r="B53">
-        <v>287.4387193847877</v>
+        <v>287.5871656381791</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>263.3737373737374</v>
+        <v>263.0888888888888</v>
       </c>
       <c r="B54">
-        <v>293.1098229834785</v>
+        <v>293.2477505300798</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>268.3232323232323</v>
+        <v>268.0444444444444</v>
       </c>
       <c r="B55">
-        <v>298.7841082616019</v>
+        <v>298.9110058016444</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>273.2727272727273</v>
+        <v>273</v>
       </c>
       <c r="B56">
-        <v>304.4615182591557</v>
+        <v>304.5768833028088</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>278.2222222222222</v>
+        <v>277.9555555555555</v>
       </c>
       <c r="B57">
-        <v>310.1419980495502</v>
+        <v>310.2453366103697</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>283.1717171717172</v>
+        <v>282.9111111111111</v>
       </c>
       <c r="B58">
-        <v>315.8254946321151</v>
+        <v>315.9163209363526</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>288.1212121212121</v>
+        <v>287.8666666666667</v>
       </c>
       <c r="B59">
-        <v>321.5119568320683</v>
+        <v>321.5897930427622</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>293.0707070707071</v>
+        <v>292.8222222222222</v>
       </c>
       <c r="B60">
-        <v>327.2013352073111</v>
+        <v>327.2657111621699</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>298.020202020202</v>
+        <v>297.7777777777778</v>
       </c>
       <c r="B61">
-        <v>332.8935819614759</v>
+        <v>332.9440349236457</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>302.969696969697</v>
+        <v>302.7333333333333</v>
       </c>
       <c r="B62">
-        <v>338.5886508627097</v>
+        <v>338.6247252835914</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>307.9191919191919</v>
+        <v>307.6888888888889</v>
       </c>
       <c r="B63">
-        <v>344.2864971677276</v>
+        <v>344.307744461077</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>312.8686868686869</v>
+        <v>312.6444444444444</v>
       </c>
       <c r="B64">
-        <v>349.9870775507161</v>
+        <v>349.993055877318</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>317.8181818181818</v>
+        <v>317.6</v>
       </c>
       <c r="B65">
-        <v>355.6903500367021</v>
+        <v>355.6806240989681</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>322.7676767676768</v>
+        <v>322.5555555555555</v>
       </c>
       <c r="B66">
-        <v>361.3962739390456</v>
+        <v>361.3704147849296</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>327.7171717171718</v>
+        <v>327.5111111111111</v>
       </c>
       <c r="B67">
-        <v>367.1048098007374</v>
+        <v>367.0623946364145</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>332.6666666666667</v>
+        <v>332.4666666666666</v>
       </c>
       <c r="B68">
-        <v>372.8159193392195</v>
+        <v>372.7565313500093</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>337.6161616161617</v>
+        <v>337.4222222222222</v>
       </c>
       <c r="B69">
-        <v>378.5295653944661</v>
+        <v>378.4527935735218</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>342.5656565656566</v>
+        <v>342.3777777777777</v>
       </c>
       <c r="B70">
-        <v>384.2457118800868</v>
+        <v>384.1511508644074</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>347.5151515151516</v>
+        <v>347.3333333333333</v>
       </c>
       <c r="B71">
-        <v>389.964323737237</v>
+        <v>389.8515736505871</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>352.4646464646465</v>
+        <v>352.2888888888889</v>
       </c>
       <c r="B72">
-        <v>395.6853668911342</v>
+        <v>395.5540331934884</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>357.4141414141415</v>
+        <v>357.2444444444444</v>
       </c>
       <c r="B73">
-        <v>401.4088082100006</v>
+        <v>401.2585015531545</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>362.3636363636364</v>
+        <v>362.2</v>
       </c>
       <c r="B74">
-        <v>407.134615466263</v>
+        <v>406.964951555277</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>367.3131313131314</v>
+        <v>367.1555555555556</v>
       </c>
       <c r="B75">
-        <v>412.8627572998581</v>
+        <v>412.6733567600223</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>372.2626262626263</v>
+        <v>372.1111111111111</v>
       </c>
       <c r="B76">
-        <v>418.5932031835009</v>
+        <v>418.3836914325316</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>377.2121212121212</v>
+        <v>377.0666666666667</v>
       </c>
       <c r="B77">
-        <v>424.3259233897883</v>
+        <v>424.0959305149823</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>382.1616161616162</v>
+        <v>382.0222222222222</v>
       </c>
       <c r="B78">
-        <v>430.0608889600148</v>
+        <v>429.8100496001096</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>387.1111111111111</v>
+        <v>386.9777777777778</v>
       </c>
       <c r="B79">
-        <v>435.7980716745953</v>
+        <v>435.5260249060941</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>392.0606060606061</v>
+        <v>391.9333333333333</v>
       </c>
       <c r="B80">
-        <v>441.5374440249866</v>
+        <v>441.2438332527279</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>397.010101010101</v>
+        <v>396.8888888888889</v>
       </c>
       <c r="B81">
-        <v>447.278979187019</v>
+        <v>446.9634520387788</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82">
-        <v>401.959595959596</v>
+        <v>401.8444444444444</v>
       </c>
       <c r="B82">
-        <v>453.0226509955469</v>
+        <v>452.6848592204785</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83">
-        <v>406.9090909090909</v>
+        <v>406.8</v>
       </c>
       <c r="B83">
-        <v>458.7684339203399</v>
+        <v>458.4080332910651</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84">
-        <v>411.8585858585859</v>
+        <v>411.7555555555555</v>
       </c>
       <c r="B84">
-        <v>464.5163030431381</v>
+        <v>464.1329532613172</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85">
-        <v>416.8080808080808</v>
+        <v>416.7111111111111</v>
       </c>
       <c r="B85">
-        <v>470.266234035802</v>
+        <v>469.8595986410191</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86">
-        <v>421.7575757575758</v>
+        <v>421.6666666666666</v>
       </c>
       <c r="B86">
-        <v>476.0182031394944</v>
+        <v>475.5879494213023</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87">
-        <v>426.7070707070707</v>
+        <v>426.6222222222222</v>
       </c>
       <c r="B87">
-        <v>481.7721871448301</v>
+        <v>481.3179860578123</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88">
-        <v>431.6565656565657</v>
+        <v>431.5777777777778</v>
       </c>
       <c r="B88">
-        <v>487.5281633729426</v>
+        <v>487.0496894546528</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89">
-        <v>436.6060606060606</v>
+        <v>436.5333333333333</v>
       </c>
       <c r="B89">
-        <v>493.2861096574107</v>
+        <v>492.7830409490628</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90">
-        <v>441.5555555555556</v>
+        <v>441.4888888888889</v>
       </c>
       <c r="B90">
-        <v>499.0460043270007</v>
+        <v>498.5180222967855</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91">
-        <v>446.5050505050505</v>
+        <v>446.4444444444445</v>
       </c>
       <c r="B91">
-        <v>504.8078261891748</v>
+        <v>504.2546156580901</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92">
-        <v>451.4545454545455</v>
+        <v>451.4</v>
       </c>
       <c r="B92">
-        <v>510.5715545143277</v>
+        <v>509.9928035844103</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93">
-        <v>456.4040404040404</v>
+        <v>456.3555555555556</v>
       </c>
       <c r="B93">
-        <v>516.3371690207069</v>
+        <v>515.7325690055666</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94">
-        <v>461.3535353535354</v>
+        <v>461.3111111111111</v>
       </c>
       <c r="B94">
-        <v>522.1046498599859</v>
+        <v>521.4738952175392</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95">
-        <v>466.3030303030303</v>
+        <v>466.2666666666667</v>
       </c>
       <c r="B95">
-        <v>527.8739776034479</v>
+        <v>527.2167658707642</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96">
-        <v>471.2525252525253</v>
+        <v>471.2222222222222</v>
       </c>
       <c r="B96">
-        <v>533.6451332287552</v>
+        <v>532.961164958924</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97">
-        <v>476.2020202020202</v>
+        <v>476.1777777777777</v>
       </c>
       <c r="B97">
-        <v>539.4180981072691</v>
+        <v>538.7070768082059</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98">
-        <v>481.1515151515152</v>
+        <v>481.1333333333333</v>
       </c>
       <c r="B98">
-        <v>545.1928539918933</v>
+        <v>544.454486067006</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99">
-        <v>486.1010101010102</v>
+        <v>486.0888888888889</v>
       </c>
       <c r="B99">
-        <v>550.9693830054133</v>
+        <v>550.203377696054</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100">
-        <v>491.0505050505051</v>
+        <v>491.0444444444444</v>
       </c>
       <c r="B100">
-        <v>556.7476676293085</v>
+        <v>555.9537369589386</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1721,7 +5111,7 @@
         <v>496</v>
       </c>
       <c r="B101">
-        <v>562.5276906930112</v>
+        <v>561.7055494130136</v>
       </c>
     </row>
   </sheetData>
@@ -1736,28 +5126,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1765,25 +5155,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="C2">
-        <v>1.273664878302853</v>
+        <v>0.9451631252505217</v>
       </c>
       <c r="D2">
-        <v>1.567263</v>
+        <v>1.501667</v>
       </c>
       <c r="E2">
-        <v>0.1059014148583483</v>
+        <v>0.09251132663445416</v>
       </c>
       <c r="F2">
-        <v>0.7781512503836436</v>
+        <v>0.7323937598229685</v>
       </c>
       <c r="G2">
-        <v>0.1951418808749138</v>
+        <v>0.1765736369981793</v>
       </c>
       <c r="H2">
-        <v>0.2388171056877338</v>
+        <v>0.2291877003782468</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1791,25 +5181,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>16.5</v>
+        <v>17.2</v>
       </c>
       <c r="C3">
-        <v>2.944863701807305</v>
+        <v>3.349295116554792</v>
       </c>
       <c r="D3">
-        <v>1.927077</v>
+        <v>1.97426</v>
       </c>
       <c r="E3">
-        <v>0.08889780622277595</v>
+        <v>0.08059558037234768</v>
       </c>
       <c r="F3">
-        <v>1.217483944213906</v>
+        <v>1.235528446907549</v>
       </c>
       <c r="G3">
-        <v>0.284899068058154</v>
+        <v>0.2954043464742966</v>
       </c>
       <c r="H3">
-        <v>0.268703766341072</v>
+        <v>0.2661134305363873</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1817,25 +5207,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>31.4</v>
+        <v>39.6</v>
       </c>
       <c r="C4">
-        <v>6.491361781458322</v>
+        <v>6.899597411765735</v>
       </c>
       <c r="D4">
-        <v>2.06712</v>
+        <v>2.122567</v>
       </c>
       <c r="E4">
-        <v>0.06553245891244361</v>
+        <v>0.03074466172452635</v>
       </c>
       <c r="F4">
-        <v>1.496929648073215</v>
+        <v>1.597695185925512</v>
       </c>
       <c r="G4">
-        <v>0.3153656889277745</v>
+        <v>0.3268614078776109</v>
       </c>
       <c r="H4">
-        <v>0.2877137308612701</v>
+        <v>0.2926933337323337</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1843,25 +5233,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>50</v>
+        <v>70.5</v>
       </c>
       <c r="C5">
-        <v>7.049034606872695</v>
+        <v>11.99837952021485</v>
       </c>
       <c r="D5">
-        <v>2.105783</v>
+        <v>2.155135</v>
       </c>
       <c r="E5">
-        <v>0.03783272134747321</v>
+        <v>0.03848652942553045</v>
       </c>
       <c r="F5">
-        <v>1.698970004336019</v>
+        <v>1.848189116991399</v>
       </c>
       <c r="G5">
-        <v>0.3234136153023646</v>
+        <v>0.333474480027471</v>
       </c>
       <c r="H5">
-        <v>0.3014580108811834</v>
+        <v>0.3110774196286731</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1869,25 +5259,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>77.2</v>
+        <v>103</v>
       </c>
       <c r="C6">
-        <v>12.8</v>
+        <v>13.03755259923341</v>
       </c>
       <c r="D6">
-        <v>2.101004</v>
+        <v>2.182181</v>
       </c>
       <c r="E6">
-        <v>0.02090798652296399</v>
+        <v>0.03400409574840458</v>
       </c>
       <c r="F6">
-        <v>1.887617300335736</v>
+        <v>2.012837224705172</v>
       </c>
       <c r="G6">
-        <v>0.3224268792390197</v>
+        <v>0.3388907701025115</v>
       </c>
       <c r="H6">
-        <v>0.3142911958407613</v>
+        <v>0.3231611652986774</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1895,25 +5285,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>156.8</v>
+        <v>135.6</v>
       </c>
       <c r="C7">
-        <v>19.21214893411631</v>
+        <v>17.64224727433806</v>
       </c>
       <c r="D7">
-        <v>2.208656</v>
+        <v>2.16201</v>
       </c>
       <c r="E7">
-        <v>0.03128599239986554</v>
+        <v>0.02434110401038629</v>
       </c>
       <c r="F7">
-        <v>2.19534605834842</v>
+        <v>2.132259689531045</v>
       </c>
       <c r="G7">
-        <v>0.3441280794135139</v>
+        <v>0.334857698375282</v>
       </c>
       <c r="H7">
-        <v>0.3352251829834335</v>
+        <v>0.331925740320393</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1921,25 +5311,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>157.3</v>
+        <v>199.5</v>
       </c>
       <c r="C8">
-        <v>17.51002887236658</v>
+        <v>22.33743743384883</v>
       </c>
       <c r="D8">
-        <v>2.148046</v>
+        <v>2.190303</v>
       </c>
       <c r="E8">
-        <v>0.015994988395675</v>
+        <v>0.0238138253985182</v>
       </c>
       <c r="F8">
-        <v>2.196728722623287</v>
+        <v>2.299942900022767</v>
       </c>
       <c r="G8">
-        <v>0.3320435774615302</v>
+        <v>0.3405041980025053</v>
       </c>
       <c r="H8">
-        <v>0.3353192420383611</v>
+        <v>0.3442322362579849</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1947,25 +5337,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>268.4</v>
+        <v>246</v>
       </c>
       <c r="C9">
-        <v>15.93751688452264</v>
+        <v>25.42527176736651</v>
       </c>
       <c r="D9">
-        <v>2.213014</v>
+        <v>2.200518</v>
       </c>
       <c r="E9">
-        <v>0.008185803048910686</v>
+        <v>0.02204883029399366</v>
       </c>
       <c r="F9">
-        <v>2.428782511496955</v>
+        <v>2.390935107103379</v>
       </c>
       <c r="G9">
-        <v>0.3449841613757507</v>
+        <v>0.3425249253955337</v>
       </c>
       <c r="H9">
-        <v>0.3511052578272706</v>
+        <v>0.350910276495325</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1973,25 +5363,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>311.6</v>
+        <v>301.9</v>
       </c>
       <c r="C10">
-        <v>26.19847323795797</v>
+        <v>22.93587679694073</v>
       </c>
       <c r="D10">
-        <v>2.226885</v>
+        <v>2.224956</v>
       </c>
       <c r="E10">
-        <v>0.01392093501409539</v>
+        <v>0.008657177779802771</v>
       </c>
       <c r="F10">
-        <v>2.493597449000527</v>
+        <v>2.479863113023098</v>
       </c>
       <c r="G10">
-        <v>0.3476977899325617</v>
+        <v>0.3473214269366589</v>
       </c>
       <c r="H10">
-        <v>0.3555144494709614</v>
+        <v>0.3574368222382168</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1999,25 +5389,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>343.4</v>
+        <v>333.9</v>
       </c>
       <c r="C11">
-        <v>28.52297319705644</v>
+        <v>28.02516726087464</v>
       </c>
       <c r="D11">
-        <v>2.236785</v>
+        <v>2.229349</v>
       </c>
       <c r="E11">
-        <v>0.009397004871529828</v>
+        <v>0.009009424257101242</v>
       </c>
       <c r="F11">
-        <v>2.535800290824898</v>
+        <v>2.523616419054371</v>
       </c>
       <c r="G11">
-        <v>0.3496242416732986</v>
+        <v>0.3481780617102401</v>
       </c>
       <c r="H11">
-        <v>0.3583853990495484</v>
+        <v>0.3606479361079423</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2043,7 +5433,7 @@
         <v>0.3560564671791732</v>
       </c>
       <c r="H12">
-        <v>0.3692481084564596</v>
+        <v>0.3732613580852823</v>
       </c>
     </row>
   </sheetData>
@@ -2058,802 +5448,802 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="B2">
-        <v>1.760677699531628</v>
+        <v>1.7382395832899</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>10.94949494949495</v>
+        <v>10.35555555555556</v>
       </c>
       <c r="B3">
-        <v>1.828422796121607</v>
+        <v>1.813967594164094</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>15.8989898989899</v>
+        <v>15.31111111111111</v>
       </c>
       <c r="B4">
-        <v>1.871728820147263</v>
+        <v>1.861025388117591</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>20.84848484848485</v>
+        <v>20.26666666666667</v>
       </c>
       <c r="B5">
-        <v>1.903840736599299</v>
+        <v>1.895516908706569</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>25.7979797979798</v>
+        <v>25.22222222222222</v>
       </c>
       <c r="B6">
-        <v>1.92946555562133</v>
+        <v>1.922868115872758</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>30.74747474747475</v>
+        <v>30.17777777777778</v>
       </c>
       <c r="B7">
-        <v>1.950837846333064</v>
+        <v>1.945591249216023</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>35.6969696969697</v>
+        <v>35.13333333333333</v>
       </c>
       <c r="B8">
-        <v>1.969199347648592</v>
+        <v>1.965061732271691</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>40.64646464646465</v>
+        <v>40.08888888888889</v>
       </c>
       <c r="B9">
-        <v>1.985313337755314</v>
+        <v>1.982116662349557</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>45.5959595959596</v>
+        <v>45.04444444444444</v>
       </c>
       <c r="B10">
-        <v>1.999683353636969</v>
+        <v>1.997304360519206</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>50.54545454545455</v>
+        <v>50</v>
       </c>
       <c r="B11">
-        <v>2.012659470909559</v>
+        <v>2.011004004750077</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>55.49494949494949</v>
+        <v>54.95555555555556</v>
       </c>
       <c r="B12">
-        <v>2.024495147255233</v>
+        <v>2.023488982404036</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>60.44444444444445</v>
+        <v>59.91111111111111</v>
       </c>
       <c r="B13">
-        <v>2.035379917654685</v>
+        <v>2.034963052015085</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>65.39393939393941</v>
+        <v>64.86666666666667</v>
       </c>
       <c r="B14">
-        <v>2.045459306643067</v>
+        <v>2.045582233634623</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>70.34343434343435</v>
+        <v>69.82222222222222</v>
       </c>
       <c r="B15">
-        <v>2.054847529263604</v>
+        <v>2.055468702811512</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>75.2929292929293</v>
+        <v>74.77777777777779</v>
       </c>
       <c r="B16">
-        <v>2.063635907850051</v>
+        <v>2.064719960394096</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>80.24242424242425</v>
+        <v>79.73333333333335</v>
       </c>
       <c r="B17">
-        <v>2.071898631878178</v>
+        <v>2.073415086099789</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>85.1919191919192</v>
+        <v>84.6888888888889</v>
       </c>
       <c r="B18">
-        <v>2.079696809165901</v>
+        <v>2.081619124042019</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>90.14141414141415</v>
+        <v>89.64444444444445</v>
       </c>
       <c r="B19">
-        <v>2.087081383568123</v>
+        <v>2.089386233187803</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>95.09090909090909</v>
+        <v>94.60000000000001</v>
       </c>
       <c r="B20">
-        <v>2.094095280188565</v>
+        <v>2.096761998575758</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>100.040404040404</v>
+        <v>99.55555555555557</v>
       </c>
       <c r="B21">
-        <v>2.100775011589487</v>
+        <v>2.103785158450297</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>104.989898989899</v>
+        <v>104.5111111111111</v>
       </c>
       <c r="B22">
-        <v>2.107151900003449</v>
+        <v>2.110488916219901</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>109.939393939394</v>
+        <v>109.4666666666667</v>
       </c>
       <c r="B23">
-        <v>2.113253020864831</v>
+        <v>2.11690195171283</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>114.8888888888889</v>
+        <v>114.4222222222222</v>
       </c>
       <c r="B24">
-        <v>2.119101940713338</v>
+        <v>2.123049210953511</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>119.8383838383838</v>
+        <v>119.3777777777778</v>
       </c>
       <c r="B25">
-        <v>2.124719301089494</v>
+        <v>2.12895253032662</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>124.7878787878788</v>
+        <v>124.3333333333333</v>
       </c>
       <c r="B26">
-        <v>2.130123285513141</v>
+        <v>2.134631135198107</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>129.7373737373737</v>
+        <v>129.2888888888889</v>
       </c>
       <c r="B27">
-        <v>2.135329996604065</v>
+        <v>2.140102042176534</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>134.6868686868687</v>
+        <v>134.2444444444444</v>
       </c>
       <c r="B28">
-        <v>2.140353763360163</v>
+        <v>2.145380386568904</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>139.6363636363637</v>
+        <v>139.2</v>
       </c>
       <c r="B29">
-        <v>2.145207393587139</v>
+        <v>2.150479691155431</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>144.5858585858586</v>
+        <v>144.1555555555556</v>
       </c>
       <c r="B30">
-        <v>2.149902382843427</v>
+        <v>2.155412088488259</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>149.5353535353536</v>
+        <v>149.1111111111111</v>
       </c>
       <c r="B31">
-        <v>2.15444908860566</v>
+        <v>2.160188506053071</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>154.4848484848485</v>
+        <v>154.0666666666667</v>
       </c>
       <c r="B32">
-        <v>2.158856876389921</v>
+        <v>2.16481882151132</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>159.4343434343434</v>
+        <v>159.0222222222222</v>
       </c>
       <c r="B33">
-        <v>2.16313424308807</v>
+        <v>2.169311993653505</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>164.3838383838384</v>
+        <v>163.9777777777778</v>
       </c>
       <c r="B34">
-        <v>2.167288921661169</v>
+        <v>2.173676173493734</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>169.3333333333333</v>
+        <v>168.9333333333333</v>
       </c>
       <c r="B35">
-        <v>2.171327970478336</v>
+        <v>2.177918799019689</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>174.2828282828283</v>
+        <v>173.8888888888889</v>
       </c>
       <c r="B36">
-        <v>2.175257849931133</v>
+        <v>2.182046676406467</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>179.2323232323232</v>
+        <v>178.8444444444445</v>
       </c>
       <c r="B37">
-        <v>2.179084488441947</v>
+        <v>2.186066049954688</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>184.1818181818182</v>
+        <v>183.8</v>
       </c>
       <c r="B38">
-        <v>2.182813339583932</v>
+        <v>2.189982662584256</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>189.1313131313131</v>
+        <v>188.7555555555556</v>
       </c>
       <c r="B39">
-        <v>2.18644943171367</v>
+        <v>2.193801808376825</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>194.0808080808081</v>
+        <v>193.7111111111111</v>
       </c>
       <c r="B40">
-        <v>2.189997411266342</v>
+        <v>2.19752837839133</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>199.030303030303</v>
+        <v>198.6666666666667</v>
       </c>
       <c r="B41">
-        <v>2.193461580662015</v>
+        <v>2.201166900762238</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>203.979797979798</v>
+        <v>203.6222222222222</v>
       </c>
       <c r="B42">
-        <v>2.196845931609889</v>
+        <v>2.204721575917429</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>208.929292929293</v>
+        <v>208.5777777777778</v>
       </c>
       <c r="B43">
-        <v>2.200154174466262</v>
+        <v>2.208196307612911</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>213.8787878787879</v>
+        <v>213.5333333333333</v>
       </c>
       <c r="B44">
-        <v>2.203389764195388</v>
+        <v>2.21159473036793</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>218.8282828282829</v>
+        <v>218.4888888888889</v>
       </c>
       <c r="B45">
-        <v>2.206555923395126</v>
+        <v>2.214920233791075</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>223.7777777777778</v>
+        <v>223.4444444444445</v>
       </c>
       <c r="B46">
-        <v>2.209655662777549</v>
+        <v>2.2181759842116</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>228.7272727272727</v>
+        <v>228.4</v>
       </c>
       <c r="B47">
-        <v>2.212691799435388</v>
+        <v>2.22136494396712</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>233.6767676767677</v>
+        <v>233.3555555555556</v>
       </c>
       <c r="B48">
-        <v>2.215666973176025</v>
+        <v>2.224489888646501</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>238.6262626262626</v>
+        <v>238.3111111111111</v>
       </c>
       <c r="B49">
-        <v>2.21858366116373</v>
+        <v>2.227553422543188</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>243.5757575757576</v>
+        <v>243.2666666666667</v>
       </c>
       <c r="B50">
-        <v>2.221444191076524</v>
+        <v>2.230557992537752</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>248.5252525252525</v>
+        <v>248.2222222222222</v>
       </c>
       <c r="B51">
-        <v>2.22425075295523</v>
+        <v>2.233505900597796</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>253.4747474747475</v>
+        <v>253.1777777777778</v>
       </c>
       <c r="B52">
-        <v>2.227005409897973</v>
+        <v>2.236399315057576</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>258.4242424242424</v>
+        <v>258.1333333333333</v>
       </c>
       <c r="B53">
-        <v>2.229710107732774</v>
+        <v>2.239240280817825</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>263.3737373737374</v>
+        <v>263.0888888888888</v>
       </c>
       <c r="B54">
-        <v>2.232366683783468</v>
+        <v>2.242030728587728</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>268.3232323232323</v>
+        <v>268.0444444444444</v>
       </c>
       <c r="B55">
-        <v>2.234976874829218</v>
+        <v>2.24477248327523</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>273.2727272727273</v>
+        <v>273</v>
       </c>
       <c r="B56">
-        <v>2.237542324345223</v>
+        <v>2.247467271618311</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>278.2222222222222</v>
+        <v>277.9555555555555</v>
       </c>
       <c r="B57">
-        <v>2.24006458910128</v>
+        <v>2.250116729138353</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>283.1717171717172</v>
+        <v>282.9111111111111</v>
       </c>
       <c r="B58">
-        <v>2.242545145185469</v>
+        <v>2.252722406486719</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>288.1212121212121</v>
+        <v>287.8666666666667</v>
       </c>
       <c r="B59">
-        <v>2.244985393512151</v>
+        <v>2.255285775247137</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>293.0707070707071</v>
+        <v>292.8222222222222</v>
       </c>
       <c r="B60">
-        <v>2.247386664866469</v>
+        <v>2.257808233249051</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>298.020202020202</v>
+        <v>297.7777777777778</v>
       </c>
       <c r="B61">
-        <v>2.249750224531466</v>
+        <v>2.260291109440669</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>302.969696969697</v>
+        <v>302.7333333333333</v>
       </c>
       <c r="B62">
-        <v>2.252077276538662</v>
+        <v>2.262735668364868</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>307.9191919191919</v>
+        <v>307.6888888888889</v>
       </c>
       <c r="B63">
-        <v>2.254368967578351</v>
+        <v>2.265143114276257</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>312.8686868686869</v>
+        <v>312.6444444444444</v>
       </c>
       <c r="B64">
-        <v>2.256626390601844</v>
+        <v>2.267514594933433</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>317.8181818181818</v>
+        <v>317.6</v>
       </c>
       <c r="B65">
-        <v>2.258850588144396</v>
+        <v>2.26985120509677</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>322.7676767676768</v>
+        <v>322.5555555555555</v>
       </c>
       <c r="B66">
-        <v>2.261042555394444</v>
+        <v>2.272153989758822</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>327.7171717171718</v>
+        <v>327.5111111111111</v>
       </c>
       <c r="B67">
-        <v>2.26320324303211</v>
+        <v>2.274423947131528</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>332.6666666666667</v>
+        <v>332.4666666666666</v>
       </c>
       <c r="B68">
-        <v>2.265333559857502</v>
+        <v>2.27666203141193</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>337.6161616161617</v>
+        <v>337.4222222222222</v>
       </c>
       <c r="B69">
-        <v>2.267434375227262</v>
+        <v>2.278869155345849</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>342.5656565656566</v>
+        <v>342.3777777777777</v>
       </c>
       <c r="B70">
-        <v>2.26950652131594</v>
+        <v>2.28104619260701</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>347.5151515151516</v>
+        <v>347.3333333333333</v>
       </c>
       <c r="B71">
-        <v>2.271550795217121</v>
+        <v>2.283193980007377</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>352.4646464646465</v>
+        <v>352.2888888888889</v>
       </c>
       <c r="B72">
-        <v>2.27356796089776</v>
+        <v>2.28531331955288</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>357.4141414141415</v>
+        <v>357.2444444444444</v>
       </c>
       <c r="B73">
-        <v>2.275558751017902</v>
+        <v>2.28740498035737</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>362.3636363636364</v>
+        <v>362.2</v>
       </c>
       <c r="B74">
-        <v>2.27752386862677</v>
+        <v>2.289469700426392</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>367.3131313131314</v>
+        <v>367.1555555555556</v>
       </c>
       <c r="B75">
-        <v>2.279463988745188</v>
+        <v>2.291508188321286</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>372.2626262626263</v>
+        <v>372.1111111111111</v>
       </c>
       <c r="B76">
-        <v>2.281379759843382</v>
+        <v>2.293521124713137</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>377.2121212121212</v>
+        <v>377.0666666666667</v>
       </c>
       <c r="B77">
-        <v>2.283271805222359</v>
+        <v>2.295509163835231</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>382.1616161616162</v>
+        <v>382.0222222222222</v>
       </c>
       <c r="B78">
-        <v>2.28514072430634</v>
+        <v>2.297472934841881</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>387.1111111111111</v>
+        <v>386.9777777777778</v>
       </c>
       <c r="B79">
-        <v>2.286987093853039</v>
+        <v>2.299413043080796</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>392.0606060606061</v>
+        <v>391.9333333333333</v>
       </c>
       <c r="B80">
-        <v>2.28881146908799</v>
+        <v>2.301330071285514</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>397.010101010101</v>
+        <v>396.8888888888889</v>
       </c>
       <c r="B81">
-        <v>2.290614384768581</v>
+        <v>2.303224580693871</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82">
-        <v>401.959595959596</v>
+        <v>401.8444444444444</v>
       </c>
       <c r="B82">
-        <v>2.292396356182973</v>
+        <v>2.305097112097953</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83">
-        <v>406.9090909090909</v>
+        <v>406.8</v>
       </c>
       <c r="B83">
-        <v>2.294157880088628</v>
+        <v>2.306948186830516</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84">
-        <v>411.8585858585859</v>
+        <v>411.7555555555555</v>
       </c>
       <c r="B84">
-        <v>2.2958994355948</v>
+        <v>2.30877830769244</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85">
-        <v>416.8080808080808</v>
+        <v>416.7111111111111</v>
       </c>
       <c r="B85">
-        <v>2.297621484992936</v>
+        <v>2.310587959825414</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86">
-        <v>421.7575757575758</v>
+        <v>421.6666666666666</v>
       </c>
       <c r="B86">
-        <v>2.29932447453868</v>
+        <v>2.312377611533679</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87">
-        <v>426.7070707070707</v>
+        <v>426.6222222222222</v>
       </c>
       <c r="B87">
-        <v>2.301008835188793</v>
+        <v>2.314147715058384</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88">
-        <v>431.6565656565657</v>
+        <v>431.5777777777778</v>
       </c>
       <c r="B88">
-        <v>2.302674983296105</v>
+        <v>2.315898707307787</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89">
-        <v>436.6060606060606</v>
+        <v>436.5333333333333</v>
       </c>
       <c r="B89">
-        <v>2.304323321265331</v>
+        <v>2.317631010546302</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90">
-        <v>441.5555555555556</v>
+        <v>441.4888888888889</v>
       </c>
       <c r="B90">
-        <v>2.305954238172375</v>
+        <v>2.319345033045151</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91">
-        <v>446.5050505050505</v>
+        <v>446.4444444444445</v>
       </c>
       <c r="B91">
-        <v>2.307568110349527</v>
+        <v>2.321041169697162</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92">
-        <v>451.4545454545455</v>
+        <v>451.4</v>
       </c>
       <c r="B92">
-        <v>2.309165301938808</v>
+        <v>2.322719802598062</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93">
-        <v>456.4040404040404</v>
+        <v>456.3555555555556</v>
       </c>
       <c r="B93">
-        <v>2.310746165415508</v>
+        <v>2.324381301596442</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94">
-        <v>461.3535353535354</v>
+        <v>461.3111111111111</v>
       </c>
       <c r="B94">
-        <v>2.312311042083833</v>
+        <v>2.326026024814396</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95">
-        <v>466.3030303030303</v>
+        <v>466.2666666666667</v>
       </c>
       <c r="B95">
-        <v>2.31386026254643</v>
+        <v>2.327654319140704</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96">
-        <v>471.2525252525253</v>
+        <v>471.2222222222222</v>
       </c>
       <c r="B96">
-        <v>2.315394147149425</v>
+        <v>2.32926652069827</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97">
-        <v>476.2020202020202</v>
+        <v>476.1777777777777</v>
       </c>
       <c r="B97">
-        <v>2.316913006404496</v>
+        <v>2.330862955287424</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98">
-        <v>481.1515151515152</v>
+        <v>481.1333333333333</v>
       </c>
       <c r="B98">
-        <v>2.318417141389393</v>
+        <v>2.332443938806569</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99">
-        <v>486.1010101010102</v>
+        <v>486.0888888888889</v>
       </c>
       <c r="B99">
-        <v>2.319906844128206</v>
+        <v>2.334009777651541</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100">
-        <v>491.0505050505051</v>
+        <v>491.0444444444444</v>
       </c>
       <c r="B100">
-        <v>2.321382397952612</v>
+        <v>2.335560769094992</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2861,7 +6251,7 @@
         <v>496</v>
       </c>
       <c r="B101">
-        <v>2.322844077845233</v>
+        <v>2.337097201646944</v>
       </c>
     </row>
   </sheetData>
@@ -2876,28 +6266,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -2905,25 +6295,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="C2">
-        <v>1.273664878302853</v>
+        <v>0.9451631252505217</v>
       </c>
       <c r="D2">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="E2">
-        <v>0.5666666666666665</v>
+        <v>0.4725815626252609</v>
       </c>
       <c r="F2">
-        <v>0.7781512503836436</v>
+        <v>0.7323937598229685</v>
       </c>
       <c r="G2">
-        <v>0.4913616938342727</v>
+        <v>0.4313637641589874</v>
       </c>
       <c r="H2">
-        <v>0.5814355492798631</v>
+        <v>0.5202427051595349</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2931,25 +6321,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>16.5</v>
+        <v>17.2</v>
       </c>
       <c r="C3">
-        <v>2.944863701807305</v>
+        <v>3.349295116554792</v>
       </c>
       <c r="D3">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="E3">
-        <v>1.066666666666667</v>
+        <v>1.13968806648525</v>
       </c>
       <c r="F3">
-        <v>1.217483944213906</v>
+        <v>1.235528446907549</v>
       </c>
       <c r="G3">
-        <v>0.8195439355418687</v>
+        <v>0.8388490907372553</v>
       </c>
       <c r="H3">
-        <v>0.835477306763505</v>
+        <v>0.8231236750850274</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2957,25 +6347,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>31.4</v>
+        <v>39.6</v>
       </c>
       <c r="C4">
-        <v>6.491361781458322</v>
+        <v>6.899597411765735</v>
       </c>
       <c r="D4">
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="E4">
-        <v>2.022374841615668</v>
+        <v>1.154700538379251</v>
       </c>
       <c r="F4">
-        <v>1.496929648073215</v>
+        <v>1.597695185925512</v>
       </c>
       <c r="G4">
-        <v>1.05307844348342</v>
+        <v>1.079181246047625</v>
       </c>
       <c r="H4">
-        <v>0.9970652758052525</v>
+        <v>1.04114365264637</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2983,25 +6373,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>50</v>
+        <v>70.5</v>
       </c>
       <c r="C5">
-        <v>7.049034606872695</v>
+        <v>11.99837952021485</v>
       </c>
       <c r="D5">
-        <v>14.9</v>
+        <v>18.2</v>
       </c>
       <c r="E5">
-        <v>1.394034911088432</v>
+        <v>2.76003220593126</v>
       </c>
       <c r="F5">
-        <v>1.698970004336019</v>
+        <v>1.848189116991399</v>
       </c>
       <c r="G5">
-        <v>1.173186268412274</v>
+        <v>1.260071387985075</v>
       </c>
       <c r="H5">
-        <v>1.11389402064584</v>
+        <v>1.191937956337324</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3009,25 +6399,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>77.2</v>
+        <v>103</v>
       </c>
       <c r="C6">
-        <v>12.8</v>
+        <v>13.03755259923341</v>
       </c>
       <c r="D6">
-        <v>18.8</v>
+        <v>21.1</v>
       </c>
       <c r="E6">
-        <v>2.230097157823697</v>
+        <v>1.846618531261939</v>
       </c>
       <c r="F6">
-        <v>1.887617300335736</v>
+        <v>2.012837224705172</v>
       </c>
       <c r="G6">
-        <v>1.27415784926368</v>
+        <v>1.324282455297693</v>
       </c>
       <c r="H6">
-        <v>1.222978300721797</v>
+        <v>1.291054117160402</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3035,25 +6425,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>156.8</v>
+        <v>135.6</v>
       </c>
       <c r="C7">
-        <v>19.21214893411631</v>
+        <v>17.64224727433806</v>
       </c>
       <c r="D7">
-        <v>26.5</v>
+        <v>25.9</v>
       </c>
       <c r="E7">
-        <v>1.035481637800604</v>
+        <v>2.06801031589948</v>
       </c>
       <c r="F7">
-        <v>2.19534605834842</v>
+        <v>2.132259689531045</v>
       </c>
       <c r="G7">
-        <v>1.423245873936808</v>
+        <v>1.413299764081252</v>
       </c>
       <c r="H7">
-        <v>1.40092079307818</v>
+        <v>1.362944990331849</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -3061,25 +6451,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>157.3</v>
+        <v>199.5</v>
       </c>
       <c r="C8">
-        <v>17.51002887236658</v>
+        <v>22.33743743384883</v>
       </c>
       <c r="D8">
-        <v>28.5</v>
+        <v>30.3</v>
       </c>
       <c r="E8">
-        <v>1.833333333333333</v>
+        <v>1.556705923844749</v>
       </c>
       <c r="F8">
-        <v>2.196728722623287</v>
+        <v>2.299942900022767</v>
       </c>
       <c r="G8">
-        <v>1.45484486000851</v>
+        <v>1.481442628502305</v>
       </c>
       <c r="H8">
-        <v>1.401720311227705</v>
+        <v>1.463888246159122</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3087,25 +6477,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>268.4</v>
+        <v>246</v>
       </c>
       <c r="C9">
-        <v>15.93751688452264</v>
+        <v>25.42527176736651</v>
       </c>
       <c r="D9">
-        <v>34.2</v>
+        <v>33.4</v>
       </c>
       <c r="E9">
-        <v>1.093414631123782</v>
+        <v>0.9092121131323903</v>
       </c>
       <c r="F9">
-        <v>2.428782511496955</v>
+        <v>2.390935107103379</v>
       </c>
       <c r="G9">
-        <v>1.534026106056135</v>
+        <v>1.523746466811565</v>
       </c>
       <c r="H9">
-        <v>1.535904161380638</v>
+        <v>1.518664449517178</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -3113,25 +6503,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>311.6</v>
+        <v>301.9</v>
       </c>
       <c r="C10">
-        <v>26.19847323795797</v>
+        <v>22.93587679694073</v>
       </c>
       <c r="D10">
-        <v>35.2</v>
+        <v>35.9</v>
       </c>
       <c r="E10">
-        <v>0.7118052168020874</v>
+        <v>1.004987562112089</v>
       </c>
       <c r="F10">
-        <v>2.493597449000527</v>
+        <v>2.479863113023098</v>
       </c>
       <c r="G10">
-        <v>1.546542663478131</v>
+        <v>1.555094448578319</v>
       </c>
       <c r="H10">
-        <v>1.57338304894315</v>
+        <v>1.57219802885073</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3139,25 +6529,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>343.4</v>
+        <v>333.9</v>
       </c>
       <c r="C11">
-        <v>28.52297319705644</v>
+        <v>28.02516726087464</v>
       </c>
       <c r="D11">
-        <v>37.9</v>
+        <v>37.7</v>
       </c>
       <c r="E11">
-        <v>0.7810249675906654</v>
+        <v>0.775313556640867</v>
       </c>
       <c r="F11">
-        <v>2.535800290824898</v>
+        <v>2.523616419054371</v>
       </c>
       <c r="G11">
-        <v>1.578639209968072</v>
+        <v>1.576341350205793</v>
       </c>
       <c r="H11">
-        <v>1.597786614301319</v>
+        <v>1.598536987599506</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -3183,7 +6573,7 @@
         <v>1.602059991327962</v>
       </c>
       <c r="H12">
-        <v>1.690121513163885</v>
+        <v>1.701997784886788</v>
       </c>
     </row>
   </sheetData>
@@ -3198,802 +6588,802 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="B2">
-        <v>5.66198792140861</v>
+        <v>5.351541450006782</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>10.94949494949495</v>
+        <v>10.35555555555556</v>
       </c>
       <c r="B3">
-        <v>7.474959053098556</v>
+        <v>7.247765290314378</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>15.8989898989899</v>
+        <v>15.31111111111111</v>
       </c>
       <c r="B4">
-        <v>8.879894374116928</v>
+        <v>8.695936502322844</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>20.84848484848485</v>
+        <v>20.26666666666667</v>
       </c>
       <c r="B5">
-        <v>10.06382377374156</v>
+        <v>9.909282917243257</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>25.7979797979798</v>
+        <v>25.22222222222222</v>
       </c>
       <c r="B6">
-        <v>11.10411535929186</v>
+        <v>10.97225464198619</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>30.74747474747475</v>
+        <v>30.17777777777778</v>
       </c>
       <c r="B7">
-        <v>12.0415804968403</v>
+        <v>11.92848533348722</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>35.6969696969697</v>
+        <v>35.13333333333333</v>
       </c>
       <c r="B8">
-        <v>12.90083240864015</v>
+        <v>12.80396751980204</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>40.64646464646465</v>
+        <v>40.08888888888889</v>
       </c>
       <c r="B9">
-        <v>13.69805321732124</v>
+        <v>13.61565024870889</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>45.5959595959596</v>
+        <v>45.04444444444444</v>
       </c>
       <c r="B10">
-        <v>14.44454710712743</v>
+        <v>14.37530420933263</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>50.54545454545455</v>
+        <v>50</v>
       </c>
       <c r="B11">
-        <v>15.14857494310264</v>
+        <v>15.09149352804115</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>55.49494949494949</v>
+        <v>54.95555555555556</v>
       </c>
       <c r="B12">
-        <v>15.81638801519555</v>
+        <v>15.77067700762347</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>60.44444444444445</v>
+        <v>59.91111111111111</v>
       </c>
       <c r="B13">
-        <v>16.45285047275812</v>
+        <v>16.41786670815784</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>65.39393939393941</v>
+        <v>64.86666666666667</v>
       </c>
       <c r="B14">
-        <v>17.0618342083371</v>
+        <v>17.03704351827169</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>70.34343434343435</v>
+        <v>69.82222222222222</v>
       </c>
       <c r="B15">
-        <v>17.64648020420153</v>
+        <v>17.63143099364619</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>75.2929292929293</v>
+        <v>74.77777777777779</v>
       </c>
       <c r="B16">
-        <v>18.20937765834915</v>
+        <v>18.2036823674218</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>80.24242424242425</v>
+        <v>79.73333333333335</v>
       </c>
       <c r="B17">
-        <v>18.7526904251764</v>
+        <v>18.75601215562893</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>85.1919191919192</v>
+        <v>84.6888888888889</v>
       </c>
       <c r="B18">
-        <v>19.27824853836678</v>
+        <v>19.2902911722703</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>90.14141414141415</v>
+        <v>89.64444444444445</v>
       </c>
       <c r="B19">
-        <v>19.78761591309307</v>
+        <v>19.80811665830866</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>95.09090909090909</v>
+        <v>94.60000000000001</v>
       </c>
       <c r="B20">
-        <v>20.28214138565716</v>
+        <v>20.31086504846764</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>100.040404040404</v>
+        <v>99.55555555555557</v>
       </c>
       <c r="B21">
-        <v>20.76299783920173</v>
+        <v>20.79973235228462</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>104.989898989899</v>
+        <v>104.5111111111111</v>
       </c>
       <c r="B22">
-        <v>21.23121264421505</v>
+        <v>21.27576552420068</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>109.939393939394</v>
+        <v>109.4666666666667</v>
       </c>
       <c r="B23">
-        <v>21.68769165749161</v>
+        <v>21.73988716244691</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>114.8888888888889</v>
+        <v>114.4222222222222</v>
       </c>
       <c r="B24">
-        <v>22.13323836928446</v>
+        <v>22.19291519115275</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>119.8383838383838</v>
+        <v>119.3777777777778</v>
       </c>
       <c r="B25">
-        <v>22.56856934486709</v>
+        <v>22.63557871634857</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>124.7878787878788</v>
+        <v>124.3333333333333</v>
       </c>
       <c r="B26">
-        <v>22.99432680005626</v>
+        <v>23.06853092653482</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>129.7373737373737</v>
+        <v>129.2888888888889</v>
       </c>
       <c r="B27">
-        <v>23.41108893447495</v>
+        <v>23.49235968375414</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>134.6868686868687</v>
+        <v>134.2444444444444</v>
       </c>
       <c r="B28">
-        <v>23.81937849209228</v>
+        <v>23.90759629072261</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>139.6363636363637</v>
+        <v>139.2</v>
       </c>
       <c r="B29">
-        <v>24.21966990671201</v>
+        <v>24.31472280343758</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>144.5858585858586</v>
+        <v>144.1555555555556</v>
       </c>
       <c r="B30">
-        <v>24.61239530786796</v>
+        <v>24.71417817344459</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>149.5353535353536</v>
+        <v>149.1111111111111</v>
       </c>
       <c r="B31">
-        <v>24.99794960142191</v>
+        <v>25.10636344061646</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>154.4848484848485</v>
+        <v>154.0666666666667</v>
       </c>
       <c r="B32">
-        <v>25.3766947931423</v>
+        <v>25.49164614970635</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>159.4343434343434</v>
+        <v>159.0222222222222</v>
       </c>
       <c r="B33">
-        <v>25.74896368855654</v>
+        <v>25.87036412779394</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>164.3838383838384</v>
+        <v>163.9777777777778</v>
       </c>
       <c r="B34">
-        <v>26.11506307551329</v>
+        <v>26.24282873202679</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>169.3333333333333</v>
+        <v>168.9333333333333</v>
       </c>
       <c r="B35">
-        <v>26.47527647508695</v>
+        <v>26.60932765560827</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>174.2828282828283</v>
+        <v>173.8888888888889</v>
       </c>
       <c r="B36">
-        <v>26.82986653020564</v>
+        <v>26.97012736324237</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>179.2323232323232</v>
+        <v>178.8444444444445</v>
       </c>
       <c r="B37">
-        <v>27.1790770885887</v>
+        <v>27.32547521407438</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>184.1818181818182</v>
+        <v>183.8</v>
       </c>
       <c r="B38">
-        <v>27.52313502643036</v>
+        <v>27.67560131972754</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>189.1313131313131</v>
+        <v>188.7555555555556</v>
       </c>
       <c r="B39">
-        <v>27.86225185116032</v>
+        <v>28.02072017670413</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>194.0808080808081</v>
+        <v>193.7111111111111</v>
       </c>
       <c r="B40">
-        <v>28.19662511509476</v>
+        <v>28.36103210572482</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>199.030303030303</v>
+        <v>198.6666666666667</v>
       </c>
       <c r="B41">
-        <v>28.52643966651966</v>
+        <v>28.69672452516916</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>203.979797979798</v>
+        <v>203.6222222222222</v>
       </c>
       <c r="B42">
-        <v>28.85186876045853</v>
+        <v>29.02797308137902</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>208.929292929293</v>
+        <v>208.5777777777778</v>
       </c>
       <c r="B43">
-        <v>29.17307504786788</v>
+        <v>29.35494265498845</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>213.8787878787879</v>
+        <v>213.5333333333333</v>
       </c>
       <c r="B44">
-        <v>29.4902114591167</v>
+        <v>29.67778825948582</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>218.8282828282829</v>
+        <v>218.4888888888889</v>
       </c>
       <c r="B45">
-        <v>29.80342199522129</v>
+        <v>29.99665584577013</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>223.7777777777778</v>
+        <v>223.4444444444445</v>
       </c>
       <c r="B46">
-        <v>30.1128424383253</v>
+        <v>30.31168302443514</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>228.7272727272727</v>
+        <v>228.4</v>
       </c>
       <c r="B47">
-        <v>30.41860099126242</v>
+        <v>30.62299971582411</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>233.6767676767677</v>
+        <v>233.3555555555556</v>
       </c>
       <c r="B48">
-        <v>30.72081885465492</v>
+        <v>30.93072873648121</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>238.6262626262626</v>
+        <v>238.3111111111111</v>
       </c>
       <c r="B49">
-        <v>31.01961074883639</v>
+        <v>31.23498632943538</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>243.5757575757576</v>
+        <v>243.2666666666667</v>
       </c>
       <c r="B50">
-        <v>31.31508538690397</v>
+        <v>31.53588264474693</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>248.5252525252525</v>
+        <v>248.2222222222222</v>
       </c>
       <c r="B51">
-        <v>31.60734590437189</v>
+        <v>31.83352217589574</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>253.4747474747475</v>
+        <v>253.1777777777778</v>
       </c>
       <c r="B52">
-        <v>31.89649025018883</v>
+        <v>32.12800415686554</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>258.4242424242424</v>
+        <v>258.1333333333333</v>
       </c>
       <c r="B53">
-        <v>32.18261154327715</v>
+        <v>32.41942292416121</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>263.3737373737374</v>
+        <v>263.0888888888888</v>
       </c>
       <c r="B54">
-        <v>32.46579839823307</v>
+        <v>32.70786824746661</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>268.3232323232323</v>
+        <v>268.0444444444444</v>
       </c>
       <c r="B55">
-        <v>32.74613522338262</v>
+        <v>32.99342563219673</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>273.2727272727273</v>
+        <v>273</v>
       </c>
       <c r="B56">
-        <v>33.02370249400405</v>
+        <v>33.27617659680629</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>278.2222222222222</v>
+        <v>277.9555555555555</v>
       </c>
       <c r="B57">
-        <v>33.29857700319631</v>
+        <v>33.55619892737932</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>283.1717171717172</v>
+        <v>282.9111111111111</v>
       </c>
       <c r="B58">
-        <v>33.57083209258622</v>
+        <v>33.83356691173121</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>288.1212121212121</v>
+        <v>287.8666666666667</v>
       </c>
       <c r="B59">
-        <v>33.84053786481708</v>
+        <v>34.10835155500047</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>293.0707070707071</v>
+        <v>292.8222222222222</v>
       </c>
       <c r="B60">
-        <v>34.10776137954467</v>
+        <v>34.38062077848618</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>298.020202020202</v>
+        <v>297.7777777777778</v>
       </c>
       <c r="B61">
-        <v>34.37256683447649</v>
+        <v>34.65043960329334</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>302.969696969697</v>
+        <v>302.7333333333333</v>
       </c>
       <c r="B62">
-        <v>34.63501573282411</v>
+        <v>34.91787032017982</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>307.9191919191919</v>
+        <v>307.6888888888889</v>
       </c>
       <c r="B63">
-        <v>34.89516703839288</v>
+        <v>35.18297264684927</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>312.8686868686869</v>
+        <v>312.6444444444444</v>
       </c>
       <c r="B64">
-        <v>35.15307731940494</v>
+        <v>35.44580387380483</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>317.8181818181818</v>
+        <v>317.6</v>
       </c>
       <c r="B65">
-        <v>35.40880088203876</v>
+        <v>35.70641899976284</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>322.7676767676768</v>
+        <v>322.5555555555555</v>
       </c>
       <c r="B66">
-        <v>35.66238989456853</v>
+        <v>35.96487085752445</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>327.7171717171718</v>
+        <v>327.5111111111111</v>
       </c>
       <c r="B67">
-        <v>35.91389450289861</v>
+        <v>36.22121023111349</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>332.6666666666667</v>
+        <v>332.4666666666666</v>
       </c>
       <c r="B68">
-        <v>36.16336293821002</v>
+        <v>36.47548596490884</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>337.6161616161617</v>
+        <v>337.4222222222222</v>
       </c>
       <c r="B69">
-        <v>36.41084161736654</v>
+        <v>36.72774506542952</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>342.5656565656566</v>
+        <v>342.3777777777777</v>
       </c>
       <c r="B70">
-        <v>36.65637523666582</v>
+        <v>36.9780327963671</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>347.5151515151516</v>
+        <v>347.3333333333333</v>
       </c>
       <c r="B71">
-        <v>36.90000685946637</v>
+        <v>37.22639276740455</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>352.4646464646465</v>
+        <v>352.2888888888889</v>
       </c>
       <c r="B72">
-        <v>37.14177799817146</v>
+        <v>37.47286701731033</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>357.4141414141415</v>
+        <v>357.2444444444444</v>
       </c>
       <c r="B73">
-        <v>37.38172869100734</v>
+        <v>37.71749609175171</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>362.3636363636364</v>
+        <v>362.2</v>
       </c>
       <c r="B74">
-        <v>37.61989757399358</v>
+        <v>37.96031911623141</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>367.3131313131314</v>
+        <v>367.1555555555556</v>
       </c>
       <c r="B75">
-        <v>37.85632194846798</v>
+        <v>38.20137386451535</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>372.2626262626263</v>
+        <v>372.1111111111111</v>
       </c>
       <c r="B76">
-        <v>38.09103784449657</v>
+        <v>38.4406968228873</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>377.2121212121212</v>
+        <v>377.0666666666667</v>
       </c>
       <c r="B77">
-        <v>38.32408008047075</v>
+        <v>38.67832325053692</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>382.1616161616162</v>
+        <v>382.0222222222222</v>
       </c>
       <c r="B78">
-        <v>38.5554823191676</v>
+        <v>38.91428723636132</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>387.1111111111111</v>
+        <v>386.9777777777778</v>
       </c>
       <c r="B79">
-        <v>38.78527712052637</v>
+        <v>39.14862175243701</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>392.0606060606061</v>
+        <v>391.9333333333333</v>
       </c>
       <c r="B80">
-        <v>39.01349599137271</v>
+        <v>39.38135870439723</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>397.010101010101</v>
+        <v>396.8888888888889</v>
       </c>
       <c r="B81">
-        <v>39.2401694323035</v>
+        <v>39.61252897893059</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82">
-        <v>401.959595959596</v>
+        <v>401.8444444444444</v>
       </c>
       <c r="B82">
-        <v>39.46532698192765</v>
+        <v>39.84216248859926</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83">
-        <v>406.9090909090909</v>
+        <v>406.8</v>
       </c>
       <c r="B83">
-        <v>39.68899725864252</v>
+        <v>40.07028821415912</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84">
-        <v>411.8585858585859</v>
+        <v>411.7555555555555</v>
       </c>
       <c r="B84">
-        <v>39.91120800011161</v>
+        <v>40.29693424454972</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85">
-        <v>416.8080808080808</v>
+        <v>416.7111111111111</v>
       </c>
       <c r="B85">
-        <v>40.13198610059595</v>
+        <v>40.52212781470875</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86">
-        <v>421.7575757575758</v>
+        <v>421.6666666666666</v>
       </c>
       <c r="B86">
-        <v>40.35135764627979</v>
+        <v>40.74589534135383</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87">
-        <v>426.7070707070707</v>
+        <v>426.6222222222222</v>
       </c>
       <c r="B87">
-        <v>40.56934794872086</v>
+        <v>40.96826245686332</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88">
-        <v>431.6565656565657</v>
+        <v>431.5777777777778</v>
       </c>
       <c r="B88">
-        <v>40.78598157654493</v>
+        <v>41.18925404137805</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89">
-        <v>436.6060606060606</v>
+        <v>436.5333333333333</v>
       </c>
       <c r="B89">
-        <v>41.00128238549618</v>
+        <v>41.4088942532368</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90">
-        <v>441.5555555555556</v>
+        <v>441.4888888888889</v>
       </c>
       <c r="B90">
-        <v>41.21527354694609</v>
+        <v>41.6272065578496</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91">
-        <v>446.5050505050505</v>
+        <v>446.4444444444445</v>
       </c>
       <c r="B91">
-        <v>41.42797757495629</v>
+        <v>41.84421375510601</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92">
-        <v>451.4545454545455</v>
+        <v>451.4</v>
       </c>
       <c r="B92">
-        <v>41.63941635198401</v>
+        <v>42.05993800540772</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93">
-        <v>456.4040404040404</v>
+        <v>456.3555555555556</v>
       </c>
       <c r="B93">
-        <v>41.8496111533121</v>
+        <v>42.27440085440915</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94">
-        <v>461.3535353535354</v>
+        <v>461.3111111111111</v>
       </c>
       <c r="B94">
-        <v>42.05858267028029</v>
+        <v>42.48762325654327</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95">
-        <v>466.3030303030303</v>
+        <v>466.2666666666667</v>
       </c>
       <c r="B95">
-        <v>42.26635103238843</v>
+        <v>42.69962559740471</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96">
-        <v>471.2525252525253</v>
+        <v>471.2222222222222</v>
       </c>
       <c r="B96">
-        <v>42.47293582833804</v>
+        <v>42.91042771505723</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97">
-        <v>476.2020202020202</v>
+        <v>476.1777777777777</v>
       </c>
       <c r="B97">
-        <v>42.67835612607366</v>
+        <v>43.12004892032794</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98">
-        <v>481.1515151515152</v>
+        <v>481.1333333333333</v>
       </c>
       <c r="B98">
-        <v>42.8826304918814</v>
+        <v>43.32850801614649</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99">
-        <v>486.1010101010102</v>
+        <v>486.0888888888889</v>
       </c>
       <c r="B99">
-        <v>43.08577700859843</v>
+        <v>43.53582331598345</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100">
-        <v>491.0505050505051</v>
+        <v>491.0444444444444</v>
       </c>
       <c r="B100">
-        <v>43.28781329298308</v>
+        <v>43.74201266143878</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -4001,7 +7391,7 @@
         <v>496</v>
       </c>
       <c r="B101">
-        <v>43.48875651229272</v>
+        <v>43.9470934390274</v>
       </c>
     </row>
   </sheetData>
@@ -4016,28 +7406,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4045,25 +7435,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="C2">
-        <v>1.273664878302853</v>
+        <v>0.9451631252505217</v>
       </c>
       <c r="D2">
-        <v>0.482737</v>
+        <v>0.498333</v>
       </c>
       <c r="E2">
-        <v>0.09437648425381776</v>
+        <v>0.09251132663445415</v>
       </c>
       <c r="F2">
-        <v>0.7781512503836436</v>
+        <v>0.7323937598229685</v>
       </c>
       <c r="G2">
-        <v>-0.3162894128448587</v>
+        <v>-0.3024803525572923</v>
       </c>
       <c r="H2">
-        <v>-0.2209149646077408</v>
+        <v>-0.2107884276787153</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4071,25 +7461,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>16.5</v>
+        <v>17.2</v>
       </c>
       <c r="C3">
-        <v>2.944863701807305</v>
+        <v>3.349295116554792</v>
       </c>
       <c r="D3">
-        <v>0.207871</v>
+        <v>0.199502</v>
       </c>
       <c r="E3">
-        <v>0.05391448311807216</v>
+        <v>0.04633378020887616</v>
       </c>
       <c r="F3">
-        <v>1.217483944213906</v>
+        <v>1.235528446907549</v>
       </c>
       <c r="G3">
-        <v>-0.6822060946919265</v>
+        <v>-0.7000527461696641</v>
       </c>
       <c r="H3">
-        <v>-0.7032441531724856</v>
+        <v>-0.7478759089492744</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4097,25 +7487,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>31.4</v>
+        <v>39.6</v>
       </c>
       <c r="C4">
-        <v>6.491361781458322</v>
+        <v>6.899597411765735</v>
       </c>
       <c r="D4">
-        <v>0.130971</v>
+        <v>0.074767</v>
       </c>
       <c r="E4">
-        <v>0.03730612852393617</v>
+        <v>0.01339708144418859</v>
       </c>
       <c r="F4">
-        <v>1.496929648073215</v>
+        <v>1.597695185925512</v>
       </c>
       <c r="G4">
-        <v>-0.882824856513954</v>
+        <v>-1.126290044919513</v>
       </c>
       <c r="H4">
-        <v>-1.010038574537445</v>
+        <v>-1.134482570450294</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4123,25 +7513,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>50</v>
+        <v>70.5</v>
       </c>
       <c r="C5">
-        <v>7.049034606872695</v>
+        <v>11.99837952021485</v>
       </c>
       <c r="D5">
-        <v>0.054354</v>
+        <v>0.050638</v>
       </c>
       <c r="E5">
-        <v>0.01008088490383877</v>
+        <v>0.01334863312186766</v>
       </c>
       <c r="F5">
-        <v>1.698970004336019</v>
+        <v>1.848189116991399</v>
       </c>
       <c r="G5">
-        <v>-1.264768489958457</v>
+        <v>-1.295523455560142</v>
       </c>
       <c r="H5">
-        <v>-1.231852162422211</v>
+        <v>-1.401880462035378</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -4149,25 +7539,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>77.2</v>
+        <v>103</v>
       </c>
       <c r="C6">
-        <v>12.8</v>
+        <v>13.03755259923341</v>
       </c>
       <c r="D6">
-        <v>0.042733</v>
+        <v>0.028524</v>
       </c>
       <c r="E6">
-        <v>0.01217511743498007</v>
+        <v>0.007565691449637045</v>
       </c>
       <c r="F6">
-        <v>1.887617300335736</v>
+        <v>2.012837224705172</v>
       </c>
       <c r="G6">
-        <v>-1.36923661718254</v>
+        <v>-1.544789572224195</v>
       </c>
       <c r="H6">
-        <v>-1.438961941599336</v>
+        <v>-1.577639438186208</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4175,25 +7565,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>156.8</v>
+        <v>135.6</v>
       </c>
       <c r="C7">
-        <v>19.21214893411631</v>
+        <v>17.64224727433806</v>
       </c>
       <c r="D7">
-        <v>0.016318</v>
+        <v>0.02064</v>
       </c>
       <c r="E7">
-        <v>0.002021445467426163</v>
+        <v>0.004317254271460559</v>
       </c>
       <c r="F7">
-        <v>2.19534605834842</v>
+        <v>2.132259689531045</v>
       </c>
       <c r="G7">
-        <v>-1.787333071206577</v>
+        <v>-1.685290307044826</v>
       </c>
       <c r="H7">
-        <v>-1.776807415507179</v>
+        <v>-1.705120831313984</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -4201,25 +7591,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>157.3</v>
+        <v>199.5</v>
       </c>
       <c r="C8">
-        <v>17.51002887236658</v>
+        <v>22.33743743384883</v>
       </c>
       <c r="D8">
-        <v>0.016206</v>
+        <v>0.012745</v>
       </c>
       <c r="E8">
-        <v>0.00285167288134916</v>
+        <v>0.001774988732358603</v>
       </c>
       <c r="F8">
-        <v>2.196728722623287</v>
+        <v>2.299942900022767</v>
       </c>
       <c r="G8">
-        <v>-1.790324165428905</v>
+        <v>-1.894660160194714</v>
       </c>
       <c r="H8">
-        <v>-1.778325397999991</v>
+        <v>-1.884119726612214</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -4227,25 +7617,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>268.4</v>
+        <v>246</v>
       </c>
       <c r="C9">
-        <v>15.93751688452264</v>
+        <v>25.42527176736651</v>
       </c>
       <c r="D9">
-        <v>0.008544999999999999</v>
+        <v>0.009915</v>
       </c>
       <c r="E9">
-        <v>0.0005071428683210371</v>
+        <v>0.001022463528281898</v>
       </c>
       <c r="F9">
-        <v>2.428782511496955</v>
+        <v>2.390935107103379</v>
       </c>
       <c r="G9">
-        <v>-2.068287932943245</v>
+        <v>-2.003707281458678</v>
       </c>
       <c r="H9">
-        <v>-2.033089765101825</v>
+        <v>-1.981252316693326</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -4253,25 +7643,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>311.6</v>
+        <v>301.9</v>
       </c>
       <c r="C10">
-        <v>26.19847323795797</v>
+        <v>22.93587679694073</v>
       </c>
       <c r="D10">
-        <v>0.007674</v>
+        <v>0.007771999999999999</v>
       </c>
       <c r="E10">
-        <v>0.0006741384625332295</v>
+        <v>0.0005564706241622783</v>
       </c>
       <c r="F10">
-        <v>2.493597449000527</v>
+        <v>2.479863113023098</v>
       </c>
       <c r="G10">
-        <v>-2.114978205137703</v>
+        <v>-2.109467208072255</v>
       </c>
       <c r="H10">
-        <v>-2.104247993596996</v>
+        <v>-2.076181408127258</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -4279,25 +7669,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>343.4</v>
+        <v>333.9</v>
       </c>
       <c r="C11">
-        <v>28.52297319705644</v>
+        <v>28.02516726087464</v>
       </c>
       <c r="D11">
-        <v>0.006926</v>
+        <v>0.00711</v>
       </c>
       <c r="E11">
-        <v>0.0005297173250370847</v>
+        <v>0.000550680387238268</v>
       </c>
       <c r="F11">
-        <v>2.535800290824898</v>
+        <v>2.523616419054371</v>
       </c>
       <c r="G11">
-        <v>-2.159517512786558</v>
+        <v>-2.148130399270234</v>
       </c>
       <c r="H11">
-        <v>-2.150581131872699</v>
+        <v>-2.122887297299327</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -4323,7 +7713,7 @@
         <v>-2.338187314462739</v>
       </c>
       <c r="H12">
-        <v>-2.325890172739562</v>
+        <v>-2.306350454588276</v>
       </c>
     </row>
   </sheetData>
@@ -4338,802 +7728,802 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="B2">
-        <v>0.4875477315086367</v>
+        <v>0.5028284915917663</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>10.94949494949495</v>
+        <v>10.35555555555556</v>
       </c>
       <c r="B3">
-        <v>0.2834110796830337</v>
+        <v>0.2802084644936864</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>15.8989898989899</v>
+        <v>15.31111111111111</v>
       </c>
       <c r="B4">
-        <v>0.2024604612236869</v>
+        <v>0.1972283928226809</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>20.84848484848485</v>
+        <v>20.26666666666667</v>
       </c>
       <c r="B5">
-        <v>0.1585581945027434</v>
+        <v>0.153325310220527</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>25.7979797979798</v>
+        <v>25.22222222222222</v>
       </c>
       <c r="B6">
-        <v>0.1308452648313374</v>
+        <v>0.1259801411409661</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>30.74747474747475</v>
+        <v>30.17777777777778</v>
       </c>
       <c r="B7">
-        <v>0.1116904563683539</v>
+        <v>0.1072367614490337</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>35.6969696969697</v>
+        <v>35.13333333333333</v>
       </c>
       <c r="B8">
-        <v>0.09762404962657725</v>
+        <v>0.09355053560765708</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>40.64646464646465</v>
+        <v>40.08888888888889</v>
       </c>
       <c r="B9">
-        <v>0.08683614647417781</v>
+        <v>0.08309716022904533</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>45.5959595959596</v>
+        <v>45.04444444444444</v>
       </c>
       <c r="B10">
-        <v>0.07828801653308547</v>
+        <v>0.07483960280907326</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>50.54545454545455</v>
+        <v>50</v>
       </c>
       <c r="B11">
-        <v>0.07133991436893462</v>
+        <v>0.06814371979582363</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>55.49494949494949</v>
+        <v>54.95555555555556</v>
       </c>
       <c r="B12">
-        <v>0.06557579233850865</v>
+        <v>0.0625993923668251</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>60.44444444444445</v>
+        <v>59.91111111111111</v>
       </c>
       <c r="B13">
-        <v>0.06071311110798542</v>
+        <v>0.057929340232794</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>65.39393939393941</v>
+        <v>64.86666666666667</v>
       </c>
       <c r="B14">
-        <v>0.05655310503935577</v>
+        <v>0.05393920213817548</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>70.34343434343435</v>
+        <v>69.82222222222222</v>
       </c>
       <c r="B15">
-        <v>0.05295177971504177</v>
+        <v>0.05048859689311276</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>75.2929292929293</v>
+        <v>74.77777777777779</v>
       </c>
       <c r="B16">
-        <v>0.04980220138445488</v>
+        <v>0.04747353768332609</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>80.24242424242425</v>
+        <v>79.73333333333335</v>
       </c>
       <c r="B17">
-        <v>0.04702325500791905</v>
+        <v>0.04481531511345983</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>85.1919191919192</v>
+        <v>84.6888888888889</v>
       </c>
       <c r="B18">
-        <v>0.0445522689441346</v>
+        <v>0.04245322938165015</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>90.14141414141415</v>
+        <v>89.64444444444445</v>
       </c>
       <c r="B19">
-        <v>0.04234003662875545</v>
+        <v>0.04033969929230484</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>95.09090909090909</v>
+        <v>94.60000000000001</v>
       </c>
       <c r="B20">
-        <v>0.04034737175077859</v>
+        <v>0.03843688674436072</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>100.040404040404</v>
+        <v>99.55555555555557</v>
       </c>
       <c r="B21">
-        <v>0.03854267190896647</v>
+        <v>0.03671431490923084</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>104.989898989899</v>
+        <v>104.5111111111111</v>
       </c>
       <c r="B22">
-        <v>0.03690016180004265</v>
+        <v>0.03514715423504296</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>109.939393939394</v>
+        <v>109.4666666666667</v>
       </c>
       <c r="B23">
-        <v>0.03539860429195095</v>
+        <v>0.03371496721597732</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>114.8888888888889</v>
+        <v>114.4222222222222</v>
       </c>
       <c r="B24">
-        <v>0.03402033994824714</v>
+        <v>0.03240077454731944</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>119.8383838383838</v>
+        <v>119.3777777777778</v>
       </c>
       <c r="B25">
-        <v>0.0327505611742873</v>
+        <v>0.03119035043055002</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>124.7878787878788</v>
+        <v>124.3333333333333</v>
       </c>
       <c r="B26">
-        <v>0.03157675662462606</v>
+        <v>0.03007168389110922</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>129.7373737373737</v>
+        <v>129.2888888888889</v>
       </c>
       <c r="B27">
-        <v>0.03048828095179117</v>
+        <v>0.02903456212472765</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>134.6868686868687</v>
+        <v>134.2444444444444</v>
       </c>
       <c r="B28">
-        <v>0.0294760180454342</v>
+        <v>0.02807024473755674</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>139.6363636363637</v>
+        <v>139.2</v>
       </c>
       <c r="B29">
-        <v>0.02853211484837238</v>
+        <v>0.02717120651644143</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>144.5858585858586</v>
+        <v>144.1555555555556</v>
       </c>
       <c r="B30">
-        <v>0.0276497690451309</v>
+        <v>0.02633093244883227</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>149.5353535353536</v>
+        <v>149.1111111111111</v>
       </c>
       <c r="B31">
-        <v>0.02682305829505003</v>
+        <v>0.0255437529928481</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>154.4848484848485</v>
+        <v>154.0666666666667</v>
       </c>
       <c r="B32">
-        <v>0.02604680180820675</v>
+        <v>0.02480471065162982</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>159.4343434343434</v>
+        <v>159.0222222222222</v>
       </c>
       <c r="B33">
-        <v>0.02531644732326848</v>
+        <v>0.02410945111159793</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>164.3838383838384</v>
+        <v>163.9777777777778</v>
       </c>
       <c r="B34">
-        <v>0.02462797820033746</v>
+        <v>0.02345413381566652</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>169.3333333333333</v>
+        <v>168.9333333333333</v>
       </c>
       <c r="B35">
-        <v>0.02397783656478548</v>
+        <v>0.02283535803262562</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>174.2828282828283</v>
+        <v>173.8888888888889</v>
       </c>
       <c r="B36">
-        <v>0.02336285935139925</v>
+        <v>0.02225010137180151</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>179.2323232323232</v>
+        <v>178.8444444444445</v>
       </c>
       <c r="B37">
-        <v>0.02278022478664015</v>
+        <v>0.02169566836076156</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>184.1818181818182</v>
+        <v>183.8</v>
       </c>
       <c r="B38">
-        <v>0.02222740737037925</v>
+        <v>0.02116964721184194</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>189.1313131313131</v>
+        <v>188.7555555555556</v>
       </c>
       <c r="B39">
-        <v>0.02170213981989436</v>
+        <v>0.02066987329244516</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>194.0808080808081</v>
+        <v>193.7111111111111</v>
       </c>
       <c r="B40">
-        <v>0.02120238074909173</v>
+        <v>0.02019439811451589</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>199.030303030303</v>
+        <v>198.6666666666667</v>
       </c>
       <c r="B41">
-        <v>0.02072628709733862</v>
+        <v>0.01974146289228772</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>203.979797979798</v>
+        <v>203.6222222222222</v>
       </c>
       <c r="B42">
-        <v>0.02027219051150431</v>
+        <v>0.01930947590040709</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>208.929292929293</v>
+        <v>208.5777777777778</v>
       </c>
       <c r="B43">
-        <v>0.01983857703406896</v>
+        <v>0.01889699300881549</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>213.8787878787879</v>
+        <v>213.5333333333333</v>
       </c>
       <c r="B44">
-        <v>0.01942406956863548</v>
+        <v>0.01850270088521627</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>218.8282828282829</v>
+        <v>218.4888888888889</v>
       </c>
       <c r="B45">
-        <v>0.01902741268877517</v>
+        <v>0.01812540244727257</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>223.7777777777778</v>
+        <v>223.4444444444445</v>
       </c>
       <c r="B46">
-        <v>0.01864745943208572</v>
+        <v>0.01776400421996111</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>228.7272727272727</v>
+        <v>228.4</v>
       </c>
       <c r="B47">
-        <v>0.01828315978264344</v>
+        <v>0.01741750531262116</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>233.6767676767677</v>
+        <v>233.3555555555556</v>
       </c>
       <c r="B48">
-        <v>0.01793355059476268</v>
+        <v>0.01708498777817004</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>238.6262626262626</v>
+        <v>238.3111111111111</v>
       </c>
       <c r="B49">
-        <v>0.01759774675151514</v>
+        <v>0.01676560815600985</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>243.5757575757576</v>
+        <v>243.2666666666667</v>
       </c>
       <c r="B50">
-        <v>0.01727493338466043</v>
+        <v>0.01645859003211674</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>248.5252525252525</v>
+        <v>248.2222222222222</v>
       </c>
       <c r="B51">
-        <v>0.01696435900994654</v>
+        <v>0.01616321747608683</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>253.4747474747475</v>
+        <v>253.1777777777778</v>
       </c>
       <c r="B52">
-        <v>0.01666532945429469</v>
+        <v>0.01587882923661219</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>258.4242424242424</v>
+        <v>258.1333333333333</v>
       </c>
       <c r="B53">
-        <v>0.01637720247008973</v>
+        <v>0.01560481359485056</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>263.3737373737374</v>
+        <v>263.0888888888888</v>
       </c>
       <c r="B54">
-        <v>0.01609938294737109</v>
+        <v>0.01534060379012323</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>268.3232323232323</v>
+        <v>268.0444444444444</v>
       </c>
       <c r="B55">
-        <v>0.01583131864773404</v>
+        <v>0.01508567394488208</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>273.2727272727273</v>
+        <v>273</v>
       </c>
       <c r="B56">
-        <v>0.01557249639466486</v>
+        <v>0.0148395354263707</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>278.2222222222222</v>
+        <v>277.9555555555555</v>
       </c>
       <c r="B57">
-        <v>0.01532243866421807</v>
+        <v>0.01460173359122417</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>283.1717171717172</v>
+        <v>282.9111111111111</v>
       </c>
       <c r="B58">
-        <v>0.01508070052769744</v>
+        <v>0.01437184486669542</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>288.1212121212121</v>
+        <v>287.8666666666667</v>
       </c>
       <c r="B59">
-        <v>0.01484686690457024</v>
+        <v>0.01414947412849881</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>293.0707070707071</v>
+        <v>292.8222222222222</v>
       </c>
       <c r="B60">
-        <v>0.01462055008942256</v>
+        <v>0.01393425234061365</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>298.020202020202</v>
+        <v>297.7777777777778</v>
       </c>
       <c r="B61">
-        <v>0.0144013875215177</v>
+        <v>0.01372583442694986</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>302.969696969697</v>
+        <v>302.7333333333333</v>
       </c>
       <c r="B62">
-        <v>0.01418903976958098</v>
+        <v>0.01352389734867242</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>307.9191919191919</v>
+        <v>307.6888888888889</v>
       </c>
       <c r="B63">
-        <v>0.01398318870791426</v>
+        <v>0.01332813836431718</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>312.8686868686869</v>
+        <v>312.6444444444444</v>
       </c>
       <c r="B64">
-        <v>0.01378353586293347</v>
+        <v>0.01313827345269581</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>317.8181818181818</v>
+        <v>317.6</v>
       </c>
       <c r="B65">
-        <v>0.0135898009117967</v>
+        <v>0.01295403588105449</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>322.7676767676768</v>
+        <v>322.5555555555555</v>
       </c>
       <c r="B66">
-        <v>0.01340172031701382</v>
+        <v>0.01277517490308044</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>327.7171717171718</v>
+        <v>327.5111111111111</v>
       </c>
       <c r="B67">
-        <v>0.01321904608285247</v>
+        <v>0.012601454573193</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>332.6666666666667</v>
+        <v>332.4666666666666</v>
       </c>
       <c r="B68">
-        <v>0.01304154462102402</v>
+        <v>0.01243265266515383</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>337.6161616161617</v>
+        <v>337.4222222222222</v>
       </c>
       <c r="B69">
-        <v>0.01286899571458437</v>
+        <v>0.01226855968441979</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>342.5656565656566</v>
+        <v>342.3777777777777</v>
       </c>
       <c r="B70">
-        <v>0.01270119157024843</v>
+        <v>0.0121089779648721</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>347.5151515151516</v>
+        <v>347.3333333333333</v>
       </c>
       <c r="B71">
-        <v>0.01253793595042098</v>
+        <v>0.01195372084161154</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>352.4646464646465</v>
+        <v>352.2888888888889</v>
       </c>
       <c r="B72">
-        <v>0.01237904337721266</v>
+        <v>0.01180261189243341</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>357.4141414141415</v>
+        <v>357.2444444444444</v>
       </c>
       <c r="B73">
-        <v>0.01222433840155585</v>
+        <v>0.01165548424140579</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>362.3636363636364</v>
+        <v>362.2</v>
       </c>
       <c r="B74">
-        <v>0.01207365493127947</v>
+        <v>0.01151217991868578</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>367.3131313131314</v>
+        <v>367.1555555555556</v>
       </c>
       <c r="B75">
-        <v>0.01192683561265549</v>
+        <v>0.01137254927133407</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>372.2626262626263</v>
+        <v>372.1111111111111</v>
       </c>
       <c r="B76">
-        <v>0.01178373126050731</v>
+        <v>0.0112364504204398</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>377.2121212121212</v>
+        <v>377.0666666666667</v>
       </c>
       <c r="B77">
-        <v>0.01164420033247908</v>
+        <v>0.01110374876035441</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>382.1616161616162</v>
+        <v>382.0222222222222</v>
       </c>
       <c r="B78">
-        <v>0.0115081084435161</v>
+        <v>0.01097431649626405</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>387.1111111111111</v>
+        <v>386.9777777777778</v>
       </c>
       <c r="B79">
-        <v>0.0113753279170056</v>
+        <v>0.01084803221671174</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>392.0606060606061</v>
+        <v>391.9333333333333</v>
       </c>
       <c r="B80">
-        <v>0.01124573736938153</v>
+        <v>0.01072478049801898</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>397.010101010101</v>
+        <v>396.8888888888889</v>
       </c>
       <c r="B81">
-        <v>0.01111922132531227</v>
+        <v>0.01060445153785763</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82">
-        <v>401.959595959596</v>
+        <v>401.8444444444444</v>
       </c>
       <c r="B82">
-        <v>0.01099566986087049</v>
+        <v>0.01048694081549065</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83">
-        <v>406.9090909090909</v>
+        <v>406.8</v>
       </c>
       <c r="B83">
-        <v>0.01087497827233463</v>
+        <v>0.0103721487764395</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84">
-        <v>411.8585858585859</v>
+        <v>411.7555555555555</v>
       </c>
       <c r="B84">
-        <v>0.01075704676849478</v>
+        <v>0.01025998053954884</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85">
-        <v>416.8080808080808</v>
+        <v>416.7111111111111</v>
       </c>
       <c r="B85">
-        <v>0.01064178018453541</v>
+        <v>0.01015034562461027</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86">
-        <v>421.7575757575758</v>
+        <v>421.6666666666666</v>
       </c>
       <c r="B86">
-        <v>0.01052908771574629</v>
+        <v>0.01004315769887733</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87">
-        <v>426.7070707070707</v>
+        <v>426.6222222222222</v>
       </c>
       <c r="B87">
-        <v>0.01041888266947336</v>
+        <v>0.009938334340957243</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88">
-        <v>431.6565656565657</v>
+        <v>431.5777777777778</v>
       </c>
       <c r="B88">
-        <v>0.01031108223386522</v>
+        <v>0.009835796820702167</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89">
-        <v>436.6060606060606</v>
+        <v>436.5333333333333</v>
       </c>
       <c r="B89">
-        <v>0.01020560726210032</v>
+        <v>0.009735469893846426</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90">
-        <v>441.5555555555556</v>
+        <v>441.4888888888889</v>
       </c>
       <c r="B90">
-        <v>0.01010238207089663</v>
+        <v>0.009637281610247244</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91">
-        <v>446.5050505050505</v>
+        <v>446.4444444444445</v>
       </c>
       <c r="B91">
-        <v>0.01000133425221042</v>
+        <v>0.009541163134686831</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92">
-        <v>451.4545454545455</v>
+        <v>451.4</v>
       </c>
       <c r="B92">
-        <v>0.009902394497125629</v>
+        <v>0.009447048579284032</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93">
-        <v>456.4040404040404</v>
+        <v>456.3555555555556</v>
       </c>
       <c r="B93">
-        <v>0.009805496431020874</v>
+        <v>0.009354874846645388</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94">
-        <v>461.3535353535354</v>
+        <v>461.3111111111111</v>
       </c>
       <c r="B94">
-        <v>0.009710576459178636</v>
+        <v>0.009264581482959456</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95">
-        <v>466.3030303030303</v>
+        <v>466.2666666666667</v>
       </c>
       <c r="B95">
-        <v>0.009617573622071237</v>
+        <v>0.009176110540304911</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96">
-        <v>471.2525252525253</v>
+        <v>471.2222222222222</v>
       </c>
       <c r="B96">
-        <v>0.009526429459621746</v>
+        <v>0.009089406447503763</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97">
-        <v>476.2020202020202</v>
+        <v>476.1777777777777</v>
       </c>
       <c r="B97">
-        <v>0.009437087883795719</v>
+        <v>0.009004415888905899</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98">
-        <v>481.1515151515152</v>
+        <v>481.1333333333333</v>
       </c>
       <c r="B98">
-        <v>0.009349495058931932</v>
+        <v>0.008921087690541112</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99">
-        <v>486.1010101010102</v>
+        <v>486.0888888888889</v>
       </c>
       <c r="B99">
-        <v>0.009263599289268032</v>
+        <v>0.008839372713120309</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100">
-        <v>491.0505050505051</v>
+        <v>491.0444444444444</v>
       </c>
       <c r="B100">
-        <v>0.009179350913160295</v>
+        <v>0.008759223751408784</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -5141,7 +8531,7 @@
         <v>496</v>
       </c>
       <c r="B101">
-        <v>0.00909670220353624</v>
+        <v>0.008680595439532219</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sgt_files/InVitroBioFilm_SGT_scaling.xlsx
+++ b/datasets/sgt_files/InVitroBioFilm_SGT_scaling.xlsx
@@ -14,13 +14,15 @@
     <sheet name="Nodes-Average degree (Fitting)" sheetId="5" r:id="rId5"/>
     <sheet name="Nodes-Network diamet." sheetId="6" r:id="rId6"/>
     <sheet name="Nodes-Network diamet. (Fitting)" sheetId="7" r:id="rId7"/>
+    <sheet name="Nodes-Graph density" sheetId="8" r:id="rId8"/>
+    <sheet name="Nodes-Graph density (Fitting)" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="11">
   <si>
     <t>kernel-dim</t>
   </si>
@@ -50,6 +52,9 @@
   </si>
   <si>
     <t>Pwr. Law y-fit</t>
+  </si>
+  <si>
+    <t>Trunc. Pwr. Law y-fit</t>
   </si>
 </sst>
 </file>
@@ -426,10 +431,10 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="C2">
-        <v>0.8432740427115677</v>
+        <v>1.28279209365959</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -437,10 +442,10 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>18.6</v>
+        <v>15.5</v>
       </c>
       <c r="C3">
-        <v>2.028683207293725</v>
+        <v>2.982355519458477</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -448,10 +453,10 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>34.6</v>
+        <v>46.5</v>
       </c>
       <c r="C4">
-        <v>7.126164622166838</v>
+        <v>7.473285756613352</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -459,10 +464,10 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>66.5</v>
+        <v>63.7</v>
       </c>
       <c r="C5">
-        <v>11.36588462607875</v>
+        <v>11.87906655517268</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -470,10 +475,10 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>102.7</v>
+        <v>111</v>
       </c>
       <c r="C6">
-        <v>16.29863661646444</v>
+        <v>13.88684429395118</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -481,10 +486,10 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>159.9</v>
+        <v>163.4</v>
       </c>
       <c r="C7">
-        <v>20.1132626227903</v>
+        <v>11.71153277756588</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -492,10 +497,10 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>195.5</v>
+        <v>203</v>
       </c>
       <c r="C8">
-        <v>21.28549323417764</v>
+        <v>20.33988965336614</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -503,10 +508,10 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>258.4</v>
+        <v>234.3</v>
       </c>
       <c r="C9">
-        <v>21.7011008425328</v>
+        <v>25.92169833256387</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -514,10 +519,10 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>293.9</v>
+        <v>274.2</v>
       </c>
       <c r="C10">
-        <v>26.76126969251563</v>
+        <v>24.15082239225451</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -525,10 +530,10 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>385.6</v>
+        <v>398.7</v>
       </c>
       <c r="C11">
-        <v>27.37038139627904</v>
+        <v>22.06356977261637</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -580,25 +585,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="C2">
-        <v>0.8432740427115677</v>
+        <v>1.28279209365959</v>
       </c>
       <c r="D2">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="E2">
-        <v>0.9797958971132712</v>
+        <v>1.356465996625054</v>
       </c>
       <c r="F2">
-        <v>0.8450980400142568</v>
+        <v>0.7558748556724915</v>
       </c>
       <c r="G2">
-        <v>0.8061799739838872</v>
+        <v>0.6812412373755872</v>
       </c>
       <c r="H2">
-        <v>0.8258292216964651</v>
+        <v>0.7170460186318706</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -606,25 +611,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>18.6</v>
+        <v>15.5</v>
       </c>
       <c r="C3">
-        <v>2.028683207293725</v>
+        <v>2.982355519458477</v>
       </c>
       <c r="D3">
-        <v>18.9</v>
+        <v>15.8</v>
       </c>
       <c r="E3">
-        <v>2.354428451521374</v>
+        <v>3.469870314579494</v>
       </c>
       <c r="F3">
-        <v>1.269512944217916</v>
+        <v>1.190331698170291</v>
       </c>
       <c r="G3">
-        <v>1.276461804173244</v>
+        <v>1.198657086954423</v>
       </c>
       <c r="H3">
-        <v>1.269277677464648</v>
+        <v>1.175752892705166</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -632,25 +637,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>34.6</v>
+        <v>46.5</v>
       </c>
       <c r="C4">
-        <v>7.126164622166838</v>
+        <v>7.473285756613352</v>
       </c>
       <c r="D4">
-        <v>36.8</v>
+        <v>49.7</v>
       </c>
       <c r="E4">
-        <v>7.828438186793355</v>
+        <v>8.466994744299774</v>
       </c>
       <c r="F4">
-        <v>1.539076098792777</v>
+        <v>1.667452952889954</v>
       </c>
       <c r="G4">
-        <v>1.565847818673518</v>
+        <v>1.696356388733332</v>
       </c>
       <c r="H4">
-        <v>1.550929814192769</v>
+        <v>1.679505573979815</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -658,25 +663,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>66.5</v>
+        <v>63.7</v>
       </c>
       <c r="C5">
-        <v>11.36588462607875</v>
+        <v>11.87906655517268</v>
       </c>
       <c r="D5">
-        <v>71.40000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="E5">
-        <v>12.76644908430775</v>
+        <v>14.04599587070991</v>
       </c>
       <c r="F5">
-        <v>1.822821645303105</v>
+        <v>1.80413943233535</v>
       </c>
       <c r="G5">
-        <v>1.853698211776174</v>
+        <v>1.846955325019824</v>
       </c>
       <c r="H5">
-        <v>1.847400374450768</v>
+        <v>1.823821468175449</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -684,25 +689,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>102.7</v>
+        <v>111</v>
       </c>
       <c r="C6">
-        <v>16.29863661646444</v>
+        <v>13.88684429395118</v>
       </c>
       <c r="D6">
-        <v>113.4</v>
+        <v>121.9</v>
       </c>
       <c r="E6">
-        <v>19.04042483186175</v>
+        <v>16.19221349222452</v>
       </c>
       <c r="F6">
-        <v>2.011570443597278</v>
+        <v>2.045322978786658</v>
       </c>
       <c r="G6">
-        <v>2.054613054556888</v>
+        <v>2.086003705618382</v>
       </c>
       <c r="H6">
-        <v>2.044613908430449</v>
+        <v>2.078467131101452</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -710,25 +715,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>159.9</v>
+        <v>163.4</v>
       </c>
       <c r="C7">
-        <v>20.1132626227903</v>
+        <v>11.71153277756588</v>
       </c>
       <c r="D7">
-        <v>176.2</v>
+        <v>179.4</v>
       </c>
       <c r="E7">
-        <v>22.926355527597</v>
+        <v>15.07035353120674</v>
       </c>
       <c r="F7">
-        <v>2.203848463746235</v>
+        <v>2.213252052196397</v>
       </c>
       <c r="G7">
-        <v>2.246005904076029</v>
+        <v>2.253822438708073</v>
       </c>
       <c r="H7">
-        <v>2.245514937750341</v>
+        <v>2.255769483820632</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -736,25 +741,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>195.5</v>
+        <v>203</v>
       </c>
       <c r="C8">
-        <v>21.28549323417764</v>
+        <v>20.33988965336614</v>
       </c>
       <c r="D8">
-        <v>217.2</v>
+        <v>225.3</v>
       </c>
       <c r="E8">
-        <v>25.89714699001074</v>
+        <v>24.25606453377519</v>
       </c>
       <c r="F8">
-        <v>2.291146761731885</v>
+        <v>2.307496037913213</v>
       </c>
       <c r="G8">
-        <v>2.336859820916809</v>
+        <v>2.352761191723831</v>
       </c>
       <c r="H8">
-        <v>2.336728264731787</v>
+        <v>2.355273876109236</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -762,25 +767,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>258.4</v>
+        <v>234.3</v>
       </c>
       <c r="C9">
-        <v>21.7011008425328</v>
+        <v>25.92169833256387</v>
       </c>
       <c r="D9">
-        <v>287.3</v>
+        <v>259.8</v>
       </c>
       <c r="E9">
-        <v>25.87235762138597</v>
+        <v>30.98415365598644</v>
       </c>
       <c r="F9">
-        <v>2.412292509323046</v>
+        <v>2.369772288596963</v>
       </c>
       <c r="G9">
-        <v>2.458335625991948</v>
+        <v>2.414639146737009</v>
       </c>
       <c r="H9">
-        <v>2.463306983245412</v>
+        <v>2.421026193683317</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -788,25 +793,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>293.9</v>
+        <v>274.2</v>
       </c>
       <c r="C10">
-        <v>26.76126969251563</v>
+        <v>24.15082239225451</v>
       </c>
       <c r="D10">
-        <v>327.4</v>
+        <v>304.2</v>
       </c>
       <c r="E10">
-        <v>31.76133218588638</v>
+        <v>28.5084003214647</v>
       </c>
       <c r="F10">
-        <v>2.468199586072612</v>
+        <v>2.438067450453494</v>
       </c>
       <c r="G10">
-        <v>2.515078675075923</v>
+        <v>2.483159209716979</v>
       </c>
       <c r="H10">
-        <v>2.521721300474978</v>
+        <v>2.493133379357801</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -814,25 +819,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>385.6</v>
+        <v>398.7</v>
       </c>
       <c r="C11">
-        <v>27.37038139627904</v>
+        <v>22.06356977261637</v>
       </c>
       <c r="D11">
-        <v>433.7</v>
+        <v>447.7</v>
       </c>
       <c r="E11">
-        <v>31.86640515931751</v>
+        <v>25.61945875046284</v>
       </c>
       <c r="F11">
-        <v>2.586137025230793</v>
+        <v>2.600646235662394</v>
       </c>
       <c r="G11">
-        <v>2.637189422148762</v>
+        <v>2.650987094383445</v>
       </c>
       <c r="H11">
-        <v>2.644947828935564</v>
+        <v>2.664786807406148</v>
       </c>
     </row>
   </sheetData>
@@ -842,815 +847,1118 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="B2">
-        <v>7.216401280521548</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>170.9087932591283</v>
+      </c>
+      <c r="C2">
+        <v>172.8676414891828</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3">
-        <v>10.82424242424242</v>
+        <v>9.66969696969697</v>
       </c>
       <c r="B3">
-        <v>11.2636647920348</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>170.0078705761628</v>
+      </c>
+      <c r="C3">
+        <v>171.2953425236751</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4">
-        <v>14.64848484848485</v>
+        <v>13.63939393939394</v>
       </c>
       <c r="B4">
-        <v>15.34237926631829</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>169.4241071314306</v>
+      </c>
+      <c r="C4">
+        <v>170.2779222328356</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5">
-        <v>18.47272727272728</v>
+        <v>17.60909090909091</v>
       </c>
       <c r="B5">
-        <v>19.44425839003345</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>168.9918603624605</v>
+      </c>
+      <c r="C5">
+        <v>169.5252746864759</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6">
-        <v>22.2969696969697</v>
+        <v>21.57878787878788</v>
       </c>
       <c r="B6">
-        <v>23.56452026570208</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>168.6486565058405</v>
+      </c>
+      <c r="C6">
+        <v>168.9280993234077</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7">
-        <v>26.12121212121212</v>
+        <v>25.54848484848485</v>
       </c>
       <c r="B7">
-        <v>27.70003967405061</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>168.3641045265195</v>
+      </c>
+      <c r="C7">
+        <v>168.4332660638095</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8">
-        <v>29.94545454545455</v>
+        <v>29.51818181818182</v>
       </c>
       <c r="B8">
-        <v>31.84861004796428</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>168.1211144717728</v>
+      </c>
+      <c r="C8">
+        <v>168.0109158896182</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9">
-        <v>33.76969696969697</v>
+        <v>33.48787878787879</v>
       </c>
       <c r="B9">
-        <v>36.00858854333596</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>167.9091178318769</v>
+      </c>
+      <c r="C9">
+        <v>167.6425930275263</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10">
-        <v>37.59393939393939</v>
+        <v>37.45757575757576</v>
       </c>
       <c r="B10">
-        <v>40.17870360369619</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>167.7211222361782</v>
+      </c>
+      <c r="C10">
+        <v>167.3160919196247</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11">
-        <v>41.41818181818182</v>
+        <v>41.42727272727273</v>
       </c>
       <c r="B11">
-        <v>44.35794138698524</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>167.5522610632239</v>
+      </c>
+      <c r="C11">
+        <v>167.0229207930924</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12">
-        <v>45.24242424242425</v>
+        <v>45.3969696969697</v>
       </c>
       <c r="B12">
-        <v>48.54547433627083</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>167.3990109346927</v>
+      </c>
+      <c r="C12">
+        <v>166.7569337489469</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13">
-        <v>49.06666666666667</v>
+        <v>49.36666666666667</v>
       </c>
       <c r="B13">
-        <v>52.7406139730086</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>167.258739018926</v>
+      </c>
+      <c r="C13">
+        <v>166.5135396662841</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14">
-        <v>52.8909090909091</v>
+        <v>53.33636363636364</v>
       </c>
       <c r="B14">
-        <v>56.94277843161908</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>167.1294262556302</v>
+      </c>
+      <c r="C14">
+        <v>166.2892186801018</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15">
-        <v>56.71515151515152</v>
+        <v>57.30606060606061</v>
       </c>
       <c r="B15">
-        <v>61.15146938954693</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>167.0094903633141</v>
+      </c>
+      <c r="C15">
+        <v>166.0812130638097</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16">
-        <v>60.53939393939395</v>
+        <v>61.27575757575758</v>
       </c>
       <c r="B16">
-        <v>65.36625521859804</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>166.8976683577022</v>
+      </c>
+      <c r="C16">
+        <v>165.8873220997683</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
-        <v>64.36363636363637</v>
+        <v>65.24545454545455</v>
       </c>
       <c r="B17">
-        <v>69.58675839011339</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>166.7929360799364</v>
+      </c>
+      <c r="C17">
+        <v>165.7057616039244</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
-        <v>68.18787878787879</v>
+        <v>69.21515151515152</v>
       </c>
       <c r="B18">
-        <v>73.8126458694969</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>166.6944515720154</v>
+      </c>
+      <c r="C18">
+        <v>165.5350651008133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
-        <v>72.01212121212122</v>
+        <v>73.18484848484849</v>
       </c>
       <c r="B19">
-        <v>78.04362166178434</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>166.6015142933477</v>
+      </c>
+      <c r="C19">
+        <v>165.374012659997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20">
-        <v>75.83636363636364</v>
+        <v>77.15454545454546</v>
       </c>
       <c r="B20">
-        <v>82.27942093732436</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>166.5135351421989</v>
+      </c>
+      <c r="C20">
+        <v>165.2215785960639</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21">
-        <v>79.66060606060607</v>
+        <v>81.12424242424242</v>
       </c>
       <c r="B21">
-        <v>86.51980533948044</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>166.4300140198809</v>
+      </c>
+      <c r="C21">
+        <v>165.0768923345704</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
-        <v>83.4848484848485</v>
+        <v>85.09393939393939</v>
       </c>
       <c r="B22">
-        <v>90.76455919094528</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>166.3505227695516</v>
+      </c>
+      <c r="C22">
+        <v>164.9392086577856</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
-        <v>87.30909090909091</v>
+        <v>89.06363636363636</v>
       </c>
       <c r="B23">
-        <v>95.01348639313845</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>166.2746920153506</v>
+      </c>
+      <c r="C23">
+        <v>164.8078847562022</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24">
-        <v>91.13333333333334</v>
+        <v>93.03333333333333</v>
       </c>
       <c r="B24">
-        <v>99.26640786714634</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>166.2022008787648</v>
+      </c>
+      <c r="C24">
+        <v>164.6823622997869</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25">
-        <v>94.95757575757577</v>
+        <v>97.0030303030303</v>
       </c>
       <c r="B25">
-        <v>103.5231594227902</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>166.1327688490972</v>
+      </c>
+      <c r="C25">
+        <v>164.5621532668136</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26">
-        <v>98.7818181818182</v>
+        <v>100.9727272727273</v>
       </c>
       <c r="B26">
-        <v>107.7835899697877</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>166.0661492884109</v>
+      </c>
+      <c r="C26">
+        <v>164.4468286234418</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27">
-        <v>102.6060606060606</v>
+        <v>104.9424242424243</v>
       </c>
       <c r="B27">
-        <v>112.0475600049332</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>166.0021241919015</v>
+      </c>
+      <c r="C27">
+        <v>164.3360091926343</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28">
-        <v>106.430303030303</v>
+        <v>108.9121212121212</v>
       </c>
       <c r="B28">
-        <v>116.3149403239822</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>165.9404999233838</v>
+      </c>
+      <c r="C28">
+        <v>164.22935822335</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29">
-        <v>110.2545454545455</v>
+        <v>112.8818181818182</v>
       </c>
       <c r="B29">
-        <v>120.5856109179659</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>165.8811037159705</v>
+      </c>
+      <c r="C29">
+        <v>164.1265752938161</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30">
-        <v>114.0787878787879</v>
+        <v>116.8515151515152</v>
       </c>
       <c r="B30">
-        <v>124.8594600220365</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>165.8237807789201</v>
+      </c>
+      <c r="C30">
+        <v>164.027391271496</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31">
-        <v>117.9030303030303</v>
+        <v>120.8212121212121</v>
       </c>
       <c r="B31">
-        <v>129.1363832913448</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>165.7683918888868</v>
+      </c>
+      <c r="C31">
+        <v>163.9315641173933</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32">
-        <v>121.7272727272727</v>
+        <v>124.7909090909091</v>
       </c>
       <c r="B32">
-        <v>133.4162830834045</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>165.7148113714217</v>
+      </c>
+      <c r="C32">
+        <v>163.8388753704998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33">
-        <v>125.5515151515152</v>
+        <v>128.7606060606061</v>
       </c>
       <c r="B33">
-        <v>137.6990678302662</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>165.6629253992461</v>
+      </c>
+      <c r="C33">
+        <v>163.7491271842727</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34">
-        <v>129.3757575757576</v>
+        <v>132.730303030303</v>
       </c>
       <c r="B34">
-        <v>141.9846514868621</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>165.6126305494712</v>
+      </c>
+      <c r="C34">
+        <v>163.662139814317</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
-        <v>133.2</v>
+        <v>136.7</v>
       </c>
       <c r="B35">
-        <v>146.2729530442983</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>165.5638325738848</v>
+      </c>
+      <c r="C35">
+        <v>163.5777494772954</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36">
-        <v>137.0242424242424</v>
+        <v>140.669696969697</v>
       </c>
       <c r="B36">
-        <v>150.5638960988001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>165.5164453456377</v>
+      </c>
+      <c r="C36">
+        <v>163.4958065171506</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
-        <v>140.8484848484849</v>
+        <v>144.6393939393939</v>
       </c>
       <c r="B37">
-        <v>154.8574084685684</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>165.4703899528186</v>
+      </c>
+      <c r="C37">
+        <v>163.4161738272009</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38">
-        <v>144.6727272727273</v>
+        <v>148.6090909090909</v>
       </c>
       <c r="B38">
-        <v>159.1534218520637</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>165.425593915008</v>
+      </c>
+      <c r="C38">
+        <v>163.3387254864417</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39">
-        <v>148.4969696969697</v>
+        <v>152.5787878787879</v>
       </c>
       <c r="B39">
-        <v>163.4518715222609</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>165.3819905033225</v>
+      </c>
+      <c r="C39">
+        <v>163.2633455760916</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40">
-        <v>152.3212121212121</v>
+        <v>156.5484848484848</v>
       </c>
       <c r="B40">
-        <v>167.7526960522568</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>165.3395181479706</v>
+      </c>
+      <c r="C40">
+        <v>163.1899271485391</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41">
-        <v>156.1454545454546</v>
+        <v>160.5181818181818</v>
       </c>
       <c r="B41">
-        <v>172.055837068309</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>165.2981199201468</v>
+      </c>
+      <c r="C41">
+        <v>163.1183713257382</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42">
-        <v>159.969696969697</v>
+        <v>164.4878787878788</v>
       </c>
       <c r="B42">
-        <v>176.3612390269583</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>165.2577430773467</v>
+      </c>
+      <c r="C42">
+        <v>163.0485865080337</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43">
-        <v>163.7939393939394</v>
+        <v>168.4575757575757</v>
       </c>
       <c r="B43">
-        <v>180.6688490133651</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>165.218338663013</v>
+      </c>
+      <c r="C43">
+        <v>162.9804876775799</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44">
-        <v>167.6181818181818</v>
+        <v>172.4272727272727</v>
       </c>
       <c r="B44">
-        <v>184.9786165583924</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>165.179861152904</v>
+      </c>
+      <c r="C44">
+        <v>162.9139957831007</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45">
-        <v>171.4424242424243</v>
+        <v>176.3969696969697</v>
       </c>
       <c r="B45">
-        <v>189.2904934723038</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+        <v>165.1422681417943</v>
+      </c>
+      <c r="C45">
+        <v>162.8490371948585</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46">
-        <v>175.2666666666667</v>
+        <v>180.3666666666666</v>
       </c>
       <c r="B46">
-        <v>193.6044336932307</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>165.1055200651101</v>
+      </c>
+      <c r="C46">
+        <v>162.7855432204343</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47">
-        <v>179.0909090909091</v>
+        <v>184.3363636363636</v>
       </c>
       <c r="B47">
-        <v>197.9203931488023</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>165.0695799509286</v>
+      </c>
+      <c r="C47">
+        <v>162.7234496733575</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48">
-        <v>182.9151515151515</v>
+        <v>188.3060606060606</v>
       </c>
       <c r="B48">
-        <v>202.2383296295388</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
+        <v>165.0344131984539</v>
+      </c>
+      <c r="C48">
+        <v>162.6626964878145</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49">
-        <v>186.7393939393939</v>
+        <v>192.2757575757576</v>
       </c>
       <c r="B49">
-        <v>206.5582026727819</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>164.9999873796473</v>
+      </c>
+      <c r="C49">
+        <v>162.6032273736548</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50">
-        <v>190.5636363636364</v>
+        <v>196.2454545454545</v>
       </c>
       <c r="B50">
-        <v>210.8799734560882</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
+        <v>164.9662720611686</v>
+      </c>
+      <c r="C50">
+        <v>162.5449895067408</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51">
-        <v>194.3878787878788</v>
+        <v>200.2151515151515</v>
       </c>
       <c r="B51">
-        <v>215.2036046991383</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
+        <v>164.9332386441849</v>
+      </c>
+      <c r="C51">
+        <v>162.4879332503883</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52">
-        <v>198.2121212121212</v>
+        <v>204.1848484848485</v>
       </c>
       <c r="B52">
-        <v>219.5290605733291</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
+        <v>164.9008602199364</v>
+      </c>
+      <c r="C52">
+        <v>162.4320119042233</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53">
-        <v>202.0363636363637</v>
+        <v>208.1545454545455</v>
       </c>
       <c r="B53">
-        <v>223.8563066183084</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
+        <v>164.8691114392361</v>
+      </c>
+      <c r="C53">
+        <v>162.3771814772825</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54">
-        <v>205.8606060606061</v>
+        <v>212.1242424242424</v>
       </c>
       <c r="B54">
-        <v>228.1853096647989</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
+        <v>164.8379683943228</v>
+      </c>
+      <c r="C54">
+        <v>162.3234004826036</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55">
-        <v>209.6848484848485</v>
+        <v>216.0939393939394</v>
       </c>
       <c r="B55">
-        <v>232.5160377631291</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
+        <v>164.8074085116884</v>
+      </c>
+      <c r="C55">
+        <v>162.2706297509077</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56">
-        <v>213.5090909090909</v>
+        <v>220.0636363636364</v>
       </c>
       <c r="B56">
-        <v>236.8484601169522</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
+        <v>164.7774104546797</v>
+      </c>
+      <c r="C56">
+        <v>162.2188322612856</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57">
-        <v>217.3333333333333</v>
+        <v>224.0333333333333</v>
       </c>
       <c r="B57">
-        <v>241.182547021691</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
+        <v>164.7479540348261</v>
+      </c>
+      <c r="C57">
+        <v>162.1679729870589</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58">
-        <v>221.1575757575758</v>
+        <v>228.0030303030303</v>
       </c>
       <c r="B58">
-        <v>245.5182698072938</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
+        <v>164.7190201309683</v>
+      </c>
+      <c r="C58">
+        <v>162.1180187552138</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
       <c r="A59">
-        <v>224.9818181818182</v>
+        <v>231.9727272727273</v>
       </c>
       <c r="B59">
-        <v>249.8556007849301</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
+        <v>164.6905906153826</v>
+      </c>
+      <c r="C59">
+        <v>162.0689381179977</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60">
-        <v>228.8060606060606</v>
+        <v>235.9424242424242</v>
       </c>
       <c r="B60">
-        <v>254.1945131972936</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
+        <v>164.6626482861844</v>
+      </c>
+      <c r="C60">
+        <v>162.0207012354392</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
       <c r="A61">
-        <v>232.6303030303031</v>
+        <v>239.9121212121212</v>
       </c>
       <c r="B61">
-        <v>258.5349811722098</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
+        <v>164.6351768053833</v>
+      </c>
+      <c r="C61">
+        <v>161.9732797676943</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62">
-        <v>236.4545454545455</v>
+        <v>243.8818181818182</v>
       </c>
       <c r="B62">
-        <v>262.8769796792803</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
+        <v>164.6081606420307</v>
+      </c>
+      <c r="C62">
+        <v>161.9266467762489</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
       <c r="A63">
-        <v>240.2787878787879</v>
+        <v>247.8515151515151</v>
       </c>
       <c r="B63">
-        <v>267.220484489318</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
+        <v>164.581585019967</v>
+      </c>
+      <c r="C63">
+        <v>161.8807766331194</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
       <c r="A64">
-        <v>244.1030303030303</v>
+        <v>251.8212121212121</v>
       </c>
       <c r="B64">
-        <v>271.5654721363509</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
+        <v>164.5554358697283</v>
+      </c>
+      <c r="C64">
+        <v>161.8356449372851</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65">
-        <v>247.9272727272728</v>
+        <v>255.7909090909091</v>
       </c>
       <c r="B65">
-        <v>275.9119198819963</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
+        <v>164.5296997842219</v>
+      </c>
+      <c r="C65">
+        <v>161.7912284376739</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66">
-        <v>251.7515151515152</v>
+        <v>259.7606060606061</v>
       </c>
       <c r="B66">
-        <v>280.2598056820212</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
+        <v>164.5043639778218</v>
+      </c>
+      <c r="C66">
+        <v>161.747504962093</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67">
-        <v>255.5757575757576</v>
+        <v>263.730303030303</v>
       </c>
       <c r="B67">
-        <v>284.6091081549252</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
+        <v>164.4794162485721</v>
+      </c>
+      <c r="C67">
+        <v>161.7044533515637</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
       <c r="A68">
-        <v>259.4</v>
+        <v>267.7</v>
       </c>
       <c r="B68">
-        <v>288.9598065523939</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
+        <v>164.4548449432203</v>
+      </c>
+      <c r="C68">
+        <v>161.6620533995745</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
       <c r="A69">
-        <v>263.2242424242424</v>
+        <v>271.669696969697</v>
       </c>
       <c r="B69">
-        <v>293.3118807314857</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
+        <v>164.430638924828</v>
+      </c>
+      <c r="C69">
+        <v>161.6202857958159</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
       <c r="A70">
-        <v>267.0484848484849</v>
+        <v>275.6393939393939</v>
       </c>
       <c r="B70">
-        <v>297.6653111284276</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
+        <v>164.4067875427371</v>
+      </c>
+      <c r="C70">
+        <v>161.5791320740082</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71">
-        <v>270.8727272727273</v>
+        <v>279.6090909090909</v>
       </c>
       <c r="B71">
-        <v>302.0200787339037</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
+        <v>164.3832806046866</v>
+      </c>
+      <c r="C71">
+        <v>161.538574563468</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72">
-        <v>274.6969696969697</v>
+        <v>283.5787878787879</v>
       </c>
       <c r="B72">
-        <v>306.3761650697327</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
+        <v>164.3601083508989</v>
+      </c>
+      <c r="C72">
+        <v>161.4985963440984</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
       <c r="A73">
-        <v>278.5212121212122</v>
+        <v>287.5484848484849</v>
       </c>
       <c r="B73">
-        <v>310.7335521668373</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
+        <v>164.3372614299716</v>
+      </c>
+      <c r="C73">
+        <v>161.4591812045158</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
       <c r="A74">
-        <v>282.3454545454546</v>
+        <v>291.5181818181818</v>
       </c>
       <c r="B74">
-        <v>315.0922225444174</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
+        <v>164.3147308764243</v>
+      </c>
+      <c r="C74">
+        <v>161.4203136030545</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75">
-        <v>286.169696969697</v>
+        <v>295.4878787878788</v>
       </c>
       <c r="B75">
-        <v>319.4521591902466</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
+        <v>164.2925080897678</v>
+      </c>
+      <c r="C75">
+        <v>161.3819786314156</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
       <c r="A76">
-        <v>289.9939393939394</v>
+        <v>299.4575757575757</v>
       </c>
       <c r="B76">
-        <v>323.8133455420156</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
+        <v>164.2705848149725</v>
+      </c>
+      <c r="C76">
+        <v>161.3441619807474</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
       <c r="A77">
-        <v>293.8181818181819</v>
+        <v>303.4272727272727</v>
       </c>
       <c r="B77">
-        <v>328.1757654696555</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
+        <v>164.2489531242247</v>
+      </c>
+      <c r="C77">
+        <v>161.3068499099662</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
       <c r="A78">
-        <v>297.6424242424243</v>
+        <v>307.3969696969697</v>
       </c>
       <c r="B78">
-        <v>332.5394032585762</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
+        <v>164.2276053998723</v>
+      </c>
+      <c r="C78">
+        <v>161.2700292161394</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
       <c r="A79">
-        <v>301.4666666666667</v>
+        <v>311.3666666666667</v>
       </c>
       <c r="B79">
-        <v>336.9042435937625</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
+        <v>164.2065343184656</v>
+      </c>
+      <c r="C79">
+        <v>161.233687206776</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
       <c r="A80">
-        <v>305.2909090909091</v>
+        <v>315.3363636363636</v>
       </c>
       <c r="B80">
-        <v>341.2702715446728</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
+        <v>164.1857328358117</v>
+      </c>
+      <c r="C80">
+        <v>161.1978116738748</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81">
-        <v>309.1151515151515</v>
+        <v>319.3060606060606</v>
       </c>
       <c r="B81">
-        <v>345.6374725508897</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
+        <v>164.1651941729656</v>
+      </c>
+      <c r="C81">
+        <v>161.1623908696016</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
       <c r="A82">
-        <v>312.939393939394</v>
+        <v>323.2757575757576</v>
       </c>
       <c r="B82">
-        <v>350.005832408479</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
+        <v>164.144911803088</v>
+      </c>
+      <c r="C82">
+        <v>161.1274134834724</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83">
-        <v>316.7636363636364</v>
+        <v>327.2454545454545</v>
       </c>
       <c r="B83">
-        <v>354.37533725701</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
+        <v>164.1248794391076</v>
+      </c>
+      <c r="C83">
+        <v>161.0928686209321</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
       <c r="A84">
-        <v>320.5878787878788</v>
+        <v>331.2151515151515</v>
       </c>
       <c r="B84">
-        <v>358.7459735672013</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
+        <v>164.1050910221275</v>
+      </c>
+      <c r="C84">
+        <v>161.0587457832294</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
       <c r="A85">
-        <v>324.4121212121212</v>
+        <v>335.1848484848485</v>
       </c>
       <c r="B85">
-        <v>363.1177281291515</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
+        <v>164.0855407105246</v>
+      </c>
+      <c r="C85">
+        <v>161.0250348484922</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
       <c r="A86">
-        <v>328.2363636363636</v>
+        <v>339.1545454545454</v>
       </c>
       <c r="B86">
-        <v>367.490588041123</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
+        <v>164.0662228696919</v>
+      </c>
+      <c r="C86">
+        <v>160.9917260539209</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
       <c r="A87">
-        <v>332.0606060606061</v>
+        <v>343.1242424242424</v>
       </c>
       <c r="B87">
-        <v>371.8645406988456</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
+        <v>164.047132062378</v>
+      </c>
+      <c r="C87">
+        <v>160.9588099790202</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
       <c r="A88">
-        <v>335.8848484848485</v>
+        <v>347.0939393939394</v>
       </c>
       <c r="B88">
-        <v>376.2395737853099</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
+        <v>164.0282630395844</v>
+      </c>
+      <c r="C88">
+        <v>160.9262775297977</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
       <c r="A89">
-        <v>339.7090909090909</v>
+        <v>351.0636363636364</v>
       </c>
       <c r="B89">
-        <v>380.615675261024</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
+        <v>164.0096107319807</v>
+      </c>
+      <c r="C89">
+        <v>160.8941199238634</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
       <c r="A90">
-        <v>343.5333333333334</v>
+        <v>355.0333333333333</v>
       </c>
       <c r="B90">
-        <v>384.9928333547057</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
+        <v>163.9911702418037</v>
+      </c>
+      <c r="C90">
+        <v>160.8623286763694</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
       <c r="A91">
-        <v>347.3575757575758</v>
+        <v>359.0030303030303</v>
       </c>
       <c r="B91">
-        <v>389.3710365543878</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
+        <v>163.9729368352075</v>
+      </c>
+      <c r="C91">
+        <v>160.830895586733</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
       <c r="A92">
-        <v>351.1818181818182</v>
+        <v>362.9727272727272</v>
       </c>
       <c r="B92">
-        <v>393.7502735989129</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
+        <v>163.9549059350355</v>
+      </c>
+      <c r="C92">
+        <v>160.7998127260914</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
       <c r="A93">
-        <v>355.0060606060607</v>
+        <v>366.9424242424242</v>
       </c>
       <c r="B93">
-        <v>398.1305334697962</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
+        <v>163.9370731139862</v>
+      </c>
+      <c r="C93">
+        <v>160.7690724254416</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
       <c r="A94">
-        <v>358.8303030303031</v>
+        <v>370.9121212121212</v>
       </c>
       <c r="B94">
-        <v>402.5118053834383</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
+        <v>163.9194340881467</v>
+      </c>
+      <c r="C94">
+        <v>160.7386672644188</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
       <c r="A95">
-        <v>362.6545454545455</v>
+        <v>374.8818181818182</v>
       </c>
       <c r="B95">
-        <v>406.8940787836671</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
+        <v>163.9019847108722</v>
+      </c>
+      <c r="C95">
+        <v>160.7085900606741</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
       <c r="A96">
-        <v>366.4787878787879</v>
+        <v>378.8515151515151</v>
       </c>
       <c r="B96">
-        <v>411.2773433345929</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
+        <v>163.8847209669879</v>
+      </c>
+      <c r="C96">
+        <v>160.6788338598139</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97">
-        <v>370.3030303030304</v>
+        <v>382.8212121212121</v>
       </c>
       <c r="B97">
-        <v>415.6615889137613</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
+        <v>163.8676389672935</v>
+      </c>
+      <c r="C97">
+        <v>160.6493919258635</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98">
-        <v>374.1272727272728</v>
+        <v>386.7909090909091</v>
       </c>
       <c r="B98">
-        <v>420.0468056055855</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
+        <v>163.8507349433522</v>
+      </c>
+      <c r="C98">
+        <v>160.6202577322252</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
       <c r="A99">
-        <v>377.9515151515152</v>
+        <v>390.7606060606061</v>
       </c>
       <c r="B99">
-        <v>424.4329836950478</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
+        <v>163.8340052425458</v>
+      </c>
+      <c r="C99">
+        <v>160.5914249530989</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
       <c r="A100">
-        <v>381.7757575757576</v>
+        <v>394.730303030303</v>
       </c>
       <c r="B100">
-        <v>428.820113661653</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
+        <v>163.8174463233807</v>
+      </c>
+      <c r="C100">
+        <v>160.5628874553363</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
       <c r="A101">
-        <v>385.6</v>
+        <v>398.7</v>
       </c>
       <c r="B101">
-        <v>433.2081861736244</v>
+        <v>163.8010547510291</v>
+      </c>
+      <c r="C101">
+        <v>160.5346392907061</v>
       </c>
     </row>
   </sheetData>
@@ -1694,25 +2002,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="C2">
-        <v>0.8432740427115677</v>
+        <v>1.28279209365959</v>
       </c>
       <c r="D2">
-        <v>1.768334</v>
+        <v>1.51</v>
       </c>
       <c r="E2">
-        <v>0.07695788330422469</v>
+        <v>0.0998825853912705</v>
       </c>
       <c r="F2">
-        <v>0.8450980400142568</v>
+        <v>0.7558748556724915</v>
       </c>
       <c r="G2">
-        <v>0.2475642972479138</v>
+        <v>0.1789769472931694</v>
       </c>
       <c r="H2">
-        <v>0.268588363841006</v>
+        <v>0.2245979620400547</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1720,25 +2028,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>18.6</v>
+        <v>15.5</v>
       </c>
       <c r="C3">
-        <v>2.028683207293725</v>
+        <v>2.982355519458477</v>
       </c>
       <c r="D3">
-        <v>2.000293</v>
+        <v>1.935719</v>
       </c>
       <c r="E3">
-        <v>0.05053576933552445</v>
+        <v>0.08132708911071525</v>
       </c>
       <c r="F3">
-        <v>1.269512944217916</v>
+        <v>1.190331698170291</v>
       </c>
       <c r="G3">
-        <v>0.3010936151455668</v>
+        <v>0.2868423128862378</v>
       </c>
       <c r="H3">
-        <v>0.2904653280710791</v>
+        <v>0.2586715531000379</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1746,25 +2054,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>34.6</v>
+        <v>46.5</v>
       </c>
       <c r="C4">
-        <v>7.126164622166838</v>
+        <v>7.473285756613352</v>
       </c>
       <c r="D4">
-        <v>2.078329</v>
+        <v>2.09252</v>
       </c>
       <c r="E4">
-        <v>0.04164757507813496</v>
+        <v>0.0403244972690299</v>
       </c>
       <c r="F4">
-        <v>1.539076098792777</v>
+        <v>1.667452952889954</v>
       </c>
       <c r="G4">
-        <v>0.3177142975882189</v>
+        <v>0.3206696176082504</v>
       </c>
       <c r="H4">
-        <v>0.3043602771691674</v>
+        <v>0.2960912296457611</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1772,25 +2080,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>66.5</v>
+        <v>63.7</v>
       </c>
       <c r="C5">
-        <v>11.36588462607875</v>
+        <v>11.87906655517268</v>
       </c>
       <c r="D5">
-        <v>2.118862</v>
+        <v>2.148916</v>
       </c>
       <c r="E5">
-        <v>0.02445186249665976</v>
+        <v>0.03795106747730118</v>
       </c>
       <c r="F5">
-        <v>1.822821645303105</v>
+        <v>1.80413943233535</v>
       </c>
       <c r="G5">
-        <v>0.3261026723360208</v>
+        <v>0.3322194394795881</v>
       </c>
       <c r="H5">
-        <v>0.3189862743006683</v>
+        <v>0.3068112799441398</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1798,25 +2106,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>102.7</v>
+        <v>111</v>
       </c>
       <c r="C6">
-        <v>16.29863661646444</v>
+        <v>13.88684429395118</v>
       </c>
       <c r="D6">
-        <v>2.171153</v>
+        <v>2.177831</v>
       </c>
       <c r="E6">
-        <v>0.0324393770679333</v>
+        <v>0.02892106147006978</v>
       </c>
       <c r="F6">
-        <v>2.011570443597278</v>
+        <v>2.045322978786658</v>
       </c>
       <c r="G6">
-        <v>0.336690429034536</v>
+        <v>0.3380241754128099</v>
       </c>
       <c r="H6">
-        <v>0.3287155525796645</v>
+        <v>0.3257268285747726</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1824,25 +2132,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>159.9</v>
+        <v>163.4</v>
       </c>
       <c r="C7">
-        <v>20.1132626227903</v>
+        <v>11.71153277756588</v>
       </c>
       <c r="D7">
-        <v>2.187549999999999</v>
+        <v>2.179318</v>
       </c>
       <c r="E7">
-        <v>0.01651810326749279</v>
+        <v>0.02649991848205494</v>
       </c>
       <c r="F7">
-        <v>2.203848463746235</v>
+        <v>2.213252052196397</v>
       </c>
       <c r="G7">
-        <v>0.339957988311919</v>
+        <v>0.3383206059088347</v>
       </c>
       <c r="H7">
-        <v>0.338626748740225</v>
+        <v>0.3388971737385142</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1850,25 +2158,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>195.5</v>
+        <v>203</v>
       </c>
       <c r="C8">
-        <v>21.28549323417764</v>
+        <v>20.33988965336614</v>
       </c>
       <c r="D8">
-        <v>2.198026</v>
+        <v>2.200566</v>
       </c>
       <c r="E8">
-        <v>0.02502032663433651</v>
+        <v>0.02418361328576759</v>
       </c>
       <c r="F8">
-        <v>2.291146761731885</v>
+        <v>2.307496037913213</v>
       </c>
       <c r="G8">
-        <v>0.3420328252984571</v>
+        <v>0.3425343985776553</v>
       </c>
       <c r="H8">
-        <v>0.3431266419425191</v>
+        <v>0.3462885431797584</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1876,25 +2184,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>258.4</v>
+        <v>234.3</v>
       </c>
       <c r="C9">
-        <v>21.7011008425328</v>
+        <v>25.92169833256387</v>
       </c>
       <c r="D9">
-        <v>2.212594999999999</v>
+        <v>2.195059</v>
       </c>
       <c r="E9">
-        <v>0.01577493280492819</v>
+        <v>0.02322330742307536</v>
       </c>
       <c r="F9">
-        <v>2.412292509323046</v>
+        <v>2.369772288596963</v>
       </c>
       <c r="G9">
-        <v>0.3449019266421982</v>
+        <v>0.3414461979403587</v>
       </c>
       <c r="H9">
-        <v>0.3493712416500862</v>
+        <v>0.3511727463755174</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1902,25 +2210,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>293.9</v>
+        <v>274.2</v>
       </c>
       <c r="C10">
-        <v>26.76126969251563</v>
+        <v>24.15082239225451</v>
       </c>
       <c r="D10">
-        <v>2.215678</v>
+        <v>2.209068</v>
       </c>
       <c r="E10">
-        <v>0.01594446408980594</v>
+        <v>0.0130777449466217</v>
       </c>
       <c r="F10">
-        <v>2.468199586072612</v>
+        <v>2.438067450453494</v>
       </c>
       <c r="G10">
-        <v>0.3455066455039472</v>
+        <v>0.3442090846221068</v>
       </c>
       <c r="H10">
-        <v>0.3522530375204577</v>
+        <v>0.3565290008727327</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1928,25 +2236,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>385.6</v>
+        <v>398.7</v>
       </c>
       <c r="C11">
-        <v>27.37038139627904</v>
+        <v>22.06356977261637</v>
       </c>
       <c r="D11">
-        <v>2.245231</v>
+        <v>2.242969</v>
       </c>
       <c r="E11">
-        <v>0.007954256365829145</v>
+        <v>0.006876881633414962</v>
       </c>
       <c r="F11">
-        <v>2.586137025230793</v>
+        <v>2.600646235662394</v>
       </c>
       <c r="G11">
-        <v>0.3512610299114312</v>
+        <v>0.3508232712548467</v>
       </c>
       <c r="H11">
-        <v>0.3583322612053352</v>
+        <v>0.369279733512569</v>
       </c>
     </row>
   </sheetData>
@@ -1956,815 +2264,1118 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="B2">
-        <v>1.866617549339758</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>2.143803318930547</v>
+      </c>
+      <c r="C2">
+        <v>2.183268060480812</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3">
-        <v>10.82424242424242</v>
+        <v>9.66969696969697</v>
       </c>
       <c r="B3">
-        <v>1.907294870392893</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>2.13250254849615</v>
+      </c>
+      <c r="C3">
+        <v>2.163322430014004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4">
-        <v>14.64848484848485</v>
+        <v>13.63939393939394</v>
       </c>
       <c r="B4">
-        <v>1.93604955679545</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>2.125180081428059</v>
+      </c>
+      <c r="C4">
+        <v>2.150416082898324</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5">
-        <v>18.47272727272728</v>
+        <v>17.60909090909091</v>
       </c>
       <c r="B5">
-        <v>1.958388501559025</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>2.119758171646565</v>
+      </c>
+      <c r="C5">
+        <v>2.140868621686479</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6">
-        <v>22.2969696969697</v>
+        <v>21.57878787878788</v>
       </c>
       <c r="B6">
-        <v>1.976698148409296</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>2.115453176257731</v>
+      </c>
+      <c r="C6">
+        <v>2.133293441068206</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7">
-        <v>26.12121212121212</v>
+        <v>25.54848484848485</v>
       </c>
       <c r="B7">
-        <v>1.992234759098052</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>2.111883883736007</v>
+      </c>
+      <c r="C7">
+        <v>2.127016532415504</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8">
-        <v>29.94545454545455</v>
+        <v>29.51818181818182</v>
       </c>
       <c r="B8">
-        <v>2.005742929088586</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>2.108835925372371</v>
+      </c>
+      <c r="C8">
+        <v>2.121659107752297</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9">
-        <v>33.76969696969697</v>
+        <v>33.48787878787879</v>
       </c>
       <c r="B9">
-        <v>2.01770107818556</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>2.106176734516568</v>
+      </c>
+      <c r="C9">
+        <v>2.116987041253829</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10">
-        <v>37.59393939393939</v>
+        <v>37.45757575757576</v>
       </c>
       <c r="B10">
-        <v>2.028435197566699</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>2.10381860200438</v>
+      </c>
+      <c r="C10">
+        <v>2.112845497031101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11">
-        <v>41.41818181818182</v>
+        <v>41.42727272727273</v>
       </c>
       <c r="B11">
-        <v>2.038177585359036</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>2.10170048311702</v>
+      </c>
+      <c r="C11">
+        <v>2.109126751779533</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12">
-        <v>45.24242424242425</v>
+        <v>45.3969696969697</v>
       </c>
       <c r="B12">
-        <v>2.047099723555242</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>2.099778182175643</v>
+      </c>
+      <c r="C12">
+        <v>2.105752841462443</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13">
-        <v>49.06666666666667</v>
+        <v>49.36666666666667</v>
       </c>
       <c r="B13">
-        <v>2.055331869911684</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>2.098018674119686</v>
+      </c>
+      <c r="C13">
+        <v>2.102665525530379</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14">
-        <v>52.8909090909091</v>
+        <v>53.33636363636364</v>
       </c>
       <c r="B14">
-        <v>2.062975333428251</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>2.096396632761561</v>
+      </c>
+      <c r="C14">
+        <v>2.099820153026731</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15">
-        <v>56.71515151515152</v>
+        <v>57.30606060606061</v>
       </c>
       <c r="B15">
-        <v>2.070110488500537</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>2.094892210671257</v>
+      </c>
+      <c r="C15">
+        <v>2.097181741184752</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16">
-        <v>60.53939393939395</v>
+        <v>61.27575757575758</v>
       </c>
       <c r="B16">
-        <v>2.07680218994204</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>2.093489565539962</v>
+      </c>
+      <c r="C16">
+        <v>2.094722373206998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
-        <v>64.36363636363637</v>
+        <v>65.24545454545455</v>
       </c>
       <c r="B17">
-        <v>2.08310354010715</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>2.092175850777884</v>
+      </c>
+      <c r="C17">
+        <v>2.092419416237264</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
-        <v>68.18787878787879</v>
+        <v>69.21515151515152</v>
       </c>
       <c r="B18">
-        <v>2.089058576159379</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>2.090940505241133</v>
+      </c>
+      <c r="C18">
+        <v>2.090254267701019</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
-        <v>72.01212121212122</v>
+        <v>73.18484848484849</v>
       </c>
       <c r="B19">
-        <v>2.094704229281312</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>2.089774741662437</v>
+      </c>
+      <c r="C19">
+        <v>2.088211452552237</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20">
-        <v>75.83636363636364</v>
+        <v>77.15454545454546</v>
       </c>
       <c r="B20">
-        <v>2.100071780672932</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>2.088671170613618</v>
+      </c>
+      <c r="C20">
+        <v>2.086277959818118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21">
-        <v>79.66060606060607</v>
+        <v>81.12424242424242</v>
       </c>
       <c r="B21">
-        <v>2.105187962061542</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>2.087623519080823</v>
+      </c>
+      <c r="C21">
+        <v>2.084442746162749</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
-        <v>83.4848484848485</v>
+        <v>85.09393939393939</v>
       </c>
       <c r="B22">
-        <v>2.110075800165285</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>2.086626416456481</v>
+      </c>
+      <c r="C22">
+        <v>2.082696358439618</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
-        <v>87.30909090909091</v>
+        <v>89.06363636363636</v>
       </c>
       <c r="B23">
-        <v>2.114755273513655</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>2.085675229455314</v>
+      </c>
+      <c r="C23">
+        <v>2.081030642579416</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24">
-        <v>91.13333333333334</v>
+        <v>93.03333333333333</v>
       </c>
       <c r="B24">
-        <v>2.119243829597138</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>2.08476593312104</v>
+      </c>
+      <c r="C24">
+        <v>2.079438516156153</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25">
-        <v>94.95757575757577</v>
+        <v>97.0030303030303</v>
       </c>
       <c r="B25">
-        <v>2.123556796580766</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>2.083895008853172</v>
+      </c>
+      <c r="C25">
+        <v>2.077913788620235</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26">
-        <v>98.7818181818182</v>
+        <v>100.9727272727273</v>
       </c>
       <c r="B26">
-        <v>2.127707714401377</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>2.083059362935946</v>
+      </c>
+      <c r="C26">
+        <v>2.076451017694732</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27">
-        <v>102.6060606060606</v>
+        <v>104.9424242424243</v>
       </c>
       <c r="B27">
-        <v>2.131708603502769</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>2.082256260814785</v>
+      </c>
+      <c r="C27">
+        <v>2.075045393544475</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28">
-        <v>106.430303030303</v>
+        <v>108.9121212121212</v>
       </c>
       <c r="B28">
-        <v>2.135570184811413</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>2.081483273604146</v>
+      </c>
+      <c r="C28">
+        <v>2.073692644513924</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29">
-        <v>110.2545454545455</v>
+        <v>112.8818181818182</v>
       </c>
       <c r="B29">
-        <v>2.139302061211877</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>2.080738234193614</v>
+      </c>
+      <c r="C29">
+        <v>2.072388959788414</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30">
-        <v>114.0787878787879</v>
+        <v>116.8515151515152</v>
       </c>
       <c r="B30">
-        <v>2.142912868345665</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>2.080019200957487</v>
+      </c>
+      <c r="C30">
+        <v>2.071130925460009</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31">
-        <v>117.9030303030303</v>
+        <v>120.8212121212121</v>
       </c>
       <c r="B31">
-        <v>2.146410400761287</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>2.079324427540504</v>
+      </c>
+      <c r="C31">
+        <v>2.069915471304095</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32">
-        <v>121.7272727272727</v>
+        <v>124.7909090909091</v>
       </c>
       <c r="B32">
-        <v>2.149801718103975</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>2.078652337538688</v>
+      </c>
+      <c r="C32">
+        <v>2.068739826183835</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33">
-        <v>125.5515151515152</v>
+        <v>128.7606060606061</v>
       </c>
       <c r="B33">
-        <v>2.153093235024026</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>2.078001503153664</v>
+      </c>
+      <c r="C33">
+        <v>2.067601480457305</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34">
-        <v>129.3757575757576</v>
+        <v>132.730303030303</v>
       </c>
       <c r="B34">
-        <v>2.156290797714417</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>2.077370627095058</v>
+      </c>
+      <c r="C34">
+        <v>2.066498154108305</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
-        <v>133.2</v>
+        <v>136.7</v>
       </c>
       <c r="B35">
-        <v>2.159399749398251</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>2.076758527155527</v>
+      </c>
+      <c r="C35">
+        <v>2.065427769586312</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36">
-        <v>137.0242424242424</v>
+        <v>140.669696969697</v>
       </c>
       <c r="B36">
-        <v>2.16242498662946</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>2.076164122998469</v>
+      </c>
+      <c r="C36">
+        <v>2.06438842854476</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
-        <v>140.8484848484849</v>
+        <v>144.6393939393939</v>
       </c>
       <c r="B37">
-        <v>2.165371007913258</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>2.075586424788228</v>
+      </c>
+      <c r="C37">
+        <v>2.063378391825146</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38">
-        <v>144.6727272727273</v>
+        <v>148.6090909090909</v>
       </c>
       <c r="B38">
-        <v>2.16824195587195</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>2.075024523362901</v>
+      </c>
+      <c r="C38">
+        <v>2.062396062158392</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39">
-        <v>148.4969696969697</v>
+        <v>152.5787878787879</v>
       </c>
       <c r="B39">
-        <v>2.171041653959275</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>2.074477581705274</v>
+      </c>
+      <c r="C39">
+        <v>2.061439969152638</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40">
-        <v>152.3212121212121</v>
+        <v>156.5484848484848</v>
       </c>
       <c r="B40">
-        <v>2.173773638548912</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>2.073944827511474</v>
+      </c>
+      <c r="C40">
+        <v>2.060508756214268</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41">
-        <v>156.1454545454546</v>
+        <v>160.5181818181818</v>
       </c>
       <c r="B41">
-        <v>2.176441187080371</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>2.073425546692072</v>
+      </c>
+      <c r="C41">
+        <v>2.059601169111034</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42">
-        <v>159.969696969697</v>
+        <v>164.4878787878788</v>
       </c>
       <c r="B42">
-        <v>2.179047342830478</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>2.072919077668729</v>
+      </c>
+      <c r="C42">
+        <v>2.058716045935979</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43">
-        <v>163.7939393939394</v>
+        <v>168.4575757575757</v>
       </c>
       <c r="B43">
-        <v>2.181594936785231</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>2.072424806352325</v>
+      </c>
+      <c r="C43">
+        <v>2.057852308271302</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44">
-        <v>167.6181818181818</v>
+        <v>172.4272727272727</v>
       </c>
       <c r="B44">
-        <v>2.184086607010618</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>2.071942161707174</v>
+      </c>
+      <c r="C44">
+        <v>2.057008953384043</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45">
-        <v>171.4424242424243</v>
+        <v>176.3969696969697</v>
       </c>
       <c r="B45">
-        <v>2.186524815858414</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+        <v>2.071470611821128</v>
+      </c>
+      <c r="C45">
+        <v>2.056185047312383</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46">
-        <v>175.2666666666667</v>
+        <v>180.3666666666666</v>
       </c>
       <c r="B46">
-        <v>2.18891186529139</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>2.071009660413902</v>
+      </c>
+      <c r="C46">
+        <v>2.055379718723331</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47">
-        <v>179.0909090909091</v>
+        <v>184.3363636363636</v>
       </c>
       <c r="B47">
-        <v>2.191249910569693</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>2.070558843726265</v>
+      </c>
+      <c r="C47">
+        <v>2.054592153440821</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48">
-        <v>182.9151515151515</v>
+        <v>188.3060606060606</v>
       </c>
       <c r="B48">
-        <v>2.193540972504586</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
+        <v>2.070117727741339</v>
+      </c>
+      <c r="C48">
+        <v>2.053821589558313</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49">
-        <v>186.7393939393939</v>
+        <v>192.2757575757576</v>
       </c>
       <c r="B49">
-        <v>2.195786948456092</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>2.069685905696333</v>
+      </c>
+      <c r="C49">
+        <v>2.05306731306258</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50">
-        <v>190.5636363636364</v>
+        <v>196.2454545454545</v>
       </c>
       <c r="B50">
-        <v>2.197989622226165</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
+        <v>2.069262995849068</v>
+      </c>
+      <c r="C50">
+        <v>2.052328653905827</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51">
-        <v>194.3878787878788</v>
+        <v>200.2151515151515</v>
       </c>
       <c r="B51">
-        <v>2.200150672978074</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
+        <v>2.068848639468599</v>
+      </c>
+      <c r="C51">
+        <v>2.051604982472189</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52">
-        <v>198.2121212121212</v>
+        <v>204.1848484848485</v>
       </c>
       <c r="B52">
-        <v>2.202271683294966</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
+        <v>2.068442499023499</v>
+      </c>
+      <c r="C52">
+        <v>2.05089570639202</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53">
-        <v>202.0363636363637</v>
+        <v>208.1545454545455</v>
       </c>
       <c r="B53">
-        <v>2.204354146475567</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
+        <v>2.068044256544928</v>
+      </c>
+      <c r="C53">
+        <v>2.0502002676637</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54">
-        <v>205.8606060606061</v>
+        <v>212.1242424242424</v>
       </c>
       <c r="B54">
-        <v>2.206399473152185</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
+        <v>2.067653612144639</v>
+      </c>
+      <c r="C54">
+        <v>2.049518140048044</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55">
-        <v>209.6848484848485</v>
+        <v>216.0939393939394</v>
       </c>
       <c r="B55">
-        <v>2.208408997305316</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
+        <v>2.067270282670663</v>
+      </c>
+      <c r="C55">
+        <v>2.048848826704898</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56">
-        <v>213.5090909090909</v>
+        <v>220.0636363636364</v>
       </c>
       <c r="B56">
-        <v>2.210383981739757</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
+        <v>2.066894000485585</v>
+      </c>
+      <c r="C56">
+        <v>2.048191858045424</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57">
-        <v>217.3333333333333</v>
+        <v>224.0333333333333</v>
       </c>
       <c r="B57">
-        <v>2.212325623079171</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
+        <v>2.066524512354274</v>
+      </c>
+      <c r="C57">
+        <v>2.047546789776877</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58">
-        <v>221.1575757575758</v>
+        <v>228.0030303030303</v>
       </c>
       <c r="B58">
-        <v>2.21423505632911</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
+        <v>2.066161578429477</v>
+      </c>
+      <c r="C58">
+        <v>2.046913201119548</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
       <c r="A59">
-        <v>224.9818181818182</v>
+        <v>231.9727272727273</v>
       </c>
       <c r="B59">
-        <v>2.216113359052536</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
+        <v>2.065804971325149</v>
+      </c>
+      <c r="C59">
+        <v>2.046290693178002</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60">
-        <v>228.8060606060606</v>
+        <v>235.9424242424242</v>
       </c>
       <c r="B60">
-        <v>2.217961555196747</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
+        <v>2.06545447526856</v>
+      </c>
+      <c r="C60">
+        <v>2.045678887450869</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
       <c r="A61">
-        <v>232.6303030303031</v>
+        <v>239.9121212121212</v>
       </c>
       <c r="B61">
-        <v>2.219780618606096</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
+        <v>2.065109885323277</v>
+      </c>
+      <c r="C61">
+        <v>2.045077424465272</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62">
-        <v>236.4545454545455</v>
+        <v>243.8818181818182</v>
       </c>
       <c r="B62">
-        <v>2.221571476251006</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
+        <v>2.064771006676043</v>
+      </c>
+      <c r="C62">
+        <v>2.044485962523621</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
       <c r="A63">
-        <v>240.2787878787879</v>
+        <v>247.8515151515151</v>
       </c>
       <c r="B63">
-        <v>2.223335011200398</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
+        <v>2.064437653981332</v>
+      </c>
+      <c r="C63">
+        <v>2.043904176551834</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
       <c r="A64">
-        <v>244.1030303030303</v>
+        <v>251.8212121212121</v>
       </c>
       <c r="B64">
-        <v>2.225072065361629</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
+        <v>2.064109650758093</v>
+      </c>
+      <c r="C64">
+        <v>2.04333175703931</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65">
-        <v>247.9272727272728</v>
+        <v>255.7909090909091</v>
       </c>
       <c r="B65">
-        <v>2.226783442009478</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
+        <v>2.063786828833762</v>
+      </c>
+      <c r="C65">
+        <v>2.042768409062024</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66">
-        <v>251.7515151515152</v>
+        <v>259.7606060606061</v>
       </c>
       <c r="B66">
-        <v>2.228469908123391</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
+        <v>2.063469027831177</v>
+      </c>
+      <c r="C66">
+        <v>2.042213851381034</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67">
-        <v>255.5757575757576</v>
+        <v>263.730303030303</v>
       </c>
       <c r="B67">
-        <v>2.230132196550207</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
+        <v>2.063156094694472</v>
+      </c>
+      <c r="C67">
+        <v>2.041667815609538</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
       <c r="A68">
-        <v>259.4</v>
+        <v>267.7</v>
       </c>
       <c r="B68">
-        <v>2.231771008007781</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
+        <v>2.062847883250465</v>
+      </c>
+      <c r="C68">
+        <v>2.041130045442316</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
       <c r="A69">
-        <v>263.2242424242424</v>
+        <v>271.669696969697</v>
       </c>
       <c r="B69">
-        <v>2.233387012943384</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
+        <v>2.062544253802396</v>
+      </c>
+      <c r="C69">
+        <v>2.040600295942028</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
       <c r="A70">
-        <v>267.0484848484849</v>
+        <v>275.6393939393939</v>
       </c>
       <c r="B70">
-        <v>2.234980853259332</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
+        <v>2.06224507275318</v>
+      </c>
+      <c r="C70">
+        <v>2.040078332877423</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71">
-        <v>270.8727272727273</v>
+        <v>279.6090909090909</v>
       </c>
       <c r="B71">
-        <v>2.236553143917105</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
+        <v>2.061950212255662</v>
+      </c>
+      <c r="C71">
+        <v>2.039563932108984</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72">
-        <v>274.6969696969697</v>
+        <v>283.5787878787879</v>
       </c>
       <c r="B72">
-        <v>2.238104474430069</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
+        <v>2.061659549887566</v>
+      </c>
+      <c r="C72">
+        <v>2.039056879017986</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
       <c r="A73">
-        <v>278.5212121212122</v>
+        <v>287.5484848484849</v>
       </c>
       <c r="B73">
-        <v>2.239635410254003</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
+        <v>2.061372968349089</v>
+      </c>
+      <c r="C73">
+        <v>2.038556967975357</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
       <c r="A74">
-        <v>282.3454545454546</v>
+        <v>291.5181818181818</v>
       </c>
       <c r="B74">
-        <v>2.241146494083695</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
+        <v>2.061090355181265</v>
+      </c>
+      <c r="C74">
+        <v>2.038064001847026</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75">
-        <v>286.169696969697</v>
+        <v>295.4878787878788</v>
       </c>
       <c r="B75">
-        <v>2.242638247063156</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
+        <v>2.06081160250341</v>
+      </c>
+      <c r="C75">
+        <v>2.037577791532836</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
       <c r="A76">
-        <v>289.9939393939394</v>
+        <v>299.4575757575757</v>
       </c>
       <c r="B76">
-        <v>2.244111169916259</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
+        <v>2.06053660676813</v>
+      </c>
+      <c r="C76">
+        <v>2.037098155536282</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
       <c r="A77">
-        <v>293.8181818181819</v>
+        <v>303.4272727272727</v>
       </c>
       <c r="B77">
-        <v>2.245565744004029</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
+        <v>2.060265268532485</v>
+      </c>
+      <c r="C77">
+        <v>2.036624919562663</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
       <c r="A78">
-        <v>297.6424242424243</v>
+        <v>307.3969696969697</v>
       </c>
       <c r="B78">
-        <v>2.247002432314208</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
+        <v>2.059997492244058</v>
+      </c>
+      <c r="C78">
+        <v>2.036157916143424</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
       <c r="A79">
-        <v>301.4666666666667</v>
+        <v>311.3666666666667</v>
       </c>
       <c r="B79">
-        <v>2.24842168038826</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
+        <v>2.059733186040781</v>
+      </c>
+      <c r="C79">
+        <v>2.035696984284652</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
       <c r="A80">
-        <v>305.2909090909091</v>
+        <v>315.3363636363636</v>
       </c>
       <c r="B80">
-        <v>2.249823917190505</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
+        <v>2.059472261563452</v>
+      </c>
+      <c r="C80">
+        <v>2.035241969137903</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81">
-        <v>309.1151515151515</v>
+        <v>319.3060606060606</v>
       </c>
       <c r="B81">
-        <v>2.251209555923665</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
+        <v>2.059214633780022</v>
+      </c>
+      <c r="C81">
+        <v>2.034792721691672</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
       <c r="A82">
-        <v>312.939393939394</v>
+        <v>323.2757575757576</v>
       </c>
       <c r="B82">
-        <v>2.252578994794753</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
+        <v>2.058960220820747</v>
+      </c>
+      <c r="C82">
+        <v>2.034349098481969</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83">
-        <v>316.7636363636364</v>
+        <v>327.2454545454545</v>
       </c>
       <c r="B83">
-        <v>2.253932617734889</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
+        <v>2.058708943823418</v>
+      </c>
+      <c r="C83">
+        <v>2.03391096132061</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
       <c r="A84">
-        <v>320.5878787878788</v>
+        <v>331.2151515151515</v>
       </c>
       <c r="B84">
-        <v>2.25527079507634</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
+        <v>2.058460726787948</v>
+      </c>
+      <c r="C84">
+        <v>2.033478177039926</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
       <c r="A85">
-        <v>324.4121212121212</v>
+        <v>335.1848484848485</v>
       </c>
       <c r="B85">
-        <v>2.256593884189795</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
+        <v>2.058215496439638</v>
+      </c>
+      <c r="C85">
+        <v>2.033050617252724</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
       <c r="A86">
-        <v>328.2363636363636</v>
+        <v>339.1545454545454</v>
       </c>
       <c r="B86">
-        <v>2.25790223008466</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
+        <v>2.057973182100497</v>
+      </c>
+      <c r="C86">
+        <v>2.032628158126411</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
       <c r="A87">
-        <v>332.0606060606061</v>
+        <v>343.1242424242424</v>
       </c>
       <c r="B87">
-        <v>2.259196165974914</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
+        <v>2.057733715568085</v>
+      </c>
+      <c r="C87">
+        <v>2.0322106801703</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
       <c r="A88">
-        <v>335.8848484848485</v>
+        <v>347.0939393939394</v>
       </c>
       <c r="B88">
-        <v>2.260476013812877</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
+        <v>2.057497031001315</v>
+      </c>
+      <c r="C88">
+        <v>2.031798068035179</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
       <c r="A89">
-        <v>339.7090909090909</v>
+        <v>351.0636363636364</v>
       </c>
       <c r="B89">
-        <v>2.261742084793056</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
+        <v>2.057263064812776</v>
+      </c>
+      <c r="C89">
+        <v>2.031390210324304</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
       <c r="A90">
-        <v>343.5333333333334</v>
+        <v>355.0333333333333</v>
       </c>
       <c r="B90">
-        <v>2.262994679828048</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
+        <v>2.057031755567123</v>
+      </c>
+      <c r="C90">
+        <v>2.030986999415046</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
       <c r="A91">
-        <v>347.3575757575758</v>
+        <v>359.0030303030303</v>
       </c>
       <c r="B91">
-        <v>2.264234089998368</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
+        <v>2.056803043885115</v>
+      </c>
+      <c r="C91">
+        <v>2.030588331290489</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
       <c r="A92">
-        <v>351.1818181818182</v>
+        <v>362.9727272727272</v>
       </c>
       <c r="B92">
-        <v>2.265460596977876</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
+        <v>2.05657687235295</v>
+      </c>
+      <c r="C92">
+        <v>2.030194105380298</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
       <c r="A93">
-        <v>355.0060606060607</v>
+        <v>366.9424242424242</v>
       </c>
       <c r="B93">
-        <v>2.266674473436385</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
+        <v>2.056353185436539</v>
+      </c>
+      <c r="C93">
+        <v>2.02980422441027</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
       <c r="A94">
-        <v>358.8303030303031</v>
+        <v>370.9121212121212</v>
       </c>
       <c r="B94">
-        <v>2.267875983420914</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
+        <v>2.056131929400403</v>
+      </c>
+      <c r="C94">
+        <v>2.029418594260007</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
       <c r="A95">
-        <v>362.6545454545455</v>
+        <v>374.8818181818182</v>
       </c>
       <c r="B95">
-        <v>2.269065382716918</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
+        <v>2.055913052230885</v>
+      </c>
+      <c r="C95">
+        <v>2.029037123828175</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
       <c r="A96">
-        <v>366.4787878787879</v>
+        <v>378.8515151515151</v>
       </c>
       <c r="B96">
-        <v>2.270242919190761</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
+        <v>2.055696503563432</v>
+      </c>
+      <c r="C96">
+        <v>2.02865972490488</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97">
-        <v>370.3030303030304</v>
+        <v>382.8212121212121</v>
       </c>
       <c r="B97">
-        <v>2.271408833114574</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
+        <v>2.055482234613657</v>
+      </c>
+      <c r="C97">
+        <v>2.028286312050721</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98">
-        <v>374.1272727272728</v>
+        <v>386.7909090909091</v>
       </c>
       <c r="B98">
-        <v>2.272563357474596</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
+        <v>2.055270198111979</v>
+      </c>
+      <c r="C98">
+        <v>2.027916802482086</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
       <c r="A99">
-        <v>377.9515151515152</v>
+        <v>390.7606060606061</v>
       </c>
       <c r="B99">
-        <v>2.273706718263973</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
+        <v>2.055060348241592</v>
+      </c>
+      <c r="C99">
+        <v>2.027551115962327</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
       <c r="A100">
-        <v>381.7757575757576</v>
+        <v>394.730303030303</v>
       </c>
       <c r="B100">
-        <v>2.274839134760976</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
+        <v>2.054852640579587</v>
+      </c>
+      <c r="C100">
+        <v>2.027189174698451</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
       <c r="A101">
-        <v>385.6</v>
+        <v>398.7</v>
       </c>
       <c r="B101">
-        <v>2.27596081979347</v>
+        <v>2.054647032041022</v>
+      </c>
+      <c r="C101">
+        <v>2.026830903242986</v>
       </c>
     </row>
   </sheetData>
@@ -2808,25 +3419,25 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="C2">
-        <v>0.8432740427115677</v>
+        <v>1.28279209365959</v>
       </c>
       <c r="D2">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="E2">
-        <v>0.4</v>
+        <v>0.5174724898753341</v>
       </c>
       <c r="F2">
-        <v>0.8450980400142568</v>
+        <v>0.7558748556724915</v>
       </c>
       <c r="G2">
-        <v>0.5314789170422551</v>
+        <v>0.4313637641589874</v>
       </c>
       <c r="H2">
-        <v>0.6029344684253471</v>
+        <v>0.5045342080399042</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2834,25 +3445,25 @@
         <v>125</v>
       </c>
       <c r="B3">
-        <v>18.6</v>
+        <v>15.5</v>
       </c>
       <c r="C3">
-        <v>2.028683207293725</v>
+        <v>2.982355519458477</v>
       </c>
       <c r="D3">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="E3">
-        <v>0.6506407098647712</v>
+        <v>1.002773930432755</v>
       </c>
       <c r="F3">
-        <v>1.269512944217916</v>
+        <v>1.190331698170291</v>
       </c>
       <c r="G3">
-        <v>0.8864907251724818</v>
+        <v>0.8129133566428556</v>
       </c>
       <c r="H3">
-        <v>0.8545169132390489</v>
+        <v>0.7789234929936251</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2860,25 +3471,25 @@
         <v>188</v>
       </c>
       <c r="B4">
-        <v>34.6</v>
+        <v>46.5</v>
       </c>
       <c r="C4">
-        <v>7.126164622166838</v>
+        <v>7.473285756613352</v>
       </c>
       <c r="D4">
-        <v>10.9</v>
+        <v>12.7</v>
       </c>
       <c r="E4">
-        <v>1.601735170231195</v>
+        <v>1.106044001535804</v>
       </c>
       <c r="F4">
-        <v>1.539076098792777</v>
+        <v>1.667452952889954</v>
       </c>
       <c r="G4">
-        <v>1.037426497940624</v>
+        <v>1.103803720955957</v>
       </c>
       <c r="H4">
-        <v>1.014307148661824</v>
+        <v>1.080258279588483</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2886,25 +3497,25 @@
         <v>251</v>
       </c>
       <c r="B5">
-        <v>66.5</v>
+        <v>63.7</v>
       </c>
       <c r="C5">
-        <v>11.36588462607875</v>
+        <v>11.87906655517268</v>
       </c>
       <c r="D5">
-        <v>17.1</v>
+        <v>16</v>
       </c>
       <c r="E5">
-        <v>1.858613581260086</v>
+        <v>1.813529401164726</v>
       </c>
       <c r="F5">
-        <v>1.822821645303105</v>
+        <v>1.80413943233535</v>
       </c>
       <c r="G5">
-        <v>1.232996110392154</v>
+        <v>1.204119982655925</v>
       </c>
       <c r="H5">
-        <v>1.182504348121655</v>
+        <v>1.166585163387197</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2912,25 +3523,25 @@
         <v>314</v>
       </c>
       <c r="B6">
-        <v>102.7</v>
+        <v>111</v>
       </c>
       <c r="C6">
-        <v>16.29863661646444</v>
+        <v>13.88684429395118</v>
       </c>
       <c r="D6">
-        <v>21.3</v>
+        <v>23.7</v>
       </c>
       <c r="E6">
-        <v>1.84421015914974</v>
+        <v>1.612796053787059</v>
       </c>
       <c r="F6">
-        <v>2.011570443597278</v>
+        <v>2.045322978786658</v>
       </c>
       <c r="G6">
-        <v>1.328379603438738</v>
+        <v>1.374748346010104</v>
       </c>
       <c r="H6">
-        <v>1.294389872546382</v>
+        <v>1.318909109933653</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2938,25 +3549,25 @@
         <v>376</v>
       </c>
       <c r="B7">
-        <v>159.9</v>
+        <v>163.4</v>
       </c>
       <c r="C7">
-        <v>20.1132626227903</v>
+        <v>11.71153277756588</v>
       </c>
       <c r="D7">
-        <v>26.3</v>
+        <v>28.2</v>
       </c>
       <c r="E7">
-        <v>1.856220772310114</v>
+        <v>0.8406346808612327</v>
       </c>
       <c r="F7">
-        <v>2.203848463746235</v>
+        <v>2.213252052196397</v>
       </c>
       <c r="G7">
-        <v>1.419955748489758</v>
+        <v>1.450249108319361</v>
       </c>
       <c r="H7">
-        <v>1.408367430624314</v>
+        <v>1.424967833996843</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2964,25 +3575,25 @@
         <v>439</v>
       </c>
       <c r="B8">
-        <v>195.5</v>
+        <v>203</v>
       </c>
       <c r="C8">
-        <v>21.28549323417764</v>
+        <v>20.33988965336614</v>
       </c>
       <c r="D8">
-        <v>28.8</v>
+        <v>30.4</v>
       </c>
       <c r="E8">
-        <v>1.171893055416463</v>
+        <v>1.32664991614216</v>
       </c>
       <c r="F8">
-        <v>2.291146761731885</v>
+        <v>2.307496037913213</v>
       </c>
       <c r="G8">
-        <v>1.459392487759231</v>
+        <v>1.482873583608754</v>
       </c>
       <c r="H8">
-        <v>1.460115658638394</v>
+        <v>1.484489372898965</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2990,25 +3601,25 @@
         <v>502</v>
       </c>
       <c r="B9">
-        <v>258.4</v>
+        <v>234.3</v>
       </c>
       <c r="C9">
-        <v>21.7011008425328</v>
+        <v>25.92169833256387</v>
       </c>
       <c r="D9">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="E9">
-        <v>0.9213516640723501</v>
+        <v>0.7571877794400363</v>
       </c>
       <c r="F9">
-        <v>2.412292509323046</v>
+        <v>2.369772288596963</v>
       </c>
       <c r="G9">
-        <v>1.526339277389844</v>
+        <v>1.521138083704036</v>
       </c>
       <c r="H9">
-        <v>1.531927800615252</v>
+        <v>1.523821095231775</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -3016,25 +3627,25 @@
         <v>565</v>
       </c>
       <c r="B10">
-        <v>293.9</v>
+        <v>274.2</v>
       </c>
       <c r="C10">
-        <v>26.76126969251563</v>
+        <v>24.15082239225451</v>
       </c>
       <c r="D10">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="E10">
-        <v>0.8465616732800195</v>
+        <v>0.5617433182117572</v>
       </c>
       <c r="F10">
-        <v>2.468199586072612</v>
+        <v>2.438067450453494</v>
       </c>
       <c r="G10">
-        <v>1.537819095073274</v>
+        <v>1.539076098792777</v>
       </c>
       <c r="H10">
-        <v>1.56506810485936</v>
+        <v>1.566954172662146</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3042,25 +3653,25 @@
         <v>628</v>
       </c>
       <c r="B11">
-        <v>385.6</v>
+        <v>398.7</v>
       </c>
       <c r="C11">
-        <v>27.37038139627904</v>
+        <v>22.06356977261637</v>
       </c>
       <c r="D11">
-        <v>38.8</v>
+        <v>39.7</v>
       </c>
       <c r="E11">
-        <v>0.9043106644167023</v>
+        <v>0.6333333333333332</v>
       </c>
       <c r="F11">
-        <v>2.586137025230793</v>
+        <v>2.600646235662394</v>
       </c>
       <c r="G11">
-        <v>1.588831725594207</v>
+        <v>1.598790506763115</v>
       </c>
       <c r="H11">
-        <v>1.634978442560989</v>
+        <v>1.669633822879281</v>
       </c>
     </row>
   </sheetData>
@@ -3070,815 +3681,2535 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2">
+        <v>5.7</v>
+      </c>
+      <c r="B2">
+        <v>23.23728125074058</v>
+      </c>
+      <c r="C2">
+        <v>23.54769476012652</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>9.66969696969697</v>
+      </c>
+      <c r="B3">
+        <v>23.11478905259195</v>
+      </c>
+      <c r="C3">
+        <v>23.33309156950662</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>13.63939393939394</v>
+      </c>
+      <c r="B4">
+        <v>23.03541879263946</v>
+      </c>
+      <c r="C4">
+        <v>23.1942252093151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>17.60909090909091</v>
+      </c>
+      <c r="B5">
+        <v>22.9766492024461</v>
+      </c>
+      <c r="C5">
+        <v>23.09149805030064</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>21.57878787878788</v>
+      </c>
+      <c r="B6">
+        <v>22.92998615842983</v>
+      </c>
+      <c r="C6">
+        <v>23.00999137434822</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>25.54848484848485</v>
+      </c>
+      <c r="B7">
+        <v>22.8912976026929</v>
+      </c>
+      <c r="C7">
+        <v>22.94245335998642</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>29.51818181818182</v>
+      </c>
+      <c r="B8">
+        <v>22.85825993309376</v>
+      </c>
+      <c r="C8">
+        <v>22.88480851376764</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>33.48787878787879</v>
+      </c>
+      <c r="B9">
+        <v>22.82943622278879</v>
+      </c>
+      <c r="C9">
+        <v>22.83453779432407</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>37.45757575757576</v>
+      </c>
+      <c r="B10">
+        <v>22.80387576771889</v>
+      </c>
+      <c r="C10">
+        <v>22.78997526188895</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>41.42727272727273</v>
+      </c>
+      <c r="B11">
+        <v>22.78091688717539</v>
+      </c>
+      <c r="C11">
+        <v>22.74996187544309</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>45.3969696969697</v>
+      </c>
+      <c r="B12">
+        <v>22.76008053188621</v>
+      </c>
+      <c r="C12">
+        <v>22.71365878409616</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>49.36666666666667</v>
+      </c>
+      <c r="B13">
+        <v>22.74100873402203</v>
+      </c>
+      <c r="C13">
+        <v>22.68043934930839</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>53.33636363636364</v>
+      </c>
+      <c r="B14">
+        <v>22.72342697598189</v>
+      </c>
+      <c r="C14">
+        <v>22.64982314841733</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>57.30606060606061</v>
+      </c>
+      <c r="B15">
+        <v>22.70712012594415</v>
+      </c>
+      <c r="C15">
+        <v>22.62143378293996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>61.27575757575758</v>
+      </c>
+      <c r="B16">
+        <v>22.6919164647113</v>
+      </c>
+      <c r="C16">
+        <v>22.59497088033887</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>65.24545454545455</v>
+      </c>
+      <c r="B17">
+        <v>22.67767674451865</v>
+      </c>
+      <c r="C17">
+        <v>22.57019092049585</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>69.21515151515152</v>
+      </c>
+      <c r="B18">
+        <v>22.66428649018615</v>
+      </c>
+      <c r="C18">
+        <v>22.54689374707903</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>73.18484848484849</v>
+      </c>
+      <c r="B19">
+        <v>22.65165045407648</v>
+      </c>
+      <c r="C19">
+        <v>22.52491285443671</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>77.15454545454546</v>
+      </c>
+      <c r="B20">
+        <v>22.63968854011957</v>
+      </c>
+      <c r="C20">
+        <v>22.50410824918678</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>81.12424242424242</v>
+      </c>
+      <c r="B21">
+        <v>22.62833275337116</v>
+      </c>
+      <c r="C21">
+        <v>22.48436110882851</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>85.09393939393939</v>
+      </c>
+      <c r="B22">
+        <v>22.61752488031997</v>
+      </c>
+      <c r="C22">
+        <v>22.4655697206043</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>89.06363636363636</v>
+      </c>
+      <c r="B23">
+        <v>22.60721469949649</v>
+      </c>
+      <c r="C23">
+        <v>22.44764634927947</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>93.03333333333333</v>
+      </c>
+      <c r="B24">
+        <v>22.59735858327855</v>
+      </c>
+      <c r="C24">
+        <v>22.43051479006519</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>97.0030303030303</v>
+      </c>
+      <c r="B25">
+        <v>22.5879183925755</v>
+      </c>
+      <c r="C25">
+        <v>22.41410843441196</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>100.9727272727273</v>
+      </c>
+      <c r="B26">
+        <v>22.57886059374052</v>
+      </c>
+      <c r="C26">
+        <v>22.39836872489992</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>104.9424242424243</v>
+      </c>
+      <c r="B27">
+        <v>22.57015554617496</v>
+      </c>
+      <c r="C27">
+        <v>22.38324390895032</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>108.9121212121212</v>
+      </c>
+      <c r="B28">
+        <v>22.56177692251195</v>
+      </c>
+      <c r="C28">
+        <v>22.36868802460624</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>112.8818181818182</v>
+      </c>
+      <c r="B29">
+        <v>22.55370123283812</v>
+      </c>
+      <c r="C29">
+        <v>22.35466006840042</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>116.8515151515152</v>
+      </c>
+      <c r="B30">
+        <v>22.54590743133172</v>
+      </c>
+      <c r="C30">
+        <v>22.34112330745037</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>120.8212121212121</v>
+      </c>
+      <c r="B31">
+        <v>22.53837658876168</v>
+      </c>
+      <c r="C31">
+        <v>22.32804470679577</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>124.7909090909091</v>
+      </c>
+      <c r="B32">
+        <v>22.53109161804628</v>
+      </c>
+      <c r="C32">
+        <v>22.31539444956805</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>128.7606060606061</v>
+      </c>
+      <c r="B33">
+        <v>22.52403704288124</v>
+      </c>
+      <c r="C33">
+        <v>22.30314553250537</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>132.730303030303</v>
+      </c>
+      <c r="B34">
+        <v>22.51719880157489</v>
+      </c>
+      <c r="C34">
+        <v>22.29127342305207</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>136.7</v>
+      </c>
+      <c r="B35">
+        <v>22.5105640798526</v>
+      </c>
+      <c r="C35">
+        <v>22.27975576712634</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>140.669696969697</v>
+      </c>
+      <c r="B36">
+        <v>22.50412116764502</v>
+      </c>
+      <c r="C36">
+        <v>22.2685721388323</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>144.6393939393939</v>
+      </c>
+      <c r="B37">
+        <v>22.49785933584783</v>
+      </c>
+      <c r="C37">
+        <v>22.25770382509587</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>148.6090909090909</v>
+      </c>
+      <c r="B38">
+        <v>22.49176872980192</v>
+      </c>
+      <c r="C38">
+        <v>22.24713363953722</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>152.5787878787879</v>
+      </c>
+      <c r="B39">
+        <v>22.4858402768446</v>
+      </c>
+      <c r="C39">
+        <v>22.23684576094422</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>156.5484848484848</v>
+      </c>
+      <c r="B40">
+        <v>22.48006560575909</v>
+      </c>
+      <c r="C40">
+        <v>22.22682559254701</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>160.5181818181818</v>
+      </c>
+      <c r="B41">
+        <v>22.47443697633119</v>
+      </c>
+      <c r="C41">
+        <v>22.2170596389605</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>164.4878787878788</v>
+      </c>
+      <c r="B42">
+        <v>22.46894721752903</v>
+      </c>
+      <c r="C42">
+        <v>22.20753539819945</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>168.4575757575757</v>
+      </c>
+      <c r="B43">
+        <v>22.46358967306959</v>
+      </c>
+      <c r="C43">
+        <v>22.19824126660407</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>172.4272727272727</v>
+      </c>
+      <c r="B44">
+        <v>22.45835815333805</v>
+      </c>
+      <c r="C44">
+        <v>22.18916645486793</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <v>176.3969696969697</v>
+      </c>
+      <c r="B45">
+        <v>22.45324689279048</v>
+      </c>
+      <c r="C45">
+        <v>22.18030091364841</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>180.3666666666666</v>
+      </c>
+      <c r="B46">
+        <v>22.44825051210665</v>
+      </c>
+      <c r="C46">
+        <v>22.17163526747708</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>184.3363636363636</v>
+      </c>
+      <c r="B47">
+        <v>22.4433639844711</v>
+      </c>
+      <c r="C47">
+        <v>22.16316075588352</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>188.3060606060606</v>
+      </c>
+      <c r="B48">
+        <v>22.43858260545399</v>
+      </c>
+      <c r="C48">
+        <v>22.15486918080816</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>192.2757575757576</v>
+      </c>
+      <c r="B49">
+        <v>22.43390196604017</v>
+      </c>
+      <c r="C49">
+        <v>22.14675285951521</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
+        <v>196.2454545454545</v>
+      </c>
+      <c r="B50">
+        <v>22.42931792841982</v>
+      </c>
+      <c r="C50">
+        <v>22.13880458232979</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>200.2151515151515</v>
+      </c>
+      <c r="B51">
+        <v>22.42482660420833</v>
+      </c>
+      <c r="C51">
+        <v>22.13101757461818</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>204.1848484848485</v>
+      </c>
+      <c r="B52">
+        <v>22.42042433480854</v>
+      </c>
+      <c r="C52">
+        <v>22.12338546251031</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
+        <v>208.1545454545455</v>
+      </c>
+      <c r="B53">
+        <v>22.41610767366764</v>
+      </c>
+      <c r="C53">
+        <v>22.11590224193109</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <v>212.1242424242424</v>
+      </c>
+      <c r="B54">
+        <v>22.41187337021341</v>
+      </c>
+      <c r="C54">
+        <v>22.10856225056479</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>216.0939393939394</v>
+      </c>
+      <c r="B55">
+        <v>22.40771835528279</v>
+      </c>
+      <c r="C55">
+        <v>22.10136014242535</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>220.0636363636364</v>
+      </c>
+      <c r="B56">
+        <v>22.40363972787929</v>
+      </c>
+      <c r="C56">
+        <v>22.09429086474736</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57">
+        <v>224.0333333333333</v>
+      </c>
+      <c r="B57">
+        <v>22.3996347431168</v>
+      </c>
+      <c r="C57">
+        <v>22.08734963694832</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58">
+        <v>228.0030303030303</v>
+      </c>
+      <c r="B58">
+        <v>22.39570080122415</v>
+      </c>
+      <c r="C58">
+        <v>22.08053193144324</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59">
+        <v>231.9727272727273</v>
+      </c>
+      <c r="B59">
+        <v>22.39183543750067</v>
+      </c>
+      <c r="C59">
+        <v>22.0738334561195</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60">
+        <v>235.9424242424242</v>
+      </c>
+      <c r="B60">
+        <v>22.38803631312563</v>
+      </c>
+      <c r="C60">
+        <v>22.06725013830244</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61">
+        <v>239.9121212121212</v>
+      </c>
+      <c r="B61">
+        <v>22.38430120673597</v>
+      </c>
+      <c r="C61">
+        <v>22.06077811006212</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62">
+        <v>243.8818181818182</v>
+      </c>
+      <c r="B62">
+        <v>22.38062800669653</v>
+      </c>
+      <c r="C62">
+        <v>22.05441369472898</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63">
+        <v>247.8515151515151</v>
+      </c>
+      <c r="B63">
+        <v>22.37701470399553</v>
+      </c>
+      <c r="C63">
+        <v>22.04815339450092</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
+        <v>251.8212121212121</v>
+      </c>
+      <c r="B64">
+        <v>22.37345938570572</v>
+      </c>
+      <c r="C64">
+        <v>22.04199387903757</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
+        <v>255.7909090909091</v>
+      </c>
+      <c r="B65">
+        <v>22.36996022895784</v>
+      </c>
+      <c r="C65">
+        <v>22.03593197494894</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66">
+        <v>259.7606060606061</v>
+      </c>
+      <c r="B66">
+        <v>22.36651549537914</v>
+      </c>
+      <c r="C66">
+        <v>22.02996465609554</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67">
+        <v>263.730303030303</v>
+      </c>
+      <c r="B67">
+        <v>22.36312352595447</v>
+      </c>
+      <c r="C67">
+        <v>22.02408903462597</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68">
+        <v>267.7</v>
+      </c>
+      <c r="B68">
+        <v>22.35978273627203</v>
+      </c>
+      <c r="C68">
+        <v>22.01830235268589</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69">
+        <v>271.669696969697</v>
+      </c>
+      <c r="B69">
+        <v>22.35649161211969</v>
+      </c>
+      <c r="C69">
+        <v>22.01260197473865</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70">
+        <v>275.6393939393939</v>
+      </c>
+      <c r="B70">
+        <v>22.35324870540146</v>
+      </c>
+      <c r="C70">
+        <v>22.00698538044453</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71">
+        <v>279.6090909090909</v>
+      </c>
+      <c r="B71">
+        <v>22.35005263034641</v>
+      </c>
+      <c r="C71">
+        <v>22.0014501580503</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72">
+        <v>283.5787878787879</v>
+      </c>
+      <c r="B72">
+        <v>22.34690205998541</v>
+      </c>
+      <c r="C72">
+        <v>21.99599399824609</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73">
+        <v>287.5484848484849</v>
+      </c>
+      <c r="B73">
+        <v>22.34379572287321</v>
+      </c>
+      <c r="C73">
+        <v>21.9906146884502</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74">
+        <v>291.5181818181818</v>
+      </c>
+      <c r="B74">
+        <v>22.34073240003575</v>
+      </c>
+      <c r="C74">
+        <v>21.98531010748694</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75">
+        <v>295.4878787878788</v>
+      </c>
+      <c r="B75">
+        <v>22.33771092212427</v>
+      </c>
+      <c r="C75">
+        <v>21.98007822062516</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76">
+        <v>299.4575757575757</v>
+      </c>
+      <c r="B76">
+        <v>22.33473016675971</v>
+      </c>
+      <c r="C76">
+        <v>21.97491707494881</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77">
+        <v>303.4272727272727</v>
+      </c>
+      <c r="B77">
+        <v>22.33178905605236</v>
+      </c>
+      <c r="C77">
+        <v>21.96982479503311</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78">
+        <v>307.3969696969697</v>
+      </c>
+      <c r="B78">
+        <v>22.32888655428296</v>
+      </c>
+      <c r="C78">
+        <v>21.9647995789024</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79">
+        <v>311.3666666666667</v>
+      </c>
+      <c r="B79">
+        <v>22.32602166573295</v>
+      </c>
+      <c r="C79">
+        <v>21.9598396942481</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80">
+        <v>315.3363636363636</v>
+      </c>
+      <c r="B80">
+        <v>22.32319343265235</v>
+      </c>
+      <c r="C80">
+        <v>21.95494347488678</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81">
+        <v>319.3060606060606</v>
+      </c>
+      <c r="B81">
+        <v>22.3204009333551</v>
+      </c>
+      <c r="C81">
+        <v>21.9501093174404</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82">
+        <v>323.2757575757576</v>
+      </c>
+      <c r="B82">
+        <v>22.31764328043223</v>
+      </c>
+      <c r="C82">
+        <v>21.94533567822218</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83">
+        <v>327.2454545454545</v>
+      </c>
+      <c r="B83">
+        <v>22.31491961907429</v>
+      </c>
+      <c r="C83">
+        <v>21.94062107031298</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84">
+        <v>331.2151515151515</v>
+      </c>
+      <c r="B84">
+        <v>22.3122291254952</v>
+      </c>
+      <c r="C84">
+        <v>21.93596406081443</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85">
+        <v>335.1848484848485</v>
+      </c>
+      <c r="B85">
+        <v>22.30957100545004</v>
+      </c>
+      <c r="C85">
+        <v>21.9313632682661</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86">
+        <v>339.1545454545454</v>
+      </c>
+      <c r="B86">
+        <v>22.30694449284044</v>
+      </c>
+      <c r="C86">
+        <v>21.92681736021511</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87">
+        <v>343.1242424242424</v>
+      </c>
+      <c r="B87">
+        <v>22.3043488484011</v>
+      </c>
+      <c r="C87">
+        <v>21.92232505092753</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88">
+        <v>347.0939393939394</v>
+      </c>
+      <c r="B88">
+        <v>22.30178335846218</v>
+      </c>
+      <c r="C88">
+        <v>21.91788509923179</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89">
+        <v>351.0636363636364</v>
+      </c>
+      <c r="B89">
+        <v>22.29924733378201</v>
+      </c>
+      <c r="C89">
+        <v>21.91349630648493</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90">
+        <v>355.0333333333333</v>
+      </c>
+      <c r="B90">
+        <v>22.29674010844577</v>
+      </c>
+      <c r="C90">
+        <v>21.90915751465361</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91">
+        <v>359.0030303030303</v>
+      </c>
+      <c r="B91">
+        <v>22.29426103882533</v>
+      </c>
+      <c r="C91">
+        <v>21.90486760450199</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92">
+        <v>362.9727272727272</v>
+      </c>
+      <c r="B92">
+        <v>22.29180950259651</v>
+      </c>
+      <c r="C92">
+        <v>21.9006254938796</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93">
+        <v>366.9424242424242</v>
+      </c>
+      <c r="B93">
+        <v>22.28938489780985</v>
+      </c>
+      <c r="C93">
+        <v>21.89643013610247</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94">
+        <v>370.9121212121212</v>
+      </c>
+      <c r="B94">
+        <v>22.2869866420115</v>
+      </c>
+      <c r="C94">
+        <v>21.89228051842165</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95">
+        <v>374.8818181818182</v>
+      </c>
+      <c r="B95">
+        <v>22.28461417141099</v>
+      </c>
+      <c r="C95">
+        <v>21.88817566057347</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96">
+        <v>378.8515151515151</v>
+      </c>
+      <c r="B96">
+        <v>22.28226694009287</v>
+      </c>
+      <c r="C96">
+        <v>21.88411461340629</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97">
+        <v>382.8212121212121</v>
+      </c>
+      <c r="B97">
+        <v>22.2799444192696</v>
+      </c>
+      <c r="C97">
+        <v>21.88009645757907</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98">
+        <v>386.7909090909091</v>
+      </c>
+      <c r="B98">
+        <v>22.27764609657301</v>
+      </c>
+      <c r="C98">
+        <v>21.87612030232725</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99">
+        <v>390.7606060606061</v>
+      </c>
+      <c r="B99">
+        <v>22.27537147538199</v>
+      </c>
+      <c r="C99">
+        <v>21.87218528429171</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100">
+        <v>394.730303030303</v>
+      </c>
+      <c r="B100">
+        <v>22.27312007418426</v>
+      </c>
+      <c r="C100">
+        <v>21.86829056640719</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101">
+        <v>398.7</v>
+      </c>
+      <c r="B101">
+        <v>22.27089142597013</v>
+      </c>
+      <c r="C101">
+        <v>21.86443533684639</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2">
+        <v>62</v>
+      </c>
       <c r="B2">
-        <v>5.163817749635423</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>5.7</v>
+      </c>
+      <c r="C2">
+        <v>1.28279209365959</v>
+      </c>
+      <c r="D2">
+        <v>0.505385</v>
+      </c>
+      <c r="E2">
+        <v>0.09240115547918699</v>
+      </c>
+      <c r="F2">
+        <v>0.7558748556724915</v>
+      </c>
+      <c r="G2">
+        <v>-0.2963776522338775</v>
+      </c>
+      <c r="H2">
+        <v>-0.2669125952075939</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3">
-        <v>10.82424242424242</v>
+        <v>125</v>
       </c>
       <c r="B3">
-        <v>6.453185754086699</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>15.5</v>
+      </c>
+      <c r="C3">
+        <v>2.982355519458477</v>
+      </c>
+      <c r="D3">
+        <v>0.185852</v>
+      </c>
+      <c r="E3">
+        <v>0.03142981237968534</v>
+      </c>
+      <c r="F3">
+        <v>1.190331698170291</v>
+      </c>
+      <c r="G3">
+        <v>-0.7308327609912295</v>
+      </c>
+      <c r="H3">
+        <v>-0.726825497597666</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4">
-        <v>14.64848484848485</v>
+        <v>188</v>
       </c>
       <c r="B4">
-        <v>7.53297548136146</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>46.5</v>
+      </c>
+      <c r="C4">
+        <v>7.473285756613352</v>
+      </c>
+      <c r="D4">
+        <v>0.061074</v>
+      </c>
+      <c r="E4">
+        <v>0.01132705641864254</v>
+      </c>
+      <c r="F4">
+        <v>1.667452952889954</v>
+      </c>
+      <c r="G4">
+        <v>-1.214143635251576</v>
+      </c>
+      <c r="H4">
+        <v>-1.23190264125256</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5">
-        <v>18.47272727272728</v>
+        <v>251</v>
       </c>
       <c r="B5">
-        <v>8.481677164694858</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>63.7</v>
+      </c>
+      <c r="C5">
+        <v>11.87906655517268</v>
+      </c>
+      <c r="D5">
+        <v>0.047158</v>
+      </c>
+      <c r="E5">
+        <v>0.008391846280765633</v>
+      </c>
+      <c r="F5">
+        <v>1.80413943233535</v>
+      </c>
+      <c r="G5">
+        <v>-1.32644462188446</v>
+      </c>
+      <c r="H5">
+        <v>-1.376597969602767</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6">
-        <v>22.2969696969697</v>
+        <v>314</v>
       </c>
       <c r="B6">
-        <v>9.338320214544426</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>111</v>
+      </c>
+      <c r="C6">
+        <v>13.88684429395118</v>
+      </c>
+      <c r="D6">
+        <v>0.025877</v>
+      </c>
+      <c r="E6">
+        <v>0.006236507044100176</v>
+      </c>
+      <c r="F6">
+        <v>2.045322978786658</v>
+      </c>
+      <c r="G6">
+        <v>-1.587086074176692</v>
+      </c>
+      <c r="H6">
+        <v>-1.631913144798133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7">
-        <v>26.12121212121212</v>
+        <v>376</v>
       </c>
       <c r="B7">
-        <v>10.12568923136956</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>163.4</v>
+      </c>
+      <c r="C7">
+        <v>11.71153277756588</v>
+      </c>
+      <c r="D7">
+        <v>0.013929</v>
+      </c>
+      <c r="E7">
+        <v>0.0007962180745387673</v>
+      </c>
+      <c r="F7">
+        <v>2.213252052196397</v>
+      </c>
+      <c r="G7">
+        <v>-1.856080061614164</v>
+      </c>
+      <c r="H7">
+        <v>-1.809681659395621</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8">
-        <v>29.94545454545455</v>
+        <v>439</v>
       </c>
       <c r="B8">
-        <v>10.85846479339515</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>203</v>
+      </c>
+      <c r="C8">
+        <v>20.33988965336614</v>
+      </c>
+      <c r="D8">
+        <v>0.012272</v>
+      </c>
+      <c r="E8">
+        <v>0.001654819761921051</v>
+      </c>
+      <c r="F8">
+        <v>2.307496037913213</v>
+      </c>
+      <c r="G8">
+        <v>-1.911084653395094</v>
+      </c>
+      <c r="H8">
+        <v>-1.909447667808871</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9">
-        <v>33.76969696969697</v>
+        <v>502</v>
       </c>
       <c r="B9">
-        <v>11.54676571690574</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>234.3</v>
+      </c>
+      <c r="C9">
+        <v>25.92169833256387</v>
+      </c>
+      <c r="D9">
+        <v>0.010571</v>
+      </c>
+      <c r="E9">
+        <v>0.001182195180350708</v>
+      </c>
+      <c r="F9">
+        <v>2.369772288596963</v>
+      </c>
+      <c r="G9">
+        <v>-1.97588392717323</v>
+      </c>
+      <c r="H9">
+        <v>-1.975372860832112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10">
-        <v>37.59393939393939</v>
+        <v>565</v>
       </c>
       <c r="B10">
-        <v>12.19791828663392</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>274.2</v>
+      </c>
+      <c r="C10">
+        <v>24.15082239225451</v>
+      </c>
+      <c r="D10">
+        <v>0.008608000000000001</v>
+      </c>
+      <c r="E10">
+        <v>0.0006645797335325703</v>
+      </c>
+      <c r="F10">
+        <v>2.438067450453494</v>
+      </c>
+      <c r="G10">
+        <v>-2.065097741677686</v>
+      </c>
+      <c r="H10">
+        <v>-2.047669630122368</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11">
-        <v>41.41818181818182</v>
+        <v>628</v>
       </c>
       <c r="B11">
-        <v>12.81742996488708</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>398.7</v>
+      </c>
+      <c r="C11">
+        <v>22.06356977261637</v>
+      </c>
+      <c r="D11">
+        <v>0.005847</v>
+      </c>
+      <c r="E11">
+        <v>0.0004215264589033</v>
+      </c>
+      <c r="F11">
+        <v>2.600646235662394</v>
+      </c>
+      <c r="G11">
+        <v>-2.233066906162716</v>
+      </c>
+      <c r="H11">
+        <v>-2.219774367943033</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>5.7</v>
+      </c>
+      <c r="B2">
+        <v>0.5056977773087862</v>
+      </c>
+      <c r="C2">
+        <v>0.5052779450312658</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>9.66969696969697</v>
+      </c>
+      <c r="B3">
+        <v>0.2972034523973348</v>
+      </c>
+      <c r="C3">
+        <v>0.298425992793763</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>13.63939393939394</v>
+      </c>
+      <c r="B4">
+        <v>0.2102936394996434</v>
+      </c>
+      <c r="C4">
+        <v>0.2117579924380368</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>17.60909090909091</v>
+      </c>
+      <c r="B5">
+        <v>0.1626508523061627</v>
+      </c>
+      <c r="C5">
+        <v>0.1640721597738324</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>21.57878787878788</v>
+      </c>
+      <c r="B6">
+        <v>0.1325764881257341</v>
+      </c>
+      <c r="C6">
+        <v>0.1338799731776548</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>25.54848484848485</v>
+      </c>
+      <c r="B7">
+        <v>0.1118699162893306</v>
+      </c>
+      <c r="C7">
+        <v>0.1130378392934138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>29.51818181818182</v>
+      </c>
+      <c r="B8">
+        <v>0.0967461827533924</v>
+      </c>
+      <c r="C8">
+        <v>0.09777900441871126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>33.48787878787879</v>
+      </c>
+      <c r="B9">
+        <v>0.08521688316364427</v>
+      </c>
+      <c r="C9">
+        <v>0.08612106955488623</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>37.45757575757576</v>
+      </c>
+      <c r="B10">
+        <v>0.07613743600608947</v>
+      </c>
+      <c r="C10">
+        <v>0.07692114396573625</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>41.42727272727273</v>
+      </c>
+      <c r="B11">
+        <v>0.06880245963754027</v>
+      </c>
+      <c r="C11">
+        <v>0.06947392609387121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12">
-        <v>45.24242424242425</v>
+        <v>45.3969696969697</v>
       </c>
       <c r="B12">
-        <v>13.40956554982373</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>0.06275358076017001</v>
+      </c>
+      <c r="C12">
+        <v>0.06332053237736522</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13">
-        <v>49.06666666666667</v>
+        <v>49.36666666666667</v>
       </c>
       <c r="B13">
-        <v>13.97770786644398</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>0.05768003415599605</v>
+      </c>
+      <c r="C13">
+        <v>0.05814950397897706</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14">
-        <v>52.8909090909091</v>
+        <v>53.33636363636364</v>
       </c>
       <c r="B14">
-        <v>14.52459400987826</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>0.05336368259624574</v>
+      </c>
+      <c r="C14">
+        <v>0.05374199178644751</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15">
-        <v>56.71515151515152</v>
+        <v>57.30606060606061</v>
       </c>
       <c r="B15">
-        <v>15.05247592774308</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>0.0496469047926025</v>
+      </c>
+      <c r="C15">
+        <v>0.04993970887053609</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16">
-        <v>60.53939393939395</v>
+        <v>61.27575757575758</v>
       </c>
       <c r="B16">
-        <v>15.56323301369378</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>0.04641297472189983</v>
+      </c>
+      <c r="C16">
+        <v>0.04662533129033453</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
-        <v>64.36363636363637</v>
+        <v>65.24545454545455</v>
       </c>
       <c r="B17">
-        <v>16.05845316161152</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>0.04357360899071557</v>
+      </c>
+      <c r="C17">
+        <v>0.04371004853830911</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
-        <v>68.18787878787879</v>
+        <v>69.21515151515152</v>
       </c>
       <c r="B18">
-        <v>16.5394924532003</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>0.04106080266559247</v>
+      </c>
+      <c r="C18">
+        <v>0.04112539493167587</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
-        <v>72.01212121212122</v>
+        <v>73.18484848484849</v>
       </c>
       <c r="B19">
-        <v>17.00751998670079</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>0.03882132421864745</v>
+      </c>
+      <c r="C19">
+        <v>0.03881773747599376</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20">
-        <v>75.83636363636364</v>
+        <v>77.15454545454546</v>
       </c>
       <c r="B20">
-        <v>17.46355213365126</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>0.03681291126212515</v>
+      </c>
+      <c r="C20">
+        <v>0.03674446403935704</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21">
-        <v>79.66060606060607</v>
+        <v>81.12424242424242</v>
       </c>
       <c r="B21">
-        <v>17.90847912105023</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>0.03500158410855748</v>
+      </c>
+      <c r="C21">
+        <v>0.03487128978925232</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
-        <v>83.4848484848485</v>
+        <v>85.09393939393939</v>
       </c>
       <c r="B22">
-        <v>18.34308594194322</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>0.03335971188132852</v>
+      </c>
+      <c r="C22">
+        <v>0.03317031695320553</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
-        <v>87.30909090909091</v>
+        <v>89.06363636363636</v>
       </c>
       <c r="B23">
-        <v>18.7680690073346</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>0.03186459622161098</v>
+      </c>
+      <c r="C23">
+        <v>0.03161861302100871</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24">
-        <v>91.13333333333334</v>
+        <v>93.03333333333333</v>
       </c>
       <c r="B24">
-        <v>19.18404955418727</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>0.03049741788713007</v>
+      </c>
+      <c r="C24">
+        <v>0.03019715264084441</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25">
-        <v>94.95757575757577</v>
+        <v>97.0030303030303</v>
       </c>
       <c r="B25">
-        <v>19.59158455025334</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>0.02924244221606698</v>
+      </c>
+      <c r="C25">
+        <v>0.02889001909564014</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26">
-        <v>98.7818181818182</v>
+        <v>100.9727272727273</v>
       </c>
       <c r="B26">
-        <v>19.99117564446232</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>0.02808641216675835</v>
+      </c>
+      <c r="C26">
+        <v>0.02768379397271615</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27">
-        <v>102.6060606060606</v>
+        <v>104.9424242424243</v>
       </c>
       <c r="B27">
-        <v>20.38327657482548</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>0.02701807923015703</v>
+      </c>
+      <c r="C27">
+        <v>0.0265670852302643</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28">
-        <v>106.430303030303</v>
+        <v>108.9121212121212</v>
       </c>
       <c r="B28">
-        <v>20.76829934694127</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>0.0260278370135389</v>
+      </c>
+      <c r="C28">
+        <v>0.02553015837569837</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29">
-        <v>110.2545454545455</v>
+        <v>112.8818181818182</v>
       </c>
       <c r="B29">
-        <v>21.14661942372767</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>0.02510743220330831</v>
+      </c>
+      <c r="C29">
+        <v>0.0245646453918245</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30">
-        <v>114.0787878787879</v>
+        <v>116.8515151515152</v>
       </c>
       <c r="B30">
-        <v>21.51858011323896</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>0.02424973449274599</v>
+      </c>
+      <c r="C30">
+        <v>0.02366331293593199</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31">
-        <v>117.9030303030303</v>
+        <v>120.8212121212121</v>
       </c>
       <c r="B31">
-        <v>21.88449630106237</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>0.0234485519036103</v>
+      </c>
+      <c r="C31">
+        <v>0.0228198761899698</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32">
-        <v>121.7272727272727</v>
+        <v>124.7909090909091</v>
       </c>
       <c r="B32">
-        <v>22.24465764316719</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>0.0226984813862734</v>
+      </c>
+      <c r="C32">
+        <v>0.02202884820435457</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33">
-        <v>125.5515151515152</v>
+        <v>128.7606060606061</v>
       </c>
       <c r="B33">
-        <v>22.59933131161421</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>0.02199478707945719</v>
+      </c>
+      <c r="C33">
+        <v>0.02128541708158832</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34">
-        <v>129.3757575757576</v>
+        <v>132.730303030303</v>
       </c>
       <c r="B34">
-        <v>22.94876436738728</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>0.02133330043469723</v>
+      </c>
+      <c r="C34">
+        <v>0.02058534517595512</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
-        <v>133.2</v>
+        <v>136.7</v>
       </c>
       <c r="B35">
-        <v>23.29318582045486</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>0.02071033775773988</v>
+      </c>
+      <c r="C35">
+        <v>0.01992488583761655</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36">
-        <v>137.0242424242424</v>
+        <v>140.669696969697</v>
       </c>
       <c r="B36">
-        <v>23.63280842604031</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>0.02012263172383806</v>
+      </c>
+      <c r="C36">
+        <v>0.01930071423827463</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
-        <v>140.8484848484849</v>
+        <v>144.6393939393939</v>
       </c>
       <c r="B37">
-        <v>23.9678302572632</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>0.01956727418034966</v>
+      </c>
+      <c r="C37">
+        <v>0.01870986957536598</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38">
-        <v>144.6727272727273</v>
+        <v>148.6090909090909</v>
       </c>
       <c r="B38">
-        <v>24.29843608727928</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>0.01904166812452631</v>
+      </c>
+      <c r="C38">
+        <v>0.01814970652898749</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39">
-        <v>148.4969696969697</v>
+        <v>152.5787878787879</v>
       </c>
       <c r="B39">
-        <v>24.62479860839757</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>0.01854348718426942</v>
+      </c>
+      <c r="C39">
+        <v>0.01761785428790531</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40">
-        <v>152.3212121212121</v>
+        <v>156.5484848484848</v>
       </c>
       <c r="B40">
-        <v>24.94707951108655</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>0.01807064126907429</v>
+      </c>
+      <c r="C40">
+        <v>0.01711218180230317</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41">
-        <v>156.1454545454546</v>
+        <v>160.5181818181818</v>
       </c>
       <c r="B41">
-        <v>25.26543044206977</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>0.01762124732223262</v>
+      </c>
+      <c r="C41">
+        <v>0.0166307681863093</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42">
-        <v>159.969696969697</v>
+        <v>164.4878787878788</v>
       </c>
       <c r="B42">
-        <v>25.57999385767572</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>0.01719360431187291</v>
+      </c>
+      <c r="C42">
+        <v>0.01617187740111764</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43">
-        <v>163.7939393939394</v>
+        <v>168.4575757575757</v>
       </c>
       <c r="B43">
-        <v>25.89090378611295</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>0.01678617176110506</v>
+      </c>
+      <c r="C43">
+        <v>0.01573393651325609</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44">
-        <v>167.6181818181818</v>
+        <v>172.4272727272727</v>
       </c>
       <c r="B44">
-        <v>26.19828651028066</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>0.01639755124649473</v>
+      </c>
+      <c r="C44">
+        <v>0.01531551695238596</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45">
-        <v>171.4424242424243</v>
+        <v>176.3969696969697</v>
       </c>
       <c r="B45">
-        <v>26.5022611810149</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+        <v>0.01602647039691807</v>
+      </c>
+      <c r="C45">
+        <v>0.01491531829656868</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46">
-        <v>175.2666666666667</v>
+        <v>180.3666666666666</v>
       </c>
       <c r="B46">
-        <v>26.80294036924476</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>0.01567176900729336</v>
+      </c>
+      <c r="C46">
+        <v>0.01453215419598931</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47">
-        <v>179.0909090909091</v>
+        <v>184.3363636363636</v>
       </c>
       <c r="B47">
-        <v>27.10043056433873</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>0.0153323869481436</v>
+      </c>
+      <c r="C47">
+        <v>0.01416494011309272</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48">
-        <v>182.9151515151515</v>
+        <v>188.3060606060606</v>
       </c>
       <c r="B48">
-        <v>27.39483262491769</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
+        <v>0.01500735360578559</v>
+      </c>
+      <c r="C48">
+        <v>0.0138126826113578</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49">
-        <v>186.7393939393939</v>
+        <v>192.2757575757576</v>
       </c>
       <c r="B49">
-        <v>27.68624218756332</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>0.01469577863177229</v>
+      </c>
+      <c r="C49">
+        <v>0.01347446996912695</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50">
-        <v>190.5636363636364</v>
+        <v>196.2454545454545</v>
       </c>
       <c r="B50">
-        <v>27.97475003813272</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
+        <v>0.01439684381606251</v>
+      </c>
+      <c r="C50">
+        <v>0.0131494639310602</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51">
-        <v>194.3878787878788</v>
+        <v>200.2151515151515</v>
       </c>
       <c r="B51">
-        <v>28.26044244977933</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
+        <v>0.01410979592783848</v>
+      </c>
+      <c r="C51">
+        <v>0.01283689243948856</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52">
-        <v>198.2121212121212</v>
+        <v>204.1848484848485</v>
       </c>
       <c r="B52">
-        <v>28.54340149125916</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
+        <v>0.01383394039218348</v>
+      </c>
+      <c r="C52">
+        <v>0.01253604321245208</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53">
-        <v>202.0363636363637</v>
+        <v>208.1545454545455</v>
       </c>
       <c r="B53">
-        <v>28.82370530865525</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
+        <v>0.01356863569095109</v>
+      </c>
+      <c r="C53">
+        <v>0.01224625805551554</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54">
-        <v>205.8606060606061</v>
+        <v>212.1242424242424</v>
       </c>
       <c r="B54">
-        <v>29.10142838327003</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
+        <v>0.0133132883928869</v>
+      </c>
+      <c r="C54">
+        <v>0.01196692781134331</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55">
-        <v>209.6848484848485</v>
+        <v>216.0939393939394</v>
       </c>
       <c r="B55">
-        <v>29.37664176810544</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
+        <v>0.01306734873202478</v>
+      </c>
+      <c r="C55">
+        <v>0.01169748786511402</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56">
-        <v>213.5090909090909</v>
+        <v>220.0636363636364</v>
       </c>
       <c r="B56">
-        <v>29.64941330506505</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
+        <v>0.01283030666507384</v>
+      </c>
+      <c r="C56">
+        <v>0.01143741413566704</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57">
-        <v>217.3333333333333</v>
+        <v>224.0333333333333</v>
       </c>
       <c r="B57">
-        <v>29.91980782476586</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
+        <v>0.01260168834833945</v>
+      </c>
+      <c r="C57">
+        <v>0.01118621949220204</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58">
-        <v>221.1575757575758</v>
+        <v>228.0030303030303</v>
       </c>
       <c r="B58">
-        <v>30.18788733063255</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
+        <v>0.01238105298300907</v>
+      </c>
+      <c r="C58">
+        <v>0.01094345054472733</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
       <c r="A59">
-        <v>224.9818181818182</v>
+        <v>231.9727272727273</v>
       </c>
       <c r="B59">
-        <v>30.45371116875982</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
+        <v>0.01216798998464303</v>
+      </c>
+      <c r="C59">
+        <v>0.0107086847635385</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60">
-        <v>228.8060606060606</v>
+        <v>235.9424242424242</v>
       </c>
       <c r="B60">
-        <v>30.71733618486569</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
+        <v>0.01196211643865838</v>
+      </c>
+      <c r="C60">
+        <v>0.01048152788902204</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
       <c r="A61">
-        <v>232.6303030303031</v>
+        <v>239.9121212121212</v>
       </c>
       <c r="B61">
-        <v>30.9788168695153</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
+        <v>0.01176307480865541</v>
+      </c>
+      <c r="C61">
+        <v>0.0102616115981978</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62">
-        <v>236.4545454545455</v>
+        <v>243.8818181818182</v>
       </c>
       <c r="B62">
-        <v>31.23820549266953</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
+        <v>0.0115705308687561</v>
+      </c>
+      <c r="C62">
+        <v>0.01004859139878294</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
       <c r="A63">
-        <v>240.2787878787879</v>
+        <v>247.8515151515151</v>
       </c>
       <c r="B63">
-        <v>31.49555222850272</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
+        <v>0.01138417183482006</v>
+      </c>
+      <c r="C63">
+        <v>0.009842144725300579</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
       <c r="A64">
-        <v>244.1030303030303</v>
+        <v>251.8212121212121</v>
       </c>
       <c r="B64">
-        <v>31.75090527133618</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
+        <v>0.0112037046725758</v>
+      </c>
+      <c r="C64">
+        <v>0.009641969214965929</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65">
-        <v>247.9272727272728</v>
+        <v>255.7909090909091</v>
       </c>
       <c r="B65">
-        <v>32.00431094344887</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
+        <v>0.01102885456343321</v>
+      </c>
+      <c r="C65">
+        <v>0.009447781143844479</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66">
-        <v>251.7515151515152</v>
+        <v>259.7606060606061</v>
       </c>
       <c r="B66">
-        <v>32.25581379545041</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
+        <v>0.01085936351109659</v>
+      </c>
+      <c r="C66">
+        <v>0.009259314006159288</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67">
-        <v>255.5757575757576</v>
+        <v>263.730303030303</v>
       </c>
       <c r="B67">
-        <v>32.50545669983443</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
+        <v>0.01069498907413134</v>
+      </c>
+      <c r="C67">
+        <v>0.009076317221684166</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
       <c r="A68">
-        <v>259.4</v>
+        <v>267.7</v>
       </c>
       <c r="B68">
-        <v>32.75328093827024</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
+        <v>0.01053550321140008</v>
+      </c>
+      <c r="C68">
+        <v>0.008898554957944683</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
       <c r="A69">
-        <v>263.2242424242424</v>
+        <v>271.669696969697</v>
       </c>
       <c r="B69">
-        <v>32.99932628313801</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
+        <v>0.01038069122881448</v>
+      </c>
+      <c r="C69">
+        <v>0.008725805055499476</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
       <c r="A70">
-        <v>267.0484848484849</v>
+        <v>275.6393939393939</v>
       </c>
       <c r="B70">
-        <v>33.24363107376475</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
+        <v>0.01023035081718093</v>
+      </c>
+      <c r="C70">
+        <v>0.008557858045924212</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71">
-        <v>270.8727272727273</v>
+        <v>279.6090909090909</v>
       </c>
       <c r="B71">
-        <v>33.48623228777635</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
+        <v>0.01008429117208034</v>
+      </c>
+      <c r="C71">
+        <v>0.008394516253297861</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72">
-        <v>274.6969696969697</v>
+        <v>283.5787878787879</v>
       </c>
       <c r="B72">
-        <v>33.72716560794277</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
+        <v>0.009942332187737069</v>
+      </c>
+      <c r="C72">
+        <v>0.008235592971020264</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
       <c r="A73">
-        <v>278.5212121212122</v>
+        <v>287.5484848484849</v>
       </c>
       <c r="B73">
-        <v>33.96646548485983</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
+        <v>0.009804303717721665</v>
+      </c>
+      <c r="C73">
+        <v>0.008080911706691384</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
       <c r="A74">
-        <v>282.3454545454546</v>
+        <v>291.5181818181818</v>
       </c>
       <c r="B74">
-        <v>34.20416519578015</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
+        <v>0.009670044896111651</v>
+      </c>
+      <c r="C74">
+        <v>0.007930305488573729</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75">
-        <v>286.169696969697</v>
+        <v>295.4878787878788</v>
       </c>
       <c r="B75">
-        <v>34.44029689987875</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
+        <v>0.009539403513420528</v>
+      </c>
+      <c r="C75">
+        <v>0.007783616227854917</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
       <c r="A76">
-        <v>289.9939393939394</v>
+        <v>299.4575757575757</v>
       </c>
       <c r="B76">
-        <v>34.67489169021396</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
+        <v>0.009412235442208941</v>
+      </c>
+      <c r="C76">
+        <v>0.007640694131540011</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
       <c r="A77">
-        <v>293.8181818181819</v>
+        <v>303.4272727272727</v>
       </c>
       <c r="B77">
-        <v>34.90797964262221</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
+        <v>0.009288404107824532</v>
+      </c>
+      <c r="C77">
+        <v>0.007501397161343705</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
       <c r="A78">
-        <v>297.6424242424243</v>
+        <v>307.3969696969697</v>
       </c>
       <c r="B78">
-        <v>35.13958986176475</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
+        <v>0.009167780000187906</v>
+      </c>
+      <c r="C78">
+        <v>0.007365590534430309</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
       <c r="A79">
-        <v>301.4666666666667</v>
+        <v>311.3666666666667</v>
       </c>
       <c r="B79">
-        <v>35.36975052452706</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
+        <v>0.009050240222958658</v>
+      </c>
+      <c r="C79">
+        <v>0.007233146262272397</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
       <c r="A80">
-        <v>305.2909090909091</v>
+        <v>315.3363636363636</v>
       </c>
       <c r="B80">
-        <v>35.59848892095419</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
+        <v>0.008935668076784982</v>
+      </c>
+      <c r="C80">
+        <v>0.007103942724274172</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81">
-        <v>309.1151515151515</v>
+        <v>319.3060606060606</v>
       </c>
       <c r="B81">
-        <v>35.82583149289137</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
+        <v>0.008823952673668376</v>
+      </c>
+      <c r="C81">
+        <v>0.006977864273138717</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
       <c r="A82">
-        <v>312.939393939394</v>
+        <v>323.2757575757576</v>
       </c>
       <c r="B82">
-        <v>36.05180387048497</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
+        <v>0.008714988579766847</v>
+      </c>
+      <c r="C82">
+        <v>0.006854800869254762</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83">
-        <v>316.7636363636364</v>
+        <v>327.2454545454545</v>
       </c>
       <c r="B83">
-        <v>36.27643090668717</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
+        <v>0.008608675484219877</v>
+      </c>
+      <c r="C83">
+        <v>0.00673464774164264</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
       <c r="A84">
-        <v>320.5878787878788</v>
+        <v>331.2151515151515</v>
       </c>
       <c r="B84">
-        <v>36.4997367098959</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
+        <v>0.008504917891810354</v>
+      </c>
+      <c r="C84">
+        <v>0.00661730507323469</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
       <c r="A85">
-        <v>324.4121212121212</v>
+        <v>335.1848484848485</v>
       </c>
       <c r="B85">
-        <v>36.72174467485226</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
+        <v>0.008403624837485711</v>
+      </c>
+      <c r="C85">
+        <v>0.006502677708475952</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
       <c r="A86">
-        <v>328.2363636363636</v>
+        <v>339.1545454545454</v>
       </c>
       <c r="B86">
-        <v>36.9424775119074</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
+        <v>0.008304709620946002</v>
+      </c>
+      <c r="C86">
+        <v>0.006390674881419317</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
       <c r="A87">
-        <v>332.0606060606061</v>
+        <v>343.1242424242424</v>
       </c>
       <c r="B87">
-        <v>37.16195727476314</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
+        <v>0.00820808955967243</v>
+      </c>
+      <c r="C87">
+        <v>0.006281209962658055</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
       <c r="A88">
-        <v>335.8848484848485</v>
+        <v>347.0939393939394</v>
       </c>
       <c r="B88">
-        <v>37.38020538678244</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
+        <v>0.008113685758918937</v>
+      </c>
+      <c r="C88">
+        <v>0.006174200223590152</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
       <c r="A89">
-        <v>339.7090909090909</v>
+        <v>351.0636363636364</v>
       </c>
       <c r="B89">
-        <v>37.59724266595884</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
+        <v>0.008021422897323102</v>
+      </c>
+      <c r="C89">
+        <v>0.006069566616644783</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
       <c r="A90">
-        <v>343.5333333333334</v>
+        <v>355.0333333333333</v>
       </c>
       <c r="B90">
-        <v>37.81308934862759</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
+        <v>0.007931229026912887</v>
+      </c>
+      <c r="C90">
+        <v>0.005967233570223726</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
       <c r="A91">
-        <v>347.3575757575758</v>
+        <v>359.0030303030303</v>
       </c>
       <c r="B91">
-        <v>38.02776511199502</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
+        <v>0.007843035386394132</v>
+      </c>
+      <c r="C91">
+        <v>0.005867128797220601</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
       <c r="A92">
-        <v>351.1818181818182</v>
+        <v>362.9727272727272</v>
       </c>
       <c r="B92">
-        <v>38.24128909555758</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
+        <v>0.007756776226701226</v>
+      </c>
+      <c r="C92">
+        <v>0.005769183116080261</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
       <c r="A93">
-        <v>355.0060606060607</v>
+        <v>366.9424242424242</v>
       </c>
       <c r="B93">
-        <v>38.45367992147639</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
+        <v>0.007672388647881593</v>
+      </c>
+      <c r="C93">
+        <v>0.00567333028345027</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
       <c r="A94">
-        <v>358.8303030303031</v>
+        <v>370.9121212121212</v>
       </c>
       <c r="B94">
-        <v>38.66495571396942</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
+        <v>0.007589812446464244</v>
+      </c>
+      <c r="C94">
+        <v>0.005579506837557558</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
       <c r="A95">
-        <v>362.6545454545455</v>
+        <v>374.8818181818182</v>
       </c>
       <c r="B95">
-        <v>38.87513411777812</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
+        <v>0.007508989972534624</v>
+      </c>
+      <c r="C95">
+        <v>0.00548765195151655</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
       <c r="A96">
-        <v>366.4787878787879</v>
+        <v>378.8515151515151</v>
       </c>
       <c r="B96">
-        <v>39.08423231576221</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
+        <v>0.00742986599580331</v>
+      </c>
+      <c r="C96">
+        <v>0.00539770729584169</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97">
-        <v>370.3030303030304</v>
+        <v>382.8212121212121</v>
       </c>
       <c r="B97">
-        <v>39.29226704567237</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
+        <v>0.007352387580015185</v>
+      </c>
+      <c r="C97">
+        <v>0.005309616909497291</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98">
-        <v>374.1272727272728</v>
+        <v>386.7909090909091</v>
       </c>
       <c r="B98">
-        <v>39.49925461614731</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
+        <v>0.007276503965099425</v>
+      </c>
+      <c r="C98">
+        <v>0.005223327078872543</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
       <c r="A99">
-        <v>377.9515151515152</v>
+        <v>390.7606060606061</v>
       </c>
       <c r="B99">
-        <v>39.7052109219787</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
+        <v>0.007202166456509426</v>
+      </c>
+      <c r="C99">
+        <v>0.005138786224119057</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
       <c r="A100">
-        <v>381.7757575757576</v>
+        <v>394.730303030303</v>
       </c>
       <c r="B100">
-        <v>39.9101514586844</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
+        <v>0.007129328321246096</v>
+      </c>
+      <c r="C100">
+        <v>0.005055944792333566</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
       <c r="A101">
-        <v>385.6</v>
+        <v>398.7</v>
       </c>
       <c r="B101">
-        <v>40.11409133642802</v>
+        <v>0.007057944690098365</v>
+      </c>
+      <c r="C101">
+        <v>0.004974755157109563</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sgt_files/InVitroBioFilm_SGT_scaling.xlsx
+++ b/datasets/sgt_files/InVitroBioFilm_SGT_scaling.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="13">
   <si>
     <t>kernel-dim</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t>Log-Normal y-fit</t>
+  </si>
+  <si>
+    <t>-inf</t>
   </si>
 </sst>
 </file>
@@ -413,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -429,42 +432,119 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="B2">
-        <v>38.4</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>10.77775486824598</v>
+        <v>1.299572579307862</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>418</v>
+        <v>125</v>
       </c>
       <c r="B3">
-        <v>226.2</v>
+        <v>19.7</v>
       </c>
       <c r="C3">
-        <v>14.38540927467828</v>
+        <v>3.296631277194612</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
+        <v>188</v>
+      </c>
+      <c r="B4">
+        <v>37.6</v>
+      </c>
+      <c r="C4">
+        <v>7.60876687337267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>251</v>
+      </c>
+      <c r="B5">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="C5">
+        <v>9.59652714961685</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>314</v>
+      </c>
+      <c r="B6">
+        <v>100.7</v>
+      </c>
+      <c r="C6">
+        <v>15.14819387840602</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>376</v>
+      </c>
+      <c r="B7">
+        <v>146.6</v>
+      </c>
+      <c r="C7">
+        <v>19.73051781716165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>439</v>
+      </c>
+      <c r="B8">
+        <v>192.4</v>
+      </c>
+      <c r="C8">
+        <v>23.34104634425039</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>502</v>
+      </c>
+      <c r="B9">
+        <v>248.5</v>
+      </c>
+      <c r="C9">
+        <v>21.17716275194159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>565</v>
+      </c>
+      <c r="B10">
+        <v>282.1</v>
+      </c>
+      <c r="C10">
+        <v>24.09631138208133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
         <v>628</v>
       </c>
-      <c r="B4">
-        <v>365.8</v>
-      </c>
-      <c r="C4">
-        <v>46.70160596810349</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
+      <c r="B11">
+        <v>343.5</v>
+      </c>
+      <c r="C11">
+        <v>29.50075328605092</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
         <v>0</v>
       </c>
     </row>
@@ -475,7 +555,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -506,80 +586,262 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="B2">
-        <v>38.4</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>10.77775486824598</v>
+        <v>1.299572579307862</v>
       </c>
       <c r="D2">
-        <v>39.6</v>
+        <v>6.3</v>
       </c>
       <c r="E2">
-        <v>11.64302366226231</v>
+        <v>1.398809017223819</v>
       </c>
       <c r="F2">
-        <v>1.584331224367531</v>
+        <v>0.8450980400142568</v>
       </c>
       <c r="G2">
-        <v>1.597695185925512</v>
+        <v>0.7993405494535817</v>
       </c>
       <c r="H2">
-        <v>1.598742348155465</v>
+        <v>0.8284652749722544</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3">
-        <v>418</v>
+        <v>125</v>
       </c>
       <c r="B3">
-        <v>226.2</v>
+        <v>19.7</v>
       </c>
       <c r="C3">
-        <v>14.38540927467828</v>
+        <v>3.296631277194612</v>
       </c>
       <c r="D3">
-        <v>253.8</v>
+        <v>20.7</v>
       </c>
       <c r="E3">
-        <v>17.98721768367748</v>
+        <v>3.870256953858346</v>
       </c>
       <c r="F3">
-        <v>2.354492600589436</v>
+        <v>1.294466226161593</v>
       </c>
       <c r="G3">
-        <v>2.404491617758686</v>
+        <v>1.315970345456918</v>
       </c>
       <c r="H3">
-        <v>2.399581079948826</v>
+        <v>1.297574666810162</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4">
+        <v>188</v>
+      </c>
+      <c r="B4">
+        <v>37.6</v>
+      </c>
+      <c r="C4">
+        <v>7.60876687337267</v>
+      </c>
+      <c r="D4">
+        <v>40.7</v>
+      </c>
+      <c r="E4">
+        <v>8.828048733692199</v>
+      </c>
+      <c r="F4">
+        <v>1.575187844927661</v>
+      </c>
+      <c r="G4">
+        <v>1.60959440922522</v>
+      </c>
+      <c r="H4">
+        <v>1.590628674447288</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>251</v>
+      </c>
+      <c r="B5">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="C5">
+        <v>9.59652714961685</v>
+      </c>
+      <c r="D5">
+        <v>72.5</v>
+      </c>
+      <c r="E5">
+        <v>11.36197361572559</v>
+      </c>
+      <c r="F5">
+        <v>1.823474229170301</v>
+      </c>
+      <c r="G5">
+        <v>1.860338006570994</v>
+      </c>
+      <c r="H5">
+        <v>1.849822534413843</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>314</v>
+      </c>
+      <c r="B6">
+        <v>100.7</v>
+      </c>
+      <c r="C6">
+        <v>15.14819387840602</v>
+      </c>
+      <c r="D6">
+        <v>109.6</v>
+      </c>
+      <c r="E6">
+        <v>17.29624236647949</v>
+      </c>
+      <c r="F6">
+        <v>2.003029470553618</v>
+      </c>
+      <c r="G6">
+        <v>2.03981055414835</v>
+      </c>
+      <c r="H6">
+        <v>2.037265821863256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>376</v>
+      </c>
+      <c r="B7">
+        <v>146.6</v>
+      </c>
+      <c r="C7">
+        <v>19.73051781716165</v>
+      </c>
+      <c r="D7">
+        <v>163.1</v>
+      </c>
+      <c r="E7">
+        <v>23.13172424759266</v>
+      </c>
+      <c r="F7">
+        <v>2.166133970305109</v>
+      </c>
+      <c r="G7">
+        <v>2.212453961040276</v>
+      </c>
+      <c r="H7">
+        <v>2.207535669714393</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>439</v>
+      </c>
+      <c r="B8">
+        <v>192.4</v>
+      </c>
+      <c r="C8">
+        <v>23.34104634425039</v>
+      </c>
+      <c r="D8">
+        <v>213.1</v>
+      </c>
+      <c r="E8">
+        <v>28.29740859749057</v>
+      </c>
+      <c r="F8">
+        <v>2.284205067701794</v>
+      </c>
+      <c r="G8">
+        <v>2.328583449714202</v>
+      </c>
+      <c r="H8">
+        <v>2.330793751618822</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>502</v>
+      </c>
+      <c r="B9">
+        <v>248.5</v>
+      </c>
+      <c r="C9">
+        <v>21.17716275194159</v>
+      </c>
+      <c r="D9">
+        <v>273.9</v>
+      </c>
+      <c r="E9">
+        <v>25.08494457726475</v>
+      </c>
+      <c r="F9">
+        <v>2.395326393069351</v>
+      </c>
+      <c r="G9">
+        <v>2.437592032253961</v>
+      </c>
+      <c r="H9">
+        <v>2.446796750874994</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>565</v>
+      </c>
+      <c r="B10">
+        <v>282.1</v>
+      </c>
+      <c r="C10">
+        <v>24.09631138208133</v>
+      </c>
+      <c r="D10">
+        <v>314</v>
+      </c>
+      <c r="E10">
+        <v>28.63719415181747</v>
+      </c>
+      <c r="F10">
+        <v>2.450403086155367</v>
+      </c>
+      <c r="G10">
+        <v>2.496929648073215</v>
+      </c>
+      <c r="H10">
+        <v>2.504293019624097</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
         <v>628</v>
       </c>
-      <c r="B4">
-        <v>365.8</v>
-      </c>
-      <c r="C4">
-        <v>46.70160596810349</v>
-      </c>
-      <c r="D4">
-        <v>410</v>
-      </c>
-      <c r="E4">
-        <v>54.52705750359173</v>
-      </c>
-      <c r="F4">
-        <v>2.563243701140398</v>
-      </c>
-      <c r="G4">
-        <v>2.612783856719735</v>
-      </c>
-      <c r="H4">
-        <v>2.616647232299644</v>
+      <c r="B11">
+        <v>343.5</v>
+      </c>
+      <c r="C11">
+        <v>29.50075328605092</v>
+      </c>
+      <c r="D11">
+        <v>385.6</v>
+      </c>
+      <c r="E11">
+        <v>34.62856880926178</v>
+      </c>
+      <c r="F11">
+        <v>2.535926741395569</v>
+      </c>
+      <c r="G11">
+        <v>2.586137025230793</v>
+      </c>
+      <c r="H11">
+        <v>2.593573816828401</v>
       </c>
     </row>
   </sheetData>
@@ -608,1402 +870,1402 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
-        <v>38.4</v>
+        <v>7</v>
       </c>
       <c r="B2">
-        <v>236.1462075935406</v>
+        <v>162.5855482524931</v>
       </c>
       <c r="C2">
-        <v>236.8370312154781</v>
+        <v>164.2679681603324</v>
       </c>
       <c r="D2">
-        <v>2.562308198581967E-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3">
-        <v>41.70707070707071</v>
+        <v>10.3989898989899</v>
       </c>
       <c r="B3">
-        <v>235.9512001786524</v>
+        <v>161.9433088723715</v>
       </c>
       <c r="C3">
-        <v>236.4968283775719</v>
+        <v>163.1499866260929</v>
       </c>
       <c r="D3">
-        <v>8.2230885676331E-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4">
-        <v>45.01414141414141</v>
+        <v>13.7979797979798</v>
       </c>
       <c r="B4">
-        <v>235.7712238877707</v>
+        <v>161.4859583398004</v>
       </c>
       <c r="C4">
-        <v>236.18292681073</v>
+        <v>162.3546769296511</v>
       </c>
       <c r="D4">
-        <v>2.809246165039642E-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
-        <v>48.32121212121212</v>
+        <v>17.1969696969697</v>
       </c>
       <c r="B5">
-        <v>235.6041356017762</v>
+        <v>161.1307397582214</v>
       </c>
       <c r="C5">
-        <v>235.8915711513892</v>
+        <v>161.7374466895176</v>
       </c>
       <c r="D5">
-        <v>1.014293024139562E-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6">
-        <v>51.62828282828283</v>
+        <v>20.5959595959596</v>
       </c>
       <c r="B6">
-        <v>235.4482196318504</v>
+        <v>160.8403834888322</v>
       </c>
       <c r="C6">
-        <v>235.6197557038701</v>
+        <v>161.2332330915446</v>
       </c>
       <c r="D6">
-        <v>3.847281049449188E-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7">
-        <v>54.93535353535353</v>
+        <v>23.99494949494949</v>
       </c>
       <c r="B7">
-        <v>235.3020811735974</v>
+        <v>160.5948898376004</v>
       </c>
       <c r="C7">
-        <v>235.3650374459949</v>
+        <v>160.8071444496369</v>
       </c>
       <c r="D7">
-        <v>1.525367403038516E-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
-        <v>58.24242424242424</v>
+        <v>27.39393939393939</v>
       </c>
       <c r="B8">
-        <v>235.1645710098915</v>
+        <v>160.3822771154913</v>
       </c>
       <c r="C8">
-        <v>235.1254039063156</v>
+        <v>160.4382883504577</v>
       </c>
       <c r="D8">
-        <v>6.29460175951091E-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
-        <v>61.54949494949495</v>
+        <v>30.79292929292929</v>
       </c>
       <c r="B9">
-        <v>235.034731073642</v>
+        <v>160.1947983795439</v>
       </c>
       <c r="C9">
-        <v>234.8991776629887</v>
+        <v>160.1131625023103</v>
       </c>
       <c r="D9">
-        <v>2.693668507564989E-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
-        <v>64.85656565656566</v>
+        <v>34.19191919191919</v>
       </c>
       <c r="B10">
-        <v>234.9117542998544</v>
+        <v>160.0271554133458</v>
       </c>
       <c r="C10">
-        <v>234.6849459240512</v>
+        <v>159.8225361217669</v>
       </c>
       <c r="D10">
-        <v>1.191591606324724E-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
-        <v>68.16363636363636</v>
+        <v>37.59090909090909</v>
       </c>
       <c r="B11">
-        <v>234.7949544906462</v>
+        <v>159.8755648717731</v>
       </c>
       <c r="C11">
-        <v>234.4815076798087</v>
+        <v>159.559819961901</v>
       </c>
       <c r="D11">
-        <v>5.43402547908315E-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12">
-        <v>71.47070707070708</v>
+        <v>40.98989898989899</v>
       </c>
       <c r="B12">
-        <v>234.6837433390503</v>
+        <v>159.7372309832656</v>
       </c>
       <c r="C12">
-        <v>234.2878334162887</v>
+        <v>159.320146279743</v>
       </c>
       <c r="D12">
-        <v>2.548464553622947E-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13">
-        <v>74.77777777777777</v>
+        <v>44.38888888888889</v>
       </c>
       <c r="B13">
-        <v>234.5776126635638</v>
+        <v>159.6100293594884</v>
       </c>
       <c r="C13">
-        <v>234.1030339701664</v>
+        <v>159.0998173187953</v>
       </c>
       <c r="D13">
-        <v>1.22651886996608E-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14">
-        <v>78.08484848484849</v>
+        <v>47.78787878787878</v>
       </c>
       <c r="B14">
-        <v>234.4761204970113</v>
+        <v>159.4923079851164</v>
       </c>
       <c r="C14">
-        <v>233.9263361444608</v>
+        <v>158.8959582825028</v>
       </c>
       <c r="D14">
-        <v>6.046299299780876E-15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15">
-        <v>81.39191919191919</v>
+        <v>51.18686868686869</v>
       </c>
       <c r="B15">
-        <v>234.3788800680985</v>
+        <v>159.382756862226</v>
       </c>
       <c r="C15">
-        <v>233.7570633974926</v>
+        <v>158.7062900839606</v>
       </c>
       <c r="D15">
-        <v>3.0478620728676E-15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16">
-        <v>84.69898989898991</v>
+        <v>54.58585858585858</v>
       </c>
       <c r="B16">
-        <v>234.285550982753</v>
+        <v>159.2803197187523</v>
       </c>
       <c r="C16">
-        <v>233.5946203893301</v>
+        <v>158.5289754630504</v>
       </c>
       <c r="D16">
-        <v>1.568694490763997E-15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17">
-        <v>88.0060606060606</v>
+        <v>57.98484848484848</v>
       </c>
       <c r="B17">
-        <v>234.1958320985404</v>
+        <v>159.1841324789212</v>
       </c>
       <c r="C17">
-        <v>233.4384804967719</v>
+        <v>158.3625117705716</v>
       </c>
       <c r="D17">
-        <v>8.232505773933698E-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18">
-        <v>91.31313131313132</v>
+        <v>61.38383838383838</v>
       </c>
       <c r="B18">
-        <v>234.1094557165757</v>
+        <v>159.0934793174404</v>
       </c>
       <c r="C18">
-        <v>233.2881756380481</v>
+        <v>158.2056544080018</v>
       </c>
       <c r="D18">
-        <v>4.399940952958961E-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19">
-        <v>94.62020202020202</v>
+        <v>64.78282828282828</v>
       </c>
       <c r="B19">
-        <v>234.0261828090788</v>
+        <v>159.00776059334</v>
       </c>
       <c r="C19">
-        <v>233.143287912896</v>
+        <v>158.0573609741687</v>
       </c>
       <c r="D19">
-        <v>2.392231766586932E-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20">
-        <v>97.92727272727274</v>
+        <v>68.18181818181819</v>
       </c>
       <c r="B20">
-        <v>233.9457990686389</v>
+        <v>158.9264690075433</v>
       </c>
       <c r="C20">
-        <v>233.0034426828397</v>
+        <v>157.9167497436646</v>
       </c>
       <c r="D20">
-        <v>1.321799172991716E-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21">
-        <v>101.2343434343434</v>
+        <v>71.58080808080808</v>
       </c>
       <c r="B21">
-        <v>233.8681116150946</v>
+        <v>158.8491715768648</v>
       </c>
       <c r="C21">
-        <v>232.8683028039295</v>
+        <v>157.7830682799373</v>
       </c>
       <c r="D21">
-        <v>7.415428056720535E-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22">
-        <v>104.5414141414142</v>
+        <v>74.97979797979798</v>
       </c>
       <c r="B22">
-        <v>233.792946232928</v>
+        <v>158.7754958010286</v>
       </c>
       <c r="C22">
-        <v>232.7375637891002</v>
+        <v>157.6556693531762</v>
       </c>
       <c r="D22">
-        <v>4.220386473087408E-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23">
-        <v>107.8484848484848</v>
+        <v>78.37878787878788</v>
       </c>
       <c r="B23">
-        <v>233.7201450398363</v>
+        <v>158.7051189044256</v>
       </c>
       <c r="C23">
-        <v>232.6109497259987</v>
+        <v>157.5339922139537</v>
       </c>
       <c r="D23">
-        <v>2.434895648115851E-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24">
-        <v>111.1555555555556</v>
+        <v>81.77777777777777</v>
       </c>
       <c r="B24">
-        <v>233.6495645081843</v>
+        <v>158.6377593674657</v>
       </c>
       <c r="C24">
-        <v>232.4882098130331</v>
+        <v>157.4175478544129</v>
       </c>
       <c r="D24">
-        <v>1.42303102020611E-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25">
-        <v>114.4626262626263</v>
+        <v>85.17676767676767</v>
       </c>
       <c r="B25">
-        <v>233.5810737771411</v>
+        <v>158.5731701867296</v>
       </c>
       <c r="C25">
-        <v>232.3691154046287</v>
+        <v>157.3059072798946</v>
       </c>
       <c r="D25">
-        <v>8.419222946263476E-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26">
-        <v>117.769696969697</v>
+        <v>88.57575757575756</v>
       </c>
       <c r="B26">
-        <v>233.5145532057244</v>
+        <v>158.5111334570825</v>
       </c>
       <c r="C26">
-        <v>232.2534574784543</v>
+        <v>157.1986920822407</v>
       </c>
       <c r="D26">
-        <v>5.039559064913113E-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27">
-        <v>121.0767676767677</v>
+        <v>91.97474747474747</v>
       </c>
       <c r="B27">
-        <v>233.4498931266465</v>
+        <v>158.4514559763873</v>
       </c>
       <c r="C27">
-        <v>232.1410444543356</v>
+        <v>157.095566793321</v>
       </c>
       <c r="D27">
-        <v>3.050243816365308E-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28">
-        <v>124.3838383838384</v>
+        <v>95.37373737373737</v>
       </c>
       <c r="B28">
-        <v>233.3869927684313</v>
+        <v>158.3939656496634</v>
       </c>
       <c r="C28">
-        <v>232.0317003078563</v>
+        <v>156.9962326301237</v>
       </c>
       <c r="D28">
-        <v>1.865838708984186E-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29">
-        <v>127.6909090909091</v>
+        <v>98.77272727272727</v>
       </c>
       <c r="B29">
-        <v>233.3257593192594</v>
+        <v>158.3385085243526</v>
       </c>
       <c r="C29">
-        <v>231.9252629321387</v>
+        <v>156.9004223382571</v>
       </c>
       <c r="D29">
-        <v>1.152930115495227E-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30">
-        <v>130.9979797979798</v>
+        <v>102.1717171717172</v>
       </c>
       <c r="B30">
-        <v>233.2661071107565</v>
+        <v>158.2849463283028</v>
       </c>
       <c r="C30">
-        <v>231.8215827096408</v>
+        <v>156.8078959103053</v>
       </c>
       <c r="D30">
-        <v>7.193285915191711E-19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31">
-        <v>134.3050505050505</v>
+        <v>105.5707070707071</v>
       </c>
       <c r="B31">
-        <v>233.2079569037492</v>
+        <v>158.2331544115494</v>
       </c>
       <c r="C31">
-        <v>231.7205212624782</v>
+        <v>156.7184370068142</v>
       </c>
       <c r="D31">
-        <v>4.529666489055615E-19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32">
-        <v>137.6121212121212</v>
+        <v>108.969696969697</v>
       </c>
       <c r="B32">
-        <v>233.1512352610777</v>
+        <v>158.1830200149607</v>
       </c>
       <c r="C32">
-        <v>231.6219503551534</v>
+        <v>156.6318499459776</v>
       </c>
       <c r="D32">
-        <v>2.877733992102098E-19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33">
-        <v>140.9191919191919</v>
+        <v>112.3686868686869</v>
       </c>
       <c r="B33">
-        <v>233.0958739950386</v>
+        <v>158.1344408053861</v>
       </c>
       <c r="C33">
-        <v>231.5257509279276</v>
+        <v>156.5479571569525</v>
       </c>
       <c r="D33">
-        <v>1.843836232654822E-19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34">
-        <v>144.2262626262626</v>
+        <v>115.7676767676768</v>
       </c>
       <c r="B34">
-        <v>233.0418096790509</v>
+        <v>158.0873236295584</v>
       </c>
       <c r="C34">
-        <v>231.4318122426084</v>
+        <v>156.4665970137028</v>
       </c>
       <c r="D34">
-        <v>1.19105818251586E-19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35">
-        <v>147.5333333333333</v>
+        <v>119.1666666666667</v>
       </c>
       <c r="B35">
-        <v>232.9889832147941</v>
+        <v>158.0415834486965</v>
       </c>
       <c r="C35">
-        <v>231.3400311254272</v>
+        <v>156.3876219831392</v>
       </c>
       <c r="D35">
-        <v>7.754311979675519E-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36">
-        <v>150.8404040404041</v>
+        <v>122.5656565656566</v>
       </c>
       <c r="B36">
-        <v>232.9373394474261</v>
+        <v>157.9971424232542</v>
       </c>
       <c r="C36">
-        <v>231.2503112940632</v>
+        <v>156.3108970343911</v>
       </c>
       <c r="D36">
-        <v>5.0865378960042E-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37">
-        <v>154.1474747474747</v>
+        <v>125.9646464646465</v>
       </c>
       <c r="B37">
-        <v>232.886826822613</v>
+        <v>157.953929123126</v>
       </c>
       <c r="C37">
-        <v>231.1625627578385</v>
+        <v>156.2362982662498</v>
       </c>
       <c r="D37">
-        <v>3.360831596062942E-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38">
-        <v>157.4545454545455</v>
+        <v>129.3636363636364</v>
       </c>
       <c r="B38">
-        <v>232.837397080037</v>
+        <v>157.9118778432275</v>
       </c>
       <c r="C38">
-        <v>231.0767012817452</v>
+        <v>156.1637117178434</v>
       </c>
       <c r="D38">
-        <v>2.236147643776004E-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39">
-        <v>160.7616161616162</v>
+        <v>132.7626262626263</v>
       </c>
       <c r="B39">
-        <v>232.7890049788236</v>
+        <v>157.8709280080224</v>
       </c>
       <c r="C39">
-        <v>230.9926479063235</v>
+        <v>156.0930323339648</v>
       </c>
       <c r="D39">
-        <v>1.497868856356833E-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40">
-        <v>164.0686868686869</v>
+        <v>136.1616161616162</v>
       </c>
       <c r="B40">
-        <v>232.7416080509821</v>
+        <v>157.8310236514797</v>
       </c>
       <c r="C40">
-        <v>230.9103285165537</v>
+        <v>156.0241630615383</v>
       </c>
       <c r="D40">
-        <v>1.009864440269148E-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41">
-        <v>167.3757575757576</v>
+        <v>139.5606060606061</v>
       </c>
       <c r="B41">
-        <v>232.6951663794995</v>
+        <v>157.7921129612798</v>
       </c>
       <c r="C41">
-        <v>230.8296734538787</v>
+        <v>155.957014057779</v>
       </c>
       <c r="D41">
-        <v>6.851257989489441E-21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42">
-        <v>170.6828282828283</v>
+        <v>142.959595959596</v>
       </c>
       <c r="B42">
-        <v>232.6496423981873</v>
+        <v>157.7541478779773</v>
       </c>
       <c r="C42">
-        <v>230.7506171662835</v>
+        <v>155.8915019938824</v>
       </c>
       <c r="D42">
-        <v>4.676303529589522E-21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43">
-        <v>173.989898989899</v>
+        <v>146.3585858585859</v>
       </c>
       <c r="B43">
-        <v>232.6050007107734</v>
+        <v>157.7170837413574</v>
       </c>
       <c r="C43">
-        <v>230.6730978920377</v>
+        <v>155.8275494407432</v>
       </c>
       <c r="D43">
-        <v>3.210496490616638E-21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44">
-        <v>177.2969696969697</v>
+        <v>149.7575757575758</v>
       </c>
       <c r="B44">
-        <v>232.5612079270607</v>
+        <v>157.680878977474</v>
       </c>
       <c r="C44">
-        <v>230.5970573732928</v>
+        <v>155.7650843253779</v>
       </c>
       <c r="D44">
-        <v>2.216640905322756E-21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45">
-        <v>180.6040404040404</v>
+        <v>153.1565656565656</v>
       </c>
       <c r="B45">
-        <v>232.518232514256</v>
+        <v>157.6454948208796</v>
       </c>
       <c r="C45">
-        <v>230.5224405962131</v>
+        <v>155.70403944851</v>
       </c>
       <c r="D45">
-        <v>1.538837685779879E-21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46">
-        <v>183.9111111111111</v>
+        <v>156.5555555555555</v>
       </c>
       <c r="B46">
-        <v>232.4760446618159</v>
+        <v>157.6108950674061</v>
       </c>
       <c r="C46">
-        <v>230.4491955547467</v>
+        <v>155.6443520552419</v>
       </c>
       <c r="D46">
-        <v>1.073962724409227E-21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47">
-        <v>187.2181818181818</v>
+        <v>159.9545454545454</v>
       </c>
       <c r="B47">
-        <v>232.43461615836</v>
+        <v>157.5770458535503</v>
       </c>
       <c r="C47">
-        <v>230.3772730355034</v>
+        <v>155.585963451958</v>
       </c>
       <c r="D47">
-        <v>7.533777255146351E-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48">
-        <v>190.5252525252525</v>
+        <v>163.3535353535353</v>
       </c>
       <c r="B48">
-        <v>232.3939202793837</v>
+        <v>157.5439154591024</v>
       </c>
       <c r="C48">
-        <v>230.3066264215149</v>
+        <v>155.5288186636129</v>
       </c>
       <c r="D48">
-        <v>5.311230885680746E-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49">
-        <v>193.8323232323233</v>
+        <v>166.7525252525252</v>
       </c>
       <c r="B49">
-        <v>232.3539316846515</v>
+        <v>157.5114741301406</v>
       </c>
       <c r="C49">
-        <v>230.2372115129267</v>
+        <v>155.4728661264019</v>
       </c>
       <c r="D49">
-        <v>3.762454765687669E-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50">
-        <v>197.139393939394</v>
+        <v>170.1515151515151</v>
       </c>
       <c r="B50">
-        <v>232.3146263242871</v>
+        <v>157.4796939199211</v>
       </c>
       <c r="C50">
-        <v>230.1689863628951</v>
+        <v>155.4180574115226</v>
       </c>
       <c r="D50">
-        <v>2.677805045458624E-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51">
-        <v>200.4464646464646</v>
+        <v>173.5505050505051</v>
       </c>
       <c r="B51">
-        <v>232.2759813526922</v>
+        <v>157.4485485455358</v>
       </c>
       <c r="C51">
-        <v>230.1019111271722</v>
+        <v>155.3643469763274</v>
       </c>
       <c r="D51">
-        <v>1.914515387891604E-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52">
-        <v>203.7535353535354</v>
+        <v>176.9494949494949</v>
       </c>
       <c r="B52">
-        <v>232.237975049521</v>
+        <v>157.4180132585006</v>
       </c>
       <c r="C52">
-        <v>230.0359479260296</v>
+        <v>155.3116919396733</v>
       </c>
       <c r="D52">
-        <v>1.374846854218998E-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53">
-        <v>207.0606060606061</v>
+        <v>180.3484848484848</v>
       </c>
       <c r="B53">
-        <v>232.2005867470306</v>
+        <v>157.3880647276798</v>
       </c>
       <c r="C53">
-        <v>229.971060717326</v>
+        <v>155.2600518786999</v>
       </c>
       <c r="D53">
-        <v>9.915420812122112E-23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54">
-        <v>210.3676767676768</v>
+        <v>183.7474747474747</v>
       </c>
       <c r="B54">
-        <v>232.1637967631983</v>
+        <v>157.3586809331633</v>
       </c>
       <c r="C54">
-        <v>229.9072151796587</v>
+        <v>155.2093886446298</v>
       </c>
       <c r="D54">
-        <v>7.180876980882303E-23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55">
-        <v>213.6747474747475</v>
+        <v>187.1464646464646</v>
       </c>
       <c r="B55">
-        <v>232.1275863400662</v>
+        <v>157.3298410698893</v>
       </c>
       <c r="C55">
-        <v>229.8443786046522</v>
+        <v>155.1596661954954</v>
       </c>
       <c r="D55">
-        <v>5.221601031102078E-23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56">
-        <v>216.9818181818182</v>
+        <v>190.5454545454545</v>
       </c>
       <c r="B56">
-        <v>232.0919375868295</v>
+        <v>157.301525459958</v>
       </c>
       <c r="C56">
-        <v>229.7825197975385</v>
+        <v>155.1108504439583</v>
       </c>
       <c r="D56">
-        <v>3.811905973109489E-23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57">
-        <v>220.2888888888889</v>
+        <v>193.9444444444444</v>
       </c>
       <c r="B57">
-        <v>232.0568334272378</v>
+        <v>157.2737154727141</v>
       </c>
       <c r="C57">
-        <v>229.7216089852783</v>
+        <v>155.0629091186188</v>
       </c>
       <c r="D57">
-        <v>2.793491571485038E-23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58">
-        <v>223.5959595959596</v>
+        <v>197.3434343434343</v>
       </c>
       <c r="B58">
-        <v>232.0222575509244</v>
+        <v>157.2463934517846</v>
       </c>
       <c r="C58">
-        <v>229.6616177315443</v>
+        <v>155.0158116374044</v>
       </c>
       <c r="D58">
-        <v>2.054828093364562E-23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59">
-        <v>226.9030303030303</v>
+        <v>200.7424242424242</v>
       </c>
       <c r="B59">
-        <v>231.9881943683134</v>
+        <v>157.2195426483601</v>
       </c>
       <c r="C59">
-        <v>229.6025188579624</v>
+        <v>154.9695289917978</v>
       </c>
       <c r="D59">
-        <v>1.516996482447516E-23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60">
-        <v>230.210101010101</v>
+        <v>204.1414141414141</v>
       </c>
       <c r="B60">
-        <v>231.9546289687982</v>
+        <v>157.1931471600884</v>
       </c>
       <c r="C60">
-        <v>229.5442863710654</v>
+        <v>154.9240336408098</v>
       </c>
       <c r="D60">
-        <v>1.123917074086109E-23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61">
-        <v>233.5171717171717</v>
+        <v>207.540404040404</v>
       </c>
       <c r="B61">
-        <v>231.9215470819073</v>
+        <v>157.1671918750234</v>
       </c>
       <c r="C61">
-        <v>229.486895394471</v>
+        <v>154.8792994137291</v>
       </c>
       <c r="D61">
-        <v>8.355757336449895E-24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62">
-        <v>236.8242424242424</v>
+        <v>210.9393939393939</v>
       </c>
       <c r="B62">
-        <v>231.8889350412059</v>
+        <v>157.1416624201366</v>
       </c>
       <c r="C62">
-        <v>229.430322105839</v>
+        <v>154.8353014207924</v>
       </c>
       <c r="D62">
-        <v>6.233069267254806E-24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63">
-        <v>240.1313131313131</v>
+        <v>214.3383838383838</v>
       </c>
       <c r="B63">
-        <v>231.8567797507065</v>
+        <v>157.1165451139513</v>
       </c>
       <c r="C63">
-        <v>229.3745436782135</v>
+        <v>154.7920159710125</v>
       </c>
       <c r="D63">
-        <v>4.664948081066482E-24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64">
-        <v>243.4383838383839</v>
+        <v>217.7373737373737</v>
       </c>
       <c r="B64">
-        <v>231.8250686535807</v>
+        <v>157.0918269229114</v>
       </c>
       <c r="C64">
-        <v>229.3195382253854</v>
+        <v>154.7494204964881</v>
       </c>
       <c r="D64">
-        <v>3.502562455856988E-24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65">
-        <v>246.7454545454546</v>
+        <v>221.1363636363636</v>
       </c>
       <c r="B65">
-        <v>231.7937897029861</v>
+        <v>157.0674954211358</v>
       </c>
       <c r="C65">
-        <v>229.2652847509518</v>
+        <v>154.7074934825907</v>
       </c>
       <c r="D65">
-        <v>2.638067681502723E-24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66">
-        <v>250.0525252525253</v>
+        <v>224.5353535353535</v>
       </c>
       <c r="B66">
-        <v>231.7629313348395</v>
+        <v>157.0435387532486</v>
       </c>
       <c r="C66">
-        <v>229.2117631007749</v>
+        <v>154.6662144034904</v>
       </c>
       <c r="D66">
-        <v>1.99303498407814E-24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67">
-        <v>253.359595959596</v>
+        <v>227.9343434343434</v>
       </c>
       <c r="B67">
-        <v>231.7324824423819</v>
+        <v>157.0199456000071</v>
       </c>
       <c r="C67">
-        <v>229.1589539185722</v>
+        <v>154.6255636625377</v>
       </c>
       <c r="D67">
-        <v>1.510226121172507E-24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68">
-        <v>256.6666666666667</v>
+        <v>231.3333333333333</v>
       </c>
       <c r="B68">
-        <v>231.7024323523964</v>
+        <v>156.9967051464791</v>
       </c>
       <c r="C68">
-        <v>229.1068386043941</v>
+        <v>154.5855225370691</v>
       </c>
       <c r="D68">
-        <v>1.147723624931739E-24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69">
-        <v>259.9737373737374</v>
+        <v>234.7323232323232</v>
       </c>
       <c r="B69">
-        <v>231.6727708029515</v>
+        <v>156.9738070525452</v>
       </c>
       <c r="C69">
-        <v>229.0553992757661</v>
+        <v>154.5460731272487</v>
       </c>
       <c r="D69">
-        <v>8.747263692021389E-25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70">
-        <v>263.2808080808081</v>
+        <v>238.1313131313131</v>
       </c>
       <c r="B70">
-        <v>231.6434879225536</v>
+        <v>156.9512414255266</v>
       </c>
       <c r="C70">
-        <v>229.0046187312939</v>
+        <v>154.5071983085968</v>
       </c>
       <c r="D70">
-        <v>6.685269686955906E-25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71">
-        <v>266.5878787878788</v>
+        <v>241.530303030303</v>
       </c>
       <c r="B71">
-        <v>231.6145742106033</v>
+        <v>156.9289987947557</v>
       </c>
       <c r="C71">
-        <v>228.9544804165447</v>
+        <v>154.4688816878912</v>
       </c>
       <c r="D71">
-        <v>5.12331042204633E-25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72">
-        <v>269.8949494949495</v>
+        <v>244.9292929292929</v>
       </c>
       <c r="B72">
-        <v>231.5860205190596</v>
+        <v>156.9070700879274</v>
       </c>
       <c r="C72">
-        <v>228.9049683920391</v>
+        <v>154.4311075621581</v>
       </c>
       <c r="D72">
-        <v>3.936783690714354E-25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73">
-        <v>273.2020202020202</v>
+        <v>248.3282828282828</v>
       </c>
       <c r="B73">
-        <v>231.5578180352216</v>
+        <v>156.8854466090834</v>
       </c>
       <c r="C73">
-        <v>228.8560673031953</v>
+        <v>154.3938608804959</v>
       </c>
       <c r="D73">
-        <v>3.032959143365849E-25</v>
+        <v>2.574963799116809E-12</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74">
-        <v>276.5090909090909</v>
+        <v>251.7272727272727</v>
       </c>
       <c r="B74">
-        <v>231.5299582655496</v>
+        <v>156.8641200180957</v>
       </c>
       <c r="C74">
-        <v>228.8077623520873</v>
+        <v>154.3571272085011</v>
       </c>
       <c r="D74">
-        <v>2.342618130567095E-25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75">
-        <v>279.8161616161616</v>
+        <v>255.1262626262626</v>
       </c>
       <c r="B75">
-        <v>231.5024330204485</v>
+        <v>156.8430823115295</v>
       </c>
       <c r="C75">
-        <v>228.7600392708865</v>
+        <v>154.3208926950863</v>
       </c>
       <c r="D75">
-        <v>1.813940221842646E-25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76">
-        <v>283.1232323232323</v>
+        <v>258.5252525252525</v>
       </c>
       <c r="B76">
-        <v>231.4752343999477</v>
+        <v>156.8223258047739</v>
       </c>
       <c r="C76">
-        <v>228.7128842968665</v>
+        <v>154.2851440414989</v>
       </c>
       <c r="D76">
-        <v>1.408018382171691E-25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77">
-        <v>286.430303030303</v>
+        <v>261.9242424242424</v>
       </c>
       <c r="B77">
-        <v>231.4483547802144</v>
+        <v>156.8018431153425</v>
       </c>
       <c r="C77">
-        <v>228.6662841488643</v>
+        <v>154.2498684723693</v>
       </c>
       <c r="D77">
-        <v>1.095558661666711E-25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78">
-        <v>289.7373737373737</v>
+        <v>265.3232323232323</v>
       </c>
       <c r="B78">
-        <v>231.4217868008416</v>
+        <v>156.7816271472535</v>
       </c>
       <c r="C78">
-        <v>228.620226005095</v>
+        <v>154.2150537086301</v>
       </c>
       <c r="D78">
-        <v>8.544441362323672E-26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79">
-        <v>293.0444444444444</v>
+        <v>268.7222222222222</v>
       </c>
       <c r="B79">
-        <v>231.39552335286</v>
+        <v>156.7616710764044</v>
       </c>
       <c r="C79">
-        <v>228.5746974822298</v>
+        <v>154.1806879421631</v>
       </c>
       <c r="D79">
-        <v>6.679314057687823E-26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80">
-        <v>296.3515151515152</v>
+        <v>272.1212121212121</v>
       </c>
       <c r="B80">
-        <v>231.369557567423</v>
+        <v>156.741968336869</v>
       </c>
       <c r="C80">
-        <v>228.5296866156498</v>
+        <v>154.1467598120444</v>
       </c>
       <c r="D80">
-        <v>5.233114917441986E-26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81">
-        <v>299.6585858585859</v>
+        <v>275.520202020202</v>
       </c>
       <c r="B81">
-        <v>231.3438828051214</v>
+        <v>156.7225126080461</v>
       </c>
       <c r="C81">
-        <v>228.4851818407997</v>
+        <v>154.1132583822674</v>
       </c>
       <c r="D81">
-        <v>4.109127038136847E-26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82">
-        <v>302.9656565656566</v>
+        <v>278.9191919191919</v>
       </c>
       <c r="B82">
-        <v>231.3184926458853</v>
+        <v>156.7032978025976</v>
       </c>
       <c r="C82">
-        <v>228.4411719755662</v>
+        <v>154.0801731208351</v>
       </c>
       <c r="D82">
-        <v>3.233560629823866E-26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83">
-        <v>306.2727272727273</v>
+        <v>282.3181818181818</v>
       </c>
       <c r="B83">
-        <v>231.2933808794354</v>
+        <v>156.6843180551186</v>
       </c>
       <c r="C83">
-        <v>228.397646203616</v>
+        <v>154.0474938801216</v>
       </c>
       <c r="D83">
-        <v>2.549977848071352E-26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84">
-        <v>309.5797979797979</v>
+        <v>285.7171717171717</v>
       </c>
       <c r="B84">
-        <v>231.2685414962484</v>
+        <v>156.6655677114869</v>
       </c>
       <c r="C84">
-        <v>228.3545940586312</v>
+        <v>154.015210878413</v>
       </c>
       <c r="D84">
-        <v>2.015107030459595E-26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85">
-        <v>312.8868686868687</v>
+        <v>289.1161616161616</v>
       </c>
       <c r="B85">
-        <v>231.2439686790024</v>
+        <v>156.6470413188435</v>
       </c>
       <c r="C85">
-        <v>228.3120054093836</v>
+        <v>153.9833146825408</v>
       </c>
       <c r="D85">
-        <v>1.595691782485823E-26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86">
-        <v>316.1939393939394</v>
+        <v>292.5151515151515</v>
       </c>
       <c r="B86">
-        <v>231.219656794474</v>
+        <v>156.6287336161599</v>
       </c>
       <c r="C86">
-        <v>228.2698704455965</v>
+        <v>153.9517961915344</v>
       </c>
       <c r="D86">
-        <v>1.266112926706902E-26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87">
-        <v>319.5010101010101</v>
+        <v>295.9141414141414</v>
       </c>
       <c r="B87">
-        <v>231.1956003858572</v>
+        <v>156.610639525351</v>
       </c>
       <c r="C87">
-        <v>228.2281796645433</v>
+        <v>153.9206466212198</v>
       </c>
       <c r="D87">
-        <v>1.006589190072041E-26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88">
-        <v>322.8080808080808</v>
+        <v>299.3131313131313</v>
       </c>
       <c r="B88">
-        <v>231.1717941654786</v>
+        <v>156.5927541428973</v>
       </c>
       <c r="C88">
-        <v>228.1869238583387</v>
+        <v>153.8898574897</v>
       </c>
       <c r="D88">
-        <v>8.018123947611832E-27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89">
-        <v>326.1151515151515</v>
+        <v>302.7121212121212</v>
       </c>
       <c r="B89">
-        <v>231.1482330078849</v>
+        <v>156.5750727319397</v>
       </c>
       <c r="C89">
-        <v>228.1460941018782</v>
+        <v>153.8594206036571</v>
       </c>
       <c r="D89">
-        <v>6.39909699200721E-27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90">
-        <v>329.4222222222222</v>
+        <v>306.1111111111111</v>
       </c>
       <c r="B90">
-        <v>231.1249119432794</v>
+        <v>156.5575907148182</v>
       </c>
       <c r="C90">
-        <v>228.1056817413888</v>
+        <v>153.8293280454219</v>
       </c>
       <c r="D90">
-        <v>5.116526272872954E-27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91">
-        <v>332.7292929292929</v>
+        <v>309.510101010101</v>
       </c>
       <c r="B91">
-        <v>231.1018261512872</v>
+        <v>156.5403036660221</v>
       </c>
       <c r="C91">
-        <v>228.0656783835516</v>
+        <v>153.7995721607585</v>
       </c>
       <c r="D91">
-        <v>4.098527798004709E-27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92">
-        <v>336.0363636363636</v>
+        <v>312.9090909090909</v>
       </c>
       <c r="B92">
-        <v>231.0789709550293</v>
+        <v>156.5232073055263</v>
       </c>
       <c r="C92">
-        <v>228.0260758851654</v>
+        <v>153.770145547318</v>
       </c>
       <c r="D92">
-        <v>3.288991023660699E-27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93">
-        <v>339.3434343434344</v>
+        <v>316.3080808080808</v>
       </c>
       <c r="B93">
-        <v>231.0563418154877</v>
+        <v>156.5062974924888</v>
       </c>
       <c r="C93">
-        <v>227.9868663433162</v>
+        <v>153.7410410437178</v>
       </c>
       <c r="D93">
-        <v>2.644027470027391E-27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94">
-        <v>342.650505050505</v>
+        <v>319.7070707070707</v>
       </c>
       <c r="B94">
-        <v>231.0339343261437</v>
+        <v>156.4895702192847</v>
       </c>
       <c r="C94">
-        <v>227.9480420860259</v>
+        <v>153.7122517192055</v>
       </c>
       <c r="D94">
-        <v>2.129239033650374E-27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95">
-        <v>345.9575757575757</v>
+        <v>323.1060606060606</v>
       </c>
       <c r="B95">
-        <v>231.0117442078747</v>
+        <v>156.4730216058574</v>
       </c>
       <c r="C95">
-        <v>227.9095956633499</v>
+        <v>153.6837708638716</v>
       </c>
       <c r="D95">
-        <v>1.717612210903897E-27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96">
-        <v>349.2646464646465</v>
+        <v>326.5050505050505</v>
       </c>
       <c r="B96">
-        <v>230.989767304094</v>
+        <v>156.4566478943653</v>
       </c>
       <c r="C96">
-        <v>227.8715198389008</v>
+        <v>153.6555919793745</v>
       </c>
       <c r="D96">
-        <v>1.387891333565681E-27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97">
-        <v>352.5717171717172</v>
+        <v>329.9040404040404</v>
       </c>
       <c r="B97">
-        <v>230.9679995761202</v>
+        <v>156.4404454441062</v>
       </c>
       <c r="C97">
-        <v>227.8338075817717</v>
+        <v>153.6277087701483</v>
       </c>
       <c r="D97">
-        <v>1.123319203176768E-27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98">
-        <v>355.8787878787879</v>
+        <v>333.3030303030303</v>
       </c>
       <c r="B98">
-        <v>230.9464370987633</v>
+        <v>156.4244107267026</v>
       </c>
       <c r="C98">
-        <v>227.796452058837</v>
+        <v>153.600115135061</v>
       </c>
       <c r="D98">
-        <v>9.106601285340489E-28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99">
-        <v>359.1858585858586</v>
+        <v>336.7020202020202</v>
       </c>
       <c r="B99">
-        <v>230.9250760561152</v>
+        <v>156.4085403215318</v>
       </c>
       <c r="C99">
-        <v>227.7594466274116</v>
+        <v>153.5728051594986</v>
       </c>
       <c r="D99">
-        <v>7.394404963787656E-28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100">
-        <v>362.4929292929293</v>
+        <v>340.1010101010101</v>
       </c>
       <c r="B100">
-        <v>230.9039127375329</v>
+        <v>156.3928309113857</v>
       </c>
       <c r="C100">
-        <v>227.7227848282462</v>
+        <v>153.5457731078463</v>
       </c>
       <c r="D100">
-        <v>6.013572572439084E-28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101">
-        <v>365.8</v>
+        <v>343.5</v>
       </c>
       <c r="B101">
-        <v>230.882943533806</v>
+        <v>156.3772792783472</v>
       </c>
       <c r="C101">
-        <v>227.686460378842</v>
+        <v>153.5190134163453</v>
       </c>
       <c r="D101">
-        <v>4.898162927508457E-28</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2013,7 +2275,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2044,80 +2306,262 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="B2">
-        <v>38.4</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>10.77775486824598</v>
+        <v>1.299572579307862</v>
       </c>
       <c r="D2">
-        <v>2.035916</v>
+        <v>1.666667</v>
       </c>
       <c r="E2">
-        <v>0.02625636867504716</v>
+        <v>0.09938073688877314</v>
       </c>
       <c r="F2">
-        <v>1.584331224367531</v>
+        <v>0.8450980400142568</v>
       </c>
       <c r="G2">
-        <v>0.3087598554480953</v>
+        <v>0.221848836475244</v>
       </c>
       <c r="H2">
-        <v>0.3100083105992292</v>
+        <v>0.248747537131865</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3">
-        <v>418</v>
+        <v>125</v>
       </c>
       <c r="B3">
-        <v>226.2</v>
+        <v>19.7</v>
       </c>
       <c r="C3">
-        <v>14.38540927467828</v>
+        <v>3.296631277194612</v>
       </c>
       <c r="D3">
-        <v>2.24036</v>
+        <v>1.932764</v>
       </c>
       <c r="E3">
-        <v>0.01722203849722789</v>
+        <v>0.12480583326111</v>
       </c>
       <c r="F3">
-        <v>2.354492600589436</v>
+        <v>1.294466226161593</v>
       </c>
       <c r="G3">
-        <v>0.3503178100534986</v>
+        <v>0.2861788277714631</v>
       </c>
       <c r="H3">
-        <v>0.3444633339769141</v>
+        <v>0.2782991086707649</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4">
+        <v>188</v>
+      </c>
+      <c r="B4">
+        <v>37.6</v>
+      </c>
+      <c r="C4">
+        <v>7.60876687337267</v>
+      </c>
+      <c r="D4">
+        <v>2.080082</v>
+      </c>
+      <c r="E4">
+        <v>0.0587396677023098</v>
+      </c>
+      <c r="F4">
+        <v>1.575187844927661</v>
+      </c>
+      <c r="G4">
+        <v>0.3180804558500521</v>
+      </c>
+      <c r="H4">
+        <v>0.2967600617493643</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>251</v>
+      </c>
+      <c r="B5">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="C5">
+        <v>9.59652714961685</v>
+      </c>
+      <c r="D5">
+        <v>2.1471</v>
+      </c>
+      <c r="E5">
+        <v>0.02948695312243101</v>
+      </c>
+      <c r="F5">
+        <v>1.823474229170301</v>
+      </c>
+      <c r="G5">
+        <v>0.3318522719336047</v>
+      </c>
+      <c r="H5">
+        <v>0.313087992992088</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>314</v>
+      </c>
+      <c r="B6">
+        <v>100.7</v>
+      </c>
+      <c r="C6">
+        <v>15.14819387840602</v>
+      </c>
+      <c r="D6">
+        <v>2.136678</v>
+      </c>
+      <c r="E6">
+        <v>0.03184509998239742</v>
+      </c>
+      <c r="F6">
+        <v>2.003029470553618</v>
+      </c>
+      <c r="G6">
+        <v>0.3297390783831212</v>
+      </c>
+      <c r="H6">
+        <v>0.3248959930341377</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>376</v>
+      </c>
+      <c r="B7">
+        <v>146.6</v>
+      </c>
+      <c r="C7">
+        <v>19.73051781716165</v>
+      </c>
+      <c r="D7">
+        <v>2.198078</v>
+      </c>
+      <c r="E7">
+        <v>0.02650340983513046</v>
+      </c>
+      <c r="F7">
+        <v>2.166133970305109</v>
+      </c>
+      <c r="G7">
+        <v>0.3420430995381293</v>
+      </c>
+      <c r="H7">
+        <v>0.3356221513188329</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>439</v>
+      </c>
+      <c r="B8">
+        <v>192.4</v>
+      </c>
+      <c r="C8">
+        <v>23.34104634425039</v>
+      </c>
+      <c r="D8">
+        <v>2.184345</v>
+      </c>
+      <c r="E8">
+        <v>0.02950073032052673</v>
+      </c>
+      <c r="F8">
+        <v>2.284205067701794</v>
+      </c>
+      <c r="G8">
+        <v>0.3393212328254086</v>
+      </c>
+      <c r="H8">
+        <v>0.3433868008622488</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>502</v>
+      </c>
+      <c r="B9">
+        <v>248.5</v>
+      </c>
+      <c r="C9">
+        <v>21.17716275194159</v>
+      </c>
+      <c r="D9">
+        <v>2.193182</v>
+      </c>
+      <c r="E9">
+        <v>0.01524514281847024</v>
+      </c>
+      <c r="F9">
+        <v>2.395326393069351</v>
+      </c>
+      <c r="G9">
+        <v>0.3410746728612913</v>
+      </c>
+      <c r="H9">
+        <v>0.3506944160814092</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>565</v>
+      </c>
+      <c r="B10">
+        <v>282.1</v>
+      </c>
+      <c r="C10">
+        <v>24.09631138208133</v>
+      </c>
+      <c r="D10">
+        <v>2.216921</v>
+      </c>
+      <c r="E10">
+        <v>0.01244043107952631</v>
+      </c>
+      <c r="F10">
+        <v>2.450403086155367</v>
+      </c>
+      <c r="G10">
+        <v>0.345750217302414</v>
+      </c>
+      <c r="H10">
+        <v>0.3543163966444118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
         <v>628</v>
       </c>
-      <c r="B4">
-        <v>365.8</v>
-      </c>
-      <c r="C4">
-        <v>46.70160596810349</v>
-      </c>
-      <c r="D4">
-        <v>2.234582</v>
-      </c>
-      <c r="E4">
-        <v>0.01545291765331066</v>
-      </c>
-      <c r="F4">
-        <v>2.563243701140398</v>
-      </c>
-      <c r="G4">
-        <v>0.3491962961161355</v>
-      </c>
-      <c r="H4">
-        <v>0.3538023170415861</v>
+      <c r="B11">
+        <v>343.5</v>
+      </c>
+      <c r="C11">
+        <v>29.50075328605092</v>
+      </c>
+      <c r="D11">
+        <v>2.238012</v>
+      </c>
+      <c r="E11">
+        <v>0.009774614831854551</v>
+      </c>
+      <c r="F11">
+        <v>2.535926741395569</v>
+      </c>
+      <c r="G11">
+        <v>0.3498624108428276</v>
+      </c>
+      <c r="H11">
+        <v>0.3599406452984329</v>
       </c>
     </row>
   </sheetData>
@@ -2146,1402 +2590,1402 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
-        <v>38.4</v>
+        <v>7</v>
       </c>
       <c r="B2">
-        <v>2.198394166025069</v>
+        <v>2.150421673188267</v>
       </c>
       <c r="C2">
-        <v>2.219653307407915</v>
+        <v>2.189952068103618</v>
       </c>
       <c r="D2">
-        <v>2.562308198581967E-10</v>
+        <v>1.680873926997722</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3">
-        <v>41.70707070707071</v>
+        <v>10.3989898989899</v>
       </c>
       <c r="B3">
-        <v>2.196578751889937</v>
+        <v>2.14192715754876</v>
       </c>
       <c r="C3">
-        <v>2.216418939220919</v>
+        <v>2.174507583149814</v>
       </c>
       <c r="D3">
-        <v>8.2230885676331E-11</v>
+        <v>1.780612786958067</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4">
-        <v>45.01414141414141</v>
+        <v>13.7979797979798</v>
       </c>
       <c r="B4">
-        <v>2.194903269433833</v>
+        <v>2.135878055964665</v>
       </c>
       <c r="C4">
-        <v>2.213434662372056</v>
+        <v>2.16352227098157</v>
       </c>
       <c r="D4">
-        <v>2.809246165039642E-11</v>
+        <v>1.847777371911753</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
-        <v>48.32121212121212</v>
+        <v>17.1969696969697</v>
       </c>
       <c r="B5">
-        <v>2.193347767370574</v>
+        <v>2.13117979252885</v>
       </c>
       <c r="C5">
-        <v>2.210664765400159</v>
+        <v>2.154997618735145</v>
       </c>
       <c r="D5">
-        <v>1.014293024139562E-11</v>
+        <v>1.897260253313159</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6">
-        <v>51.62828282828283</v>
+        <v>20.5959595959596</v>
       </c>
       <c r="B6">
-        <v>2.191896273560154</v>
+        <v>2.127339424049906</v>
       </c>
       <c r="C6">
-        <v>2.20808066613255</v>
+        <v>2.14803445248919</v>
       </c>
       <c r="D6">
-        <v>3.847281049449188E-12</v>
+        <v>1.935738501774749</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7">
-        <v>54.93535353535353</v>
+        <v>23.99494949494949</v>
       </c>
       <c r="B7">
-        <v>2.190535803123935</v>
+        <v>2.124092426552815</v>
       </c>
       <c r="C7">
-        <v>2.205659133317436</v>
+        <v>2.142150609185036</v>
       </c>
       <c r="D7">
-        <v>1.525367403038516E-12</v>
+        <v>1.966763651469004</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
-        <v>58.24242424242424</v>
+        <v>27.39393939393939</v>
       </c>
       <c r="B8">
-        <v>2.189255657468658</v>
+        <v>2.121280325412628</v>
       </c>
       <c r="C8">
-        <v>2.203381030114909</v>
+        <v>2.137057400761905</v>
       </c>
       <c r="D8">
-        <v>6.29460175951091E-13</v>
+        <v>1.992440425680921</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
-        <v>61.54949494949495</v>
+        <v>30.79292929292929</v>
       </c>
       <c r="B9">
-        <v>2.188046917505067</v>
+        <v>2.118800656454491</v>
       </c>
       <c r="C9">
-        <v>2.201230405875639</v>
+        <v>2.132568266261439</v>
       </c>
       <c r="D9">
-        <v>2.693668507564989E-13</v>
+        <v>2.014113599194683</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
-        <v>64.85656565656566</v>
+        <v>34.19191919191919</v>
       </c>
       <c r="B10">
-        <v>2.186902069892195</v>
+        <v>2.116583343343057</v>
       </c>
       <c r="C10">
-        <v>2.199193826451984</v>
+        <v>2.128555670968802</v>
       </c>
       <c r="D10">
-        <v>1.191591606324724E-13</v>
+        <v>2.032691547524151</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
-        <v>68.16363636363636</v>
+        <v>37.59090909090909</v>
       </c>
       <c r="B11">
-        <v>2.185814726496874</v>
+        <v>2.114578346038241</v>
       </c>
       <c r="C11">
-        <v>2.197259871624067</v>
+        <v>2.124928580618759</v>
       </c>
       <c r="D11">
-        <v>5.43402547908315E-14</v>
+        <v>2.04881477259211</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12">
-        <v>71.47070707070708</v>
+        <v>40.98989898989899</v>
       </c>
       <c r="B12">
-        <v>2.184779410497699</v>
+        <v>2.112748686544023</v>
       </c>
       <c r="C12">
-        <v>2.195418751983425</v>
+        <v>2.121619747405626</v>
       </c>
       <c r="D12">
-        <v>2.548464553622947E-14</v>
+        <v>2.062950595399469</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13">
-        <v>74.77777777777777</v>
+        <v>44.38888888888889</v>
       </c>
       <c r="B13">
-        <v>2.183791390998237</v>
+        <v>2.111066266848205</v>
       </c>
       <c r="C13">
-        <v>2.193662012752639</v>
+        <v>2.118578088860949</v>
       </c>
       <c r="D13">
-        <v>1.22651886996608E-14</v>
+        <v>2.075449620796198</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14">
-        <v>78.08484848484849</v>
+        <v>47.78787878787878</v>
       </c>
       <c r="B14">
-        <v>2.182846553521824</v>
+        <v>2.109509236733487</v>
       </c>
       <c r="C14">
-        <v>2.191982301899781</v>
+        <v>2.115763892671003</v>
       </c>
       <c r="D14">
-        <v>6.046299299780876E-15</v>
+        <v>2.086581060992301</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15">
-        <v>81.39191919191919</v>
+        <v>51.18686868686869</v>
       </c>
       <c r="B15">
-        <v>2.181941297435764</v>
+        <v>2.108060269641899</v>
       </c>
       <c r="C15">
-        <v>2.190373186499104</v>
+        <v>2.113145676665321</v>
       </c>
       <c r="D15">
-        <v>3.0478620728676E-15</v>
+        <v>2.096555725219558</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16">
-        <v>84.69898989898991</v>
+        <v>54.58585858585858</v>
       </c>
       <c r="B16">
-        <v>2.181072453854342</v>
+        <v>2.106705394895447</v>
       </c>
       <c r="C16">
-        <v>2.188829005775802</v>
+        <v>2.110698062623984</v>
       </c>
       <c r="D16">
-        <v>1.568694490763997E-15</v>
+        <v>2.105541487762224</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17">
-        <v>88.0060606060606</v>
+        <v>57.98484848484848</v>
       </c>
       <c r="B17">
-        <v>2.180237219303485</v>
+        <v>2.105433183881368</v>
       </c>
       <c r="C17">
-        <v>2.187344752380862</v>
+        <v>2.108400294926286</v>
       </c>
       <c r="D17">
-        <v>8.232505773933698E-16</v>
+        <v>2.113673994333158</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18">
-        <v>91.31313131313132</v>
+        <v>61.38383838383838</v>
       </c>
       <c r="B18">
-        <v>2.179433101650574</v>
+        <v>2.104234168807233</v>
       </c>
       <c r="C18">
-        <v>2.185915975630631</v>
+        <v>2.106235182784142</v>
       </c>
       <c r="D18">
-        <v>4.399940952958961E-16</v>
+        <v>2.12106425607822</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19">
-        <v>94.62020202020202</v>
+        <v>64.78282828282828</v>
       </c>
       <c r="B19">
-        <v>2.17865787567555</v>
+        <v>2.10310041858106</v>
       </c>
       <c r="C19">
-        <v>2.184538702009938</v>
+        <v>2.10418832858567</v>
       </c>
       <c r="D19">
-        <v>2.392231766586932E-16</v>
+        <v>2.127804152120436</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20">
-        <v>97.92727272727274</v>
+        <v>68.18181818181819</v>
       </c>
       <c r="B20">
-        <v>2.177909546291701</v>
+        <v>2.10202522346179</v>
       </c>
       <c r="C20">
-        <v>2.183209369370938</v>
+        <v>2.102247554257239</v>
       </c>
       <c r="D20">
-        <v>1.321799172991716E-16</v>
+        <v>2.13397049222517</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21">
-        <v>101.2343434343434</v>
+        <v>71.58080808080808</v>
       </c>
       <c r="B21">
-        <v>2.177186317888475</v>
+        <v>2.101002856640141</v>
       </c>
       <c r="C21">
-        <v>2.181924772091283</v>
+        <v>2.100402467650572</v>
       </c>
       <c r="D21">
-        <v>7.415428056720535E-17</v>
+        <v>2.139628066758228</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22">
-        <v>104.5414141414142</v>
+        <v>74.97979797979798</v>
       </c>
       <c r="B22">
-        <v>2.176486568613116</v>
+        <v>2.10002839127806</v>
       </c>
       <c r="C22">
-        <v>2.18068201507247</v>
+        <v>2.098644129853764</v>
       </c>
       <c r="D22">
-        <v>4.220386473087408E-17</v>
+        <v>2.144831970712503</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23">
-        <v>107.8484848484848</v>
+        <v>78.37878787878788</v>
       </c>
       <c r="B23">
-        <v>2.175808828666309</v>
+        <v>2.099097558215875</v>
       </c>
       <c r="C23">
-        <v>2.17947847492224</v>
+        <v>2.096964796496361</v>
       </c>
       <c r="D23">
-        <v>2.434895648115851E-17</v>
+        <v>2.149629398441337</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24">
-        <v>111.1555555555556</v>
+        <v>81.77777777777777</v>
       </c>
       <c r="B24">
-        <v>2.175151761882979</v>
+        <v>2.098206633962574</v>
       </c>
       <c r="C24">
-        <v>2.178311767015872</v>
+        <v>2.095357714144494</v>
       </c>
       <c r="D24">
-        <v>1.42303102020611E-17</v>
+        <v>2.154061046512157</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25">
-        <v>114.4626262626263</v>
+        <v>85.17676767676767</v>
       </c>
       <c r="B25">
-        <v>2.17451415001918</v>
+        <v>2.097352351551859</v>
       </c>
       <c r="C25">
-        <v>2.177179717399663</v>
+        <v>2.093816958285943</v>
       </c>
       <c r="D25">
-        <v>8.419222946263476E-18</v>
+        <v>2.158162222364806</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26">
-        <v>117.769696969697</v>
+        <v>88.57575757575756</v>
       </c>
       <c r="B26">
-        <v>2.173894879281726</v>
+        <v>2.09653182888302</v>
       </c>
       <c r="C26">
-        <v>2.17608033870704</v>
+        <v>2.09233730311285</v>
       </c>
       <c r="D26">
-        <v>5.039559064913113E-18</v>
+        <v>2.161963729302681</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27">
-        <v>121.0767676767677</v>
+        <v>91.97474747474747</v>
       </c>
       <c r="B27">
-        <v>2.173292928727158</v>
+        <v>2.095742510587098</v>
       </c>
       <c r="C27">
-        <v>2.175011809418928</v>
+        <v>2.090914115897705</v>
       </c>
       <c r="D27">
-        <v>3.050243816365308E-18</v>
+        <v>2.165492579463276</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28">
-        <v>124.3838383838384</v>
+        <v>95.37373737373737</v>
       </c>
       <c r="B28">
-        <v>2.172707360227241</v>
+        <v>2.094982120466854</v>
       </c>
       <c r="C28">
-        <v>2.17397245592634</v>
+        <v>2.089543270593106</v>
       </c>
       <c r="D28">
-        <v>1.865838708984186E-18</v>
+        <v>2.168772573080747</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29">
-        <v>127.6909090909091</v>
+        <v>98.77272727272727</v>
       </c>
       <c r="B29">
-        <v>2.172137309753862</v>
+        <v>2.094248622284003</v>
       </c>
       <c r="C29">
-        <v>2.172960736952947</v>
+        <v>2.088221076605225</v>
       </c>
       <c r="D29">
-        <v>1.152930115495227E-18</v>
+        <v>2.1718247728018</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30">
-        <v>130.9979797979798</v>
+        <v>102.1717171717172</v>
       </c>
       <c r="B30">
-        <v>2.171581979780537</v>
+        <v>2.093540187195601</v>
       </c>
       <c r="C30">
-        <v>2.171975229974702</v>
+        <v>2.086944219652561</v>
       </c>
       <c r="D30">
-        <v>7.193285915191711E-19</v>
+        <v>2.174667894884134</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31">
-        <v>134.3050505050505</v>
+        <v>105.5707070707071</v>
       </c>
       <c r="B31">
-        <v>2.171040632633186</v>
+        <v>2.09285516653122</v>
       </c>
       <c r="C31">
-        <v>2.171014619337046</v>
+        <v>2.085709712330689</v>
       </c>
       <c r="D31">
-        <v>4.529666489055615E-19</v>
+        <v>2.177318634013873</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32">
-        <v>137.6121212121212</v>
+        <v>108.969696969697</v>
       </c>
       <c r="B32">
-        <v>2.170512584651356</v>
+        <v>2.09219206889336</v>
       </c>
       <c r="C32">
-        <v>2.170077685821378</v>
+        <v>2.084514852532807</v>
       </c>
       <c r="D32">
-        <v>2.877733992102098E-19</v>
+        <v>2.179791934695538</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33">
-        <v>140.9191919191919</v>
+        <v>112.3686868686869</v>
       </c>
       <c r="B33">
-        <v>2.169997201044205</v>
+        <v>2.091549540782723</v>
       </c>
       <c r="C33">
-        <v>2.169163297453771</v>
+        <v>2.083357188274597</v>
       </c>
       <c r="D33">
-        <v>1.843836232654822E-19</v>
+        <v>2.182101219328193</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34">
-        <v>144.2262626262626</v>
+        <v>115.7676767676768</v>
       </c>
       <c r="B34">
-        <v>2.169493891344383</v>
+        <v>2.090926350116834</v>
       </c>
       <c r="C34">
-        <v>2.168270401382653</v>
+        <v>2.082234487775404</v>
       </c>
       <c r="D34">
-        <v>1.19105818251586E-19</v>
+        <v>2.18425858092872</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35">
-        <v>147.5333333333333</v>
+        <v>119.1666666666667</v>
       </c>
       <c r="B35">
-        <v>2.169002105378318</v>
+        <v>2.090321372138666</v>
       </c>
       <c r="C35">
-        <v>2.167398016679698</v>
+        <v>2.081144713880787</v>
       </c>
       <c r="D35">
-        <v>7.754311979675519E-20</v>
+        <v>2.186274946816959</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36">
-        <v>150.8404040404041</v>
+        <v>122.5656565656566</v>
       </c>
       <c r="B36">
-        <v>2.168521329684095</v>
+        <v>2.089733577311163</v>
       </c>
       <c r="C36">
-        <v>2.166545227940842</v>
+        <v>2.08008600209206</v>
       </c>
       <c r="D36">
-        <v>5.0865378960042E-20</v>
+        <v>2.188160218307508</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37">
-        <v>154.1474747474747</v>
+        <v>125.9646464646465</v>
       </c>
       <c r="B37">
-        <v>2.1680510843186</v>
+        <v>2.089162020871095</v>
       </c>
       <c r="C37">
-        <v>2.165711179583087</v>
+        <v>2.079056641609358</v>
       </c>
       <c r="D37">
-        <v>3.360831596062942E-20</v>
+        <v>2.189923390465473</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38">
-        <v>157.4545454545455</v>
+        <v>129.3636363636364</v>
       </c>
       <c r="B38">
-        <v>2.167590920004233</v>
+        <v>2.088605833776663</v>
       </c>
       <c r="C38">
-        <v>2.164895070748243</v>
+        <v>2.078055058905587</v>
       </c>
       <c r="D38">
-        <v>2.236147643776004E-20</v>
+        <v>2.191572655210075</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39">
-        <v>160.7616161616162</v>
+        <v>132.7626262626263</v>
       </c>
       <c r="B39">
-        <v>2.167140415572789</v>
+        <v>2.08806421483153</v>
       </c>
       <c r="C39">
-        <v>2.164096150737757</v>
+        <v>2.077079803436499</v>
       </c>
       <c r="D39">
-        <v>1.497868856356833E-20</v>
+        <v>2.193115490440067</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40">
-        <v>164.0686868686869</v>
+        <v>136.1616161616162</v>
       </c>
       <c r="B40">
-        <v>2.166699175670119</v>
+        <v>2.087536423806519</v>
       </c>
       <c r="C40">
-        <v>2.163313714913596</v>
+        <v>2.076129535162071</v>
       </c>
       <c r="D40">
-        <v>1.009864440269148E-20</v>
+        <v>2.194558737370101</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41">
-        <v>167.3757575757576</v>
+        <v>139.5606060606061</v>
       </c>
       <c r="B41">
-        <v>2.166266828690303</v>
+        <v>2.087021775411112</v>
       </c>
       <c r="C41">
-        <v>2.162547101009237</v>
+        <v>2.075203013610595</v>
       </c>
       <c r="D41">
-        <v>6.851257989489441E-21</v>
+        <v>2.195908667880361</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42">
-        <v>170.6828282828283</v>
+        <v>142.959595959596</v>
       </c>
       <c r="B42">
-        <v>2.165843024912333</v>
+        <v>2.086519633991806</v>
       </c>
       <c r="C42">
-        <v>2.16179568580253</v>
+        <v>2.074299088262209</v>
       </c>
       <c r="D42">
-        <v>4.676303529589522E-21</v>
+        <v>2.197171043370369</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43">
-        <v>173.989898989899</v>
+        <v>146.3585858585859</v>
       </c>
       <c r="B43">
-        <v>2.165427434815958</v>
+        <v>2.086029408854689</v>
       </c>
       <c r="C43">
-        <v>2.161058882108654</v>
+        <v>2.073416690065391</v>
       </c>
       <c r="D43">
-        <v>3.210496490616638E-21</v>
+        <v>2.198351166356545</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44">
-        <v>177.2969696969697</v>
+        <v>149.7575757575758</v>
       </c>
       <c r="B44">
-        <v>2.165019747556402</v>
+        <v>2.085550550126072</v>
       </c>
       <c r="C44">
-        <v>2.160336136056933</v>
+        <v>2.072554823929998</v>
       </c>
       <c r="D44">
-        <v>2.216640905322756E-21</v>
+        <v>2.199453925848397</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45">
-        <v>180.6040404040404</v>
+        <v>153.1565656565656</v>
       </c>
       <c r="B45">
-        <v>2.164619669580324</v>
+        <v>2.085082545078601</v>
       </c>
       <c r="C45">
-        <v>2.159626924619964</v>
+        <v>2.071712562065024</v>
       </c>
       <c r="D45">
-        <v>1.538837685779879E-21</v>
+        <v>2.200483837371582</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46">
-        <v>183.9111111111111</v>
+        <v>156.5555555555555</v>
       </c>
       <c r="B46">
-        <v>2.164226923367599</v>
+        <v>2.084624914861426</v>
       </c>
       <c r="C46">
-        <v>2.158930753367513</v>
+        <v>2.070889038049575</v>
       </c>
       <c r="D46">
-        <v>1.073962724409227E-21</v>
+        <v>2.20144507836877</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47">
-        <v>187.2181818181818</v>
+        <v>159.9545454545454</v>
       </c>
       <c r="B47">
-        <v>2.163841246285451</v>
+        <v>2.08417721158227</v>
       </c>
       <c r="C47">
-        <v>2.158247154421113</v>
+        <v>2.07008344154234</v>
       </c>
       <c r="D47">
-        <v>7.533777255146351E-22</v>
+        <v>2.202341519596458</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48">
-        <v>190.5252525252525</v>
+        <v>163.3535353535353</v>
       </c>
       <c r="B48">
-        <v>2.163462389543119</v>
+        <v>2.083739015696917</v>
       </c>
       <c r="C48">
-        <v>2.157575684588201</v>
+        <v>2.069295013548817</v>
       </c>
       <c r="D48">
-        <v>5.311230885680746E-22</v>
+        <v>2.203176753042174</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49">
-        <v>193.8323232323233</v>
+        <v>166.7525252525252</v>
       </c>
       <c r="B49">
-        <v>2.163090117236639</v>
+        <v>2.083309933668064</v>
       </c>
       <c r="C49">
-        <v>2.156915923657244</v>
+        <v>2.068523042177209</v>
       </c>
       <c r="D49">
-        <v>3.762454765687669E-22</v>
+        <v>2.203954116808916</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50">
-        <v>197.139393939394</v>
+        <v>170.1515151515151</v>
       </c>
       <c r="B50">
-        <v>2.162724205474603</v>
+        <v>2.082889595860866</v>
       </c>
       <c r="C50">
-        <v>2.156267472837449</v>
+        <v>2.067766858823709</v>
       </c>
       <c r="D50">
-        <v>2.677805045458624E-22</v>
+        <v>2.204676717348316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51">
-        <v>200.4464646464646</v>
+        <v>173.5505050505051</v>
       </c>
       <c r="B51">
-        <v>2.162364441576778</v>
+        <v>2.08247765464704</v>
       </c>
       <c r="C51">
-        <v>2.155629953328615</v>
+        <v>2.067025834736067</v>
       </c>
       <c r="D51">
-        <v>1.914515387891604E-22</v>
+        <v>2.20534744937016</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52">
-        <v>203.7535353535354</v>
+        <v>176.9494949494949</v>
       </c>
       <c r="B52">
-        <v>2.162010623338426</v>
+        <v>2.082073782693208</v>
       </c>
       <c r="C52">
-        <v>2.155003005008303</v>
+        <v>2.066299377911333</v>
       </c>
       <c r="D52">
-        <v>1.374846854218998E-22</v>
+        <v>2.205969013709556</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53">
-        <v>207.0606060606061</v>
+        <v>180.3484848484848</v>
       </c>
       <c r="B53">
-        <v>2.161662558353981</v>
+        <v>2.081677671412412</v>
       </c>
       <c r="C53">
-        <v>2.154386285224983</v>
+        <v>2.065586930289543</v>
       </c>
       <c r="D53">
-        <v>9.915420812122112E-23</v>
+        <v>2.206543933394649</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54">
-        <v>210.3676767676768</v>
+        <v>183.7474747474747</v>
       </c>
       <c r="B54">
-        <v>2.161320063394399</v>
+        <v>2.08128902956049</v>
       </c>
       <c r="C54">
-        <v>2.153779467687038</v>
+        <v>2.064887965210096</v>
       </c>
       <c r="D54">
-        <v>7.180876980882303E-23</v>
+        <v>2.207074568125035</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55">
-        <v>213.6747474747475</v>
+        <v>187.1464646464646</v>
       </c>
       <c r="B55">
-        <v>2.160982963833181</v>
+        <v>2.080907581961346</v>
       </c>
       <c r="C55">
-        <v>2.153182241438655</v>
+        <v>2.064201985101892</v>
       </c>
       <c r="D55">
-        <v>5.221601031102078E-23</v>
+        <v>2.207563127343166</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56">
-        <v>216.9818181818182</v>
+        <v>190.5454545454545</v>
       </c>
       <c r="B56">
-        <v>2.160651093116557</v>
+        <v>2.08053306834719</v>
       </c>
       <c r="C56">
-        <v>2.152594309914567</v>
+        <v>2.063528519381904</v>
       </c>
       <c r="D56">
-        <v>3.811905973109489E-23</v>
+        <v>2.208011682057254</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57">
-        <v>220.2888888888889</v>
+        <v>193.9444444444444</v>
       </c>
       <c r="B57">
-        <v>2.160324292273825</v>
+        <v>2.080165242301498</v>
       </c>
       <c r="C57">
-        <v>2.152015390066476</v>
+        <v>2.062867122540043</v>
       </c>
       <c r="D57">
-        <v>2.793491571485038E-23</v>
+        <v>2.20842217555406</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58">
-        <v>223.5959595959596</v>
+        <v>197.3434343434343</v>
       </c>
       <c r="B58">
-        <v>2.16000240946424</v>
+        <v>2.079803870294</v>
       </c>
       <c r="C58">
-        <v>2.151445211554729</v>
+        <v>2.062217372390829</v>
       </c>
       <c r="D58">
-        <v>2.054828093364562E-23</v>
+        <v>2.208796433122429</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59">
-        <v>226.9030303030303</v>
+        <v>200.7424242424242</v>
       </c>
       <c r="B59">
-        <v>2.15968529955724</v>
+        <v>2.079448730798226</v>
       </c>
       <c r="C59">
-        <v>2.150883515999502</v>
+        <v>2.061578868474762</v>
       </c>
       <c r="D59">
-        <v>1.516996482447516E-23</v>
+        <v>2.209136170893543</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60">
-        <v>230.210101010101</v>
+        <v>204.1414141414141</v>
       </c>
       <c r="B60">
-        <v>2.159372823743096</v>
+        <v>2.079099613483286</v>
       </c>
       <c r="C60">
-        <v>2.150330056286292</v>
+        <v>2.060951230594254</v>
       </c>
       <c r="D60">
-        <v>1.123917074086109E-23</v>
+        <v>2.209443003891004</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61">
-        <v>233.5171717171717</v>
+        <v>207.540404040404</v>
       </c>
       <c r="B61">
-        <v>2.159064849171396</v>
+        <v>2.078756318472522</v>
       </c>
       <c r="C61">
-        <v>2.149784595921077</v>
+        <v>2.060334097470777</v>
       </c>
       <c r="D61">
-        <v>8.355757336449895E-24</v>
+        <v>2.209718453372655</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62">
-        <v>236.8242424242424</v>
+        <v>210.9393939393939</v>
       </c>
       <c r="B62">
-        <v>2.158761248614982</v>
+        <v>2.078418655662491</v>
       </c>
       <c r="C62">
-        <v>2.149246908430934</v>
+        <v>2.059727125511376</v>
       </c>
       <c r="D62">
-        <v>6.233069267254806E-24</v>
+        <v>2.209963953536548</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63">
-        <v>240.1313131313131</v>
+        <v>214.3383838383838</v>
       </c>
       <c r="B63">
-        <v>2.158461900157256</v>
+        <v>2.078086444096496</v>
       </c>
       <c r="C63">
-        <v>2.148716776806327</v>
+        <v>2.059129987674039</v>
       </c>
       <c r="D63">
-        <v>4.664948081066482E-24</v>
+        <v>2.210180857654735</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64">
-        <v>243.4383838383839</v>
+        <v>217.7373737373737</v>
       </c>
       <c r="B64">
-        <v>2.1581666869009</v>
+        <v>2.077759511387498</v>
       </c>
       <c r="C64">
-        <v>2.14819399298164</v>
+        <v>2.058542372422564</v>
       </c>
       <c r="D64">
-        <v>3.502562455856988E-24</v>
+        <v>2.210370443691832</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65">
-        <v>246.7454545454546</v>
+        <v>221.1363636363636</v>
       </c>
       <c r="B65">
-        <v>2.157875496696291</v>
+        <v>2.077437693185808</v>
       </c>
       <c r="C65">
-        <v>2.147678357350848</v>
+        <v>2.05796398276259</v>
       </c>
       <c r="D65">
-        <v>2.638067681502723E-24</v>
+        <v>2.210533919458331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66">
-        <v>250.0525252525253</v>
+        <v>224.5353535353535</v>
       </c>
       <c r="B66">
-        <v>2.157588221888036</v>
+        <v>2.077120832687469</v>
       </c>
       <c r="C66">
-        <v>2.147169678315515</v>
+        <v>2.057394535351355</v>
       </c>
       <c r="D66">
-        <v>1.99303498407814E-24</v>
+        <v>2.210672427343492</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67">
-        <v>253.359595959596</v>
+        <v>227.9343434343434</v>
       </c>
       <c r="B67">
-        <v>2.157304759078181</v>
+        <v>2.076808780179638</v>
       </c>
       <c r="C67">
-        <v>2.146667771862565</v>
+        <v>2.056833759674499</v>
       </c>
       <c r="D67">
-        <v>1.510226121172507E-24</v>
+        <v>2.210787048667588</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68">
-        <v>256.6666666666667</v>
+        <v>231.3333333333333</v>
       </c>
       <c r="B68">
-        <v>2.15702500890482</v>
+        <v>2.076501392619681</v>
       </c>
       <c r="C68">
-        <v>2.146172461169503</v>
+        <v>2.056281397283969</v>
       </c>
       <c r="D68">
-        <v>1.147723624931739E-24</v>
+        <v>2.21087880768909</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69">
-        <v>259.9737373737374</v>
+        <v>234.7323232323232</v>
       </c>
       <c r="B69">
-        <v>2.156748875834891</v>
+        <v>2.076198533245036</v>
       </c>
       <c r="C69">
-        <v>2.145683576234969</v>
+        <v>2.055737201091643</v>
       </c>
       <c r="D69">
-        <v>8.747263692021389E-25</v>
+        <v>2.210948675298397</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70">
-        <v>263.2808080808081</v>
+        <v>238.1313131313131</v>
       </c>
       <c r="B70">
-        <v>2.156476267970096</v>
+        <v>2.075900071211163</v>
       </c>
       <c r="C70">
-        <v>2.145200953532718</v>
+        <v>2.055200934713879</v>
       </c>
       <c r="D70">
-        <v>6.685269686955906E-25</v>
+        <v>2.210997572426767</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71">
-        <v>266.5878787878788</v>
+        <v>241.530303030303</v>
       </c>
       <c r="B71">
-        <v>2.156207096864967</v>
+        <v>2.075605881255213</v>
       </c>
       <c r="C71">
-        <v>2.144724435687234</v>
+        <v>2.054672371862625</v>
       </c>
       <c r="D71">
-        <v>5.12331042204633E-25</v>
+        <v>2.211026373195761</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72">
-        <v>269.8949494949495</v>
+        <v>244.9292929292929</v>
       </c>
       <c r="B72">
-        <v>2.155941277356164</v>
+        <v>2.075315843383241</v>
       </c>
       <c r="C72">
-        <v>2.144253871169409</v>
+        <v>2.054151295779195</v>
       </c>
       <c r="D72">
-        <v>3.936783690714354E-25</v>
+        <v>2.211035907830194</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73">
-        <v>273.2020202020202</v>
+        <v>248.3282828282828</v>
       </c>
       <c r="B73">
-        <v>2.155678727402181</v>
+        <v>2.075029842579013</v>
       </c>
       <c r="C73">
-        <v>2.143789114010795</v>
+        <v>2.053637498707171</v>
       </c>
       <c r="D73">
-        <v>3.032959143365849E-25</v>
+        <v>2.211026965355285</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74">
-        <v>276.5090909090909</v>
+        <v>251.7272727272727</v>
       </c>
       <c r="B74">
-        <v>2.155419367932732</v>
+        <v>2.074747768532655</v>
       </c>
       <c r="C74">
-        <v>2.143330023535093</v>
+        <v>2.053130781401225</v>
       </c>
       <c r="D74">
-        <v>2.342618130567095E-25</v>
+        <v>2.211000296096392</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75">
-        <v>279.8161616161616</v>
+        <v>255.1262626262626</v>
       </c>
       <c r="B75">
-        <v>2.155163122707091</v>
+        <v>2.074469515387524</v>
       </c>
       <c r="C75">
-        <v>2.142876464105646</v>
+        <v>2.05263095266897</v>
       </c>
       <c r="D75">
-        <v>1.813940221842646E-25</v>
+        <v>2.210956613998196</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76">
-        <v>283.1232323232323</v>
+        <v>258.5252525252525</v>
       </c>
       <c r="B76">
-        <v>2.154909918180784</v>
+        <v>2.074194981503874</v>
       </c>
       <c r="C76">
-        <v>2.142428304887809</v>
+        <v>2.052137828943212</v>
       </c>
       <c r="D76">
-        <v>1.408018382171691E-25</v>
+        <v>2.210896598778544</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77">
-        <v>286.430303030303</v>
+        <v>261.9242424242424</v>
       </c>
       <c r="B77">
-        <v>2.154659683380026</v>
+        <v>2.073924069237982</v>
       </c>
       <c r="C77">
-        <v>2.141985419625147</v>
+        <v>2.051651233882217</v>
       </c>
       <c r="D77">
-        <v>1.095558661666711E-25</v>
+        <v>2.210820897930474</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78">
-        <v>289.7373737373737</v>
+        <v>265.3232323232323</v>
       </c>
       <c r="B78">
-        <v>2.154412349783388</v>
+        <v>2.073656684735544</v>
       </c>
       <c r="C78">
-        <v>2.14154768642852</v>
+        <v>2.051170997995803</v>
       </c>
       <c r="D78">
-        <v>8.544441362323672E-26</v>
+        <v>2.210730128584876</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79">
-        <v>293.0444444444444</v>
+        <v>268.7222222222222</v>
       </c>
       <c r="B79">
-        <v>2.154167851210191</v>
+        <v>2.073392737738244</v>
       </c>
       <c r="C79">
-        <v>2.141114987577161</v>
+        <v>2.050696958295315</v>
       </c>
       <c r="D79">
-        <v>6.679314057687823E-26</v>
+        <v>2.210624879245248</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80">
-        <v>296.3515151515152</v>
+        <v>272.1212121212121</v>
       </c>
       <c r="B80">
-        <v>2.153926123715166</v>
+        <v>2.073132141402509</v>
       </c>
       <c r="C80">
-        <v>2.140687209330949</v>
+        <v>2.05022895796564</v>
       </c>
       <c r="D80">
-        <v>5.233114917441986E-26</v>
+        <v>2.210505711404382</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81">
-        <v>299.6585858585859</v>
+        <v>275.520202020202</v>
       </c>
       <c r="B81">
-        <v>2.153687105488986</v>
+        <v>2.072874812129532</v>
       </c>
       <c r="C81">
-        <v>2.140264241753127</v>
+        <v>2.04976684605764</v>
       </c>
       <c r="D81">
-        <v>4.109127038136847E-26</v>
+        <v>2.21037316105263</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82">
-        <v>302.9656565656566</v>
+        <v>278.9191919191919</v>
       </c>
       <c r="B82">
-        <v>2.153450736764253</v>
+        <v>2.072620669405738</v>
       </c>
       <c r="C82">
-        <v>2.139845978542775</v>
+        <v>2.049310477199494</v>
       </c>
       <c r="D82">
-        <v>3.233560629823866E-26</v>
+        <v>2.210227740086017</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83">
-        <v>306.2727272727273</v>
+        <v>282.3181818181818</v>
       </c>
       <c r="B83">
-        <v>2.15321695972661</v>
+        <v>2.072369635652927</v>
       </c>
       <c r="C83">
-        <v>2.139432316876394</v>
+        <v>2.048859711325565</v>
       </c>
       <c r="D83">
-        <v>2.549977848071352E-26</v>
+        <v>2.210069937621918</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84">
-        <v>309.5797979797979</v>
+        <v>285.7171717171717</v>
       </c>
       <c r="B84">
-        <v>2.152985718430624</v>
+        <v>2.072121636087414</v>
       </c>
       <c r="C84">
-        <v>2.139023157258026</v>
+        <v>2.048414413421536</v>
       </c>
       <c r="D84">
-        <v>2.015107030459595E-26</v>
+        <v>2.20990022122946</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85">
-        <v>312.8868686868687</v>
+        <v>289.1161616161616</v>
       </c>
       <c r="B85">
-        <v>2.152756958720158</v>
+        <v>2.071876598587497</v>
       </c>
       <c r="C85">
-        <v>2.138618403377362</v>
+        <v>2.047974453284657</v>
       </c>
       <c r="D85">
-        <v>1.595691782485823E-26</v>
+        <v>2.209719038080857</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86">
-        <v>316.1939393939394</v>
+        <v>292.5151515151515</v>
       </c>
       <c r="B86">
-        <v>2.152530628152934</v>
+        <v>2.071634453568704</v>
       </c>
       <c r="C86">
-        <v>2.138217961975315</v>
+        <v>2.047539705298043</v>
       </c>
       <c r="D86">
-        <v>1.266112926706902E-26</v>
+        <v>2.209526816029812</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87">
-        <v>319.5010101010101</v>
+        <v>295.9141414141414</v>
       </c>
       <c r="B87">
-        <v>2.152306675929022</v>
+        <v>2.071395133866244</v>
       </c>
       <c r="C87">
-        <v>2.137821742716618</v>
+        <v>2.047110048218038</v>
       </c>
       <c r="D87">
-        <v>1.006589190072041E-26</v>
+        <v>2.209323964622174</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88">
-        <v>322.8080808080808</v>
+        <v>299.3131313131313</v>
       </c>
       <c r="B88">
-        <v>2.152085052823029</v>
+        <v>2.071158574624201</v>
       </c>
       <c r="C88">
-        <v>2.137429658068993</v>
+        <v>2.046685364973763</v>
       </c>
       <c r="D88">
-        <v>8.018123947611832E-27</v>
+        <v>2.209110876043773</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89">
-        <v>326.1151515151515</v>
+        <v>302.7121212121212</v>
       </c>
       <c r="B89">
-        <v>2.151865711119739</v>
+        <v>2.070924713190978</v>
       </c>
       <c r="C89">
-        <v>2.137041623188495</v>
+        <v>2.046265542478007</v>
       </c>
       <c r="D89">
-        <v>6.39909699200721E-27</v>
+        <v>2.208887926010147</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90">
-        <v>329.4222222222222</v>
+        <v>306.1111111111111</v>
       </c>
       <c r="B90">
-        <v>2.151648604553019</v>
+        <v>2.070693489020607</v>
       </c>
       <c r="C90">
-        <v>2.136657555810656</v>
+        <v>2.0458504714487</v>
       </c>
       <c r="D90">
-        <v>5.116526272872954E-27</v>
+        <v>2.208655474602077</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91">
-        <v>332.7292929292929</v>
+        <v>309.510101010101</v>
       </c>
       <c r="B91">
-        <v>2.151433688247773</v>
+        <v>2.070464843579507</v>
       </c>
       <c r="C91">
-        <v>2.136277376147081</v>
+        <v>2.045440046240281</v>
       </c>
       <c r="D91">
-        <v>4.098527798004709E-27</v>
+        <v>2.208413867050886</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92">
-        <v>336.0363636363636</v>
+        <v>312.9090909090909</v>
       </c>
       <c r="B92">
-        <v>2.151220918664773</v>
+        <v>2.070238720258351</v>
       </c>
       <c r="C92">
-        <v>2.135901006787169</v>
+        <v>2.045034164684286</v>
       </c>
       <c r="D92">
-        <v>3.288991023660699E-27</v>
+        <v>2.208163434476963</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93">
-        <v>339.3434343434344</v>
+        <v>316.3080808080808</v>
       </c>
       <c r="B93">
-        <v>2.151010253548202</v>
+        <v>2.0700150642887</v>
       </c>
       <c r="C93">
-        <v>2.135528372604657</v>
+        <v>2.044632727938586</v>
       </c>
       <c r="D93">
-        <v>2.644027470027391E-27</v>
+        <v>2.207904494584731</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94">
-        <v>342.650505050505</v>
+        <v>319.7070707070707</v>
       </c>
       <c r="B94">
-        <v>2.150801651875741</v>
+        <v>2.069793822664103</v>
       </c>
       <c r="C94">
-        <v>2.135159400668716</v>
+        <v>2.044235640344685</v>
       </c>
       <c r="D94">
-        <v>2.129239033650374E-27</v>
+        <v>2.207637352317117</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95">
-        <v>345.9575757575757</v>
+        <v>323.1060606060606</v>
       </c>
       <c r="B95">
-        <v>2.150595073811061</v>
+        <v>2.069574944065374</v>
       </c>
       <c r="C95">
-        <v>2.134794020159318</v>
+        <v>2.043842809292603</v>
       </c>
       <c r="D95">
-        <v>1.717612210903897E-27</v>
+        <v>2.207362300472076</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96">
-        <v>349.2646464646465</v>
+        <v>326.5050505050505</v>
       </c>
       <c r="B96">
-        <v>2.150390480658576</v>
+        <v>2.069358378789791</v>
       </c>
       <c r="C96">
-        <v>2.134432162286647</v>
+        <v>2.043454145092835</v>
       </c>
       <c r="D96">
-        <v>1.387891333565681E-27</v>
+        <v>2.207079620283986</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97">
-        <v>352.5717171717172</v>
+        <v>329.9040404040404</v>
       </c>
       <c r="B97">
-        <v>2.150187834820334</v>
+        <v>2.069144078683967</v>
       </c>
       <c r="C97">
-        <v>2.134073760214312</v>
+        <v>2.043069560854962</v>
       </c>
       <c r="D97">
-        <v>1.123319203176768E-27</v>
+        <v>2.206789581971961</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98">
-        <v>355.8787878787879</v>
+        <v>333.3030303030303</v>
       </c>
       <c r="B98">
-        <v>2.14998709975493</v>
+        <v>2.068931997080167</v>
       </c>
       <c r="C98">
-        <v>2.133718748986162</v>
+        <v>2.042688972372499</v>
       </c>
       <c r="D98">
-        <v>9.106601285340489E-28</v>
+        <v>2.206492445257469</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99">
-        <v>359.1858585858586</v>
+        <v>336.7020202020202</v>
       </c>
       <c r="B99">
-        <v>2.149788239938307</v>
+        <v>2.068722088735861</v>
       </c>
       <c r="C99">
-        <v>2.133367065456481</v>
+        <v>2.04231229801361</v>
       </c>
       <c r="D99">
-        <v>7.394404963787656E-28</v>
+        <v>2.206188459853114</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100">
-        <v>362.4929292929293</v>
+        <v>340.1010101010101</v>
       </c>
       <c r="B100">
-        <v>2.14959122082638</v>
+        <v>2.068514309776328</v>
       </c>
       <c r="C100">
-        <v>2.133018648223405</v>
+        <v>2.041939458617303</v>
       </c>
       <c r="D100">
-        <v>6.013572572439084E-28</v>
+        <v>2.205877865924548</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101">
-        <v>365.8</v>
+        <v>343.5</v>
       </c>
       <c r="B101">
-        <v>2.149396008819338</v>
+        <v>2.068308617640102</v>
       </c>
       <c r="C101">
-        <v>2.13267343756536</v>
+        <v>2.041570377394828</v>
       </c>
       <c r="D101">
-        <v>4.898162927508457E-28</v>
+        <v>2.205560894527128</v>
       </c>
     </row>
   </sheetData>
@@ -3551,7 +3995,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3582,80 +4026,232 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="B2">
-        <v>38.4</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>10.77775486824598</v>
+        <v>1.299572579307862</v>
       </c>
       <c r="D2">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0.4898979485566357</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>1.584331224367531</v>
-      </c>
-      <c r="G2">
-        <v>-0.09691001300805639</v>
-      </c>
-      <c r="H2">
-        <v>-0.07691252197913112</v>
+        <v>0.8450980400142568</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3">
-        <v>418</v>
+        <v>125</v>
       </c>
       <c r="B3">
-        <v>226.2</v>
+        <v>19.7</v>
       </c>
       <c r="C3">
-        <v>14.38540927467828</v>
+        <v>3.296631277194612</v>
       </c>
       <c r="D3">
-        <v>10.4</v>
+        <v>0.1</v>
       </c>
       <c r="E3">
-        <v>2.908607914449798</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="F3">
-        <v>2.354492600589436</v>
+        <v>1.294466226161593</v>
       </c>
       <c r="G3">
-        <v>1.01703333929878</v>
-      </c>
-      <c r="H3">
-        <v>0.9232575775389558</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4">
+        <v>188</v>
+      </c>
+      <c r="B4">
+        <v>37.6</v>
+      </c>
+      <c r="C4">
+        <v>7.60876687337267</v>
+      </c>
+      <c r="D4">
+        <v>0.5</v>
+      </c>
+      <c r="E4">
+        <v>0.268741924943285</v>
+      </c>
+      <c r="F4">
+        <v>1.575187844927661</v>
+      </c>
+      <c r="G4">
+        <v>-0.3010299956639812</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>251</v>
+      </c>
+      <c r="B5">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="C5">
+        <v>9.59652714961685</v>
+      </c>
+      <c r="D5">
+        <v>1.5</v>
+      </c>
+      <c r="E5">
+        <v>0.5821416398857659</v>
+      </c>
+      <c r="F5">
+        <v>1.823474229170301</v>
+      </c>
+      <c r="G5">
+        <v>0.1760912590556812</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>314</v>
+      </c>
+      <c r="B6">
+        <v>100.7</v>
+      </c>
+      <c r="C6">
+        <v>15.14819387840602</v>
+      </c>
+      <c r="D6">
+        <v>3.4</v>
+      </c>
+      <c r="E6">
+        <v>1.045625809423875</v>
+      </c>
+      <c r="F6">
+        <v>2.003029470553618</v>
+      </c>
+      <c r="G6">
+        <v>0.5314789170422551</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>376</v>
+      </c>
+      <c r="B7">
+        <v>146.6</v>
+      </c>
+      <c r="C7">
+        <v>19.73051781716165</v>
+      </c>
+      <c r="D7">
+        <v>6.6</v>
+      </c>
+      <c r="E7">
+        <v>1.857118436957882</v>
+      </c>
+      <c r="F7">
+        <v>2.166133970305109</v>
+      </c>
+      <c r="G7">
+        <v>0.8195439355418687</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>439</v>
+      </c>
+      <c r="B8">
+        <v>192.4</v>
+      </c>
+      <c r="C8">
+        <v>23.34104634425039</v>
+      </c>
+      <c r="D8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E8">
+        <v>1.793816539609828</v>
+      </c>
+      <c r="F8">
+        <v>2.284205067701794</v>
+      </c>
+      <c r="G8">
+        <v>0.9444826721501687</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>502</v>
+      </c>
+      <c r="B9">
+        <v>248.5</v>
+      </c>
+      <c r="C9">
+        <v>21.17716275194159</v>
+      </c>
+      <c r="D9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E9">
+        <v>1.412641340027806</v>
+      </c>
+      <c r="F9">
+        <v>2.395326393069351</v>
+      </c>
+      <c r="G9">
+        <v>0.9444826721501687</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>565</v>
+      </c>
+      <c r="B10">
+        <v>282.1</v>
+      </c>
+      <c r="C10">
+        <v>24.09631138208133</v>
+      </c>
+      <c r="D10">
+        <v>11.6</v>
+      </c>
+      <c r="E10">
+        <v>2.587147721590967</v>
+      </c>
+      <c r="F10">
+        <v>2.450403086155367</v>
+      </c>
+      <c r="G10">
+        <v>1.064457989226918</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
         <v>628</v>
       </c>
-      <c r="B4">
-        <v>365.8</v>
-      </c>
-      <c r="C4">
-        <v>46.70160596810349</v>
-      </c>
-      <c r="D4">
-        <v>13.2</v>
-      </c>
-      <c r="E4">
-        <v>2.615339366124404</v>
-      </c>
-      <c r="F4">
-        <v>2.563243701140398</v>
-      </c>
-      <c r="G4">
-        <v>1.12057393120585</v>
-      </c>
-      <c r="H4">
-        <v>1.19435220193675</v>
+      <c r="B11">
+        <v>343.5</v>
+      </c>
+      <c r="C11">
+        <v>29.50075328605092</v>
+      </c>
+      <c r="D11">
+        <v>11.4</v>
+      </c>
+      <c r="E11">
+        <v>1.275408431313933</v>
+      </c>
+      <c r="F11">
+        <v>2.535926741395569</v>
+      </c>
+      <c r="G11">
+        <v>1.056904851336473</v>
       </c>
     </row>
   </sheetData>
@@ -3684,55 +4280,55 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
-        <v>38.4</v>
+        <v>7</v>
       </c>
       <c r="B2">
-        <v>8.189791101205701</v>
+        <v>5.352926039013622</v>
       </c>
       <c r="C2">
-        <v>8.229119669427403</v>
+        <v>5.407557256910533</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>24.55546072408488</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3">
-        <v>41.70707070707071</v>
+        <v>10.3989898989899</v>
       </c>
       <c r="B3">
-        <v>8.183028045353995</v>
+        <v>5.33178110984812</v>
       </c>
       <c r="C3">
-        <v>8.21733339022223</v>
+        <v>5.370618332352392</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2.371212752325636E-85</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4">
-        <v>45.01414141414141</v>
+        <v>13.7979797979798</v>
       </c>
       <c r="B4">
-        <v>8.176786284198842</v>
+        <v>5.316723414984894</v>
       </c>
       <c r="C4">
-        <v>8.206458286868008</v>
+        <v>5.344341093801665</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>3.009696526388845E-252</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
-        <v>48.32121212121212</v>
+        <v>17.1969696969697</v>
       </c>
       <c r="B5">
-        <v>8.170991492185452</v>
+        <v>5.305028287002653</v>
       </c>
       <c r="C5">
-        <v>8.196364261228631</v>
+        <v>5.323947862354129</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -3740,13 +4336,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6">
-        <v>51.62828282828283</v>
+        <v>20.5959595959596</v>
       </c>
       <c r="B6">
-        <v>8.165584167477384</v>
+        <v>5.295468669609164</v>
       </c>
       <c r="C6">
-        <v>8.18694718588257</v>
+        <v>5.307288831343508</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -3754,13 +4350,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7">
-        <v>54.93535353535353</v>
+        <v>23.99494949494949</v>
       </c>
       <c r="B7">
-        <v>8.160515936836957</v>
+        <v>5.287386097866378</v>
       </c>
       <c r="C7">
-        <v>8.178122426128219</v>
+        <v>5.293211119212121</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -3768,13 +4364,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
-        <v>58.24242424242424</v>
+        <v>27.39393939393939</v>
       </c>
       <c r="B8">
-        <v>8.155746944243248</v>
+        <v>5.280386089632954</v>
       </c>
       <c r="C8">
-        <v>8.16982026288116</v>
+        <v>5.281024409516142</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -3782,13 +4378,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
-        <v>61.54949494949495</v>
+        <v>30.79292929292929</v>
       </c>
       <c r="B9">
-        <v>8.151243962953329</v>
+        <v>5.274213586491064</v>
       </c>
       <c r="C9">
-        <v>8.161982584241018</v>
+        <v>5.270282569157416</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -3796,13 +4392,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
-        <v>64.85656565656566</v>
+        <v>34.19191919191919</v>
       </c>
       <c r="B10">
-        <v>8.146979003130825</v>
+        <v>5.268694151285018</v>
       </c>
       <c r="C10">
-        <v>8.154560445945352</v>
+        <v>5.260680602788578</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -3810,13 +4406,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
-        <v>68.16363636363636</v>
+        <v>37.59090909090909</v>
       </c>
       <c r="B11">
-        <v>8.142928266733973</v>
+        <v>5.263703222103585</v>
       </c>
       <c r="C11">
-        <v>8.1475122405698</v>
+        <v>5.25200079538887</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -3824,13 +4420,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12">
-        <v>71.47070707070708</v>
+        <v>40.98989898989899</v>
       </c>
       <c r="B12">
-        <v>8.139071350677698</v>
+        <v>5.259148751661233</v>
       </c>
       <c r="C12">
-        <v>8.140802301878828</v>
+        <v>5.244082312753937</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -3838,13 +4434,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13">
-        <v>74.77777777777777</v>
+        <v>44.38888888888889</v>
       </c>
       <c r="B13">
-        <v>8.13539063070966</v>
+        <v>5.254960797126278</v>
       </c>
       <c r="C13">
-        <v>8.134399825863282</v>
+        <v>5.236802978456676</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -3852,13 +4448,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14">
-        <v>78.08484848484849</v>
+        <v>47.78787878787878</v>
       </c>
       <c r="B14">
-        <v>8.131870778957873</v>
+        <v>5.251084967958202</v>
       </c>
       <c r="C14">
-        <v>8.128278025990802</v>
+        <v>5.230067807568101</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -3866,13 +4462,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15">
-        <v>81.39191919191919</v>
+        <v>51.18686868686869</v>
       </c>
       <c r="B15">
-        <v>8.128498381799757</v>
+        <v>5.247478134112107</v>
       </c>
       <c r="C15">
-        <v>8.122413464209105</v>
+        <v>5.22380149799217</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -3880,13 +4476,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16">
-        <v>84.69898989898991</v>
+        <v>54.58585858585858</v>
       </c>
       <c r="B16">
-        <v>8.125261634022028</v>
+        <v>5.244105519149976</v>
       </c>
       <c r="C16">
-        <v>8.116785515584342</v>
+        <v>5.217943345978917</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -3894,13 +4490,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17">
-        <v>88.0060606060606</v>
+        <v>57.98484848484848</v>
       </c>
       <c r="B17">
-        <v>8.122150091698209</v>
+        <v>5.240938674456543</v>
       </c>
       <c r="C17">
-        <v>8.111375935778677</v>
+        <v>5.212443703585587</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -3908,13 +4504,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18">
-        <v>91.31313131313132</v>
+        <v>61.38383838383838</v>
       </c>
       <c r="B18">
-        <v>8.119154470758206</v>
+        <v>5.237954032378416</v>
       </c>
       <c r="C18">
-        <v>8.106168508543716</v>
+        <v>5.207261449043079</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -3922,13 +4518,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19">
-        <v>94.62020202020202</v>
+        <v>64.78282828282828</v>
       </c>
       <c r="B19">
-        <v>8.116266481475035</v>
+        <v>5.235131850485867</v>
       </c>
       <c r="C19">
-        <v>8.101148756104292</v>
+        <v>5.202362141306127</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -3936,13 +4532,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20">
-        <v>97.92727272727274</v>
+        <v>68.18181818181819</v>
       </c>
       <c r="B20">
-        <v>8.11347869144933</v>
+        <v>5.232455426590628</v>
       </c>
       <c r="C20">
-        <v>8.096303699435454</v>
+        <v>5.197716648142008</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -3950,13 +4546,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21">
-        <v>101.2343434343434</v>
+        <v>71.58080808080808</v>
       </c>
       <c r="B21">
-        <v>8.110784411400553</v>
+        <v>5.229910505262287</v>
       </c>
       <c r="C21">
-        <v>8.091621658464481</v>
+        <v>5.193300109080663</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -3964,13 +4560,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22">
-        <v>104.5414141414142</v>
+        <v>74.97979797979798</v>
       </c>
       <c r="B22">
-        <v>8.108177599357029</v>
+        <v>5.22748482239467</v>
       </c>
       <c r="C22">
-        <v>8.087092084477911</v>
+        <v>5.189091139723202</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -3978,13 +4574,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23">
-        <v>107.8484848484848</v>
+        <v>78.37878787878788</v>
       </c>
       <c r="B23">
-        <v>8.105652779799616</v>
+        <v>5.225167751004131</v>
       </c>
       <c r="C23">
-        <v>8.082705418700529</v>
+        <v>5.185071213009931</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -3992,13 +4588,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24">
-        <v>111.1555555555556</v>
+        <v>81.77777777777777</v>
       </c>
       <c r="B24">
-        <v>8.103204975043685</v>
+        <v>5.222950022409897</v>
       </c>
       <c r="C24">
-        <v>8.078452972291672</v>
+        <v>5.181224172240698</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -4006,13 +4602,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25">
-        <v>114.4626262626263</v>
+        <v>85.17676767676767</v>
       </c>
       <c r="B25">
-        <v>8.100829646702271</v>
+        <v>5.220823504333001</v>
       </c>
       <c r="C25">
-        <v>8.074326823982121</v>
+        <v>5.177535843562779</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -4020,13 +4616,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26">
-        <v>117.769696969697</v>
+        <v>88.57575757575756</v>
       </c>
       <c r="B26">
-        <v>8.098522645504207</v>
+        <v>5.218781022519136</v>
       </c>
       <c r="C26">
-        <v>8.070319732329549</v>
+        <v>5.17399372450804</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -4034,13 +4630,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27">
-        <v>121.0767676767677</v>
+        <v>91.97474747474747</v>
       </c>
       <c r="B27">
-        <v>8.096280168076207</v>
+        <v>5.216816216029325</v>
       </c>
       <c r="C27">
-        <v>8.066425060157622</v>
+        <v>5.170586731350029</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -4048,13 +4644,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28">
-        <v>124.3838383838384</v>
+        <v>95.37373737373737</v>
       </c>
       <c r="B28">
-        <v>8.094098719560799</v>
+        <v>5.214923418851351</v>
       </c>
       <c r="C28">
-        <v>8.062636709204066</v>
+        <v>5.167304992439291</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -4062,13 +4658,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29">
-        <v>127.6909090909091</v>
+        <v>98.77272727272727</v>
       </c>
       <c r="B29">
-        <v>8.091975081149513</v>
+        <v>5.213097562289586</v>
       </c>
       <c r="C29">
-        <v>8.05894906336661</v>
+        <v>5.164139677830922</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -4076,13 +4672,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30">
-        <v>130.9979797979798</v>
+        <v>102.1717171717172</v>
       </c>
       <c r="B30">
-        <v>8.089906281775839</v>
+        <v>5.21133409390618</v>
       </c>
       <c r="C30">
-        <v>8.055356939224604</v>
+        <v>5.161082857817788</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -4090,13 +4686,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31">
-        <v>134.3050505050505</v>
+        <v>105.5707070707071</v>
       </c>
       <c r="B31">
-        <v>8.0878895733445</v>
+        <v>5.209628909756789</v>
       </c>
       <c r="C31">
-        <v>8.051855542745381</v>
+        <v>5.158127384679067</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -4104,13 +4700,13 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32">
-        <v>137.6121212121212</v>
+        <v>108.969696969697</v>
       </c>
       <c r="B32">
-        <v>8.085922408979966</v>
+        <v>5.207978297387893</v>
       </c>
       <c r="C32">
-        <v>8.048440431270608</v>
+        <v>5.155266793218883</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -4118,13 +4714,13 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33">
-        <v>140.9191919191919</v>
+        <v>112.3686868686869</v>
       </c>
       <c r="B33">
-        <v>8.084002423863204</v>
+        <v>5.206378887608354</v>
       </c>
       <c r="C33">
-        <v>8.045107480028493</v>
+        <v>5.152495216623487</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -4132,13 +4728,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34">
-        <v>144.2262626262626</v>
+        <v>115.7676767676768</v>
       </c>
       <c r="B34">
-        <v>8.082127418295755</v>
+        <v>5.204827613463242</v>
       </c>
       <c r="C34">
-        <v>8.041852852540554</v>
+        <v>5.149807314891233</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -4146,13 +4742,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35">
-        <v>147.5333333333333</v>
+        <v>119.1666666666667</v>
       </c>
       <c r="B35">
-        <v>8.080295342687648</v>
+        <v>5.203321675156937</v>
       </c>
       <c r="C35">
-        <v>8.038672974391915</v>
+        <v>5.147198213647012</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -4160,13 +4756,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36">
-        <v>150.8404040404041</v>
+        <v>122.5656565656566</v>
       </c>
       <c r="B36">
-        <v>8.078504284212755</v>
+        <v>5.201858509919639</v>
       </c>
       <c r="C36">
-        <v>8.035564509916737</v>
+        <v>5.144663451584583</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -4174,13 +4770,13 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37">
-        <v>154.1474747474747</v>
+        <v>125.9646464646465</v>
       </c>
       <c r="B37">
-        <v>8.076752454914248</v>
+        <v>5.200435766004364</v>
       </c>
       <c r="C37">
-        <v>8.032524341418611</v>
+        <v>5.142198935117318</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -4188,13 +4784,13 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38">
-        <v>157.4545454545455</v>
+        <v>129.3636363636364</v>
       </c>
       <c r="B38">
-        <v>8.075038181075129</v>
+        <v>5.1990512801533</v>
       </c>
       <c r="C38">
-        <v>8.029549550602271</v>
+        <v>5.139800899083003</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -4202,13 +4798,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39">
-        <v>160.7616161616162</v>
+        <v>132.7626262626263</v>
       </c>
       <c r="B39">
-        <v>8.073359893695773</v>
+        <v>5.197703057992607</v>
       </c>
       <c r="C39">
-        <v>8.026637401940267</v>
+        <v>5.13746587255836</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -4216,13 +4812,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40">
-        <v>164.0686868686869</v>
+        <v>136.1616161616162</v>
       </c>
       <c r="B40">
-        <v>8.071716119942993</v>
+        <v>5.196389256910633</v>
       </c>
       <c r="C40">
-        <v>8.023785327737617</v>
+        <v>5.135190649006447</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -4230,13 +4826,13 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41">
-        <v>167.3757575757576</v>
+        <v>139.5606060606061</v>
       </c>
       <c r="B41">
-        <v>8.070105475454097</v>
+        <v>5.195108171051491</v>
       </c>
       <c r="C41">
-        <v>8.020990914690692</v>
+        <v>5.132972260114392</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -4244,13 +4840,13 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42">
-        <v>170.6828282828283</v>
+        <v>142.959595959596</v>
       </c>
       <c r="B42">
-        <v>8.068526657395394</v>
+        <v>5.193858218117987</v>
       </c>
       <c r="C42">
-        <v>8.018251891764509</v>
+        <v>5.130807952787431</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -4258,13 +4854,13 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43">
-        <v>173.989898989899</v>
+        <v>146.3585858585859</v>
       </c>
       <c r="B43">
-        <v>8.066978438188102</v>
+        <v>5.192637927728353</v>
       </c>
       <c r="C43">
-        <v>8.015566119236306</v>
+        <v>5.128695168853215</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -4272,13 +4868,13 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44">
-        <v>177.2969696969697</v>
+        <v>149.7575757575758</v>
       </c>
       <c r="B44">
-        <v>8.065459659826157</v>
+        <v>5.191445931112351</v>
       </c>
       <c r="C44">
-        <v>8.01293157877333</v>
+        <v>5.12663152710219</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -4286,13 +4882,13 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45">
-        <v>180.6040404040404</v>
+        <v>153.1565656565656</v>
       </c>
       <c r="B45">
-        <v>8.063969228720168</v>
+        <v>5.190280951966059</v>
       </c>
       <c r="C45">
-        <v>8.010346364429903</v>
+        <v>5.12461480734873</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -4300,13 +4896,13 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46">
-        <v>183.9111111111111</v>
+        <v>156.5555555555555</v>
       </c>
       <c r="B46">
-        <v>8.062506111010107</v>
+        <v>5.189141798312476</v>
       </c>
       <c r="C46">
-        <v>8.007808674463462</v>
+        <v>5.122642936246315</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -4314,13 +4910,13 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47">
-        <v>187.2181818181818</v>
+        <v>159.9545454545454</v>
       </c>
       <c r="B47">
-        <v>8.06106932829656</v>
+        <v>5.188027355238066</v>
       </c>
       <c r="C47">
-        <v>8.005316803881799</v>
+        <v>5.120713974630146</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -4328,13 +4924,13 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48">
-        <v>190.5252525252525</v>
+        <v>163.3535353535353</v>
       </c>
       <c r="B48">
-        <v>8.059657953746475</v>
+        <v>5.186936578394556</v>
       </c>
       <c r="C48">
-        <v>8.002869137644524</v>
+        <v>5.118826106194075</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -4342,13 +4938,13 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49">
-        <v>193.8323232323233</v>
+        <v>166.7525252525252</v>
       </c>
       <c r="B49">
-        <v>8.058271108534665</v>
+        <v>5.185868488171249</v>
       </c>
       <c r="C49">
-        <v>8.000464144451023</v>
+        <v>5.116977627336608</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -4356,13 +4952,13 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50">
-        <v>197.139393939394</v>
+        <v>170.1515151515151</v>
       </c>
       <c r="B50">
-        <v>8.056907958586917</v>
+        <v>5.184822164456516</v>
       </c>
       <c r="C50">
-        <v>7.998100371055274</v>
+        <v>5.115166938034089</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -4370,13 +4966,13 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51">
-        <v>200.4464646464646</v>
+        <v>173.5505050505051</v>
       </c>
       <c r="B51">
-        <v>8.055567711594598</v>
+        <v>5.18379674191845</v>
       </c>
       <c r="C51">
-        <v>7.995776437054795</v>
+        <v>5.113392533618912</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -4384,13 +4980,13 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52">
-        <v>203.7535353535354</v>
+        <v>176.9494949494949</v>
       </c>
       <c r="B52">
-        <v>8.054249614273985</v>
+        <v>5.182791405744132</v>
       </c>
       <c r="C52">
-        <v>7.993491030107091</v>
+        <v>5.111652997357205</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -4398,13 +4994,13 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53">
-        <v>207.0606060606061</v>
+        <v>180.3484848484848</v>
       </c>
       <c r="B53">
-        <v>8.052952949846695</v>
+        <v>5.181805387785071</v>
       </c>
       <c r="C53">
-        <v>7.99124290153218</v>
+        <v>5.109946993734476</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -4412,181 +5008,181 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54">
-        <v>210.3676767676768</v>
+        <v>183.7474747474747</v>
       </c>
       <c r="B54">
-        <v>8.051677035720129</v>
+        <v>5.180837963063238</v>
       </c>
       <c r="C54">
-        <v>7.989030862264439</v>
+        <v>5.108273262369786</v>
       </c>
       <c r="D54">
-        <v>1.225622337830707E-219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55">
-        <v>213.6747474747475</v>
+        <v>187.1464646464646</v>
       </c>
       <c r="B55">
-        <v>8.05042122134919</v>
+        <v>5.179888446597965</v>
       </c>
       <c r="C55">
-        <v>7.986853779121008</v>
+        <v>5.106630612489119</v>
       </c>
       <c r="D55">
-        <v>3.123826698404085E-135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56">
-        <v>216.9818181818182</v>
+        <v>190.5454545454545</v>
       </c>
       <c r="B56">
-        <v>8.049184886262536</v>
+        <v>5.178956190518993</v>
       </c>
       <c r="C56">
-        <v>7.984710571357474</v>
+        <v>5.105017917897456</v>
       </c>
       <c r="D56">
-        <v>5.451769375092256E-72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57">
-        <v>220.2888888888889</v>
+        <v>193.9444444444444</v>
       </c>
       <c r="B57">
-        <v>8.047967438238413</v>
+        <v>5.178040581435266</v>
       </c>
       <c r="C57">
-        <v>7.982600207484768</v>
+        <v>5.103434112396518</v>
       </c>
       <c r="D57">
-        <v>5.655621102085995E-29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58">
-        <v>223.5959595959596</v>
+        <v>197.3434343434343</v>
       </c>
       <c r="B58">
-        <v>8.04676831161667</v>
+        <v>5.177141038032769</v>
       </c>
       <c r="C58">
-        <v>7.980521702323813</v>
+        <v>5.101878185601618</v>
       </c>
       <c r="D58">
-        <v>2.693426318664569E-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59">
-        <v>226.9030303030303</v>
+        <v>200.7424242424242</v>
       </c>
       <c r="B59">
-        <v>8.045586965734939</v>
+        <v>5.176257008877876</v>
       </c>
       <c r="C59">
-        <v>7.978474114276977</v>
+        <v>5.100349179116631</v>
       </c>
       <c r="D59">
-        <v>4.077440255195063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60">
-        <v>230.210101010101</v>
+        <v>204.1414141414141</v>
       </c>
       <c r="B60">
-        <v>8.044422883478191</v>
+        <v>5.175387970405509</v>
       </c>
       <c r="C60">
-        <v>7.976456542797425</v>
+        <v>5.098846183030945</v>
       </c>
       <c r="D60">
-        <v>1.226851979633576E-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61">
-        <v>233.5171717171717</v>
+        <v>207.540404040404</v>
       </c>
       <c r="B61">
-        <v>8.043275569931927</v>
+        <v>5.174533425073728</v>
       </c>
       <c r="C61">
-        <v>7.974468126039435</v>
+        <v>5.097368332706382</v>
       </c>
       <c r="D61">
-        <v>4.169967470751121E-42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62">
-        <v>236.8242424242424</v>
+        <v>210.9393939393939</v>
       </c>
       <c r="B62">
-        <v>8.042144551130265</v>
+        <v>5.173692899668521</v>
       </c>
       <c r="C62">
-        <v>7.972508038674366</v>
+        <v>5.095914805825806</v>
       </c>
       <c r="D62">
-        <v>8.321731754707866E-88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63">
-        <v>240.1313131313131</v>
+        <v>214.3383838383838</v>
       </c>
       <c r="B63">
-        <v>8.041029372891019</v>
+        <v>5.172865943744368</v>
       </c>
       <c r="C63">
-        <v>7.970575489858434</v>
+        <v>5.094484819678242</v>
       </c>
       <c r="D63">
-        <v>4.660919783437533E-149</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64">
-        <v>243.4383838383839</v>
+        <v>217.7373737373737</v>
       </c>
       <c r="B64">
-        <v>8.039929599730581</v>
+        <v>5.172052128187715</v>
       </c>
       <c r="C64">
-        <v>7.96866972133985</v>
+        <v>5.093077628658119</v>
       </c>
       <c r="D64">
-        <v>3.237671905294903E-225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65">
-        <v>246.7454545454546</v>
+        <v>221.1363636363636</v>
       </c>
       <c r="B65">
-        <v>8.03884481385218</v>
+        <v>5.171251043891955</v>
       </c>
       <c r="C65">
-        <v>7.966790005694002</v>
+        <v>5.091692521958724</v>
       </c>
       <c r="D65">
-        <v>1.144999930648644E-315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66">
-        <v>250.0525252525253</v>
+        <v>224.5353535353535</v>
       </c>
       <c r="B66">
-        <v>8.037774614201631</v>
+        <v>5.170462300533645</v>
       </c>
       <c r="C66">
-        <v>7.964935644676411</v>
+        <v>5.090328821442015</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -4594,13 +5190,13 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67">
-        <v>253.359595959596</v>
+        <v>227.9343434343434</v>
       </c>
       <c r="B67">
-        <v>8.036718615585212</v>
+        <v>5.169685525440863</v>
       </c>
       <c r="C67">
-        <v>7.963105967684175</v>
+        <v>5.088985879668899</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -4608,13 +5204,13 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68">
-        <v>256.6666666666667</v>
+        <v>231.3333333333333</v>
       </c>
       <c r="B68">
-        <v>8.035676447844887</v>
+        <v>5.168920362545476</v>
       </c>
       <c r="C68">
-        <v>7.961300330317451</v>
+        <v>5.087663078075651</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -4622,13 +5218,13 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69">
-        <v>259.9737373737374</v>
+        <v>234.7323232323232</v>
       </c>
       <c r="B69">
-        <v>8.034647755086416</v>
+        <v>5.168166471411979</v>
       </c>
       <c r="C69">
-        <v>7.959518113033231</v>
+        <v>5.086359825283697</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -4636,13 +5232,13 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70">
-        <v>263.2808080808081</v>
+        <v>238.1313131313131</v>
       </c>
       <c r="B70">
-        <v>8.033632194956336</v>
+        <v>5.167423526336277</v>
       </c>
       <c r="C70">
-        <v>7.95775871988445</v>
+        <v>5.085075555531207</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -4650,13 +5246,13 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71">
-        <v>266.5878787878788</v>
+        <v>241.530303030303</v>
       </c>
       <c r="B71">
-        <v>8.032629437964188</v>
+        <v>5.166691215508473</v>
       </c>
       <c r="C71">
-        <v>7.956021577337983</v>
+        <v>5.083809727216106</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -4664,13 +5260,13 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72">
-        <v>269.8949494949495</v>
+        <v>244.9292929292929</v>
       </c>
       <c r="B72">
-        <v>8.031639166846583</v>
+        <v>5.165969240234258</v>
       </c>
       <c r="C72">
-        <v>7.954306133165703</v>
+        <v>5.082561821541181</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -4678,13 +5274,13 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73">
-        <v>273.2020202020202</v>
+        <v>248.3282828282828</v>
       </c>
       <c r="B73">
-        <v>8.03066107597008</v>
+        <v>5.165257314210066</v>
       </c>
       <c r="C73">
-        <v>7.952611855403229</v>
+        <v>5.081331341252786</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -4692,13 +5288,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74">
-        <v>276.5090909090909</v>
+        <v>251.7272727272727</v>
       </c>
       <c r="B74">
-        <v>8.02969487077006</v>
+        <v>5.164555162847611</v>
       </c>
       <c r="C74">
-        <v>7.9509382313715</v>
+        <v>5.0801178094655</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -4706,13 +5302,13 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75">
-        <v>279.8161616161616</v>
+        <v>255.1262626262626</v>
       </c>
       <c r="B75">
-        <v>8.028740267223021</v>
+        <v>5.163862522643794</v>
       </c>
       <c r="C75">
-        <v>7.949284766756651</v>
+        <v>5.078920768565828</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -4720,13 +5316,13 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76">
-        <v>283.1232323232323</v>
+        <v>258.5252525252525</v>
       </c>
       <c r="B76">
-        <v>8.027796991349941</v>
+        <v>5.163179140592402</v>
       </c>
       <c r="C76">
-        <v>7.947650984744077</v>
+        <v>5.077739779188626</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -4734,13 +5330,13 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77">
-        <v>286.430303030303</v>
+        <v>261.9242424242424</v>
       </c>
       <c r="B77">
-        <v>8.026864778748521</v>
+        <v>5.162504773634302</v>
       </c>
       <c r="C77">
-        <v>7.946036425202927</v>
+        <v>5.07657441926055</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -4748,13 +5344,13 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78">
-        <v>289.7373737373737</v>
+        <v>265.3232323232323</v>
       </c>
       <c r="B78">
-        <v>8.025943374152352</v>
+        <v>5.16183918814315</v>
       </c>
       <c r="C78">
-        <v>7.944440643917518</v>
+        <v>5.075424283105344</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -4762,13 +5358,13 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79">
-        <v>293.0444444444444</v>
+        <v>268.7222222222222</v>
       </c>
       <c r="B79">
-        <v>8.025032531015132</v>
+        <v>5.161182159443904</v>
       </c>
       <c r="C79">
-        <v>7.942863211862472</v>
+        <v>5.074288980606212</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -4776,13 +5372,13 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80">
-        <v>296.3515151515152</v>
+        <v>272.1212121212121</v>
       </c>
       <c r="B80">
-        <v>8.024132011118262</v>
+        <v>5.160533471361647</v>
       </c>
       <c r="C80">
-        <v>7.941303714518645</v>
+        <v>5.073168136420972</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -4790,13 +5386,13 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81">
-        <v>299.6585858585859</v>
+        <v>275.520202020202</v>
       </c>
       <c r="B81">
-        <v>8.023241584200267</v>
+        <v>5.159892915798478</v>
       </c>
       <c r="C81">
-        <v>7.939761751227097</v>
+        <v>5.072061389246056</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -4804,13 +5400,13 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82">
-        <v>302.9656565656566</v>
+        <v>278.9191919191919</v>
       </c>
       <c r="B82">
-        <v>8.02236102760658</v>
+        <v>5.159260292336397</v>
       </c>
       <c r="C82">
-        <v>7.938236934578625</v>
+        <v>5.070968391125741</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -4818,13 +5414,13 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83">
-        <v>306.2727272727273</v>
+        <v>282.3181818181818</v>
       </c>
       <c r="B83">
-        <v>8.021490125958392</v>
+        <v>5.158635407864275</v>
       </c>
       <c r="C83">
-        <v>7.936728889836497</v>
+        <v>5.069888806803331</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -4832,13 +5428,13 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84">
-        <v>309.5797979797979</v>
+        <v>285.7171717171717</v>
       </c>
       <c r="B84">
-        <v>8.020628670839304</v>
+        <v>5.158018076227205</v>
       </c>
       <c r="C84">
-        <v>7.935237254390283</v>
+        <v>5.068822313111262</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -4846,13 +5442,13 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85">
-        <v>312.8868686868687</v>
+        <v>289.1161616161616</v>
       </c>
       <c r="B85">
-        <v>8.019776460498667</v>
+        <v>5.157408117896617</v>
       </c>
       <c r="C85">
-        <v>7.933761677238782</v>
+        <v>5.067768598397367</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -4860,13 +5456,13 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86">
-        <v>316.1939393939394</v>
+        <v>292.5151515151515</v>
       </c>
       <c r="B86">
-        <v>8.018933299570556</v>
+        <v>5.156805359659719</v>
       </c>
       <c r="C86">
-        <v>7.93230181850018</v>
+        <v>5.066727361984748</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -4874,13 +5470,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87">
-        <v>319.5010101010101</v>
+        <v>295.9141414141414</v>
       </c>
       <c r="B87">
-        <v>8.018098998807375</v>
+        <v>5.156209634326909</v>
       </c>
       <c r="C87">
-        <v>7.930857348947782</v>
+        <v>5.065698313662948</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -4888,13 +5484,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88">
-        <v>322.8080808080808</v>
+        <v>299.3131313131313</v>
       </c>
       <c r="B88">
-        <v>8.017273374827226</v>
+        <v>5.155620780455926</v>
       </c>
       <c r="C88">
-        <v>7.929427949569698</v>
+        <v>5.064681173208235</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -4902,13 +5498,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89">
-        <v>326.1151515151515</v>
+        <v>302.7121212121212</v>
       </c>
       <c r="B89">
-        <v>8.016456249874166</v>
+        <v>5.155038642091609</v>
       </c>
       <c r="C89">
-        <v>7.928013311151027</v>
+        <v>5.063675669931057</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -4916,13 +5512,13 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90">
-        <v>329.4222222222222</v>
+        <v>306.1111111111111</v>
       </c>
       <c r="B90">
-        <v>8.015647451590578</v>
+        <v>5.15446306852022</v>
       </c>
       <c r="C90">
-        <v>7.926613133877178</v>
+        <v>5.062681542248821</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -4930,13 +5526,13 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91">
-        <v>332.7292929292929</v>
+        <v>309.510101010101</v>
       </c>
       <c r="B91">
-        <v>8.014846812800952</v>
+        <v>5.153893914037345</v>
       </c>
       <c r="C91">
-        <v>7.925227126957052</v>
+        <v>5.061698537282322</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -4944,13 +5540,13 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92">
-        <v>336.0363636363636</v>
+        <v>312.9090909090909</v>
       </c>
       <c r="B92">
-        <v>8.014054171306361</v>
+        <v>5.153331037728511</v>
       </c>
       <c r="C92">
-        <v>7.923855008264904</v>
+        <v>5.060726410474269</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -4958,13 +5554,13 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93">
-        <v>339.3434343434344</v>
+        <v>316.3080808080808</v>
       </c>
       <c r="B93">
-        <v>8.013269369689031</v>
+        <v>5.152774303261661</v>
       </c>
       <c r="C93">
-        <v>7.922496503999801</v>
+        <v>5.059764925228476</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -4972,13 +5568,13 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94">
-        <v>342.650505050505</v>
+        <v>319.7070707070707</v>
       </c>
       <c r="B94">
-        <v>8.012492255126404</v>
+        <v>5.152223578690761</v>
       </c>
       <c r="C94">
-        <v>7.92115134836161</v>
+        <v>5.058813852568379</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -4986,13 +5582,13 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95">
-        <v>345.9575757575757</v>
+        <v>323.1060606060606</v>
       </c>
       <c r="B95">
-        <v>8.011722679214145</v>
+        <v>5.151678736269794</v>
       </c>
       <c r="C95">
-        <v>7.919819283242615</v>
+        <v>5.057872970813665</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -5000,13 +5596,13 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96">
-        <v>349.2646464646465</v>
+        <v>326.5050505050505</v>
       </c>
       <c r="B96">
-        <v>8.010960497797598</v>
+        <v>5.151139652276515</v>
       </c>
       <c r="C96">
-        <v>7.918500057933823</v>
+        <v>5.056942065273852</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -5014,13 +5610,13 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97">
-        <v>352.5717171717172</v>
+        <v>329.9040404040404</v>
       </c>
       <c r="B97">
-        <v>8.010205570811177</v>
+        <v>5.150606206845356</v>
       </c>
       <c r="C97">
-        <v>7.917193428845162</v>
+        <v>5.056020927957796</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -5028,13 +5624,13 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98">
-        <v>355.8787878787879</v>
+        <v>333.3030303030303</v>
       </c>
       <c r="B98">
-        <v>8.009457762125292</v>
+        <v>5.150078283808896</v>
       </c>
       <c r="C98">
-        <v>7.915899159238747</v>
+        <v>5.05510935729811</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -5042,13 +5638,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99">
-        <v>359.1858585858586</v>
+        <v>336.7020202020202</v>
       </c>
       <c r="B99">
-        <v>8.008716939400355</v>
+        <v>5.149555770547406</v>
       </c>
       <c r="C99">
-        <v>7.914617018974549</v>
+        <v>5.054207157889602</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -5056,13 +5652,13 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100">
-        <v>362.4929292929293</v>
+        <v>340.1010101010101</v>
       </c>
       <c r="B100">
-        <v>8.007982973947497</v>
+        <v>5.149038557845956</v>
       </c>
       <c r="C100">
-        <v>7.913346784267715</v>
+        <v>5.053314140240894</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -5070,13 +5666,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101">
-        <v>365.8</v>
+        <v>343.5</v>
       </c>
       <c r="B101">
-        <v>8.007255740595616</v>
+        <v>5.148526539758643</v>
       </c>
       <c r="C101">
-        <v>7.912088237456969</v>
+        <v>5.052430120538411</v>
       </c>
       <c r="D101">
         <v>0</v>
